--- a/data/RDUE.MI.xlsx
+++ b/data/RDUE.MI.xlsx
@@ -22337,6 +22337,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="956">
+      <c r="A956" s="1" t="n">
+        <v>46279.2916666667</v>
+      </c>
+      <c r="B956" t="n">
+        <v>2000</v>
+      </c>
+      <c r="C956" t="n">
+        <v>10.4499998092651</v>
+      </c>
+      <c r="D956" t="n">
+        <v>10.25</v>
+      </c>
+      <c r="E956" t="n">
+        <v>10.25</v>
+      </c>
+      <c r="F956" t="n">
+        <v>10.3500003814697</v>
+      </c>
+      <c r="G956" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/RDUE.MI.xlsx
+++ b/data/RDUE.MI.xlsx
@@ -22360,6 +22360,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="957">
+      <c r="A957" s="1" t="n">
+        <v>46280.2916666667</v>
+      </c>
+      <c r="B957" t="n">
+        <v>2700</v>
+      </c>
+      <c r="C957" t="n">
+        <v>10.3500003814697</v>
+      </c>
+      <c r="D957" t="n">
+        <v>10.1499996185303</v>
+      </c>
+      <c r="E957" t="n">
+        <v>10.3000001907349</v>
+      </c>
+      <c r="F957" t="n">
+        <v>10.25</v>
+      </c>
+      <c r="G957" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/RDUE.MI.xlsx
+++ b/data/RDUE.MI.xlsx
@@ -22383,6 +22383,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="958">
+      <c r="A958" s="1" t="n">
+        <v>46281.2916666667</v>
+      </c>
+      <c r="B958" t="n">
+        <v>1400</v>
+      </c>
+      <c r="C958" t="n">
+        <v>10.3999996185303</v>
+      </c>
+      <c r="D958" t="n">
+        <v>10.3500003814697</v>
+      </c>
+      <c r="E958" t="n">
+        <v>10.3999996185303</v>
+      </c>
+      <c r="F958" t="n">
+        <v>10.3500003814697</v>
+      </c>
+      <c r="G958" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/RDUE.MI.xlsx
+++ b/data/RDUE.MI.xlsx
@@ -22406,6 +22406,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="959">
+      <c r="A959" s="1" t="n">
+        <v>46282.2916666667</v>
+      </c>
+      <c r="B959" t="n">
+        <v>4200</v>
+      </c>
+      <c r="C959" t="n">
+        <v>10.6499996185303</v>
+      </c>
+      <c r="D959" t="n">
+        <v>10.4499998092651</v>
+      </c>
+      <c r="E959" t="n">
+        <v>10.4499998092651</v>
+      </c>
+      <c r="F959" t="n">
+        <v>10.6499996185303</v>
+      </c>
+      <c r="G959" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/RDUE.MI.xlsx
+++ b/data/RDUE.MI.xlsx
@@ -22247,22 +22247,22 @@
     </row>
     <row r="952">
       <c r="A952" s="1" t="n">
-        <v>46273.2916666667</v>
+        <v>46272.2916666667</v>
       </c>
       <c r="B952" t="n">
-        <v>1100</v>
+        <v>0</v>
       </c>
       <c r="C952" t="n">
-        <v>10.1999998092651</v>
+        <v>10.3500003814697</v>
       </c>
       <c r="D952" t="n">
-        <v>10.0500001907349</v>
+        <v>10.3500003814697</v>
       </c>
       <c r="E952" t="n">
-        <v>10.1999998092651</v>
+        <v>10.3500003814697</v>
       </c>
       <c r="F952" t="n">
-        <v>10.0500001907349</v>
+        <v>10.3500003814697</v>
       </c>
       <c r="G952" t="s">
         <v>7</v>
@@ -22270,22 +22270,22 @@
     </row>
     <row r="953">
       <c r="A953" s="1" t="n">
-        <v>46274.2916666667</v>
+        <v>46273.2916666667</v>
       </c>
       <c r="B953" t="n">
-        <v>5600</v>
+        <v>1100</v>
       </c>
       <c r="C953" t="n">
-        <v>10.3999996185303</v>
+        <v>10.1999998092651</v>
       </c>
       <c r="D953" t="n">
         <v>10.0500001907349</v>
       </c>
       <c r="E953" t="n">
-        <v>10.1499996185303</v>
+        <v>10.1999998092651</v>
       </c>
       <c r="F953" t="n">
-        <v>10.3500003814697</v>
+        <v>10.0500001907349</v>
       </c>
       <c r="G953" t="s">
         <v>7</v>
@@ -22293,22 +22293,22 @@
     </row>
     <row r="954">
       <c r="A954" s="1" t="n">
-        <v>46275.2916666667</v>
+        <v>46274.2916666667</v>
       </c>
       <c r="B954" t="n">
-        <v>6400</v>
+        <v>5600</v>
       </c>
       <c r="C954" t="n">
-        <v>10.4499998092651</v>
+        <v>10.3999996185303</v>
       </c>
       <c r="D954" t="n">
-        <v>10.25</v>
+        <v>10.0500001907349</v>
       </c>
       <c r="E954" t="n">
-        <v>10.4499998092651</v>
+        <v>10.1499996185303</v>
       </c>
       <c r="F954" t="n">
-        <v>10.4499998092651</v>
+        <v>10.3500003814697</v>
       </c>
       <c r="G954" t="s">
         <v>7</v>
@@ -22316,22 +22316,22 @@
     </row>
     <row r="955">
       <c r="A955" s="1" t="n">
-        <v>46276.2916666667</v>
+        <v>46275.2916666667</v>
       </c>
       <c r="B955" t="n">
-        <v>1300</v>
+        <v>6400</v>
       </c>
       <c r="C955" t="n">
-        <v>10.3999996185303</v>
+        <v>10.4499998092651</v>
       </c>
       <c r="D955" t="n">
-        <v>10.1999998092651</v>
+        <v>10.25</v>
       </c>
       <c r="E955" t="n">
-        <v>10.25</v>
+        <v>10.4499998092651</v>
       </c>
       <c r="F955" t="n">
-        <v>10.1999998092651</v>
+        <v>10.4499998092651</v>
       </c>
       <c r="G955" t="s">
         <v>7</v>
@@ -22339,22 +22339,22 @@
     </row>
     <row r="956">
       <c r="A956" s="1" t="n">
-        <v>46279.2916666667</v>
+        <v>46276.2916666667</v>
       </c>
       <c r="B956" t="n">
-        <v>2000</v>
+        <v>1300</v>
       </c>
       <c r="C956" t="n">
-        <v>10.4499998092651</v>
+        <v>10.3999996185303</v>
       </c>
       <c r="D956" t="n">
-        <v>10.25</v>
+        <v>10.1999998092651</v>
       </c>
       <c r="E956" t="n">
         <v>10.25</v>
       </c>
       <c r="F956" t="n">
-        <v>10.3500003814697</v>
+        <v>10.1999998092651</v>
       </c>
       <c r="G956" t="s">
         <v>7</v>
@@ -22362,22 +22362,22 @@
     </row>
     <row r="957">
       <c r="A957" s="1" t="n">
-        <v>46280.2916666667</v>
+        <v>46279.2916666667</v>
       </c>
       <c r="B957" t="n">
-        <v>2700</v>
+        <v>2000</v>
       </c>
       <c r="C957" t="n">
+        <v>10.4499998092651</v>
+      </c>
+      <c r="D957" t="n">
+        <v>10.25</v>
+      </c>
+      <c r="E957" t="n">
+        <v>10.25</v>
+      </c>
+      <c r="F957" t="n">
         <v>10.3500003814697</v>
-      </c>
-      <c r="D957" t="n">
-        <v>10.1499996185303</v>
-      </c>
-      <c r="E957" t="n">
-        <v>10.3000001907349</v>
-      </c>
-      <c r="F957" t="n">
-        <v>10.25</v>
       </c>
       <c r="G957" t="s">
         <v>7</v>
@@ -22385,22 +22385,22 @@
     </row>
     <row r="958">
       <c r="A958" s="1" t="n">
-        <v>46281.2916666667</v>
+        <v>46280.2916666667</v>
       </c>
       <c r="B958" t="n">
-        <v>1400</v>
+        <v>2700</v>
       </c>
       <c r="C958" t="n">
-        <v>10.3999996185303</v>
+        <v>10.3500003814697</v>
       </c>
       <c r="D958" t="n">
-        <v>10.3500003814697</v>
+        <v>10.1499996185303</v>
       </c>
       <c r="E958" t="n">
-        <v>10.3999996185303</v>
+        <v>10.3000001907349</v>
       </c>
       <c r="F958" t="n">
-        <v>10.3500003814697</v>
+        <v>10.25</v>
       </c>
       <c r="G958" t="s">
         <v>7</v>
@@ -22408,24 +22408,47 @@
     </row>
     <row r="959">
       <c r="A959" s="1" t="n">
-        <v>46282.2916666667</v>
+        <v>46281.2916666667</v>
       </c>
       <c r="B959" t="n">
-        <v>4200</v>
+        <v>1400</v>
       </c>
       <c r="C959" t="n">
-        <v>10.6499996185303</v>
+        <v>10.3999996185303</v>
       </c>
       <c r="D959" t="n">
+        <v>10.3500003814697</v>
+      </c>
+      <c r="E959" t="n">
+        <v>10.3999996185303</v>
+      </c>
+      <c r="F959" t="n">
+        <v>10.3500003814697</v>
+      </c>
+      <c r="G959" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="960">
+      <c r="A960" s="1" t="n">
+        <v>46283.2916666667</v>
+      </c>
+      <c r="B960" t="n">
+        <v>2700</v>
+      </c>
+      <c r="C960" t="n">
+        <v>10.6000003814697</v>
+      </c>
+      <c r="D960" t="n">
+        <v>10.1999998092651</v>
+      </c>
+      <c r="E960" t="n">
         <v>10.4499998092651</v>
       </c>
-      <c r="E959" t="n">
-        <v>10.4499998092651</v>
-      </c>
-      <c r="F959" t="n">
-        <v>10.6499996185303</v>
-      </c>
-      <c r="G959" t="s">
+      <c r="F960" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="G960" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/RDUE.MI.xlsx
+++ b/data/RDUE.MI.xlsx
@@ -447,7 +447,7 @@
         <v>12.0500001907349</v>
       </c>
       <c r="G3" t="n">
-        <v>11.2916126251221</v>
+        <v>11.2916135787964</v>
       </c>
       <c r="H3" t="s">
         <v>8</v>
@@ -525,7 +525,7 @@
         <v>12.0539999008179</v>
       </c>
       <c r="G6" t="n">
-        <v>11.2953615188599</v>
+        <v>11.2953605651855</v>
       </c>
       <c r="H6" t="s">
         <v>8</v>
@@ -603,7 +603,7 @@
         <v>11.8599996566772</v>
       </c>
       <c r="G9" t="n">
-        <v>11.1135711669922</v>
+        <v>11.1135702133179</v>
       </c>
       <c r="H9" t="s">
         <v>8</v>
@@ -707,7 +707,7 @@
         <v>11.8800001144409</v>
       </c>
       <c r="G13" t="n">
-        <v>11.1323127746582</v>
+        <v>11.1323118209839</v>
       </c>
       <c r="H13" t="s">
         <v>8</v>
@@ -785,7 +785,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G16" t="n">
-        <v>11.0573472976685</v>
+        <v>11.0573463439941</v>
       </c>
       <c r="H16" t="s">
         <v>8</v>
@@ -811,7 +811,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G17" t="n">
-        <v>11.0573472976685</v>
+        <v>11.0573463439941</v>
       </c>
       <c r="H17" t="s">
         <v>8</v>
@@ -915,7 +915,7 @@
         <v>11.3800001144409</v>
       </c>
       <c r="G21" t="n">
-        <v>10.6637811660767</v>
+        <v>10.6637802124023</v>
       </c>
       <c r="H21" t="s">
         <v>8</v>
@@ -993,7 +993,7 @@
         <v>11.2600002288818</v>
       </c>
       <c r="G24" t="n">
-        <v>10.5513334274292</v>
+        <v>10.5513324737549</v>
       </c>
       <c r="H24" t="s">
         <v>8</v>
@@ -1019,7 +1019,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G25" t="n">
-        <v>10.5888156890869</v>
+        <v>10.5888147354126</v>
       </c>
       <c r="H25" t="s">
         <v>8</v>
@@ -1123,7 +1123,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G29" t="n">
-        <v>11.3384666442871</v>
+        <v>11.3384656906128</v>
       </c>
       <c r="H29" t="s">
         <v>8</v>
@@ -1149,7 +1149,7 @@
         <v>11.8800001144409</v>
       </c>
       <c r="G30" t="n">
-        <v>11.1323127746582</v>
+        <v>11.1323118209839</v>
       </c>
       <c r="H30" t="s">
         <v>8</v>
@@ -1253,7 +1253,7 @@
         <v>11.75</v>
       </c>
       <c r="G34" t="n">
-        <v>11.0104932785034</v>
+        <v>11.0104942321777</v>
       </c>
       <c r="H34" t="s">
         <v>8</v>
@@ -1279,7 +1279,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G35" t="n">
-        <v>11.0573472976685</v>
+        <v>11.0573463439941</v>
       </c>
       <c r="H35" t="s">
         <v>8</v>
@@ -1305,7 +1305,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G36" t="n">
-        <v>11.0573472976685</v>
+        <v>11.0573463439941</v>
       </c>
       <c r="H36" t="s">
         <v>8</v>
@@ -1331,7 +1331,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G37" t="n">
-        <v>11.0573472976685</v>
+        <v>11.0573463439941</v>
       </c>
       <c r="H37" t="s">
         <v>8</v>
@@ -1487,7 +1487,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G43" t="n">
-        <v>11.0573472976685</v>
+        <v>11.0573463439941</v>
       </c>
       <c r="H43" t="s">
         <v>8</v>
@@ -1617,7 +1617,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G48" t="n">
-        <v>11.0573472976685</v>
+        <v>11.0573463439941</v>
       </c>
       <c r="H48" t="s">
         <v>8</v>
@@ -1721,7 +1721,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G52" t="n">
-        <v>11.0573472976685</v>
+        <v>11.0573463439941</v>
       </c>
       <c r="H52" t="s">
         <v>8</v>
@@ -1773,7 +1773,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G54" t="n">
-        <v>11.0573472976685</v>
+        <v>11.0573463439941</v>
       </c>
       <c r="H54" t="s">
         <v>8</v>
@@ -1799,7 +1799,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G55" t="n">
-        <v>11.0573472976685</v>
+        <v>11.0573463439941</v>
       </c>
       <c r="H55" t="s">
         <v>8</v>
@@ -1825,7 +1825,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G56" t="n">
-        <v>11.0573472976685</v>
+        <v>11.0573463439941</v>
       </c>
       <c r="H56" t="s">
         <v>8</v>
@@ -1851,7 +1851,7 @@
         <v>11.75</v>
       </c>
       <c r="G57" t="n">
-        <v>11.0104932785034</v>
+        <v>11.0104942321777</v>
       </c>
       <c r="H57" t="s">
         <v>8</v>
@@ -1877,7 +1877,7 @@
         <v>11.75</v>
       </c>
       <c r="G58" t="n">
-        <v>11.0104932785034</v>
+        <v>11.0104942321777</v>
       </c>
       <c r="H58" t="s">
         <v>8</v>
@@ -1903,7 +1903,7 @@
         <v>11.75</v>
       </c>
       <c r="G59" t="n">
-        <v>11.0104932785034</v>
+        <v>11.0104942321777</v>
       </c>
       <c r="H59" t="s">
         <v>8</v>
@@ -1929,7 +1929,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G60" t="n">
-        <v>10.8699350357056</v>
+        <v>10.8699340820312</v>
       </c>
       <c r="H60" t="s">
         <v>8</v>
@@ -2215,7 +2215,7 @@
         <v>11.5</v>
       </c>
       <c r="G71" t="n">
-        <v>10.7762279510498</v>
+        <v>10.7762269973755</v>
       </c>
       <c r="H71" t="s">
         <v>8</v>
@@ -2267,7 +2267,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G73" t="n">
-        <v>10.8699350357056</v>
+        <v>10.8699340820312</v>
       </c>
       <c r="H73" t="s">
         <v>8</v>
@@ -2293,7 +2293,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G74" t="n">
-        <v>10.8699350357056</v>
+        <v>10.8699340820312</v>
       </c>
       <c r="H74" t="s">
         <v>8</v>
@@ -2319,7 +2319,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G75" t="n">
-        <v>10.8699350357056</v>
+        <v>10.8699340820312</v>
       </c>
       <c r="H75" t="s">
         <v>8</v>
@@ -2345,7 +2345,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G76" t="n">
-        <v>10.8699350357056</v>
+        <v>10.8699340820312</v>
       </c>
       <c r="H76" t="s">
         <v>8</v>
@@ -2397,7 +2397,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G78" t="n">
-        <v>11.0573472976685</v>
+        <v>11.0573463439941</v>
       </c>
       <c r="H78" t="s">
         <v>8</v>
@@ -2423,7 +2423,7 @@
         <v>11.5</v>
       </c>
       <c r="G79" t="n">
-        <v>10.7762279510498</v>
+        <v>10.7762269973755</v>
       </c>
       <c r="H79" t="s">
         <v>8</v>
@@ -2527,7 +2527,7 @@
         <v>10.0500001907349</v>
       </c>
       <c r="G83" t="n">
-        <v>9.41748714447021</v>
+        <v>9.4174861907959</v>
       </c>
       <c r="H83" t="s">
         <v>8</v>
@@ -2553,7 +2553,7 @@
         <v>10.0500001907349</v>
       </c>
       <c r="G84" t="n">
-        <v>9.41748714447021</v>
+        <v>9.4174861907959</v>
       </c>
       <c r="H84" t="s">
         <v>8</v>
@@ -2735,7 +2735,7 @@
         <v>10.0500001907349</v>
       </c>
       <c r="G91" t="n">
-        <v>9.41748714447021</v>
+        <v>9.4174861907959</v>
       </c>
       <c r="H91" t="s">
         <v>8</v>
@@ -2761,7 +2761,7 @@
         <v>9.92000007629395</v>
       </c>
       <c r="G92" t="n">
-        <v>9.29566764831543</v>
+        <v>9.29566860198975</v>
       </c>
       <c r="H92" t="s">
         <v>8</v>
@@ -2787,7 +2787,7 @@
         <v>9.72000026702881</v>
       </c>
       <c r="G93" t="n">
-        <v>9.10825538635254</v>
+        <v>9.10825634002686</v>
       </c>
       <c r="H93" t="s">
         <v>8</v>
@@ -2813,7 +2813,7 @@
         <v>9.73999977111816</v>
       </c>
       <c r="G94" t="n">
-        <v>9.12699604034424</v>
+        <v>9.12699699401855</v>
       </c>
       <c r="H94" t="s">
         <v>8</v>
@@ -2839,7 +2839,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G95" t="n">
-        <v>9.08951377868652</v>
+        <v>9.08951473236084</v>
       </c>
       <c r="H95" t="s">
         <v>8</v>
@@ -2865,7 +2865,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G96" t="n">
-        <v>9.08951377868652</v>
+        <v>9.08951473236084</v>
       </c>
       <c r="H96" t="s">
         <v>8</v>
@@ -2891,7 +2891,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G97" t="n">
-        <v>9.08951377868652</v>
+        <v>9.08951473236084</v>
       </c>
       <c r="H97" t="s">
         <v>8</v>
@@ -2917,7 +2917,7 @@
         <v>9.53999996185303</v>
       </c>
       <c r="G98" t="n">
-        <v>8.93958282470703</v>
+        <v>8.93958377838135</v>
       </c>
       <c r="H98" t="s">
         <v>8</v>
@@ -2943,7 +2943,7 @@
         <v>9.34000015258789</v>
       </c>
       <c r="G99" t="n">
-        <v>8.75217056274414</v>
+        <v>8.75217151641846</v>
       </c>
       <c r="H99" t="s">
         <v>8</v>
@@ -2969,7 +2969,7 @@
         <v>9.14000034332275</v>
       </c>
       <c r="G100" t="n">
-        <v>8.56475830078125</v>
+        <v>8.56475925445557</v>
       </c>
       <c r="H100" t="s">
         <v>8</v>
@@ -3099,7 +3099,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G105" t="n">
-        <v>8.52727603912354</v>
+        <v>8.52727699279785</v>
       </c>
       <c r="H105" t="s">
         <v>8</v>
@@ -3203,7 +3203,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G109" t="n">
-        <v>8.80839443206787</v>
+        <v>8.80839538574219</v>
       </c>
       <c r="H109" t="s">
         <v>8</v>
@@ -3229,7 +3229,7 @@
         <v>9.4399995803833</v>
       </c>
       <c r="G110" t="n">
-        <v>8.84587669372559</v>
+        <v>8.8458776473999</v>
       </c>
       <c r="H110" t="s">
         <v>8</v>
@@ -3255,7 +3255,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G111" t="n">
-        <v>9.08951377868652</v>
+        <v>9.08951473236084</v>
       </c>
       <c r="H111" t="s">
         <v>8</v>
@@ -3359,7 +3359,7 @@
         <v>10</v>
       </c>
       <c r="G115" t="n">
-        <v>9.37063312530518</v>
+        <v>9.37063407897949</v>
       </c>
       <c r="H115" t="s">
         <v>8</v>
@@ -3463,7 +3463,7 @@
         <v>10.5</v>
       </c>
       <c r="G119" t="n">
-        <v>9.83916473388672</v>
+        <v>9.83916568756104</v>
       </c>
       <c r="H119" t="s">
         <v>8</v>
@@ -3723,7 +3723,7 @@
         <v>9.84000015258789</v>
       </c>
       <c r="G129" t="n">
-        <v>9.22070217132568</v>
+        <v>9.220703125</v>
       </c>
       <c r="H129" t="s">
         <v>8</v>
@@ -3749,7 +3749,7 @@
         <v>9.92000007629395</v>
       </c>
       <c r="G130" t="n">
-        <v>9.29566764831543</v>
+        <v>9.29566860198975</v>
       </c>
       <c r="H130" t="s">
         <v>8</v>
@@ -3775,7 +3775,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G131" t="n">
-        <v>9.65175247192383</v>
+        <v>9.65175342559814</v>
       </c>
       <c r="H131" t="s">
         <v>8</v>
@@ -3801,7 +3801,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G132" t="n">
-        <v>9.65175247192383</v>
+        <v>9.65175342559814</v>
       </c>
       <c r="H132" t="s">
         <v>8</v>
@@ -3905,7 +3905,7 @@
         <v>10.5</v>
       </c>
       <c r="G136" t="n">
-        <v>9.83916473388672</v>
+        <v>9.83916568756104</v>
       </c>
       <c r="H136" t="s">
         <v>8</v>
@@ -3957,7 +3957,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G138" t="n">
-        <v>10.0265779495239</v>
+        <v>10.0265769958496</v>
       </c>
       <c r="H138" t="s">
         <v>8</v>
@@ -3983,7 +3983,7 @@
         <v>10.5</v>
       </c>
       <c r="G139" t="n">
-        <v>9.83916473388672</v>
+        <v>9.83916568756104</v>
       </c>
       <c r="H139" t="s">
         <v>8</v>
@@ -4009,7 +4009,7 @@
         <v>10.5</v>
       </c>
       <c r="G140" t="n">
-        <v>9.83916473388672</v>
+        <v>9.83916568756104</v>
       </c>
       <c r="H140" t="s">
         <v>8</v>
@@ -4035,7 +4035,7 @@
         <v>10.5</v>
       </c>
       <c r="G141" t="n">
-        <v>9.83916473388672</v>
+        <v>9.83916568756104</v>
       </c>
       <c r="H141" t="s">
         <v>8</v>
@@ -4061,7 +4061,7 @@
         <v>10</v>
       </c>
       <c r="G142" t="n">
-        <v>9.37063312530518</v>
+        <v>9.37063407897949</v>
       </c>
       <c r="H142" t="s">
         <v>8</v>
@@ -4217,7 +4217,7 @@
         <v>9.31999969482422</v>
       </c>
       <c r="G148" t="n">
-        <v>8.73342895507812</v>
+        <v>8.73342990875244</v>
       </c>
       <c r="H148" t="s">
         <v>8</v>
@@ -4295,7 +4295,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G151" t="n">
-        <v>9.08951377868652</v>
+        <v>9.08951473236084</v>
       </c>
       <c r="H151" t="s">
         <v>8</v>
@@ -4321,7 +4321,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G152" t="n">
-        <v>9.08951377868652</v>
+        <v>9.08951473236084</v>
       </c>
       <c r="H152" t="s">
         <v>8</v>
@@ -4347,7 +4347,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G153" t="n">
-        <v>9.08951377868652</v>
+        <v>9.08951473236084</v>
       </c>
       <c r="H153" t="s">
         <v>8</v>
@@ -4399,7 +4399,7 @@
         <v>10</v>
       </c>
       <c r="G155" t="n">
-        <v>9.37063312530518</v>
+        <v>9.37063407897949</v>
       </c>
       <c r="H155" t="s">
         <v>8</v>
@@ -4425,7 +4425,7 @@
         <v>10</v>
       </c>
       <c r="G156" t="n">
-        <v>9.37063312530518</v>
+        <v>9.37063407897949</v>
       </c>
       <c r="H156" t="s">
         <v>8</v>
@@ -4451,7 +4451,7 @@
         <v>10</v>
       </c>
       <c r="G157" t="n">
-        <v>9.37063312530518</v>
+        <v>9.37063407897949</v>
       </c>
       <c r="H157" t="s">
         <v>8</v>
@@ -4477,7 +4477,7 @@
         <v>10</v>
       </c>
       <c r="G158" t="n">
-        <v>9.37063312530518</v>
+        <v>9.37063407897949</v>
       </c>
       <c r="H158" t="s">
         <v>8</v>
@@ -4503,7 +4503,7 @@
         <v>10</v>
       </c>
       <c r="G159" t="n">
-        <v>9.37063312530518</v>
+        <v>9.37063407897949</v>
       </c>
       <c r="H159" t="s">
         <v>8</v>
@@ -4529,7 +4529,7 @@
         <v>10</v>
       </c>
       <c r="G160" t="n">
-        <v>9.37063312530518</v>
+        <v>9.37063407897949</v>
       </c>
       <c r="H160" t="s">
         <v>8</v>
@@ -4555,7 +4555,7 @@
         <v>10</v>
       </c>
       <c r="G161" t="n">
-        <v>9.37063312530518</v>
+        <v>9.37063407897949</v>
       </c>
       <c r="H161" t="s">
         <v>8</v>
@@ -4581,7 +4581,7 @@
         <v>10</v>
       </c>
       <c r="G162" t="n">
-        <v>9.37063312530518</v>
+        <v>9.37063407897949</v>
       </c>
       <c r="H162" t="s">
         <v>8</v>
@@ -4711,7 +4711,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G167" t="n">
-        <v>9.08951377868652</v>
+        <v>9.08951473236084</v>
       </c>
       <c r="H167" t="s">
         <v>8</v>
@@ -4737,7 +4737,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G168" t="n">
-        <v>9.08951377868652</v>
+        <v>9.08951473236084</v>
       </c>
       <c r="H168" t="s">
         <v>8</v>
@@ -4815,7 +4815,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G171" t="n">
-        <v>8.80839443206787</v>
+        <v>8.80839538574219</v>
       </c>
       <c r="H171" t="s">
         <v>8</v>
@@ -4919,7 +4919,7 @@
         <v>9.42000007629395</v>
       </c>
       <c r="G175" t="n">
-        <v>8.82713603973389</v>
+        <v>8.8271369934082</v>
       </c>
       <c r="H175" t="s">
         <v>8</v>
@@ -5127,7 +5127,7 @@
         <v>9.42000007629395</v>
       </c>
       <c r="G183" t="n">
-        <v>8.82713603973389</v>
+        <v>8.8271369934082</v>
       </c>
       <c r="H183" t="s">
         <v>8</v>
@@ -5153,7 +5153,7 @@
         <v>9.42000007629395</v>
       </c>
       <c r="G184" t="n">
-        <v>8.82713603973389</v>
+        <v>8.8271369934082</v>
       </c>
       <c r="H184" t="s">
         <v>8</v>
@@ -5179,7 +5179,7 @@
         <v>9.72000026702881</v>
       </c>
       <c r="G185" t="n">
-        <v>9.10825538635254</v>
+        <v>9.10825634002686</v>
       </c>
       <c r="H185" t="s">
         <v>8</v>
@@ -5205,7 +5205,7 @@
         <v>9.84000015258789</v>
       </c>
       <c r="G186" t="n">
-        <v>9.22070217132568</v>
+        <v>9.220703125</v>
       </c>
       <c r="H186" t="s">
         <v>8</v>
@@ -5283,7 +5283,7 @@
         <v>9.61999988555908</v>
       </c>
       <c r="G189" t="n">
-        <v>9.01454830169678</v>
+        <v>9.01454925537109</v>
       </c>
       <c r="H189" t="s">
         <v>8</v>
@@ -5413,7 +5413,7 @@
         <v>9.64000034332275</v>
       </c>
       <c r="G194" t="n">
-        <v>9.03328990936279</v>
+        <v>9.03329086303711</v>
       </c>
       <c r="H194" t="s">
         <v>8</v>
@@ -5439,7 +5439,7 @@
         <v>9.53999996185303</v>
       </c>
       <c r="G195" t="n">
-        <v>8.93958282470703</v>
+        <v>8.93958377838135</v>
       </c>
       <c r="H195" t="s">
         <v>8</v>
@@ -5465,7 +5465,7 @@
         <v>9.53999996185303</v>
       </c>
       <c r="G196" t="n">
-        <v>8.93958282470703</v>
+        <v>8.93958377838135</v>
       </c>
       <c r="H196" t="s">
         <v>8</v>
@@ -5491,7 +5491,7 @@
         <v>9.53999996185303</v>
       </c>
       <c r="G197" t="n">
-        <v>8.93958282470703</v>
+        <v>8.93958377838135</v>
       </c>
       <c r="H197" t="s">
         <v>8</v>
@@ -5881,7 +5881,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G212" t="n">
-        <v>8.52727603912354</v>
+        <v>8.52727699279785</v>
       </c>
       <c r="H212" t="s">
         <v>8</v>
@@ -5907,7 +5907,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G213" t="n">
-        <v>8.52727603912354</v>
+        <v>8.52727699279785</v>
       </c>
       <c r="H213" t="s">
         <v>8</v>
@@ -5933,7 +5933,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G214" t="n">
-        <v>8.52727603912354</v>
+        <v>8.52727699279785</v>
       </c>
       <c r="H214" t="s">
         <v>8</v>
@@ -5959,7 +5959,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G215" t="n">
-        <v>8.52727603912354</v>
+        <v>8.52727699279785</v>
       </c>
       <c r="H215" t="s">
         <v>8</v>
@@ -5985,7 +5985,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G216" t="n">
-        <v>8.52727603912354</v>
+        <v>8.52727699279785</v>
       </c>
       <c r="H216" t="s">
         <v>8</v>
@@ -6011,7 +6011,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G217" t="n">
-        <v>8.52727603912354</v>
+        <v>8.52727699279785</v>
       </c>
       <c r="H217" t="s">
         <v>8</v>
@@ -6037,7 +6037,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G218" t="n">
-        <v>8.52727603912354</v>
+        <v>8.52727699279785</v>
       </c>
       <c r="H218" t="s">
         <v>8</v>
@@ -6063,7 +6063,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G219" t="n">
-        <v>8.52727603912354</v>
+        <v>8.52727699279785</v>
       </c>
       <c r="H219" t="s">
         <v>8</v>
@@ -6219,7 +6219,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G225" t="n">
-        <v>8.52727603912354</v>
+        <v>8.52727699279785</v>
       </c>
       <c r="H225" t="s">
         <v>8</v>
@@ -6245,7 +6245,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G226" t="n">
-        <v>8.52727603912354</v>
+        <v>8.52727699279785</v>
       </c>
       <c r="H226" t="s">
         <v>8</v>
@@ -6271,7 +6271,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G227" t="n">
-        <v>8.52727603912354</v>
+        <v>8.52727699279785</v>
       </c>
       <c r="H227" t="s">
         <v>8</v>
@@ -6297,7 +6297,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G228" t="n">
-        <v>8.52727603912354</v>
+        <v>8.52727699279785</v>
       </c>
       <c r="H228" t="s">
         <v>8</v>
@@ -6323,7 +6323,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G229" t="n">
-        <v>8.52727603912354</v>
+        <v>8.52727699279785</v>
       </c>
       <c r="H229" t="s">
         <v>8</v>
@@ -6349,7 +6349,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G230" t="n">
-        <v>8.52727603912354</v>
+        <v>8.52727699279785</v>
       </c>
       <c r="H230" t="s">
         <v>8</v>
@@ -6375,7 +6375,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G231" t="n">
-        <v>8.52727603912354</v>
+        <v>8.52727699279785</v>
       </c>
       <c r="H231" t="s">
         <v>8</v>
@@ -6401,7 +6401,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G232" t="n">
-        <v>8.52727603912354</v>
+        <v>8.52727699279785</v>
       </c>
       <c r="H232" t="s">
         <v>8</v>
@@ -6427,7 +6427,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G233" t="n">
-        <v>8.52727603912354</v>
+        <v>8.52727699279785</v>
       </c>
       <c r="H233" t="s">
         <v>8</v>
@@ -6583,7 +6583,7 @@
         <v>8.73999977111816</v>
       </c>
       <c r="G239" t="n">
-        <v>8.18993282318115</v>
+        <v>8.18993377685547</v>
       </c>
       <c r="H239" t="s">
         <v>8</v>
@@ -6635,7 +6635,7 @@
         <v>8.42000007629395</v>
       </c>
       <c r="G241" t="n">
-        <v>7.89007329940796</v>
+        <v>7.8900728225708</v>
       </c>
       <c r="H241" t="s">
         <v>8</v>
@@ -6661,7 +6661,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G242" t="n">
-        <v>7.68391895294189</v>
+        <v>7.68391942977905</v>
       </c>
       <c r="H242" t="s">
         <v>8</v>
@@ -6687,7 +6687,7 @@
         <v>8.15999984741211</v>
       </c>
       <c r="G243" t="n">
-        <v>7.64643621444702</v>
+        <v>7.64643669128418</v>
       </c>
       <c r="H243" t="s">
         <v>8</v>
@@ -6739,7 +6739,7 @@
         <v>8.0600004196167</v>
       </c>
       <c r="G245" t="n">
-        <v>7.55273056030273</v>
+        <v>7.55273103713989</v>
       </c>
       <c r="H245" t="s">
         <v>8</v>
@@ -6765,7 +6765,7 @@
         <v>8.0600004196167</v>
       </c>
       <c r="G246" t="n">
-        <v>7.55273056030273</v>
+        <v>7.55273103713989</v>
       </c>
       <c r="H246" t="s">
         <v>8</v>
@@ -6791,7 +6791,7 @@
         <v>8.0600004196167</v>
       </c>
       <c r="G247" t="n">
-        <v>7.55273056030273</v>
+        <v>7.55273103713989</v>
       </c>
       <c r="H247" t="s">
         <v>8</v>
@@ -6817,7 +6817,7 @@
         <v>8.0600004196167</v>
       </c>
       <c r="G248" t="n">
-        <v>7.55273056030273</v>
+        <v>7.55273103713989</v>
       </c>
       <c r="H248" t="s">
         <v>8</v>
@@ -6843,7 +6843,7 @@
         <v>8.03999996185303</v>
       </c>
       <c r="G249" t="n">
-        <v>7.53398942947388</v>
+        <v>7.53398895263672</v>
       </c>
       <c r="H249" t="s">
         <v>8</v>
@@ -6895,7 +6895,7 @@
         <v>8.23999977111816</v>
       </c>
       <c r="G251" t="n">
-        <v>7.72140073776245</v>
+        <v>7.72140169143677</v>
       </c>
       <c r="H251" t="s">
         <v>8</v>
@@ -6973,7 +6973,7 @@
         <v>8.03999996185303</v>
       </c>
       <c r="G254" t="n">
-        <v>7.53398942947388</v>
+        <v>7.53398895263672</v>
       </c>
       <c r="H254" t="s">
         <v>8</v>
@@ -6999,7 +6999,7 @@
         <v>7.61999988555908</v>
       </c>
       <c r="G255" t="n">
-        <v>7.14042186737061</v>
+        <v>7.14042234420776</v>
       </c>
       <c r="H255" t="s">
         <v>8</v>
@@ -7025,7 +7025,7 @@
         <v>7.71999979019165</v>
       </c>
       <c r="G256" t="n">
-        <v>7.23412799835205</v>
+        <v>7.23412847518921</v>
       </c>
       <c r="H256" t="s">
         <v>8</v>
@@ -7285,7 +7285,7 @@
         <v>7.61999988555908</v>
       </c>
       <c r="G266" t="n">
-        <v>7.14042186737061</v>
+        <v>7.14042234420776</v>
       </c>
       <c r="H266" t="s">
         <v>8</v>
@@ -7389,7 +7389,7 @@
         <v>7.71999979019165</v>
       </c>
       <c r="G270" t="n">
-        <v>7.23412799835205</v>
+        <v>7.23412847518921</v>
       </c>
       <c r="H270" t="s">
         <v>8</v>
@@ -7415,7 +7415,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G271" t="n">
-        <v>7.77762603759766</v>
+        <v>7.7776255607605</v>
       </c>
       <c r="H271" t="s">
         <v>8</v>
@@ -7441,7 +7441,7 @@
         <v>8.53999996185303</v>
       </c>
       <c r="G272" t="n">
-        <v>8.00252056121826</v>
+        <v>8.00252151489258</v>
       </c>
       <c r="H272" t="s">
         <v>8</v>
@@ -7519,7 +7519,7 @@
         <v>9.14000034332275</v>
       </c>
       <c r="G275" t="n">
-        <v>8.56475830078125</v>
+        <v>8.56475925445557</v>
       </c>
       <c r="H275" t="s">
         <v>8</v>
@@ -7545,7 +7545,7 @@
         <v>9.11999988555908</v>
       </c>
       <c r="G276" t="n">
-        <v>8.54601669311523</v>
+        <v>8.54601764678955</v>
       </c>
       <c r="H276" t="s">
         <v>8</v>
@@ -7571,7 +7571,7 @@
         <v>9.14000034332275</v>
       </c>
       <c r="G277" t="n">
-        <v>8.56475830078125</v>
+        <v>8.56475925445557</v>
       </c>
       <c r="H277" t="s">
         <v>8</v>
@@ -7623,7 +7623,7 @@
         <v>9.11999988555908</v>
       </c>
       <c r="G279" t="n">
-        <v>8.54601669311523</v>
+        <v>8.54601764678955</v>
       </c>
       <c r="H279" t="s">
         <v>8</v>
@@ -7649,7 +7649,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G280" t="n">
-        <v>8.52727603912354</v>
+        <v>8.52727699279785</v>
       </c>
       <c r="H280" t="s">
         <v>8</v>
@@ -7753,7 +7753,7 @@
         <v>8.81999969482422</v>
       </c>
       <c r="G284" t="n">
-        <v>8.26489734649658</v>
+        <v>8.2648983001709</v>
       </c>
       <c r="H284" t="s">
         <v>8</v>
@@ -7883,7 +7883,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G289" t="n">
-        <v>8.52727603912354</v>
+        <v>8.52727699279785</v>
       </c>
       <c r="H289" t="s">
         <v>8</v>
@@ -7935,7 +7935,7 @@
         <v>9.11999988555908</v>
       </c>
       <c r="G291" t="n">
-        <v>8.54601669311523</v>
+        <v>8.54601764678955</v>
       </c>
       <c r="H291" t="s">
         <v>8</v>
@@ -7961,7 +7961,7 @@
         <v>9.11999988555908</v>
       </c>
       <c r="G292" t="n">
-        <v>8.54601669311523</v>
+        <v>8.54601764678955</v>
       </c>
       <c r="H292" t="s">
         <v>8</v>
@@ -8039,7 +8039,7 @@
         <v>9.14000034332275</v>
       </c>
       <c r="G295" t="n">
-        <v>8.56475830078125</v>
+        <v>8.56475925445557</v>
       </c>
       <c r="H295" t="s">
         <v>8</v>
@@ -8091,7 +8091,7 @@
         <v>9.14000034332275</v>
       </c>
       <c r="G297" t="n">
-        <v>8.56475830078125</v>
+        <v>8.56475925445557</v>
       </c>
       <c r="H297" t="s">
         <v>8</v>
@@ -8117,7 +8117,7 @@
         <v>9.14000034332275</v>
       </c>
       <c r="G298" t="n">
-        <v>8.56475830078125</v>
+        <v>8.56475925445557</v>
       </c>
       <c r="H298" t="s">
         <v>8</v>
@@ -8143,7 +8143,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G299" t="n">
-        <v>8.52727603912354</v>
+        <v>8.52727699279785</v>
       </c>
       <c r="H299" t="s">
         <v>8</v>
@@ -8195,7 +8195,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G301" t="n">
-        <v>8.52727603912354</v>
+        <v>8.52727699279785</v>
       </c>
       <c r="H301" t="s">
         <v>8</v>
@@ -8403,7 +8403,7 @@
         <v>8.53999996185303</v>
       </c>
       <c r="G309" t="n">
-        <v>8.00252056121826</v>
+        <v>8.00252151489258</v>
       </c>
       <c r="H309" t="s">
         <v>8</v>
@@ -8481,7 +8481,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G312" t="n">
-        <v>7.83384990692139</v>
+        <v>7.83384895324707</v>
       </c>
       <c r="H312" t="s">
         <v>8</v>
@@ -8689,7 +8689,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G320" t="n">
-        <v>7.87133169174194</v>
+        <v>7.87133121490479</v>
       </c>
       <c r="H320" t="s">
         <v>8</v>
@@ -8741,7 +8741,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G322" t="n">
-        <v>7.77762603759766</v>
+        <v>7.7776255607605</v>
       </c>
       <c r="H322" t="s">
         <v>8</v>
@@ -8767,7 +8767,7 @@
         <v>8.27999973297119</v>
       </c>
       <c r="G323" t="n">
-        <v>7.75888395309448</v>
+        <v>7.75888442993164</v>
       </c>
       <c r="H323" t="s">
         <v>8</v>
@@ -8793,7 +8793,7 @@
         <v>8.27999973297119</v>
       </c>
       <c r="G324" t="n">
-        <v>7.75888395309448</v>
+        <v>7.75888442993164</v>
       </c>
       <c r="H324" t="s">
         <v>8</v>
@@ -8819,7 +8819,7 @@
         <v>8.27999973297119</v>
       </c>
       <c r="G325" t="n">
-        <v>7.75888395309448</v>
+        <v>7.75888442993164</v>
       </c>
       <c r="H325" t="s">
         <v>8</v>
@@ -8871,7 +8871,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G327" t="n">
-        <v>7.77762603759766</v>
+        <v>7.7776255607605</v>
       </c>
       <c r="H327" t="s">
         <v>8</v>
@@ -8897,7 +8897,7 @@
         <v>8.34000015258789</v>
       </c>
       <c r="G328" t="n">
-        <v>7.81510782241821</v>
+        <v>7.81510829925537</v>
       </c>
       <c r="H328" t="s">
         <v>8</v>
@@ -8923,7 +8923,7 @@
         <v>8.34000015258789</v>
       </c>
       <c r="G329" t="n">
-        <v>7.81510782241821</v>
+        <v>7.81510829925537</v>
       </c>
       <c r="H329" t="s">
         <v>8</v>
@@ -8949,7 +8949,7 @@
         <v>8.34000015258789</v>
       </c>
       <c r="G330" t="n">
-        <v>7.81510782241821</v>
+        <v>7.81510829925537</v>
       </c>
       <c r="H330" t="s">
         <v>8</v>
@@ -8975,7 +8975,7 @@
         <v>8.34000015258789</v>
       </c>
       <c r="G331" t="n">
-        <v>7.81510782241821</v>
+        <v>7.81510829925537</v>
       </c>
       <c r="H331" t="s">
         <v>8</v>
@@ -9001,7 +9001,7 @@
         <v>8.34000015258789</v>
       </c>
       <c r="G332" t="n">
-        <v>7.81510782241821</v>
+        <v>7.81510829925537</v>
       </c>
       <c r="H332" t="s">
         <v>8</v>
@@ -9079,7 +9079,7 @@
         <v>8.42000007629395</v>
       </c>
       <c r="G335" t="n">
-        <v>7.89007329940796</v>
+        <v>7.8900728225708</v>
       </c>
       <c r="H335" t="s">
         <v>8</v>
@@ -9261,7 +9261,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G342" t="n">
-        <v>8.80839443206787</v>
+        <v>8.80839538574219</v>
       </c>
       <c r="H342" t="s">
         <v>8</v>
@@ -9287,7 +9287,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G343" t="n">
-        <v>9.08951377868652</v>
+        <v>9.08951473236084</v>
       </c>
       <c r="H343" t="s">
         <v>8</v>
@@ -9339,7 +9339,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G345" t="n">
-        <v>9.08951377868652</v>
+        <v>9.08951473236084</v>
       </c>
       <c r="H345" t="s">
         <v>8</v>
@@ -9495,7 +9495,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G351" t="n">
-        <v>9.08951377868652</v>
+        <v>9.08951473236084</v>
       </c>
       <c r="H351" t="s">
         <v>8</v>
@@ -9755,7 +9755,7 @@
         <v>9.75</v>
       </c>
       <c r="G361" t="n">
-        <v>9.13636779785156</v>
+        <v>9.13636684417725</v>
       </c>
       <c r="H361" t="s">
         <v>8</v>
@@ -10015,7 +10015,7 @@
         <v>9.75</v>
       </c>
       <c r="G371" t="n">
-        <v>9.13636779785156</v>
+        <v>9.13636684417725</v>
       </c>
       <c r="H371" t="s">
         <v>8</v>
@@ -10041,7 +10041,7 @@
         <v>9.75</v>
       </c>
       <c r="G372" t="n">
-        <v>9.13636779785156</v>
+        <v>9.13636684417725</v>
       </c>
       <c r="H372" t="s">
         <v>8</v>
@@ -25384,6 +25384,32 @@
         <v>10.6000003814697</v>
       </c>
       <c r="H962" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="963">
+      <c r="A963" s="1" t="n">
+        <v>46287.2916666667</v>
+      </c>
+      <c r="B963" t="n">
+        <v>2000</v>
+      </c>
+      <c r="C963" t="n">
+        <v>10.6999998092651</v>
+      </c>
+      <c r="D963" t="n">
+        <v>10.6000003814697</v>
+      </c>
+      <c r="E963" t="n">
+        <v>10.6999998092651</v>
+      </c>
+      <c r="F963" t="n">
+        <v>10.6000003814697</v>
+      </c>
+      <c r="G963" t="n">
+        <v>10.6000003814697</v>
+      </c>
+      <c r="H963" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/RDUE.MI.xlsx
+++ b/data/RDUE.MI.xlsx
@@ -525,7 +525,7 @@
         <v>12.0539999008179</v>
       </c>
       <c r="G6" t="n">
-        <v>11.2953605651855</v>
+        <v>11.2953615188599</v>
       </c>
       <c r="H6" t="s">
         <v>8</v>
@@ -551,7 +551,7 @@
         <v>12.0900001525879</v>
       </c>
       <c r="G7" t="n">
-        <v>11.3290948867798</v>
+        <v>11.3290958404541</v>
       </c>
       <c r="H7" t="s">
         <v>8</v>
@@ -655,7 +655,7 @@
         <v>11.9180002212524</v>
       </c>
       <c r="G11" t="n">
-        <v>11.1679201126099</v>
+        <v>11.1679210662842</v>
       </c>
       <c r="H11" t="s">
         <v>8</v>
@@ -707,7 +707,7 @@
         <v>11.8800001144409</v>
       </c>
       <c r="G13" t="n">
-        <v>11.1323118209839</v>
+        <v>11.1323127746582</v>
       </c>
       <c r="H13" t="s">
         <v>8</v>
@@ -759,7 +759,7 @@
         <v>11.6199998855591</v>
       </c>
       <c r="G15" t="n">
-        <v>10.8886747360229</v>
+        <v>10.8886756896973</v>
       </c>
       <c r="H15" t="s">
         <v>8</v>
@@ -785,7 +785,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G16" t="n">
-        <v>11.0573463439941</v>
+        <v>11.0573472976685</v>
       </c>
       <c r="H16" t="s">
         <v>8</v>
@@ -811,7 +811,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G17" t="n">
-        <v>11.0573463439941</v>
+        <v>11.0573472976685</v>
       </c>
       <c r="H17" t="s">
         <v>8</v>
@@ -889,7 +889,7 @@
         <v>11.5900001525879</v>
       </c>
       <c r="G20" t="n">
-        <v>10.8605642318726</v>
+        <v>10.8605632781982</v>
       </c>
       <c r="H20" t="s">
         <v>8</v>
@@ -941,7 +941,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G22" t="n">
-        <v>10.682520866394</v>
+        <v>10.6825218200684</v>
       </c>
       <c r="H22" t="s">
         <v>8</v>
@@ -993,7 +993,7 @@
         <v>11.2600002288818</v>
       </c>
       <c r="G24" t="n">
-        <v>10.5513324737549</v>
+        <v>10.5513334274292</v>
       </c>
       <c r="H24" t="s">
         <v>8</v>
@@ -1019,7 +1019,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G25" t="n">
-        <v>10.5888147354126</v>
+        <v>10.5888156890869</v>
       </c>
       <c r="H25" t="s">
         <v>8</v>
@@ -1045,7 +1045,7 @@
         <v>11.25</v>
       </c>
       <c r="G26" t="n">
-        <v>10.5419616699219</v>
+        <v>10.5419626235962</v>
       </c>
       <c r="H26" t="s">
         <v>8</v>
@@ -1123,7 +1123,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G29" t="n">
-        <v>11.3384656906128</v>
+        <v>11.3384666442871</v>
       </c>
       <c r="H29" t="s">
         <v>8</v>
@@ -1149,7 +1149,7 @@
         <v>11.8800001144409</v>
       </c>
       <c r="G30" t="n">
-        <v>11.1323118209839</v>
+        <v>11.1323127746582</v>
       </c>
       <c r="H30" t="s">
         <v>8</v>
@@ -1175,7 +1175,7 @@
         <v>11.9799995422363</v>
       </c>
       <c r="G31" t="n">
-        <v>11.2260179519653</v>
+        <v>11.2260189056396</v>
       </c>
       <c r="H31" t="s">
         <v>8</v>
@@ -1253,7 +1253,7 @@
         <v>11.75</v>
       </c>
       <c r="G34" t="n">
-        <v>11.0104942321777</v>
+        <v>11.0104932785034</v>
       </c>
       <c r="H34" t="s">
         <v>8</v>
@@ -1279,7 +1279,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G35" t="n">
-        <v>11.0573463439941</v>
+        <v>11.0573472976685</v>
       </c>
       <c r="H35" t="s">
         <v>8</v>
@@ -1305,7 +1305,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G36" t="n">
-        <v>11.0573463439941</v>
+        <v>11.0573472976685</v>
       </c>
       <c r="H36" t="s">
         <v>8</v>
@@ -1331,7 +1331,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G37" t="n">
-        <v>11.0573463439941</v>
+        <v>11.0573472976685</v>
       </c>
       <c r="H37" t="s">
         <v>8</v>
@@ -1383,7 +1383,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G39" t="n">
-        <v>11.1510524749756</v>
+        <v>11.1510534286499</v>
       </c>
       <c r="H39" t="s">
         <v>8</v>
@@ -1409,7 +1409,7 @@
         <v>11.9799995422363</v>
       </c>
       <c r="G40" t="n">
-        <v>11.2260179519653</v>
+        <v>11.2260189056396</v>
       </c>
       <c r="H40" t="s">
         <v>8</v>
@@ -1435,7 +1435,7 @@
         <v>11.9799995422363</v>
       </c>
       <c r="G41" t="n">
-        <v>11.2260179519653</v>
+        <v>11.2260189056396</v>
       </c>
       <c r="H41" t="s">
         <v>8</v>
@@ -1487,7 +1487,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G43" t="n">
-        <v>11.0573463439941</v>
+        <v>11.0573472976685</v>
       </c>
       <c r="H43" t="s">
         <v>8</v>
@@ -1617,7 +1617,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G48" t="n">
-        <v>11.0573463439941</v>
+        <v>11.0573472976685</v>
       </c>
       <c r="H48" t="s">
         <v>8</v>
@@ -1669,7 +1669,7 @@
         <v>11.5500001907349</v>
       </c>
       <c r="G50" t="n">
-        <v>10.8230810165405</v>
+        <v>10.8230819702148</v>
       </c>
       <c r="H50" t="s">
         <v>8</v>
@@ -1695,7 +1695,7 @@
         <v>11.5500001907349</v>
       </c>
       <c r="G51" t="n">
-        <v>10.8230810165405</v>
+        <v>10.8230819702148</v>
       </c>
       <c r="H51" t="s">
         <v>8</v>
@@ -1721,7 +1721,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G52" t="n">
-        <v>11.0573463439941</v>
+        <v>11.0573472976685</v>
       </c>
       <c r="H52" t="s">
         <v>8</v>
@@ -1773,7 +1773,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G54" t="n">
-        <v>11.0573463439941</v>
+        <v>11.0573472976685</v>
       </c>
       <c r="H54" t="s">
         <v>8</v>
@@ -1799,7 +1799,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G55" t="n">
-        <v>11.0573463439941</v>
+        <v>11.0573472976685</v>
       </c>
       <c r="H55" t="s">
         <v>8</v>
@@ -1825,7 +1825,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G56" t="n">
-        <v>11.0573463439941</v>
+        <v>11.0573472976685</v>
       </c>
       <c r="H56" t="s">
         <v>8</v>
@@ -1851,7 +1851,7 @@
         <v>11.75</v>
       </c>
       <c r="G57" t="n">
-        <v>11.0104942321777</v>
+        <v>11.0104932785034</v>
       </c>
       <c r="H57" t="s">
         <v>8</v>
@@ -1877,7 +1877,7 @@
         <v>11.75</v>
       </c>
       <c r="G58" t="n">
-        <v>11.0104942321777</v>
+        <v>11.0104932785034</v>
       </c>
       <c r="H58" t="s">
         <v>8</v>
@@ -1903,7 +1903,7 @@
         <v>11.75</v>
       </c>
       <c r="G59" t="n">
-        <v>11.0104942321777</v>
+        <v>11.0104932785034</v>
       </c>
       <c r="H59" t="s">
         <v>8</v>
@@ -2033,7 +2033,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G64" t="n">
-        <v>10.682520866394</v>
+        <v>10.6825218200684</v>
       </c>
       <c r="H64" t="s">
         <v>8</v>
@@ -2059,7 +2059,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G65" t="n">
-        <v>10.682520866394</v>
+        <v>10.6825218200684</v>
       </c>
       <c r="H65" t="s">
         <v>8</v>
@@ -2085,7 +2085,7 @@
         <v>11.5500001907349</v>
       </c>
       <c r="G66" t="n">
-        <v>10.8230810165405</v>
+        <v>10.8230819702148</v>
       </c>
       <c r="H66" t="s">
         <v>8</v>
@@ -2137,7 +2137,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G68" t="n">
-        <v>10.682520866394</v>
+        <v>10.6825218200684</v>
       </c>
       <c r="H68" t="s">
         <v>8</v>
@@ -2163,7 +2163,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G69" t="n">
-        <v>10.682520866394</v>
+        <v>10.6825218200684</v>
       </c>
       <c r="H69" t="s">
         <v>8</v>
@@ -2215,7 +2215,7 @@
         <v>11.5</v>
       </c>
       <c r="G71" t="n">
-        <v>10.7762269973755</v>
+        <v>10.7762289047241</v>
       </c>
       <c r="H71" t="s">
         <v>8</v>
@@ -2241,7 +2241,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G72" t="n">
-        <v>10.682520866394</v>
+        <v>10.6825218200684</v>
       </c>
       <c r="H72" t="s">
         <v>8</v>
@@ -2397,7 +2397,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G78" t="n">
-        <v>11.0573463439941</v>
+        <v>11.0573472976685</v>
       </c>
       <c r="H78" t="s">
         <v>8</v>
@@ -2423,7 +2423,7 @@
         <v>11.5</v>
       </c>
       <c r="G79" t="n">
-        <v>10.7762269973755</v>
+        <v>10.7762289047241</v>
       </c>
       <c r="H79" t="s">
         <v>8</v>
@@ -2475,7 +2475,7 @@
         <v>11.5500001907349</v>
       </c>
       <c r="G81" t="n">
-        <v>10.8230810165405</v>
+        <v>10.8230819702148</v>
       </c>
       <c r="H81" t="s">
         <v>8</v>
@@ -2501,7 +2501,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G82" t="n">
-        <v>9.74545860290527</v>
+        <v>9.74545764923096</v>
       </c>
       <c r="H82" t="s">
         <v>8</v>
@@ -2527,7 +2527,7 @@
         <v>10.0500001907349</v>
       </c>
       <c r="G83" t="n">
-        <v>9.4174861907959</v>
+        <v>9.41748714447021</v>
       </c>
       <c r="H83" t="s">
         <v>8</v>
@@ -2553,7 +2553,7 @@
         <v>10.0500001907349</v>
       </c>
       <c r="G84" t="n">
-        <v>9.4174861907959</v>
+        <v>9.41748714447021</v>
       </c>
       <c r="H84" t="s">
         <v>8</v>
@@ -2657,7 +2657,7 @@
         <v>10.25</v>
       </c>
       <c r="G88" t="n">
-        <v>9.60489940643311</v>
+        <v>9.60489845275879</v>
       </c>
       <c r="H88" t="s">
         <v>8</v>
@@ -2683,7 +2683,7 @@
         <v>10.5500001907349</v>
       </c>
       <c r="G89" t="n">
-        <v>9.88601875305176</v>
+        <v>9.88601779937744</v>
       </c>
       <c r="H89" t="s">
         <v>8</v>
@@ -2709,7 +2709,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G90" t="n">
-        <v>9.55804634094238</v>
+        <v>9.55804538726807</v>
       </c>
       <c r="H90" t="s">
         <v>8</v>
@@ -2735,7 +2735,7 @@
         <v>10.0500001907349</v>
       </c>
       <c r="G91" t="n">
-        <v>9.4174861907959</v>
+        <v>9.41748714447021</v>
       </c>
       <c r="H91" t="s">
         <v>8</v>
@@ -2761,7 +2761,7 @@
         <v>9.92000007629395</v>
       </c>
       <c r="G92" t="n">
-        <v>9.29566860198975</v>
+        <v>9.29566764831543</v>
       </c>
       <c r="H92" t="s">
         <v>8</v>
@@ -2813,7 +2813,7 @@
         <v>9.73999977111816</v>
       </c>
       <c r="G94" t="n">
-        <v>9.12699699401855</v>
+        <v>9.12699604034424</v>
       </c>
       <c r="H94" t="s">
         <v>8</v>
@@ -2839,7 +2839,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G95" t="n">
-        <v>9.08951473236084</v>
+        <v>9.08951377868652</v>
       </c>
       <c r="H95" t="s">
         <v>8</v>
@@ -2865,7 +2865,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G96" t="n">
-        <v>9.08951473236084</v>
+        <v>9.08951377868652</v>
       </c>
       <c r="H96" t="s">
         <v>8</v>
@@ -2891,7 +2891,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G97" t="n">
-        <v>9.08951473236084</v>
+        <v>9.08951377868652</v>
       </c>
       <c r="H97" t="s">
         <v>8</v>
@@ -3099,7 +3099,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G105" t="n">
-        <v>8.52727699279785</v>
+        <v>8.52727603912354</v>
       </c>
       <c r="H105" t="s">
         <v>8</v>
@@ -3229,7 +3229,7 @@
         <v>9.4399995803833</v>
       </c>
       <c r="G110" t="n">
-        <v>8.8458776473999</v>
+        <v>8.84587669372559</v>
       </c>
       <c r="H110" t="s">
         <v>8</v>
@@ -3255,7 +3255,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G111" t="n">
-        <v>9.08951473236084</v>
+        <v>9.08951377868652</v>
       </c>
       <c r="H111" t="s">
         <v>8</v>
@@ -3307,7 +3307,7 @@
         <v>9.76000022888184</v>
       </c>
       <c r="G113" t="n">
-        <v>9.14573764801025</v>
+        <v>9.14573860168457</v>
       </c>
       <c r="H113" t="s">
         <v>8</v>
@@ -3333,7 +3333,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G114" t="n">
-        <v>9.55804634094238</v>
+        <v>9.55804538726807</v>
       </c>
       <c r="H114" t="s">
         <v>8</v>
@@ -3359,7 +3359,7 @@
         <v>10</v>
       </c>
       <c r="G115" t="n">
-        <v>9.37063407897949</v>
+        <v>9.37063312530518</v>
       </c>
       <c r="H115" t="s">
         <v>8</v>
@@ -3385,7 +3385,7 @@
         <v>10.5500001907349</v>
       </c>
       <c r="G116" t="n">
-        <v>9.88601875305176</v>
+        <v>9.88601779937744</v>
       </c>
       <c r="H116" t="s">
         <v>8</v>
@@ -3411,7 +3411,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G117" t="n">
-        <v>9.74545860290527</v>
+        <v>9.74545764923096</v>
       </c>
       <c r="H117" t="s">
         <v>8</v>
@@ -3437,7 +3437,7 @@
         <v>10.5500001907349</v>
       </c>
       <c r="G118" t="n">
-        <v>9.88601875305176</v>
+        <v>9.88601779937744</v>
       </c>
       <c r="H118" t="s">
         <v>8</v>
@@ -3463,7 +3463,7 @@
         <v>10.5</v>
       </c>
       <c r="G119" t="n">
-        <v>9.83916568756104</v>
+        <v>9.83916473388672</v>
       </c>
       <c r="H119" t="s">
         <v>8</v>
@@ -3645,7 +3645,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G126" t="n">
-        <v>8.99580860137939</v>
+        <v>8.99580764770508</v>
       </c>
       <c r="H126" t="s">
         <v>8</v>
@@ -3671,7 +3671,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G127" t="n">
-        <v>8.99580860137939</v>
+        <v>8.99580764770508</v>
       </c>
       <c r="H127" t="s">
         <v>8</v>
@@ -3749,7 +3749,7 @@
         <v>9.92000007629395</v>
       </c>
       <c r="G130" t="n">
-        <v>9.29566860198975</v>
+        <v>9.29566764831543</v>
       </c>
       <c r="H130" t="s">
         <v>8</v>
@@ -3775,7 +3775,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G131" t="n">
-        <v>9.65175342559814</v>
+        <v>9.65175151824951</v>
       </c>
       <c r="H131" t="s">
         <v>8</v>
@@ -3801,7 +3801,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G132" t="n">
-        <v>9.65175342559814</v>
+        <v>9.65175151824951</v>
       </c>
       <c r="H132" t="s">
         <v>8</v>
@@ -3827,7 +3827,7 @@
         <v>9.97999954223633</v>
       </c>
       <c r="G133" t="n">
-        <v>9.35189247131348</v>
+        <v>9.35189151763916</v>
       </c>
       <c r="H133" t="s">
         <v>8</v>
@@ -3905,7 +3905,7 @@
         <v>10.5</v>
       </c>
       <c r="G136" t="n">
-        <v>9.83916568756104</v>
+        <v>9.83916473388672</v>
       </c>
       <c r="H136" t="s">
         <v>8</v>
@@ -3931,7 +3931,7 @@
         <v>10.5500001907349</v>
       </c>
       <c r="G137" t="n">
-        <v>9.88601875305176</v>
+        <v>9.88601779937744</v>
       </c>
       <c r="H137" t="s">
         <v>8</v>
@@ -3957,7 +3957,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G138" t="n">
-        <v>10.0265769958496</v>
+        <v>10.0265779495239</v>
       </c>
       <c r="H138" t="s">
         <v>8</v>
@@ -3983,7 +3983,7 @@
         <v>10.5</v>
       </c>
       <c r="G139" t="n">
-        <v>9.83916568756104</v>
+        <v>9.83916473388672</v>
       </c>
       <c r="H139" t="s">
         <v>8</v>
@@ -4009,7 +4009,7 @@
         <v>10.5</v>
       </c>
       <c r="G140" t="n">
-        <v>9.83916568756104</v>
+        <v>9.83916473388672</v>
       </c>
       <c r="H140" t="s">
         <v>8</v>
@@ -4035,7 +4035,7 @@
         <v>10.5</v>
       </c>
       <c r="G141" t="n">
-        <v>9.83916568756104</v>
+        <v>9.83916473388672</v>
       </c>
       <c r="H141" t="s">
         <v>8</v>
@@ -4061,7 +4061,7 @@
         <v>10</v>
       </c>
       <c r="G142" t="n">
-        <v>9.37063407897949</v>
+        <v>9.37063312530518</v>
       </c>
       <c r="H142" t="s">
         <v>8</v>
@@ -4139,7 +4139,7 @@
         <v>9.5600004196167</v>
       </c>
       <c r="G145" t="n">
-        <v>8.95832538604736</v>
+        <v>8.95832633972168</v>
       </c>
       <c r="H145" t="s">
         <v>8</v>
@@ -4165,7 +4165,7 @@
         <v>9.5</v>
       </c>
       <c r="G146" t="n">
-        <v>8.90210151672363</v>
+        <v>8.90210056304932</v>
       </c>
       <c r="H146" t="s">
         <v>8</v>
@@ -4191,7 +4191,7 @@
         <v>9.5</v>
       </c>
       <c r="G147" t="n">
-        <v>8.90210151672363</v>
+        <v>8.90210056304932</v>
       </c>
       <c r="H147" t="s">
         <v>8</v>
@@ -4243,7 +4243,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G149" t="n">
-        <v>8.99580860137939</v>
+        <v>8.99580764770508</v>
       </c>
       <c r="H149" t="s">
         <v>8</v>
@@ -4269,7 +4269,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G150" t="n">
-        <v>8.99580860137939</v>
+        <v>8.99580764770508</v>
       </c>
       <c r="H150" t="s">
         <v>8</v>
@@ -4295,7 +4295,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G151" t="n">
-        <v>9.08951473236084</v>
+        <v>9.08951377868652</v>
       </c>
       <c r="H151" t="s">
         <v>8</v>
@@ -4321,7 +4321,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G152" t="n">
-        <v>9.08951473236084</v>
+        <v>9.08951377868652</v>
       </c>
       <c r="H152" t="s">
         <v>8</v>
@@ -4347,7 +4347,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G153" t="n">
-        <v>9.08951473236084</v>
+        <v>9.08951377868652</v>
       </c>
       <c r="H153" t="s">
         <v>8</v>
@@ -4399,7 +4399,7 @@
         <v>10</v>
       </c>
       <c r="G155" t="n">
-        <v>9.37063407897949</v>
+        <v>9.37063312530518</v>
       </c>
       <c r="H155" t="s">
         <v>8</v>
@@ -4425,7 +4425,7 @@
         <v>10</v>
       </c>
       <c r="G156" t="n">
-        <v>9.37063407897949</v>
+        <v>9.37063312530518</v>
       </c>
       <c r="H156" t="s">
         <v>8</v>
@@ -4451,7 +4451,7 @@
         <v>10</v>
       </c>
       <c r="G157" t="n">
-        <v>9.37063407897949</v>
+        <v>9.37063312530518</v>
       </c>
       <c r="H157" t="s">
         <v>8</v>
@@ -4477,7 +4477,7 @@
         <v>10</v>
       </c>
       <c r="G158" t="n">
-        <v>9.37063407897949</v>
+        <v>9.37063312530518</v>
       </c>
       <c r="H158" t="s">
         <v>8</v>
@@ -4503,7 +4503,7 @@
         <v>10</v>
       </c>
       <c r="G159" t="n">
-        <v>9.37063407897949</v>
+        <v>9.37063312530518</v>
       </c>
       <c r="H159" t="s">
         <v>8</v>
@@ -4529,7 +4529,7 @@
         <v>10</v>
       </c>
       <c r="G160" t="n">
-        <v>9.37063407897949</v>
+        <v>9.37063312530518</v>
       </c>
       <c r="H160" t="s">
         <v>8</v>
@@ -4555,7 +4555,7 @@
         <v>10</v>
       </c>
       <c r="G161" t="n">
-        <v>9.37063407897949</v>
+        <v>9.37063312530518</v>
       </c>
       <c r="H161" t="s">
         <v>8</v>
@@ -4581,7 +4581,7 @@
         <v>10</v>
       </c>
       <c r="G162" t="n">
-        <v>9.37063407897949</v>
+        <v>9.37063312530518</v>
       </c>
       <c r="H162" t="s">
         <v>8</v>
@@ -4633,7 +4633,7 @@
         <v>9.97999954223633</v>
       </c>
       <c r="G164" t="n">
-        <v>9.35189247131348</v>
+        <v>9.35189151763916</v>
       </c>
       <c r="H164" t="s">
         <v>8</v>
@@ -4659,7 +4659,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G165" t="n">
-        <v>9.27692699432373</v>
+        <v>9.27692604064941</v>
       </c>
       <c r="H165" t="s">
         <v>8</v>
@@ -4685,7 +4685,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G166" t="n">
-        <v>9.27692699432373</v>
+        <v>9.27692604064941</v>
       </c>
       <c r="H166" t="s">
         <v>8</v>
@@ -4711,7 +4711,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G167" t="n">
-        <v>9.08951473236084</v>
+        <v>9.08951377868652</v>
       </c>
       <c r="H167" t="s">
         <v>8</v>
@@ -4737,7 +4737,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G168" t="n">
-        <v>9.08951473236084</v>
+        <v>9.08951377868652</v>
       </c>
       <c r="H168" t="s">
         <v>8</v>
@@ -4763,7 +4763,7 @@
         <v>9.15999984741211</v>
       </c>
       <c r="G169" t="n">
-        <v>8.58350086212158</v>
+        <v>8.58349990844727</v>
       </c>
       <c r="H169" t="s">
         <v>8</v>
@@ -4789,7 +4789,7 @@
         <v>9.5</v>
       </c>
       <c r="G170" t="n">
-        <v>8.90210151672363</v>
+        <v>8.90210056304932</v>
       </c>
       <c r="H170" t="s">
         <v>8</v>
@@ -4841,7 +4841,7 @@
         <v>9.5600004196167</v>
       </c>
       <c r="G172" t="n">
-        <v>8.95832538604736</v>
+        <v>8.95832633972168</v>
       </c>
       <c r="H172" t="s">
         <v>8</v>
@@ -4867,7 +4867,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G173" t="n">
-        <v>9.27692699432373</v>
+        <v>9.27692604064941</v>
       </c>
       <c r="H173" t="s">
         <v>8</v>
@@ -4893,7 +4893,7 @@
         <v>9.27999973297119</v>
       </c>
       <c r="G174" t="n">
-        <v>8.69594764709473</v>
+        <v>8.69594669342041</v>
       </c>
       <c r="H174" t="s">
         <v>8</v>
@@ -4919,7 +4919,7 @@
         <v>9.42000007629395</v>
       </c>
       <c r="G175" t="n">
-        <v>8.8271369934082</v>
+        <v>8.82713603973389</v>
       </c>
       <c r="H175" t="s">
         <v>8</v>
@@ -4945,7 +4945,7 @@
         <v>9.27999973297119</v>
       </c>
       <c r="G176" t="n">
-        <v>8.69594764709473</v>
+        <v>8.69594669342041</v>
       </c>
       <c r="H176" t="s">
         <v>8</v>
@@ -4971,7 +4971,7 @@
         <v>9.27999973297119</v>
       </c>
       <c r="G177" t="n">
-        <v>8.69594764709473</v>
+        <v>8.69594669342041</v>
       </c>
       <c r="H177" t="s">
         <v>8</v>
@@ -5127,7 +5127,7 @@
         <v>9.42000007629395</v>
       </c>
       <c r="G183" t="n">
-        <v>8.8271369934082</v>
+        <v>8.82713603973389</v>
       </c>
       <c r="H183" t="s">
         <v>8</v>
@@ -5153,7 +5153,7 @@
         <v>9.42000007629395</v>
       </c>
       <c r="G184" t="n">
-        <v>8.8271369934082</v>
+        <v>8.82713603973389</v>
       </c>
       <c r="H184" t="s">
         <v>8</v>
@@ -5231,7 +5231,7 @@
         <v>9.97999954223633</v>
       </c>
       <c r="G187" t="n">
-        <v>9.35189247131348</v>
+        <v>9.35189151763916</v>
       </c>
       <c r="H187" t="s">
         <v>8</v>
@@ -5257,7 +5257,7 @@
         <v>9.97999954223633</v>
       </c>
       <c r="G188" t="n">
-        <v>9.35189247131348</v>
+        <v>9.35189151763916</v>
       </c>
       <c r="H188" t="s">
         <v>8</v>
@@ -5413,7 +5413,7 @@
         <v>9.64000034332275</v>
       </c>
       <c r="G194" t="n">
-        <v>9.03329086303711</v>
+        <v>9.03328990936279</v>
       </c>
       <c r="H194" t="s">
         <v>8</v>
@@ -5517,7 +5517,7 @@
         <v>9.5</v>
       </c>
       <c r="G198" t="n">
-        <v>8.90210151672363</v>
+        <v>8.90210056304932</v>
       </c>
       <c r="H198" t="s">
         <v>8</v>
@@ -5647,7 +5647,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G203" t="n">
-        <v>8.2461576461792</v>
+        <v>8.24615669250488</v>
       </c>
       <c r="H203" t="s">
         <v>8</v>
@@ -5673,7 +5673,7 @@
         <v>9.0600004196167</v>
       </c>
       <c r="G204" t="n">
-        <v>8.48979473114014</v>
+        <v>8.48979377746582</v>
       </c>
       <c r="H204" t="s">
         <v>8</v>
@@ -5881,7 +5881,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G212" t="n">
-        <v>8.52727699279785</v>
+        <v>8.52727603912354</v>
       </c>
       <c r="H212" t="s">
         <v>8</v>
@@ -5907,7 +5907,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G213" t="n">
-        <v>8.52727699279785</v>
+        <v>8.52727603912354</v>
       </c>
       <c r="H213" t="s">
         <v>8</v>
@@ -5933,7 +5933,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G214" t="n">
-        <v>8.52727699279785</v>
+        <v>8.52727603912354</v>
       </c>
       <c r="H214" t="s">
         <v>8</v>
@@ -5959,7 +5959,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G215" t="n">
-        <v>8.52727699279785</v>
+        <v>8.52727603912354</v>
       </c>
       <c r="H215" t="s">
         <v>8</v>
@@ -5985,7 +5985,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G216" t="n">
-        <v>8.52727699279785</v>
+        <v>8.52727603912354</v>
       </c>
       <c r="H216" t="s">
         <v>8</v>
@@ -6011,7 +6011,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G217" t="n">
-        <v>8.52727699279785</v>
+        <v>8.52727603912354</v>
       </c>
       <c r="H217" t="s">
         <v>8</v>
@@ -6037,7 +6037,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G218" t="n">
-        <v>8.52727699279785</v>
+        <v>8.52727603912354</v>
       </c>
       <c r="H218" t="s">
         <v>8</v>
@@ -6063,7 +6063,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G219" t="n">
-        <v>8.52727699279785</v>
+        <v>8.52727603912354</v>
       </c>
       <c r="H219" t="s">
         <v>8</v>
@@ -6219,7 +6219,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G225" t="n">
-        <v>8.52727699279785</v>
+        <v>8.52727603912354</v>
       </c>
       <c r="H225" t="s">
         <v>8</v>
@@ -6245,7 +6245,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G226" t="n">
-        <v>8.52727699279785</v>
+        <v>8.52727603912354</v>
       </c>
       <c r="H226" t="s">
         <v>8</v>
@@ -6271,7 +6271,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G227" t="n">
-        <v>8.52727699279785</v>
+        <v>8.52727603912354</v>
       </c>
       <c r="H227" t="s">
         <v>8</v>
@@ -6297,7 +6297,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G228" t="n">
-        <v>8.52727699279785</v>
+        <v>8.52727603912354</v>
       </c>
       <c r="H228" t="s">
         <v>8</v>
@@ -6323,7 +6323,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G229" t="n">
-        <v>8.52727699279785</v>
+        <v>8.52727603912354</v>
       </c>
       <c r="H229" t="s">
         <v>8</v>
@@ -6349,7 +6349,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G230" t="n">
-        <v>8.52727699279785</v>
+        <v>8.52727603912354</v>
       </c>
       <c r="H230" t="s">
         <v>8</v>
@@ -6375,7 +6375,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G231" t="n">
-        <v>8.52727699279785</v>
+        <v>8.52727603912354</v>
       </c>
       <c r="H231" t="s">
         <v>8</v>
@@ -6401,7 +6401,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G232" t="n">
-        <v>8.52727699279785</v>
+        <v>8.52727603912354</v>
       </c>
       <c r="H232" t="s">
         <v>8</v>
@@ -6427,7 +6427,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G233" t="n">
-        <v>8.52727699279785</v>
+        <v>8.52727603912354</v>
       </c>
       <c r="H233" t="s">
         <v>8</v>
@@ -6479,7 +6479,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G235" t="n">
-        <v>8.2461576461792</v>
+        <v>8.24615669250488</v>
       </c>
       <c r="H235" t="s">
         <v>8</v>
@@ -6583,7 +6583,7 @@
         <v>8.73999977111816</v>
       </c>
       <c r="G239" t="n">
-        <v>8.18993377685547</v>
+        <v>8.18993282318115</v>
       </c>
       <c r="H239" t="s">
         <v>8</v>
@@ -6609,7 +6609,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G240" t="n">
-        <v>8.05874443054199</v>
+        <v>8.05874538421631</v>
       </c>
       <c r="H240" t="s">
         <v>8</v>
@@ -6635,7 +6635,7 @@
         <v>8.42000007629395</v>
       </c>
       <c r="G241" t="n">
-        <v>7.8900728225708</v>
+        <v>7.89007329940796</v>
       </c>
       <c r="H241" t="s">
         <v>8</v>
@@ -6661,7 +6661,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G242" t="n">
-        <v>7.68391942977905</v>
+        <v>7.68391895294189</v>
       </c>
       <c r="H242" t="s">
         <v>8</v>
@@ -6687,7 +6687,7 @@
         <v>8.15999984741211</v>
       </c>
       <c r="G243" t="n">
-        <v>7.64643669128418</v>
+        <v>7.64643621444702</v>
       </c>
       <c r="H243" t="s">
         <v>8</v>
@@ -6739,7 +6739,7 @@
         <v>8.0600004196167</v>
       </c>
       <c r="G245" t="n">
-        <v>7.55273103713989</v>
+        <v>7.55273056030273</v>
       </c>
       <c r="H245" t="s">
         <v>8</v>
@@ -6765,7 +6765,7 @@
         <v>8.0600004196167</v>
       </c>
       <c r="G246" t="n">
-        <v>7.55273103713989</v>
+        <v>7.55273056030273</v>
       </c>
       <c r="H246" t="s">
         <v>8</v>
@@ -6791,7 +6791,7 @@
         <v>8.0600004196167</v>
       </c>
       <c r="G247" t="n">
-        <v>7.55273103713989</v>
+        <v>7.55273056030273</v>
       </c>
       <c r="H247" t="s">
         <v>8</v>
@@ -6817,7 +6817,7 @@
         <v>8.0600004196167</v>
       </c>
       <c r="G248" t="n">
-        <v>7.55273103713989</v>
+        <v>7.55273056030273</v>
       </c>
       <c r="H248" t="s">
         <v>8</v>
@@ -6843,7 +6843,7 @@
         <v>8.03999996185303</v>
       </c>
       <c r="G249" t="n">
-        <v>7.53398895263672</v>
+        <v>7.53398942947388</v>
       </c>
       <c r="H249" t="s">
         <v>8</v>
@@ -6895,7 +6895,7 @@
         <v>8.23999977111816</v>
       </c>
       <c r="G251" t="n">
-        <v>7.72140169143677</v>
+        <v>7.72140121459961</v>
       </c>
       <c r="H251" t="s">
         <v>8</v>
@@ -6973,7 +6973,7 @@
         <v>8.03999996185303</v>
       </c>
       <c r="G254" t="n">
-        <v>7.53398895263672</v>
+        <v>7.53398942947388</v>
       </c>
       <c r="H254" t="s">
         <v>8</v>
@@ -6999,7 +6999,7 @@
         <v>7.61999988555908</v>
       </c>
       <c r="G255" t="n">
-        <v>7.14042234420776</v>
+        <v>7.14042186737061</v>
       </c>
       <c r="H255" t="s">
         <v>8</v>
@@ -7077,7 +7077,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G258" t="n">
-        <v>7.12168121337891</v>
+        <v>7.12168073654175</v>
       </c>
       <c r="H258" t="s">
         <v>8</v>
@@ -7207,7 +7207,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G263" t="n">
-        <v>7.40280055999756</v>
+        <v>7.4028000831604</v>
       </c>
       <c r="H263" t="s">
         <v>8</v>
@@ -7285,7 +7285,7 @@
         <v>7.61999988555908</v>
       </c>
       <c r="G266" t="n">
-        <v>7.14042234420776</v>
+        <v>7.14042186737061</v>
       </c>
       <c r="H266" t="s">
         <v>8</v>
@@ -7441,7 +7441,7 @@
         <v>8.53999996185303</v>
       </c>
       <c r="G272" t="n">
-        <v>8.00252151489258</v>
+        <v>8.00252056121826</v>
       </c>
       <c r="H272" t="s">
         <v>8</v>
@@ -7545,7 +7545,7 @@
         <v>9.11999988555908</v>
       </c>
       <c r="G276" t="n">
-        <v>8.54601764678955</v>
+        <v>8.54601669311523</v>
       </c>
       <c r="H276" t="s">
         <v>8</v>
@@ -7623,7 +7623,7 @@
         <v>9.11999988555908</v>
       </c>
       <c r="G279" t="n">
-        <v>8.54601764678955</v>
+        <v>8.54601669311523</v>
       </c>
       <c r="H279" t="s">
         <v>8</v>
@@ -7649,7 +7649,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G280" t="n">
-        <v>8.52727699279785</v>
+        <v>8.52727603912354</v>
       </c>
       <c r="H280" t="s">
         <v>8</v>
@@ -7701,7 +7701,7 @@
         <v>8.92000007629395</v>
       </c>
       <c r="G282" t="n">
-        <v>8.35860443115234</v>
+        <v>8.35860538482666</v>
       </c>
       <c r="H282" t="s">
         <v>8</v>
@@ -7831,7 +7831,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G287" t="n">
-        <v>8.2461576461792</v>
+        <v>8.24615669250488</v>
       </c>
       <c r="H287" t="s">
         <v>8</v>
@@ -7883,7 +7883,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G289" t="n">
-        <v>8.52727699279785</v>
+        <v>8.52727603912354</v>
       </c>
       <c r="H289" t="s">
         <v>8</v>
@@ -7935,7 +7935,7 @@
         <v>9.11999988555908</v>
       </c>
       <c r="G291" t="n">
-        <v>8.54601764678955</v>
+        <v>8.54601669311523</v>
       </c>
       <c r="H291" t="s">
         <v>8</v>
@@ -7961,7 +7961,7 @@
         <v>9.11999988555908</v>
       </c>
       <c r="G292" t="n">
-        <v>8.54601764678955</v>
+        <v>8.54601669311523</v>
       </c>
       <c r="H292" t="s">
         <v>8</v>
@@ -8143,7 +8143,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G299" t="n">
-        <v>8.52727699279785</v>
+        <v>8.52727603912354</v>
       </c>
       <c r="H299" t="s">
         <v>8</v>
@@ -8195,7 +8195,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G301" t="n">
-        <v>8.52727699279785</v>
+        <v>8.52727603912354</v>
       </c>
       <c r="H301" t="s">
         <v>8</v>
@@ -8299,7 +8299,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G305" t="n">
-        <v>8.2461576461792</v>
+        <v>8.24615669250488</v>
       </c>
       <c r="H305" t="s">
         <v>8</v>
@@ -8325,7 +8325,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G306" t="n">
-        <v>8.2461576461792</v>
+        <v>8.24615669250488</v>
       </c>
       <c r="H306" t="s">
         <v>8</v>
@@ -8351,7 +8351,7 @@
         <v>8.64000034332275</v>
       </c>
       <c r="G307" t="n">
-        <v>8.09622764587402</v>
+        <v>8.09622669219971</v>
       </c>
       <c r="H307" t="s">
         <v>8</v>
@@ -8377,7 +8377,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G308" t="n">
-        <v>8.05874443054199</v>
+        <v>8.05874538421631</v>
       </c>
       <c r="H308" t="s">
         <v>8</v>
@@ -8403,7 +8403,7 @@
         <v>8.53999996185303</v>
       </c>
       <c r="G309" t="n">
-        <v>8.00252151489258</v>
+        <v>8.00252056121826</v>
       </c>
       <c r="H309" t="s">
         <v>8</v>
@@ -8429,7 +8429,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G310" t="n">
-        <v>8.2461576461792</v>
+        <v>8.24615669250488</v>
       </c>
       <c r="H310" t="s">
         <v>8</v>
@@ -8455,7 +8455,7 @@
         <v>8.47999954223633</v>
       </c>
       <c r="G311" t="n">
-        <v>7.94629669189453</v>
+        <v>7.94629621505737</v>
       </c>
       <c r="H311" t="s">
         <v>8</v>
@@ -8481,7 +8481,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G312" t="n">
-        <v>7.83384895324707</v>
+        <v>7.83384943008423</v>
       </c>
       <c r="H312" t="s">
         <v>8</v>
@@ -8533,7 +8533,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G314" t="n">
-        <v>8.2461576461792</v>
+        <v>8.24615669250488</v>
       </c>
       <c r="H314" t="s">
         <v>8</v>
@@ -8585,7 +8585,7 @@
         <v>8.47999954223633</v>
       </c>
       <c r="G316" t="n">
-        <v>7.94629669189453</v>
+        <v>7.94629621505737</v>
       </c>
       <c r="H316" t="s">
         <v>8</v>
@@ -8637,7 +8637,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G318" t="n">
-        <v>8.2461576461792</v>
+        <v>8.24615669250488</v>
       </c>
       <c r="H318" t="s">
         <v>8</v>
@@ -8663,7 +8663,7 @@
         <v>8.47999954223633</v>
       </c>
       <c r="G319" t="n">
-        <v>7.94629669189453</v>
+        <v>7.94629621505737</v>
       </c>
       <c r="H319" t="s">
         <v>8</v>
@@ -8897,7 +8897,7 @@
         <v>8.34000015258789</v>
       </c>
       <c r="G328" t="n">
-        <v>7.81510829925537</v>
+        <v>7.81510782241821</v>
       </c>
       <c r="H328" t="s">
         <v>8</v>
@@ -8923,7 +8923,7 @@
         <v>8.34000015258789</v>
       </c>
       <c r="G329" t="n">
-        <v>7.81510829925537</v>
+        <v>7.81510782241821</v>
       </c>
       <c r="H329" t="s">
         <v>8</v>
@@ -8949,7 +8949,7 @@
         <v>8.34000015258789</v>
       </c>
       <c r="G330" t="n">
-        <v>7.81510829925537</v>
+        <v>7.81510782241821</v>
       </c>
       <c r="H330" t="s">
         <v>8</v>
@@ -8975,7 +8975,7 @@
         <v>8.34000015258789</v>
       </c>
       <c r="G331" t="n">
-        <v>7.81510829925537</v>
+        <v>7.81510782241821</v>
       </c>
       <c r="H331" t="s">
         <v>8</v>
@@ -9001,7 +9001,7 @@
         <v>8.34000015258789</v>
       </c>
       <c r="G332" t="n">
-        <v>7.81510829925537</v>
+        <v>7.81510782241821</v>
       </c>
       <c r="H332" t="s">
         <v>8</v>
@@ -9079,7 +9079,7 @@
         <v>8.42000007629395</v>
       </c>
       <c r="G335" t="n">
-        <v>7.8900728225708</v>
+        <v>7.89007329940796</v>
       </c>
       <c r="H335" t="s">
         <v>8</v>
@@ -9105,7 +9105,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G336" t="n">
-        <v>8.2461576461792</v>
+        <v>8.24615669250488</v>
       </c>
       <c r="H336" t="s">
         <v>8</v>
@@ -9287,7 +9287,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G343" t="n">
-        <v>9.08951473236084</v>
+        <v>9.08951377868652</v>
       </c>
       <c r="H343" t="s">
         <v>8</v>
@@ -9313,7 +9313,7 @@
         <v>9.5</v>
       </c>
       <c r="G344" t="n">
-        <v>8.90210151672363</v>
+        <v>8.90210056304932</v>
       </c>
       <c r="H344" t="s">
         <v>8</v>
@@ -9339,7 +9339,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G345" t="n">
-        <v>9.08951473236084</v>
+        <v>9.08951377868652</v>
       </c>
       <c r="H345" t="s">
         <v>8</v>
@@ -9391,7 +9391,7 @@
         <v>9.5</v>
       </c>
       <c r="G347" t="n">
-        <v>8.90210151672363</v>
+        <v>8.90210056304932</v>
       </c>
       <c r="H347" t="s">
         <v>8</v>
@@ -9417,7 +9417,7 @@
         <v>9.5</v>
       </c>
       <c r="G348" t="n">
-        <v>8.90210151672363</v>
+        <v>8.90210056304932</v>
       </c>
       <c r="H348" t="s">
         <v>8</v>
@@ -9469,7 +9469,7 @@
         <v>9.5</v>
       </c>
       <c r="G350" t="n">
-        <v>8.90210151672363</v>
+        <v>8.90210056304932</v>
       </c>
       <c r="H350" t="s">
         <v>8</v>
@@ -9495,7 +9495,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G351" t="n">
-        <v>9.08951473236084</v>
+        <v>9.08951377868652</v>
       </c>
       <c r="H351" t="s">
         <v>8</v>
@@ -9521,7 +9521,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G352" t="n">
-        <v>8.99580860137939</v>
+        <v>8.99580764770508</v>
       </c>
       <c r="H352" t="s">
         <v>8</v>
@@ -9547,7 +9547,7 @@
         <v>9.5</v>
       </c>
       <c r="G353" t="n">
-        <v>8.90210151672363</v>
+        <v>8.90210056304932</v>
       </c>
       <c r="H353" t="s">
         <v>8</v>
@@ -9573,7 +9573,7 @@
         <v>9.5</v>
       </c>
       <c r="G354" t="n">
-        <v>8.90210151672363</v>
+        <v>8.90210056304932</v>
       </c>
       <c r="H354" t="s">
         <v>8</v>
@@ -9599,7 +9599,7 @@
         <v>9.5</v>
       </c>
       <c r="G355" t="n">
-        <v>8.90210151672363</v>
+        <v>8.90210056304932</v>
       </c>
       <c r="H355" t="s">
         <v>8</v>
@@ -9625,7 +9625,7 @@
         <v>9.5</v>
       </c>
       <c r="G356" t="n">
-        <v>8.90210151672363</v>
+        <v>8.90210056304932</v>
       </c>
       <c r="H356" t="s">
         <v>8</v>
@@ -9651,7 +9651,7 @@
         <v>9.5</v>
       </c>
       <c r="G357" t="n">
-        <v>8.90210151672363</v>
+        <v>8.90210056304932</v>
       </c>
       <c r="H357" t="s">
         <v>8</v>
@@ -9781,7 +9781,7 @@
         <v>9.5</v>
       </c>
       <c r="G362" t="n">
-        <v>8.90210151672363</v>
+        <v>8.90210056304932</v>
       </c>
       <c r="H362" t="s">
         <v>8</v>
@@ -9989,7 +9989,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G370" t="n">
-        <v>9.27692699432373</v>
+        <v>9.27692604064941</v>
       </c>
       <c r="H370" t="s">
         <v>8</v>
@@ -10119,7 +10119,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G375" t="n">
-        <v>9.30551815032959</v>
+        <v>9.30551719665527</v>
       </c>
       <c r="H375" t="s">
         <v>8</v>
@@ -10145,7 +10145,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G376" t="n">
-        <v>9.2575511932373</v>
+        <v>9.25755023956299</v>
       </c>
       <c r="H376" t="s">
         <v>8</v>
@@ -10197,7 +10197,7 @@
         <v>10</v>
       </c>
       <c r="G378" t="n">
-        <v>9.59331798553467</v>
+        <v>9.59331703186035</v>
       </c>
       <c r="H378" t="s">
         <v>8</v>
@@ -10535,7 +10535,7 @@
         <v>10</v>
       </c>
       <c r="G391" t="n">
-        <v>9.59331798553467</v>
+        <v>9.59331703186035</v>
       </c>
       <c r="H391" t="s">
         <v>8</v>
@@ -10665,7 +10665,7 @@
         <v>10</v>
       </c>
       <c r="G396" t="n">
-        <v>9.59331798553467</v>
+        <v>9.59331703186035</v>
       </c>
       <c r="H396" t="s">
         <v>8</v>
@@ -10691,7 +10691,7 @@
         <v>10</v>
       </c>
       <c r="G397" t="n">
-        <v>9.59331798553467</v>
+        <v>9.59331703186035</v>
       </c>
       <c r="H397" t="s">
         <v>8</v>
@@ -10743,7 +10743,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G399" t="n">
-        <v>9.30551815032959</v>
+        <v>9.30551719665527</v>
       </c>
       <c r="H399" t="s">
         <v>8</v>
@@ -10795,7 +10795,7 @@
         <v>9.35000038146973</v>
       </c>
       <c r="G401" t="n">
-        <v>8.96975231170654</v>
+        <v>8.96975135803223</v>
       </c>
       <c r="H401" t="s">
         <v>8</v>
@@ -11055,7 +11055,7 @@
         <v>10</v>
       </c>
       <c r="G411" t="n">
-        <v>9.59331798553467</v>
+        <v>9.59331703186035</v>
       </c>
       <c r="H411" t="s">
         <v>8</v>
@@ -11185,7 +11185,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G416" t="n">
-        <v>9.2575511932373</v>
+        <v>9.25755023956299</v>
       </c>
       <c r="H416" t="s">
         <v>8</v>
@@ -11211,7 +11211,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G417" t="n">
-        <v>9.2575511932373</v>
+        <v>9.25755023956299</v>
       </c>
       <c r="H417" t="s">
         <v>8</v>
@@ -11237,7 +11237,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G418" t="n">
-        <v>9.2575511932373</v>
+        <v>9.25755023956299</v>
       </c>
       <c r="H418" t="s">
         <v>8</v>
@@ -11263,7 +11263,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G419" t="n">
-        <v>9.30551815032959</v>
+        <v>9.30551719665527</v>
       </c>
       <c r="H419" t="s">
         <v>8</v>
@@ -11315,7 +11315,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G421" t="n">
-        <v>9.01771831512451</v>
+        <v>9.0177173614502</v>
       </c>
       <c r="H421" t="s">
         <v>8</v>
@@ -11367,7 +11367,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G423" t="n">
-        <v>9.2575511932373</v>
+        <v>9.25755023956299</v>
       </c>
       <c r="H423" t="s">
         <v>8</v>
@@ -11393,7 +11393,7 @@
         <v>9.35000038146973</v>
       </c>
       <c r="G424" t="n">
-        <v>8.96975231170654</v>
+        <v>8.96975135803223</v>
       </c>
       <c r="H424" t="s">
         <v>8</v>
@@ -11419,7 +11419,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G425" t="n">
-        <v>8.53805160522461</v>
+        <v>8.53805255889893</v>
       </c>
       <c r="H425" t="s">
         <v>8</v>
@@ -11523,7 +11523,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G429" t="n">
-        <v>9.2575511932373</v>
+        <v>9.25755023956299</v>
       </c>
       <c r="H429" t="s">
         <v>8</v>
@@ -11549,7 +11549,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G430" t="n">
-        <v>9.2575511932373</v>
+        <v>9.25755023956299</v>
       </c>
       <c r="H430" t="s">
         <v>8</v>
@@ -11601,7 +11601,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G432" t="n">
-        <v>9.01771831512451</v>
+        <v>9.0177173614502</v>
       </c>
       <c r="H432" t="s">
         <v>8</v>
@@ -11627,7 +11627,7 @@
         <v>9.35000038146973</v>
       </c>
       <c r="G433" t="n">
-        <v>8.96975231170654</v>
+        <v>8.96975135803223</v>
       </c>
       <c r="H433" t="s">
         <v>8</v>
@@ -11679,7 +11679,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G435" t="n">
-        <v>9.30551815032959</v>
+        <v>9.30551719665527</v>
       </c>
       <c r="H435" t="s">
         <v>8</v>
@@ -11705,7 +11705,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G436" t="n">
-        <v>9.2575511932373</v>
+        <v>9.25755023956299</v>
       </c>
       <c r="H436" t="s">
         <v>8</v>
@@ -11757,7 +11757,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G438" t="n">
-        <v>9.01771831512451</v>
+        <v>9.0177173614502</v>
       </c>
       <c r="H438" t="s">
         <v>8</v>
@@ -11783,7 +11783,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G439" t="n">
-        <v>9.30551815032959</v>
+        <v>9.30551719665527</v>
       </c>
       <c r="H439" t="s">
         <v>8</v>
@@ -11809,7 +11809,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G440" t="n">
-        <v>9.30551815032959</v>
+        <v>9.30551719665527</v>
       </c>
       <c r="H440" t="s">
         <v>8</v>
@@ -11835,7 +11835,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G441" t="n">
-        <v>9.30551815032959</v>
+        <v>9.30551719665527</v>
       </c>
       <c r="H441" t="s">
         <v>8</v>
@@ -11861,7 +11861,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G442" t="n">
-        <v>9.30551815032959</v>
+        <v>9.30551719665527</v>
       </c>
       <c r="H442" t="s">
         <v>8</v>
@@ -11939,7 +11939,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G445" t="n">
-        <v>9.01771831512451</v>
+        <v>9.0177173614502</v>
       </c>
       <c r="H445" t="s">
         <v>8</v>
@@ -11965,7 +11965,7 @@
         <v>9.44999980926514</v>
       </c>
       <c r="G446" t="n">
-        <v>9.0656852722168</v>
+        <v>9.06568431854248</v>
       </c>
       <c r="H446" t="s">
         <v>8</v>
@@ -11991,7 +11991,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G447" t="n">
-        <v>9.01771831512451</v>
+        <v>9.0177173614502</v>
       </c>
       <c r="H447" t="s">
         <v>8</v>
@@ -12017,7 +12017,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G448" t="n">
-        <v>8.82585144042969</v>
+        <v>8.825852394104</v>
       </c>
       <c r="H448" t="s">
         <v>8</v>
@@ -12173,7 +12173,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G454" t="n">
-        <v>8.82585144042969</v>
+        <v>8.825852394104</v>
       </c>
       <c r="H454" t="s">
         <v>8</v>
@@ -12199,7 +12199,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G455" t="n">
-        <v>8.82585144042969</v>
+        <v>8.825852394104</v>
       </c>
       <c r="H455" t="s">
         <v>8</v>
@@ -12225,7 +12225,7 @@
         <v>9.35000038146973</v>
       </c>
       <c r="G456" t="n">
-        <v>8.96975231170654</v>
+        <v>8.96975135803223</v>
       </c>
       <c r="H456" t="s">
         <v>8</v>
@@ -12407,7 +12407,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G463" t="n">
-        <v>8.53805160522461</v>
+        <v>8.53805255889893</v>
       </c>
       <c r="H463" t="s">
         <v>8</v>
@@ -12641,7 +12641,7 @@
         <v>7.75</v>
       </c>
       <c r="G472" t="n">
-        <v>7.43482112884521</v>
+        <v>7.43482065200806</v>
       </c>
       <c r="H472" t="s">
         <v>8</v>
@@ -12849,7 +12849,7 @@
         <v>7.5</v>
       </c>
       <c r="G480" t="n">
-        <v>7.19498777389526</v>
+        <v>7.19498825073242</v>
       </c>
       <c r="H480" t="s">
         <v>8</v>
@@ -12875,7 +12875,7 @@
         <v>7.34999990463257</v>
       </c>
       <c r="G481" t="n">
-        <v>7.05108785629272</v>
+        <v>7.05108833312988</v>
       </c>
       <c r="H481" t="s">
         <v>8</v>
@@ -12901,7 +12901,7 @@
         <v>7.34999990463257</v>
       </c>
       <c r="G482" t="n">
-        <v>7.05108785629272</v>
+        <v>7.05108833312988</v>
       </c>
       <c r="H482" t="s">
         <v>8</v>
@@ -12979,7 +12979,7 @@
         <v>7</v>
       </c>
       <c r="G485" t="n">
-        <v>6.71532201766968</v>
+        <v>6.71532249450684</v>
       </c>
       <c r="H485" t="s">
         <v>8</v>
@@ -13239,7 +13239,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G495" t="n">
-        <v>6.04379034042358</v>
+        <v>6.04378986358643</v>
       </c>
       <c r="H495" t="s">
         <v>8</v>
@@ -13499,7 +13499,7 @@
         <v>7</v>
       </c>
       <c r="G505" t="n">
-        <v>6.71532201766968</v>
+        <v>6.71532249450684</v>
       </c>
       <c r="H505" t="s">
         <v>8</v>
@@ -13551,7 +13551,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G507" t="n">
-        <v>6.81125497817993</v>
+        <v>6.81125545501709</v>
       </c>
       <c r="H507" t="s">
         <v>8</v>
@@ -13629,7 +13629,7 @@
         <v>7.75</v>
       </c>
       <c r="G510" t="n">
-        <v>7.43482112884521</v>
+        <v>7.43482065200806</v>
       </c>
       <c r="H510" t="s">
         <v>8</v>
@@ -14097,7 +14097,7 @@
         <v>7.34999990463257</v>
       </c>
       <c r="G528" t="n">
-        <v>7.05108785629272</v>
+        <v>7.05108833312988</v>
       </c>
       <c r="H528" t="s">
         <v>8</v>
@@ -14279,7 +14279,7 @@
         <v>7.5</v>
       </c>
       <c r="G535" t="n">
-        <v>7.19498777389526</v>
+        <v>7.19498825073242</v>
       </c>
       <c r="H535" t="s">
         <v>8</v>
@@ -14409,7 +14409,7 @@
         <v>7</v>
       </c>
       <c r="G540" t="n">
-        <v>6.71532201766968</v>
+        <v>6.71532249450684</v>
       </c>
       <c r="H540" t="s">
         <v>8</v>
@@ -14565,7 +14565,7 @@
         <v>6.94999980926514</v>
       </c>
       <c r="G546" t="n">
-        <v>6.66735506057739</v>
+        <v>6.66735553741455</v>
       </c>
       <c r="H546" t="s">
         <v>8</v>
@@ -14643,7 +14643,7 @@
         <v>7</v>
       </c>
       <c r="G549" t="n">
-        <v>6.71532201766968</v>
+        <v>6.71532249450684</v>
       </c>
       <c r="H549" t="s">
         <v>8</v>
@@ -14669,7 +14669,7 @@
         <v>6.94999980926514</v>
       </c>
       <c r="G550" t="n">
-        <v>6.66735506057739</v>
+        <v>6.66735553741455</v>
       </c>
       <c r="H550" t="s">
         <v>8</v>
@@ -14903,7 +14903,7 @@
         <v>7.75</v>
       </c>
       <c r="G559" t="n">
-        <v>7.43482112884521</v>
+        <v>7.43482065200806</v>
       </c>
       <c r="H559" t="s">
         <v>8</v>
@@ -15033,7 +15033,7 @@
         <v>7.75</v>
       </c>
       <c r="G564" t="n">
-        <v>7.43482112884521</v>
+        <v>7.43482065200806</v>
       </c>
       <c r="H564" t="s">
         <v>8</v>
@@ -15137,7 +15137,7 @@
         <v>7.75</v>
       </c>
       <c r="G568" t="n">
-        <v>7.43482112884521</v>
+        <v>7.43482065200806</v>
       </c>
       <c r="H568" t="s">
         <v>8</v>
@@ -15293,7 +15293,7 @@
         <v>8.14999961853027</v>
       </c>
       <c r="G574" t="n">
-        <v>7.81855344772339</v>
+        <v>7.81855297088623</v>
       </c>
       <c r="H574" t="s">
         <v>8</v>
@@ -15423,7 +15423,7 @@
         <v>7.5</v>
       </c>
       <c r="G579" t="n">
-        <v>7.19498777389526</v>
+        <v>7.19498825073242</v>
       </c>
       <c r="H579" t="s">
         <v>8</v>
@@ -15501,7 +15501,7 @@
         <v>8.25</v>
       </c>
       <c r="G582" t="n">
-        <v>7.91448736190796</v>
+        <v>7.91448640823364</v>
       </c>
       <c r="H582" t="s">
         <v>8</v>
@@ -15527,7 +15527,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G583" t="n">
-        <v>7.86652040481567</v>
+        <v>7.86651945114136</v>
       </c>
       <c r="H583" t="s">
         <v>8</v>
@@ -15579,7 +15579,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G585" t="n">
-        <v>7.86652040481567</v>
+        <v>7.86651945114136</v>
       </c>
       <c r="H585" t="s">
         <v>8</v>
@@ -15605,7 +15605,7 @@
         <v>7.75</v>
       </c>
       <c r="G586" t="n">
-        <v>7.43482112884521</v>
+        <v>7.43482065200806</v>
       </c>
       <c r="H586" t="s">
         <v>8</v>
@@ -15631,7 +15631,7 @@
         <v>7.75</v>
       </c>
       <c r="G587" t="n">
-        <v>7.43482112884521</v>
+        <v>7.43482065200806</v>
       </c>
       <c r="H587" t="s">
         <v>8</v>
@@ -15657,7 +15657,7 @@
         <v>7.75</v>
       </c>
       <c r="G588" t="n">
-        <v>7.43482112884521</v>
+        <v>7.43482065200806</v>
       </c>
       <c r="H588" t="s">
         <v>8</v>
@@ -15709,7 +15709,7 @@
         <v>7.75</v>
       </c>
       <c r="G590" t="n">
-        <v>7.43482112884521</v>
+        <v>7.43482065200806</v>
       </c>
       <c r="H590" t="s">
         <v>8</v>
@@ -15865,7 +15865,7 @@
         <v>6.94999980926514</v>
       </c>
       <c r="G596" t="n">
-        <v>6.66735506057739</v>
+        <v>6.66735553741455</v>
       </c>
       <c r="H596" t="s">
         <v>8</v>
@@ -15891,7 +15891,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G597" t="n">
-        <v>6.90718841552734</v>
+        <v>6.90718793869019</v>
       </c>
       <c r="H597" t="s">
         <v>8</v>
@@ -15917,7 +15917,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G598" t="n">
-        <v>6.90718841552734</v>
+        <v>6.90718793869019</v>
       </c>
       <c r="H598" t="s">
         <v>8</v>
@@ -15995,7 +15995,7 @@
         <v>7.34999990463257</v>
       </c>
       <c r="G601" t="n">
-        <v>7.05108785629272</v>
+        <v>7.05108833312988</v>
       </c>
       <c r="H601" t="s">
         <v>8</v>
@@ -16021,7 +16021,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G602" t="n">
-        <v>6.90718841552734</v>
+        <v>6.90718793869019</v>
       </c>
       <c r="H602" t="s">
         <v>8</v>
@@ -16073,7 +16073,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G604" t="n">
-        <v>6.81125497817993</v>
+        <v>6.81125545501709</v>
       </c>
       <c r="H604" t="s">
         <v>8</v>
@@ -25410,6 +25410,32 @@
         <v>10.6000003814697</v>
       </c>
       <c r="H963" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="964">
+      <c r="A964" s="1" t="n">
+        <v>46288.2916666667</v>
+      </c>
+      <c r="B964" t="n">
+        <v>800</v>
+      </c>
+      <c r="C964" t="n">
+        <v>10.5500001907349</v>
+      </c>
+      <c r="D964" t="n">
+        <v>10.4499998092651</v>
+      </c>
+      <c r="E964" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="F964" t="n">
+        <v>10.4499998092651</v>
+      </c>
+      <c r="G964" t="n">
+        <v>10.4499998092651</v>
+      </c>
+      <c r="H964" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/RDUE.MI.xlsx
+++ b/data/RDUE.MI.xlsx
@@ -447,7 +447,7 @@
         <v>12.0500001907349</v>
       </c>
       <c r="G3" t="n">
-        <v>11.2916135787964</v>
+        <v>11.2916126251221</v>
       </c>
       <c r="H3" t="s">
         <v>8</v>
@@ -551,7 +551,7 @@
         <v>12.0900001525879</v>
       </c>
       <c r="G7" t="n">
-        <v>11.3290958404541</v>
+        <v>11.3290948867798</v>
       </c>
       <c r="H7" t="s">
         <v>8</v>
@@ -603,7 +603,7 @@
         <v>11.8599996566772</v>
       </c>
       <c r="G9" t="n">
-        <v>11.1135702133179</v>
+        <v>11.1135711669922</v>
       </c>
       <c r="H9" t="s">
         <v>8</v>
@@ -655,7 +655,7 @@
         <v>11.9180002212524</v>
       </c>
       <c r="G11" t="n">
-        <v>11.1679210662842</v>
+        <v>11.1679201126099</v>
       </c>
       <c r="H11" t="s">
         <v>8</v>
@@ -759,7 +759,7 @@
         <v>11.6199998855591</v>
       </c>
       <c r="G15" t="n">
-        <v>10.8886756896973</v>
+        <v>10.8886747360229</v>
       </c>
       <c r="H15" t="s">
         <v>8</v>
@@ -889,7 +889,7 @@
         <v>11.5900001525879</v>
       </c>
       <c r="G20" t="n">
-        <v>10.8605632781982</v>
+        <v>10.8605642318726</v>
       </c>
       <c r="H20" t="s">
         <v>8</v>
@@ -915,7 +915,7 @@
         <v>11.3800001144409</v>
       </c>
       <c r="G21" t="n">
-        <v>10.6637802124023</v>
+        <v>10.6637811660767</v>
       </c>
       <c r="H21" t="s">
         <v>8</v>
@@ -941,7 +941,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G22" t="n">
-        <v>10.6825218200684</v>
+        <v>10.682520866394</v>
       </c>
       <c r="H22" t="s">
         <v>8</v>
@@ -1045,7 +1045,7 @@
         <v>11.25</v>
       </c>
       <c r="G26" t="n">
-        <v>10.5419626235962</v>
+        <v>10.5419616699219</v>
       </c>
       <c r="H26" t="s">
         <v>8</v>
@@ -1175,7 +1175,7 @@
         <v>11.9799995422363</v>
       </c>
       <c r="G31" t="n">
-        <v>11.2260189056396</v>
+        <v>11.2260179519653</v>
       </c>
       <c r="H31" t="s">
         <v>8</v>
@@ -1383,7 +1383,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G39" t="n">
-        <v>11.1510534286499</v>
+        <v>11.1510524749756</v>
       </c>
       <c r="H39" t="s">
         <v>8</v>
@@ -1409,7 +1409,7 @@
         <v>11.9799995422363</v>
       </c>
       <c r="G40" t="n">
-        <v>11.2260189056396</v>
+        <v>11.2260179519653</v>
       </c>
       <c r="H40" t="s">
         <v>8</v>
@@ -1435,7 +1435,7 @@
         <v>11.9799995422363</v>
       </c>
       <c r="G41" t="n">
-        <v>11.2260189056396</v>
+        <v>11.2260179519653</v>
       </c>
       <c r="H41" t="s">
         <v>8</v>
@@ -1669,7 +1669,7 @@
         <v>11.5500001907349</v>
       </c>
       <c r="G50" t="n">
-        <v>10.8230819702148</v>
+        <v>10.8230810165405</v>
       </c>
       <c r="H50" t="s">
         <v>8</v>
@@ -1695,7 +1695,7 @@
         <v>11.5500001907349</v>
       </c>
       <c r="G51" t="n">
-        <v>10.8230819702148</v>
+        <v>10.8230810165405</v>
       </c>
       <c r="H51" t="s">
         <v>8</v>
@@ -1929,7 +1929,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G60" t="n">
-        <v>10.8699340820312</v>
+        <v>10.8699350357056</v>
       </c>
       <c r="H60" t="s">
         <v>8</v>
@@ -2033,7 +2033,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G64" t="n">
-        <v>10.6825218200684</v>
+        <v>10.682520866394</v>
       </c>
       <c r="H64" t="s">
         <v>8</v>
@@ -2059,7 +2059,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G65" t="n">
-        <v>10.6825218200684</v>
+        <v>10.682520866394</v>
       </c>
       <c r="H65" t="s">
         <v>8</v>
@@ -2085,7 +2085,7 @@
         <v>11.5500001907349</v>
       </c>
       <c r="G66" t="n">
-        <v>10.8230819702148</v>
+        <v>10.8230810165405</v>
       </c>
       <c r="H66" t="s">
         <v>8</v>
@@ -2137,7 +2137,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G68" t="n">
-        <v>10.6825218200684</v>
+        <v>10.682520866394</v>
       </c>
       <c r="H68" t="s">
         <v>8</v>
@@ -2163,7 +2163,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G69" t="n">
-        <v>10.6825218200684</v>
+        <v>10.682520866394</v>
       </c>
       <c r="H69" t="s">
         <v>8</v>
@@ -2215,7 +2215,7 @@
         <v>11.5</v>
       </c>
       <c r="G71" t="n">
-        <v>10.7762289047241</v>
+        <v>10.7762279510498</v>
       </c>
       <c r="H71" t="s">
         <v>8</v>
@@ -2241,7 +2241,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G72" t="n">
-        <v>10.6825218200684</v>
+        <v>10.682520866394</v>
       </c>
       <c r="H72" t="s">
         <v>8</v>
@@ -2267,7 +2267,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G73" t="n">
-        <v>10.8699340820312</v>
+        <v>10.8699350357056</v>
       </c>
       <c r="H73" t="s">
         <v>8</v>
@@ -2293,7 +2293,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G74" t="n">
-        <v>10.8699340820312</v>
+        <v>10.8699350357056</v>
       </c>
       <c r="H74" t="s">
         <v>8</v>
@@ -2319,7 +2319,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G75" t="n">
-        <v>10.8699340820312</v>
+        <v>10.8699350357056</v>
       </c>
       <c r="H75" t="s">
         <v>8</v>
@@ -2345,7 +2345,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G76" t="n">
-        <v>10.8699340820312</v>
+        <v>10.8699350357056</v>
       </c>
       <c r="H76" t="s">
         <v>8</v>
@@ -2423,7 +2423,7 @@
         <v>11.5</v>
       </c>
       <c r="G79" t="n">
-        <v>10.7762289047241</v>
+        <v>10.7762279510498</v>
       </c>
       <c r="H79" t="s">
         <v>8</v>
@@ -2475,7 +2475,7 @@
         <v>11.5500001907349</v>
       </c>
       <c r="G81" t="n">
-        <v>10.8230819702148</v>
+        <v>10.8230810165405</v>
       </c>
       <c r="H81" t="s">
         <v>8</v>
@@ -2501,7 +2501,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G82" t="n">
-        <v>9.74545764923096</v>
+        <v>9.74545860290527</v>
       </c>
       <c r="H82" t="s">
         <v>8</v>
@@ -2657,7 +2657,7 @@
         <v>10.25</v>
       </c>
       <c r="G88" t="n">
-        <v>9.60489845275879</v>
+        <v>9.60489940643311</v>
       </c>
       <c r="H88" t="s">
         <v>8</v>
@@ -2683,7 +2683,7 @@
         <v>10.5500001907349</v>
       </c>
       <c r="G89" t="n">
-        <v>9.88601779937744</v>
+        <v>9.88601875305176</v>
       </c>
       <c r="H89" t="s">
         <v>8</v>
@@ -2709,7 +2709,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G90" t="n">
-        <v>9.55804538726807</v>
+        <v>9.55804634094238</v>
       </c>
       <c r="H90" t="s">
         <v>8</v>
@@ -2787,7 +2787,7 @@
         <v>9.72000026702881</v>
       </c>
       <c r="G93" t="n">
-        <v>9.10825634002686</v>
+        <v>9.10825538635254</v>
       </c>
       <c r="H93" t="s">
         <v>8</v>
@@ -2917,7 +2917,7 @@
         <v>9.53999996185303</v>
       </c>
       <c r="G98" t="n">
-        <v>8.93958377838135</v>
+        <v>8.93958282470703</v>
       </c>
       <c r="H98" t="s">
         <v>8</v>
@@ -2943,7 +2943,7 @@
         <v>9.34000015258789</v>
       </c>
       <c r="G99" t="n">
-        <v>8.75217151641846</v>
+        <v>8.75217056274414</v>
       </c>
       <c r="H99" t="s">
         <v>8</v>
@@ -2969,7 +2969,7 @@
         <v>9.14000034332275</v>
       </c>
       <c r="G100" t="n">
-        <v>8.56475925445557</v>
+        <v>8.56475830078125</v>
       </c>
       <c r="H100" t="s">
         <v>8</v>
@@ -3203,7 +3203,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G109" t="n">
-        <v>8.80839538574219</v>
+        <v>8.80839443206787</v>
       </c>
       <c r="H109" t="s">
         <v>8</v>
@@ -3307,7 +3307,7 @@
         <v>9.76000022888184</v>
       </c>
       <c r="G113" t="n">
-        <v>9.14573860168457</v>
+        <v>9.14573764801025</v>
       </c>
       <c r="H113" t="s">
         <v>8</v>
@@ -3333,7 +3333,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G114" t="n">
-        <v>9.55804538726807</v>
+        <v>9.55804634094238</v>
       </c>
       <c r="H114" t="s">
         <v>8</v>
@@ -3385,7 +3385,7 @@
         <v>10.5500001907349</v>
       </c>
       <c r="G116" t="n">
-        <v>9.88601779937744</v>
+        <v>9.88601875305176</v>
       </c>
       <c r="H116" t="s">
         <v>8</v>
@@ -3411,7 +3411,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G117" t="n">
-        <v>9.74545764923096</v>
+        <v>9.74545860290527</v>
       </c>
       <c r="H117" t="s">
         <v>8</v>
@@ -3437,7 +3437,7 @@
         <v>10.5500001907349</v>
       </c>
       <c r="G118" t="n">
-        <v>9.88601779937744</v>
+        <v>9.88601875305176</v>
       </c>
       <c r="H118" t="s">
         <v>8</v>
@@ -3645,7 +3645,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G126" t="n">
-        <v>8.99580764770508</v>
+        <v>8.99580860137939</v>
       </c>
       <c r="H126" t="s">
         <v>8</v>
@@ -3671,7 +3671,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G127" t="n">
-        <v>8.99580764770508</v>
+        <v>8.99580860137939</v>
       </c>
       <c r="H127" t="s">
         <v>8</v>
@@ -3723,7 +3723,7 @@
         <v>9.84000015258789</v>
       </c>
       <c r="G129" t="n">
-        <v>9.220703125</v>
+        <v>9.22070217132568</v>
       </c>
       <c r="H129" t="s">
         <v>8</v>
@@ -3775,7 +3775,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G131" t="n">
-        <v>9.65175151824951</v>
+        <v>9.65175247192383</v>
       </c>
       <c r="H131" t="s">
         <v>8</v>
@@ -3801,7 +3801,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G132" t="n">
-        <v>9.65175151824951</v>
+        <v>9.65175247192383</v>
       </c>
       <c r="H132" t="s">
         <v>8</v>
@@ -3827,7 +3827,7 @@
         <v>9.97999954223633</v>
       </c>
       <c r="G133" t="n">
-        <v>9.35189151763916</v>
+        <v>9.35189247131348</v>
       </c>
       <c r="H133" t="s">
         <v>8</v>
@@ -3931,7 +3931,7 @@
         <v>10.5500001907349</v>
       </c>
       <c r="G137" t="n">
-        <v>9.88601779937744</v>
+        <v>9.88601875305176</v>
       </c>
       <c r="H137" t="s">
         <v>8</v>
@@ -4139,7 +4139,7 @@
         <v>9.5600004196167</v>
       </c>
       <c r="G145" t="n">
-        <v>8.95832633972168</v>
+        <v>8.95832538604736</v>
       </c>
       <c r="H145" t="s">
         <v>8</v>
@@ -4165,7 +4165,7 @@
         <v>9.5</v>
       </c>
       <c r="G146" t="n">
-        <v>8.90210056304932</v>
+        <v>8.90210151672363</v>
       </c>
       <c r="H146" t="s">
         <v>8</v>
@@ -4191,7 +4191,7 @@
         <v>9.5</v>
       </c>
       <c r="G147" t="n">
-        <v>8.90210056304932</v>
+        <v>8.90210151672363</v>
       </c>
       <c r="H147" t="s">
         <v>8</v>
@@ -4217,7 +4217,7 @@
         <v>9.31999969482422</v>
       </c>
       <c r="G148" t="n">
-        <v>8.73342990875244</v>
+        <v>8.73342895507812</v>
       </c>
       <c r="H148" t="s">
         <v>8</v>
@@ -4243,7 +4243,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G149" t="n">
-        <v>8.99580764770508</v>
+        <v>8.99580860137939</v>
       </c>
       <c r="H149" t="s">
         <v>8</v>
@@ -4269,7 +4269,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G150" t="n">
-        <v>8.99580764770508</v>
+        <v>8.99580860137939</v>
       </c>
       <c r="H150" t="s">
         <v>8</v>
@@ -4633,7 +4633,7 @@
         <v>9.97999954223633</v>
       </c>
       <c r="G164" t="n">
-        <v>9.35189151763916</v>
+        <v>9.35189247131348</v>
       </c>
       <c r="H164" t="s">
         <v>8</v>
@@ -4659,7 +4659,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G165" t="n">
-        <v>9.27692604064941</v>
+        <v>9.27692699432373</v>
       </c>
       <c r="H165" t="s">
         <v>8</v>
@@ -4685,7 +4685,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G166" t="n">
-        <v>9.27692604064941</v>
+        <v>9.27692699432373</v>
       </c>
       <c r="H166" t="s">
         <v>8</v>
@@ -4763,7 +4763,7 @@
         <v>9.15999984741211</v>
       </c>
       <c r="G169" t="n">
-        <v>8.58349990844727</v>
+        <v>8.58350086212158</v>
       </c>
       <c r="H169" t="s">
         <v>8</v>
@@ -4789,7 +4789,7 @@
         <v>9.5</v>
       </c>
       <c r="G170" t="n">
-        <v>8.90210056304932</v>
+        <v>8.90210151672363</v>
       </c>
       <c r="H170" t="s">
         <v>8</v>
@@ -4815,7 +4815,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G171" t="n">
-        <v>8.80839538574219</v>
+        <v>8.80839443206787</v>
       </c>
       <c r="H171" t="s">
         <v>8</v>
@@ -4841,7 +4841,7 @@
         <v>9.5600004196167</v>
       </c>
       <c r="G172" t="n">
-        <v>8.95832633972168</v>
+        <v>8.95832538604736</v>
       </c>
       <c r="H172" t="s">
         <v>8</v>
@@ -4867,7 +4867,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G173" t="n">
-        <v>9.27692604064941</v>
+        <v>9.27692699432373</v>
       </c>
       <c r="H173" t="s">
         <v>8</v>
@@ -4893,7 +4893,7 @@
         <v>9.27999973297119</v>
       </c>
       <c r="G174" t="n">
-        <v>8.69594669342041</v>
+        <v>8.69594764709473</v>
       </c>
       <c r="H174" t="s">
         <v>8</v>
@@ -4945,7 +4945,7 @@
         <v>9.27999973297119</v>
       </c>
       <c r="G176" t="n">
-        <v>8.69594669342041</v>
+        <v>8.69594764709473</v>
       </c>
       <c r="H176" t="s">
         <v>8</v>
@@ -4971,7 +4971,7 @@
         <v>9.27999973297119</v>
       </c>
       <c r="G177" t="n">
-        <v>8.69594669342041</v>
+        <v>8.69594764709473</v>
       </c>
       <c r="H177" t="s">
         <v>8</v>
@@ -5179,7 +5179,7 @@
         <v>9.72000026702881</v>
       </c>
       <c r="G185" t="n">
-        <v>9.10825634002686</v>
+        <v>9.10825538635254</v>
       </c>
       <c r="H185" t="s">
         <v>8</v>
@@ -5205,7 +5205,7 @@
         <v>9.84000015258789</v>
       </c>
       <c r="G186" t="n">
-        <v>9.220703125</v>
+        <v>9.22070217132568</v>
       </c>
       <c r="H186" t="s">
         <v>8</v>
@@ -5231,7 +5231,7 @@
         <v>9.97999954223633</v>
       </c>
       <c r="G187" t="n">
-        <v>9.35189151763916</v>
+        <v>9.35189247131348</v>
       </c>
       <c r="H187" t="s">
         <v>8</v>
@@ -5257,7 +5257,7 @@
         <v>9.97999954223633</v>
       </c>
       <c r="G188" t="n">
-        <v>9.35189151763916</v>
+        <v>9.35189247131348</v>
       </c>
       <c r="H188" t="s">
         <v>8</v>
@@ -5283,7 +5283,7 @@
         <v>9.61999988555908</v>
       </c>
       <c r="G189" t="n">
-        <v>9.01454925537109</v>
+        <v>9.01454830169678</v>
       </c>
       <c r="H189" t="s">
         <v>8</v>
@@ -5439,7 +5439,7 @@
         <v>9.53999996185303</v>
       </c>
       <c r="G195" t="n">
-        <v>8.93958377838135</v>
+        <v>8.93958282470703</v>
       </c>
       <c r="H195" t="s">
         <v>8</v>
@@ -5465,7 +5465,7 @@
         <v>9.53999996185303</v>
       </c>
       <c r="G196" t="n">
-        <v>8.93958377838135</v>
+        <v>8.93958282470703</v>
       </c>
       <c r="H196" t="s">
         <v>8</v>
@@ -5491,7 +5491,7 @@
         <v>9.53999996185303</v>
       </c>
       <c r="G197" t="n">
-        <v>8.93958377838135</v>
+        <v>8.93958282470703</v>
       </c>
       <c r="H197" t="s">
         <v>8</v>
@@ -5517,7 +5517,7 @@
         <v>9.5</v>
       </c>
       <c r="G198" t="n">
-        <v>8.90210056304932</v>
+        <v>8.90210151672363</v>
       </c>
       <c r="H198" t="s">
         <v>8</v>
@@ -5647,7 +5647,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G203" t="n">
-        <v>8.24615669250488</v>
+        <v>8.2461576461792</v>
       </c>
       <c r="H203" t="s">
         <v>8</v>
@@ -5673,7 +5673,7 @@
         <v>9.0600004196167</v>
       </c>
       <c r="G204" t="n">
-        <v>8.48979377746582</v>
+        <v>8.48979473114014</v>
       </c>
       <c r="H204" t="s">
         <v>8</v>
@@ -6479,7 +6479,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G235" t="n">
-        <v>8.24615669250488</v>
+        <v>8.2461576461792</v>
       </c>
       <c r="H235" t="s">
         <v>8</v>
@@ -6609,7 +6609,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G240" t="n">
-        <v>8.05874538421631</v>
+        <v>8.05874443054199</v>
       </c>
       <c r="H240" t="s">
         <v>8</v>
@@ -6895,7 +6895,7 @@
         <v>8.23999977111816</v>
       </c>
       <c r="G251" t="n">
-        <v>7.72140121459961</v>
+        <v>7.72140073776245</v>
       </c>
       <c r="H251" t="s">
         <v>8</v>
@@ -7025,7 +7025,7 @@
         <v>7.71999979019165</v>
       </c>
       <c r="G256" t="n">
-        <v>7.23412847518921</v>
+        <v>7.23412799835205</v>
       </c>
       <c r="H256" t="s">
         <v>8</v>
@@ -7077,7 +7077,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G258" t="n">
-        <v>7.12168073654175</v>
+        <v>7.12168121337891</v>
       </c>
       <c r="H258" t="s">
         <v>8</v>
@@ -7207,7 +7207,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G263" t="n">
-        <v>7.4028000831604</v>
+        <v>7.40280055999756</v>
       </c>
       <c r="H263" t="s">
         <v>8</v>
@@ -7389,7 +7389,7 @@
         <v>7.71999979019165</v>
       </c>
       <c r="G270" t="n">
-        <v>7.23412847518921</v>
+        <v>7.23412799835205</v>
       </c>
       <c r="H270" t="s">
         <v>8</v>
@@ -7415,7 +7415,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G271" t="n">
-        <v>7.7776255607605</v>
+        <v>7.77762603759766</v>
       </c>
       <c r="H271" t="s">
         <v>8</v>
@@ -7519,7 +7519,7 @@
         <v>9.14000034332275</v>
       </c>
       <c r="G275" t="n">
-        <v>8.56475925445557</v>
+        <v>8.56475830078125</v>
       </c>
       <c r="H275" t="s">
         <v>8</v>
@@ -7571,7 +7571,7 @@
         <v>9.14000034332275</v>
       </c>
       <c r="G277" t="n">
-        <v>8.56475925445557</v>
+        <v>8.56475830078125</v>
       </c>
       <c r="H277" t="s">
         <v>8</v>
@@ -7701,7 +7701,7 @@
         <v>8.92000007629395</v>
       </c>
       <c r="G282" t="n">
-        <v>8.35860538482666</v>
+        <v>8.35860443115234</v>
       </c>
       <c r="H282" t="s">
         <v>8</v>
@@ -7753,7 +7753,7 @@
         <v>8.81999969482422</v>
       </c>
       <c r="G284" t="n">
-        <v>8.2648983001709</v>
+        <v>8.26489734649658</v>
       </c>
       <c r="H284" t="s">
         <v>8</v>
@@ -7831,7 +7831,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G287" t="n">
-        <v>8.24615669250488</v>
+        <v>8.2461576461792</v>
       </c>
       <c r="H287" t="s">
         <v>8</v>
@@ -8039,7 +8039,7 @@
         <v>9.14000034332275</v>
       </c>
       <c r="G295" t="n">
-        <v>8.56475925445557</v>
+        <v>8.56475830078125</v>
       </c>
       <c r="H295" t="s">
         <v>8</v>
@@ -8091,7 +8091,7 @@
         <v>9.14000034332275</v>
       </c>
       <c r="G297" t="n">
-        <v>8.56475925445557</v>
+        <v>8.56475830078125</v>
       </c>
       <c r="H297" t="s">
         <v>8</v>
@@ -8117,7 +8117,7 @@
         <v>9.14000034332275</v>
       </c>
       <c r="G298" t="n">
-        <v>8.56475925445557</v>
+        <v>8.56475830078125</v>
       </c>
       <c r="H298" t="s">
         <v>8</v>
@@ -8299,7 +8299,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G305" t="n">
-        <v>8.24615669250488</v>
+        <v>8.2461576461792</v>
       </c>
       <c r="H305" t="s">
         <v>8</v>
@@ -8325,7 +8325,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G306" t="n">
-        <v>8.24615669250488</v>
+        <v>8.2461576461792</v>
       </c>
       <c r="H306" t="s">
         <v>8</v>
@@ -8351,7 +8351,7 @@
         <v>8.64000034332275</v>
       </c>
       <c r="G307" t="n">
-        <v>8.09622669219971</v>
+        <v>8.09622764587402</v>
       </c>
       <c r="H307" t="s">
         <v>8</v>
@@ -8377,7 +8377,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G308" t="n">
-        <v>8.05874538421631</v>
+        <v>8.05874443054199</v>
       </c>
       <c r="H308" t="s">
         <v>8</v>
@@ -8429,7 +8429,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G310" t="n">
-        <v>8.24615669250488</v>
+        <v>8.2461576461792</v>
       </c>
       <c r="H310" t="s">
         <v>8</v>
@@ -8455,7 +8455,7 @@
         <v>8.47999954223633</v>
       </c>
       <c r="G311" t="n">
-        <v>7.94629621505737</v>
+        <v>7.94629669189453</v>
       </c>
       <c r="H311" t="s">
         <v>8</v>
@@ -8481,7 +8481,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G312" t="n">
-        <v>7.83384943008423</v>
+        <v>7.83384990692139</v>
       </c>
       <c r="H312" t="s">
         <v>8</v>
@@ -8533,7 +8533,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G314" t="n">
-        <v>8.24615669250488</v>
+        <v>8.2461576461792</v>
       </c>
       <c r="H314" t="s">
         <v>8</v>
@@ -8585,7 +8585,7 @@
         <v>8.47999954223633</v>
       </c>
       <c r="G316" t="n">
-        <v>7.94629621505737</v>
+        <v>7.94629669189453</v>
       </c>
       <c r="H316" t="s">
         <v>8</v>
@@ -8637,7 +8637,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G318" t="n">
-        <v>8.24615669250488</v>
+        <v>8.2461576461792</v>
       </c>
       <c r="H318" t="s">
         <v>8</v>
@@ -8663,7 +8663,7 @@
         <v>8.47999954223633</v>
       </c>
       <c r="G319" t="n">
-        <v>7.94629621505737</v>
+        <v>7.94629669189453</v>
       </c>
       <c r="H319" t="s">
         <v>8</v>
@@ -8689,7 +8689,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G320" t="n">
-        <v>7.87133121490479</v>
+        <v>7.87133169174194</v>
       </c>
       <c r="H320" t="s">
         <v>8</v>
@@ -8741,7 +8741,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G322" t="n">
-        <v>7.7776255607605</v>
+        <v>7.77762603759766</v>
       </c>
       <c r="H322" t="s">
         <v>8</v>
@@ -8767,7 +8767,7 @@
         <v>8.27999973297119</v>
       </c>
       <c r="G323" t="n">
-        <v>7.75888442993164</v>
+        <v>7.75888395309448</v>
       </c>
       <c r="H323" t="s">
         <v>8</v>
@@ -8793,7 +8793,7 @@
         <v>8.27999973297119</v>
       </c>
       <c r="G324" t="n">
-        <v>7.75888442993164</v>
+        <v>7.75888395309448</v>
       </c>
       <c r="H324" t="s">
         <v>8</v>
@@ -8819,7 +8819,7 @@
         <v>8.27999973297119</v>
       </c>
       <c r="G325" t="n">
-        <v>7.75888442993164</v>
+        <v>7.75888395309448</v>
       </c>
       <c r="H325" t="s">
         <v>8</v>
@@ -8871,7 +8871,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G327" t="n">
-        <v>7.7776255607605</v>
+        <v>7.77762603759766</v>
       </c>
       <c r="H327" t="s">
         <v>8</v>
@@ -9105,7 +9105,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G336" t="n">
-        <v>8.24615669250488</v>
+        <v>8.2461576461792</v>
       </c>
       <c r="H336" t="s">
         <v>8</v>
@@ -9261,7 +9261,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G342" t="n">
-        <v>8.80839538574219</v>
+        <v>8.80839443206787</v>
       </c>
       <c r="H342" t="s">
         <v>8</v>
@@ -9313,7 +9313,7 @@
         <v>9.5</v>
       </c>
       <c r="G344" t="n">
-        <v>8.90210056304932</v>
+        <v>8.90210151672363</v>
       </c>
       <c r="H344" t="s">
         <v>8</v>
@@ -9391,7 +9391,7 @@
         <v>9.5</v>
       </c>
       <c r="G347" t="n">
-        <v>8.90210056304932</v>
+        <v>8.90210151672363</v>
       </c>
       <c r="H347" t="s">
         <v>8</v>
@@ -9417,7 +9417,7 @@
         <v>9.5</v>
       </c>
       <c r="G348" t="n">
-        <v>8.90210056304932</v>
+        <v>8.90210151672363</v>
       </c>
       <c r="H348" t="s">
         <v>8</v>
@@ -9469,7 +9469,7 @@
         <v>9.5</v>
       </c>
       <c r="G350" t="n">
-        <v>8.90210056304932</v>
+        <v>8.90210151672363</v>
       </c>
       <c r="H350" t="s">
         <v>8</v>
@@ -9521,7 +9521,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G352" t="n">
-        <v>8.99580764770508</v>
+        <v>8.99580860137939</v>
       </c>
       <c r="H352" t="s">
         <v>8</v>
@@ -9547,7 +9547,7 @@
         <v>9.5</v>
       </c>
       <c r="G353" t="n">
-        <v>8.90210056304932</v>
+        <v>8.90210151672363</v>
       </c>
       <c r="H353" t="s">
         <v>8</v>
@@ -9573,7 +9573,7 @@
         <v>9.5</v>
       </c>
       <c r="G354" t="n">
-        <v>8.90210056304932</v>
+        <v>8.90210151672363</v>
       </c>
       <c r="H354" t="s">
         <v>8</v>
@@ -9599,7 +9599,7 @@
         <v>9.5</v>
       </c>
       <c r="G355" t="n">
-        <v>8.90210056304932</v>
+        <v>8.90210151672363</v>
       </c>
       <c r="H355" t="s">
         <v>8</v>
@@ -9625,7 +9625,7 @@
         <v>9.5</v>
       </c>
       <c r="G356" t="n">
-        <v>8.90210056304932</v>
+        <v>8.90210151672363</v>
       </c>
       <c r="H356" t="s">
         <v>8</v>
@@ -9651,7 +9651,7 @@
         <v>9.5</v>
       </c>
       <c r="G357" t="n">
-        <v>8.90210056304932</v>
+        <v>8.90210151672363</v>
       </c>
       <c r="H357" t="s">
         <v>8</v>
@@ -9755,7 +9755,7 @@
         <v>9.75</v>
       </c>
       <c r="G361" t="n">
-        <v>9.13636684417725</v>
+        <v>9.13636779785156</v>
       </c>
       <c r="H361" t="s">
         <v>8</v>
@@ -9781,7 +9781,7 @@
         <v>9.5</v>
       </c>
       <c r="G362" t="n">
-        <v>8.90210056304932</v>
+        <v>8.90210151672363</v>
       </c>
       <c r="H362" t="s">
         <v>8</v>
@@ -9989,7 +9989,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G370" t="n">
-        <v>9.27692604064941</v>
+        <v>9.27692699432373</v>
       </c>
       <c r="H370" t="s">
         <v>8</v>
@@ -10015,7 +10015,7 @@
         <v>9.75</v>
       </c>
       <c r="G371" t="n">
-        <v>9.13636684417725</v>
+        <v>9.13636779785156</v>
       </c>
       <c r="H371" t="s">
         <v>8</v>
@@ -10041,7 +10041,7 @@
         <v>9.75</v>
       </c>
       <c r="G372" t="n">
-        <v>9.13636684417725</v>
+        <v>9.13636779785156</v>
       </c>
       <c r="H372" t="s">
         <v>8</v>
@@ -10119,7 +10119,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G375" t="n">
-        <v>9.30551719665527</v>
+        <v>9.30551815032959</v>
       </c>
       <c r="H375" t="s">
         <v>8</v>
@@ -10145,7 +10145,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G376" t="n">
-        <v>9.25755023956299</v>
+        <v>9.2575511932373</v>
       </c>
       <c r="H376" t="s">
         <v>8</v>
@@ -10197,7 +10197,7 @@
         <v>10</v>
       </c>
       <c r="G378" t="n">
-        <v>9.59331703186035</v>
+        <v>9.59331798553467</v>
       </c>
       <c r="H378" t="s">
         <v>8</v>
@@ -10535,7 +10535,7 @@
         <v>10</v>
       </c>
       <c r="G391" t="n">
-        <v>9.59331703186035</v>
+        <v>9.59331798553467</v>
       </c>
       <c r="H391" t="s">
         <v>8</v>
@@ -10665,7 +10665,7 @@
         <v>10</v>
       </c>
       <c r="G396" t="n">
-        <v>9.59331703186035</v>
+        <v>9.59331798553467</v>
       </c>
       <c r="H396" t="s">
         <v>8</v>
@@ -10691,7 +10691,7 @@
         <v>10</v>
       </c>
       <c r="G397" t="n">
-        <v>9.59331703186035</v>
+        <v>9.59331798553467</v>
       </c>
       <c r="H397" t="s">
         <v>8</v>
@@ -10743,7 +10743,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G399" t="n">
-        <v>9.30551719665527</v>
+        <v>9.30551815032959</v>
       </c>
       <c r="H399" t="s">
         <v>8</v>
@@ -10795,7 +10795,7 @@
         <v>9.35000038146973</v>
       </c>
       <c r="G401" t="n">
-        <v>8.96975135803223</v>
+        <v>8.96975231170654</v>
       </c>
       <c r="H401" t="s">
         <v>8</v>
@@ -11055,7 +11055,7 @@
         <v>10</v>
       </c>
       <c r="G411" t="n">
-        <v>9.59331703186035</v>
+        <v>9.59331798553467</v>
       </c>
       <c r="H411" t="s">
         <v>8</v>
@@ -11185,7 +11185,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G416" t="n">
-        <v>9.25755023956299</v>
+        <v>9.2575511932373</v>
       </c>
       <c r="H416" t="s">
         <v>8</v>
@@ -11211,7 +11211,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G417" t="n">
-        <v>9.25755023956299</v>
+        <v>9.2575511932373</v>
       </c>
       <c r="H417" t="s">
         <v>8</v>
@@ -11237,7 +11237,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G418" t="n">
-        <v>9.25755023956299</v>
+        <v>9.2575511932373</v>
       </c>
       <c r="H418" t="s">
         <v>8</v>
@@ -11263,7 +11263,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G419" t="n">
-        <v>9.30551719665527</v>
+        <v>9.30551815032959</v>
       </c>
       <c r="H419" t="s">
         <v>8</v>
@@ -11315,7 +11315,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G421" t="n">
-        <v>9.0177173614502</v>
+        <v>9.01771831512451</v>
       </c>
       <c r="H421" t="s">
         <v>8</v>
@@ -11367,7 +11367,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G423" t="n">
-        <v>9.25755023956299</v>
+        <v>9.2575511932373</v>
       </c>
       <c r="H423" t="s">
         <v>8</v>
@@ -11393,7 +11393,7 @@
         <v>9.35000038146973</v>
       </c>
       <c r="G424" t="n">
-        <v>8.96975135803223</v>
+        <v>8.96975231170654</v>
       </c>
       <c r="H424" t="s">
         <v>8</v>
@@ -11419,7 +11419,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G425" t="n">
-        <v>8.53805255889893</v>
+        <v>8.53805160522461</v>
       </c>
       <c r="H425" t="s">
         <v>8</v>
@@ -11523,7 +11523,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G429" t="n">
-        <v>9.25755023956299</v>
+        <v>9.2575511932373</v>
       </c>
       <c r="H429" t="s">
         <v>8</v>
@@ -11549,7 +11549,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G430" t="n">
-        <v>9.25755023956299</v>
+        <v>9.2575511932373</v>
       </c>
       <c r="H430" t="s">
         <v>8</v>
@@ -11601,7 +11601,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G432" t="n">
-        <v>9.0177173614502</v>
+        <v>9.01771831512451</v>
       </c>
       <c r="H432" t="s">
         <v>8</v>
@@ -11627,7 +11627,7 @@
         <v>9.35000038146973</v>
       </c>
       <c r="G433" t="n">
-        <v>8.96975135803223</v>
+        <v>8.96975231170654</v>
       </c>
       <c r="H433" t="s">
         <v>8</v>
@@ -11679,7 +11679,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G435" t="n">
-        <v>9.30551719665527</v>
+        <v>9.30551815032959</v>
       </c>
       <c r="H435" t="s">
         <v>8</v>
@@ -11705,7 +11705,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G436" t="n">
-        <v>9.25755023956299</v>
+        <v>9.2575511932373</v>
       </c>
       <c r="H436" t="s">
         <v>8</v>
@@ -11757,7 +11757,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G438" t="n">
-        <v>9.0177173614502</v>
+        <v>9.01771831512451</v>
       </c>
       <c r="H438" t="s">
         <v>8</v>
@@ -11783,7 +11783,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G439" t="n">
-        <v>9.30551719665527</v>
+        <v>9.30551815032959</v>
       </c>
       <c r="H439" t="s">
         <v>8</v>
@@ -11809,7 +11809,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G440" t="n">
-        <v>9.30551719665527</v>
+        <v>9.30551815032959</v>
       </c>
       <c r="H440" t="s">
         <v>8</v>
@@ -11835,7 +11835,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G441" t="n">
-        <v>9.30551719665527</v>
+        <v>9.30551815032959</v>
       </c>
       <c r="H441" t="s">
         <v>8</v>
@@ -11861,7 +11861,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G442" t="n">
-        <v>9.30551719665527</v>
+        <v>9.30551815032959</v>
       </c>
       <c r="H442" t="s">
         <v>8</v>
@@ -11939,7 +11939,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G445" t="n">
-        <v>9.0177173614502</v>
+        <v>9.01771831512451</v>
       </c>
       <c r="H445" t="s">
         <v>8</v>
@@ -11965,7 +11965,7 @@
         <v>9.44999980926514</v>
       </c>
       <c r="G446" t="n">
-        <v>9.06568431854248</v>
+        <v>9.0656852722168</v>
       </c>
       <c r="H446" t="s">
         <v>8</v>
@@ -11991,7 +11991,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G447" t="n">
-        <v>9.0177173614502</v>
+        <v>9.01771831512451</v>
       </c>
       <c r="H447" t="s">
         <v>8</v>
@@ -12017,7 +12017,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G448" t="n">
-        <v>8.825852394104</v>
+        <v>8.82585144042969</v>
       </c>
       <c r="H448" t="s">
         <v>8</v>
@@ -12173,7 +12173,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G454" t="n">
-        <v>8.825852394104</v>
+        <v>8.82585144042969</v>
       </c>
       <c r="H454" t="s">
         <v>8</v>
@@ -12199,7 +12199,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G455" t="n">
-        <v>8.825852394104</v>
+        <v>8.82585144042969</v>
       </c>
       <c r="H455" t="s">
         <v>8</v>
@@ -12225,7 +12225,7 @@
         <v>9.35000038146973</v>
       </c>
       <c r="G456" t="n">
-        <v>8.96975135803223</v>
+        <v>8.96975231170654</v>
       </c>
       <c r="H456" t="s">
         <v>8</v>
@@ -12407,7 +12407,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G463" t="n">
-        <v>8.53805255889893</v>
+        <v>8.53805160522461</v>
       </c>
       <c r="H463" t="s">
         <v>8</v>
@@ -12641,7 +12641,7 @@
         <v>7.75</v>
       </c>
       <c r="G472" t="n">
-        <v>7.43482065200806</v>
+        <v>7.43482112884521</v>
       </c>
       <c r="H472" t="s">
         <v>8</v>
@@ -12849,7 +12849,7 @@
         <v>7.5</v>
       </c>
       <c r="G480" t="n">
-        <v>7.19498825073242</v>
+        <v>7.19498777389526</v>
       </c>
       <c r="H480" t="s">
         <v>8</v>
@@ -12875,7 +12875,7 @@
         <v>7.34999990463257</v>
       </c>
       <c r="G481" t="n">
-        <v>7.05108833312988</v>
+        <v>7.05108785629272</v>
       </c>
       <c r="H481" t="s">
         <v>8</v>
@@ -12901,7 +12901,7 @@
         <v>7.34999990463257</v>
       </c>
       <c r="G482" t="n">
-        <v>7.05108833312988</v>
+        <v>7.05108785629272</v>
       </c>
       <c r="H482" t="s">
         <v>8</v>
@@ -12979,7 +12979,7 @@
         <v>7</v>
       </c>
       <c r="G485" t="n">
-        <v>6.71532249450684</v>
+        <v>6.71532201766968</v>
       </c>
       <c r="H485" t="s">
         <v>8</v>
@@ -13239,7 +13239,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G495" t="n">
-        <v>6.04378986358643</v>
+        <v>6.04379034042358</v>
       </c>
       <c r="H495" t="s">
         <v>8</v>
@@ -13499,7 +13499,7 @@
         <v>7</v>
       </c>
       <c r="G505" t="n">
-        <v>6.71532249450684</v>
+        <v>6.71532201766968</v>
       </c>
       <c r="H505" t="s">
         <v>8</v>
@@ -13551,7 +13551,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G507" t="n">
-        <v>6.81125545501709</v>
+        <v>6.81125497817993</v>
       </c>
       <c r="H507" t="s">
         <v>8</v>
@@ -13629,7 +13629,7 @@
         <v>7.75</v>
       </c>
       <c r="G510" t="n">
-        <v>7.43482065200806</v>
+        <v>7.43482112884521</v>
       </c>
       <c r="H510" t="s">
         <v>8</v>
@@ -14097,7 +14097,7 @@
         <v>7.34999990463257</v>
       </c>
       <c r="G528" t="n">
-        <v>7.05108833312988</v>
+        <v>7.05108785629272</v>
       </c>
       <c r="H528" t="s">
         <v>8</v>
@@ -14279,7 +14279,7 @@
         <v>7.5</v>
       </c>
       <c r="G535" t="n">
-        <v>7.19498825073242</v>
+        <v>7.19498777389526</v>
       </c>
       <c r="H535" t="s">
         <v>8</v>
@@ -14409,7 +14409,7 @@
         <v>7</v>
       </c>
       <c r="G540" t="n">
-        <v>6.71532249450684</v>
+        <v>6.71532201766968</v>
       </c>
       <c r="H540" t="s">
         <v>8</v>
@@ -14565,7 +14565,7 @@
         <v>6.94999980926514</v>
       </c>
       <c r="G546" t="n">
-        <v>6.66735553741455</v>
+        <v>6.66735506057739</v>
       </c>
       <c r="H546" t="s">
         <v>8</v>
@@ -14643,7 +14643,7 @@
         <v>7</v>
       </c>
       <c r="G549" t="n">
-        <v>6.71532249450684</v>
+        <v>6.71532201766968</v>
       </c>
       <c r="H549" t="s">
         <v>8</v>
@@ -14669,7 +14669,7 @@
         <v>6.94999980926514</v>
       </c>
       <c r="G550" t="n">
-        <v>6.66735553741455</v>
+        <v>6.66735506057739</v>
       </c>
       <c r="H550" t="s">
         <v>8</v>
@@ -14903,7 +14903,7 @@
         <v>7.75</v>
       </c>
       <c r="G559" t="n">
-        <v>7.43482065200806</v>
+        <v>7.43482112884521</v>
       </c>
       <c r="H559" t="s">
         <v>8</v>
@@ -15033,7 +15033,7 @@
         <v>7.75</v>
       </c>
       <c r="G564" t="n">
-        <v>7.43482065200806</v>
+        <v>7.43482112884521</v>
       </c>
       <c r="H564" t="s">
         <v>8</v>
@@ -15137,7 +15137,7 @@
         <v>7.75</v>
       </c>
       <c r="G568" t="n">
-        <v>7.43482065200806</v>
+        <v>7.43482112884521</v>
       </c>
       <c r="H568" t="s">
         <v>8</v>
@@ -15293,7 +15293,7 @@
         <v>8.14999961853027</v>
       </c>
       <c r="G574" t="n">
-        <v>7.81855297088623</v>
+        <v>7.81855344772339</v>
       </c>
       <c r="H574" t="s">
         <v>8</v>
@@ -15423,7 +15423,7 @@
         <v>7.5</v>
       </c>
       <c r="G579" t="n">
-        <v>7.19498825073242</v>
+        <v>7.19498777389526</v>
       </c>
       <c r="H579" t="s">
         <v>8</v>
@@ -15501,7 +15501,7 @@
         <v>8.25</v>
       </c>
       <c r="G582" t="n">
-        <v>7.91448640823364</v>
+        <v>7.91448736190796</v>
       </c>
       <c r="H582" t="s">
         <v>8</v>
@@ -15527,7 +15527,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G583" t="n">
-        <v>7.86651945114136</v>
+        <v>7.86652040481567</v>
       </c>
       <c r="H583" t="s">
         <v>8</v>
@@ -15579,7 +15579,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G585" t="n">
-        <v>7.86651945114136</v>
+        <v>7.86652040481567</v>
       </c>
       <c r="H585" t="s">
         <v>8</v>
@@ -15605,7 +15605,7 @@
         <v>7.75</v>
       </c>
       <c r="G586" t="n">
-        <v>7.43482065200806</v>
+        <v>7.43482112884521</v>
       </c>
       <c r="H586" t="s">
         <v>8</v>
@@ -15631,7 +15631,7 @@
         <v>7.75</v>
       </c>
       <c r="G587" t="n">
-        <v>7.43482065200806</v>
+        <v>7.43482112884521</v>
       </c>
       <c r="H587" t="s">
         <v>8</v>
@@ -15657,7 +15657,7 @@
         <v>7.75</v>
       </c>
       <c r="G588" t="n">
-        <v>7.43482065200806</v>
+        <v>7.43482112884521</v>
       </c>
       <c r="H588" t="s">
         <v>8</v>
@@ -15709,7 +15709,7 @@
         <v>7.75</v>
       </c>
       <c r="G590" t="n">
-        <v>7.43482065200806</v>
+        <v>7.43482112884521</v>
       </c>
       <c r="H590" t="s">
         <v>8</v>
@@ -15865,7 +15865,7 @@
         <v>6.94999980926514</v>
       </c>
       <c r="G596" t="n">
-        <v>6.66735553741455</v>
+        <v>6.66735506057739</v>
       </c>
       <c r="H596" t="s">
         <v>8</v>
@@ -15891,7 +15891,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G597" t="n">
-        <v>6.90718793869019</v>
+        <v>6.90718841552734</v>
       </c>
       <c r="H597" t="s">
         <v>8</v>
@@ -15917,7 +15917,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G598" t="n">
-        <v>6.90718793869019</v>
+        <v>6.90718841552734</v>
       </c>
       <c r="H598" t="s">
         <v>8</v>
@@ -15995,7 +15995,7 @@
         <v>7.34999990463257</v>
       </c>
       <c r="G601" t="n">
-        <v>7.05108833312988</v>
+        <v>7.05108785629272</v>
       </c>
       <c r="H601" t="s">
         <v>8</v>
@@ -16021,7 +16021,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G602" t="n">
-        <v>6.90718793869019</v>
+        <v>6.90718841552734</v>
       </c>
       <c r="H602" t="s">
         <v>8</v>
@@ -16073,7 +16073,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G604" t="n">
-        <v>6.81125545501709</v>
+        <v>6.81125497817993</v>
       </c>
       <c r="H604" t="s">
         <v>8</v>
@@ -25436,6 +25436,32 @@
         <v>10.4499998092651</v>
       </c>
       <c r="H964" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="965">
+      <c r="A965" s="1" t="n">
+        <v>46289.2916666667</v>
+      </c>
+      <c r="B965" t="n">
+        <v>300</v>
+      </c>
+      <c r="C965" t="n">
+        <v>10.3000001907349</v>
+      </c>
+      <c r="D965" t="n">
+        <v>10.3000001907349</v>
+      </c>
+      <c r="E965" t="n">
+        <v>10.3000001907349</v>
+      </c>
+      <c r="F965" t="n">
+        <v>10.3000001907349</v>
+      </c>
+      <c r="G965" t="n">
+        <v>10.3000001907349</v>
+      </c>
+      <c r="H965" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/RDUE.MI.xlsx
+++ b/data/RDUE.MI.xlsx
@@ -25465,6 +25465,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="966">
+      <c r="A966" s="1" t="n">
+        <v>46290.2916666667</v>
+      </c>
+      <c r="B966" t="n">
+        <v>1600</v>
+      </c>
+      <c r="C966" t="n">
+        <v>10.6999998092651</v>
+      </c>
+      <c r="D966" t="n">
+        <v>10.3000001907349</v>
+      </c>
+      <c r="E966" t="n">
+        <v>10.3999996185303</v>
+      </c>
+      <c r="F966" t="n">
+        <v>10.25</v>
+      </c>
+      <c r="G966" t="n">
+        <v>10.25</v>
+      </c>
+      <c r="H966" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/RDUE.MI.xlsx
+++ b/data/RDUE.MI.xlsx
@@ -3957,7 +3957,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G138" t="n">
-        <v>10.0265769958496</v>
+        <v>10.0265779495239</v>
       </c>
       <c r="H138" t="s">
         <v>8</v>
@@ -6635,7 +6635,7 @@
         <v>8.42000007629395</v>
       </c>
       <c r="G241" t="n">
-        <v>7.8900728225708</v>
+        <v>7.89007329940796</v>
       </c>
       <c r="H241" t="s">
         <v>8</v>
@@ -6843,7 +6843,7 @@
         <v>8.03999996185303</v>
       </c>
       <c r="G249" t="n">
-        <v>7.53398895263672</v>
+        <v>7.53398942947388</v>
       </c>
       <c r="H249" t="s">
         <v>8</v>
@@ -6973,7 +6973,7 @@
         <v>8.03999996185303</v>
       </c>
       <c r="G254" t="n">
-        <v>7.53398895263672</v>
+        <v>7.53398942947388</v>
       </c>
       <c r="H254" t="s">
         <v>8</v>
@@ -8689,7 +8689,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G320" t="n">
-        <v>7.87133121490479</v>
+        <v>7.87133169174194</v>
       </c>
       <c r="H320" t="s">
         <v>8</v>
@@ -8897,7 +8897,7 @@
         <v>8.34000015258789</v>
       </c>
       <c r="G328" t="n">
-        <v>7.81510829925537</v>
+        <v>7.81510782241821</v>
       </c>
       <c r="H328" t="s">
         <v>8</v>
@@ -8923,7 +8923,7 @@
         <v>8.34000015258789</v>
       </c>
       <c r="G329" t="n">
-        <v>7.81510829925537</v>
+        <v>7.81510782241821</v>
       </c>
       <c r="H329" t="s">
         <v>8</v>
@@ -8949,7 +8949,7 @@
         <v>8.34000015258789</v>
       </c>
       <c r="G330" t="n">
-        <v>7.81510829925537</v>
+        <v>7.81510782241821</v>
       </c>
       <c r="H330" t="s">
         <v>8</v>
@@ -8975,7 +8975,7 @@
         <v>8.34000015258789</v>
       </c>
       <c r="G331" t="n">
-        <v>7.81510829925537</v>
+        <v>7.81510782241821</v>
       </c>
       <c r="H331" t="s">
         <v>8</v>
@@ -9001,7 +9001,7 @@
         <v>8.34000015258789</v>
       </c>
       <c r="G332" t="n">
-        <v>7.81510829925537</v>
+        <v>7.81510782241821</v>
       </c>
       <c r="H332" t="s">
         <v>8</v>
@@ -9079,7 +9079,7 @@
         <v>8.42000007629395</v>
       </c>
       <c r="G335" t="n">
-        <v>7.8900728225708</v>
+        <v>7.89007329940796</v>
       </c>
       <c r="H335" t="s">
         <v>8</v>
@@ -25540,6 +25540,32 @@
         <v>10.6499996185303</v>
       </c>
       <c r="H968" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="969">
+      <c r="A969" s="1" t="n">
+        <v>46295.2916666667</v>
+      </c>
+      <c r="B969" t="n">
+        <v>28500</v>
+      </c>
+      <c r="C969" t="n">
+        <v>12.1000003814697</v>
+      </c>
+      <c r="D969" t="n">
+        <v>11.0500001907349</v>
+      </c>
+      <c r="E969" t="n">
+        <v>11.0500001907349</v>
+      </c>
+      <c r="F969" t="n">
+        <v>11.3999996185303</v>
+      </c>
+      <c r="G969" t="n">
+        <v>11.3999996185303</v>
+      </c>
+      <c r="H969" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/RDUE.MI.xlsx
+++ b/data/RDUE.MI.xlsx
@@ -22721,8 +22721,31 @@
       <c r="E972" t="n">
         <v>11.4499998092651</v>
       </c>
-      <c r="F972"/>
+      <c r="F972" t="n">
+        <v>11.3999996185303</v>
+      </c>
       <c r="G972" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="973">
+      <c r="A973" s="1" t="n">
+        <v>46301.2916666667</v>
+      </c>
+      <c r="B973" t="n">
+        <v>1800</v>
+      </c>
+      <c r="C973" t="n">
+        <v>11.4499998092651</v>
+      </c>
+      <c r="D973" t="n">
+        <v>11.25</v>
+      </c>
+      <c r="E973" t="n">
+        <v>11.3000001907349</v>
+      </c>
+      <c r="F973"/>
+      <c r="G973" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/RDUE.MI.xlsx
+++ b/data/RDUE.MI.xlsx
@@ -22744,8 +22744,31 @@
       <c r="E973" t="n">
         <v>11.3000001907349</v>
       </c>
-      <c r="F973"/>
+      <c r="F973" t="n">
+        <v>11.4499998092651</v>
+      </c>
       <c r="G973" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="974">
+      <c r="A974" s="1" t="n">
+        <v>46302.2916666667</v>
+      </c>
+      <c r="B974" t="n">
+        <v>700</v>
+      </c>
+      <c r="C974" t="n">
+        <v>11.25</v>
+      </c>
+      <c r="D974" t="n">
+        <v>11.1999998092651</v>
+      </c>
+      <c r="E974" t="n">
+        <v>11.25</v>
+      </c>
+      <c r="F974"/>
+      <c r="G974" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/RDUE.MI.xlsx
+++ b/data/RDUE.MI.xlsx
@@ -22767,8 +22767,31 @@
       <c r="E974" t="n">
         <v>11.25</v>
       </c>
-      <c r="F974"/>
+      <c r="F974" t="n">
+        <v>11.1999998092651</v>
+      </c>
       <c r="G974" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="975">
+      <c r="A975" s="1" t="n">
+        <v>46303.2916666667</v>
+      </c>
+      <c r="B975" t="n">
+        <v>1700</v>
+      </c>
+      <c r="C975" t="n">
+        <v>11.3999996185303</v>
+      </c>
+      <c r="D975" t="n">
+        <v>11.1499996185303</v>
+      </c>
+      <c r="E975" t="n">
+        <v>11.1999998092651</v>
+      </c>
+      <c r="F975"/>
+      <c r="G975" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/RDUE.MI.xlsx
+++ b/data/RDUE.MI.xlsx
@@ -22790,8 +22790,31 @@
       <c r="E975" t="n">
         <v>11.1999998092651</v>
       </c>
-      <c r="F975"/>
+      <c r="F975" t="n">
+        <v>11.1499996185303</v>
+      </c>
       <c r="G975" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="976">
+      <c r="A976" s="1" t="n">
+        <v>46304.2916666667</v>
+      </c>
+      <c r="B976" t="n">
+        <v>2700</v>
+      </c>
+      <c r="C976" t="n">
+        <v>11.3000001907349</v>
+      </c>
+      <c r="D976" t="n">
+        <v>11.0500001907349</v>
+      </c>
+      <c r="E976" t="n">
+        <v>11.3000001907349</v>
+      </c>
+      <c r="F976"/>
+      <c r="G976" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/RDUE.MI.xlsx
+++ b/data/RDUE.MI.xlsx
@@ -22820,6 +22820,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="977">
+      <c r="A977" s="1" t="n">
+        <v>46307.2916666667</v>
+      </c>
+      <c r="B977" t="n">
+        <v>2500</v>
+      </c>
+      <c r="C977" t="n">
+        <v>11.3999996185303</v>
+      </c>
+      <c r="D977" t="n">
+        <v>11.1000003814697</v>
+      </c>
+      <c r="E977" t="n">
+        <v>11.3000001907349</v>
+      </c>
+      <c r="F977" t="n">
+        <v>11.1000003814697</v>
+      </c>
+      <c r="G977" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/RDUE.MI.xlsx
+++ b/data/RDUE.MI.xlsx
@@ -473,7 +473,7 @@
         <v>12.0600004196167</v>
       </c>
       <c r="G4" t="n">
-        <v>11.3009843826294</v>
+        <v>11.3009834289551</v>
       </c>
       <c r="H4" t="s">
         <v>8</v>
@@ -499,7 +499,7 @@
         <v>12.1499996185303</v>
       </c>
       <c r="G5" t="n">
-        <v>11.3853187561035</v>
+        <v>11.3853197097778</v>
       </c>
       <c r="H5" t="s">
         <v>8</v>
@@ -551,7 +551,7 @@
         <v>12.0900001525879</v>
       </c>
       <c r="G7" t="n">
-        <v>11.3290948867798</v>
+        <v>11.3290967941284</v>
       </c>
       <c r="H7" t="s">
         <v>8</v>
@@ -655,7 +655,7 @@
         <v>11.9180002212524</v>
       </c>
       <c r="G11" t="n">
-        <v>11.1679201126099</v>
+        <v>11.1679210662842</v>
       </c>
       <c r="H11" t="s">
         <v>8</v>
@@ -681,7 +681,7 @@
         <v>11.9899997711182</v>
       </c>
       <c r="G12" t="n">
-        <v>11.2353887557983</v>
+        <v>11.2353897094727</v>
       </c>
       <c r="H12" t="s">
         <v>8</v>
@@ -707,7 +707,7 @@
         <v>11.8800001144409</v>
       </c>
       <c r="G13" t="n">
-        <v>11.1323118209839</v>
+        <v>11.1323127746582</v>
       </c>
       <c r="H13" t="s">
         <v>8</v>
@@ -759,7 +759,7 @@
         <v>11.6199998855591</v>
       </c>
       <c r="G15" t="n">
-        <v>10.8886747360229</v>
+        <v>10.8886756896973</v>
       </c>
       <c r="H15" t="s">
         <v>8</v>
@@ -785,7 +785,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G16" t="n">
-        <v>11.0573463439941</v>
+        <v>11.0573472976685</v>
       </c>
       <c r="H16" t="s">
         <v>8</v>
@@ -811,7 +811,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G17" t="n">
-        <v>11.0573463439941</v>
+        <v>11.0573472976685</v>
       </c>
       <c r="H17" t="s">
         <v>8</v>
@@ -889,7 +889,7 @@
         <v>11.5900001525879</v>
       </c>
       <c r="G20" t="n">
-        <v>10.8605642318726</v>
+        <v>10.8605632781982</v>
       </c>
       <c r="H20" t="s">
         <v>8</v>
@@ -941,7 +941,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G22" t="n">
-        <v>10.682520866394</v>
+        <v>10.6825218200684</v>
       </c>
       <c r="H22" t="s">
         <v>8</v>
@@ -1019,7 +1019,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G25" t="n">
-        <v>10.5888147354126</v>
+        <v>10.5888156890869</v>
       </c>
       <c r="H25" t="s">
         <v>8</v>
@@ -1045,7 +1045,7 @@
         <v>11.25</v>
       </c>
       <c r="G26" t="n">
-        <v>10.5419616699219</v>
+        <v>10.5419626235962</v>
       </c>
       <c r="H26" t="s">
         <v>8</v>
@@ -1071,7 +1071,7 @@
         <v>11.9840002059937</v>
       </c>
       <c r="G27" t="n">
-        <v>11.2297668457031</v>
+        <v>11.2297677993774</v>
       </c>
       <c r="H27" t="s">
         <v>8</v>
@@ -1097,7 +1097,7 @@
         <v>12.0100002288818</v>
       </c>
       <c r="G28" t="n">
-        <v>11.2541313171387</v>
+        <v>11.2541303634644</v>
       </c>
       <c r="H28" t="s">
         <v>8</v>
@@ -1123,7 +1123,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G29" t="n">
-        <v>11.3384656906128</v>
+        <v>11.3384666442871</v>
       </c>
       <c r="H29" t="s">
         <v>8</v>
@@ -1149,7 +1149,7 @@
         <v>11.8800001144409</v>
       </c>
       <c r="G30" t="n">
-        <v>11.1323118209839</v>
+        <v>11.1323127746582</v>
       </c>
       <c r="H30" t="s">
         <v>8</v>
@@ -1175,7 +1175,7 @@
         <v>11.9799995422363</v>
       </c>
       <c r="G31" t="n">
-        <v>11.2260179519653</v>
+        <v>11.2260189056396</v>
       </c>
       <c r="H31" t="s">
         <v>8</v>
@@ -1279,7 +1279,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G35" t="n">
-        <v>11.0573463439941</v>
+        <v>11.0573472976685</v>
       </c>
       <c r="H35" t="s">
         <v>8</v>
@@ -1305,7 +1305,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G36" t="n">
-        <v>11.0573463439941</v>
+        <v>11.0573472976685</v>
       </c>
       <c r="H36" t="s">
         <v>8</v>
@@ -1331,7 +1331,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G37" t="n">
-        <v>11.0573463439941</v>
+        <v>11.0573472976685</v>
       </c>
       <c r="H37" t="s">
         <v>8</v>
@@ -1357,7 +1357,7 @@
         <v>11.996000289917</v>
       </c>
       <c r="G38" t="n">
-        <v>11.2410116195679</v>
+        <v>11.2410125732422</v>
       </c>
       <c r="H38" t="s">
         <v>8</v>
@@ -1409,7 +1409,7 @@
         <v>11.9799995422363</v>
       </c>
       <c r="G40" t="n">
-        <v>11.2260179519653</v>
+        <v>11.2260189056396</v>
       </c>
       <c r="H40" t="s">
         <v>8</v>
@@ -1435,7 +1435,7 @@
         <v>11.9799995422363</v>
       </c>
       <c r="G41" t="n">
-        <v>11.2260179519653</v>
+        <v>11.2260189056396</v>
       </c>
       <c r="H41" t="s">
         <v>8</v>
@@ -1487,7 +1487,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G43" t="n">
-        <v>11.0573463439941</v>
+        <v>11.0573472976685</v>
       </c>
       <c r="H43" t="s">
         <v>8</v>
@@ -1617,7 +1617,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G48" t="n">
-        <v>11.0573463439941</v>
+        <v>11.0573472976685</v>
       </c>
       <c r="H48" t="s">
         <v>8</v>
@@ -1669,7 +1669,7 @@
         <v>11.5500001907349</v>
       </c>
       <c r="G50" t="n">
-        <v>10.8230810165405</v>
+        <v>10.8230819702148</v>
       </c>
       <c r="H50" t="s">
         <v>8</v>
@@ -1695,7 +1695,7 @@
         <v>11.5500001907349</v>
       </c>
       <c r="G51" t="n">
-        <v>10.8230810165405</v>
+        <v>10.8230819702148</v>
       </c>
       <c r="H51" t="s">
         <v>8</v>
@@ -1721,7 +1721,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G52" t="n">
-        <v>11.0573463439941</v>
+        <v>11.0573472976685</v>
       </c>
       <c r="H52" t="s">
         <v>8</v>
@@ -1773,7 +1773,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G54" t="n">
-        <v>11.0573463439941</v>
+        <v>11.0573472976685</v>
       </c>
       <c r="H54" t="s">
         <v>8</v>
@@ -1799,7 +1799,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G55" t="n">
-        <v>11.0573463439941</v>
+        <v>11.0573472976685</v>
       </c>
       <c r="H55" t="s">
         <v>8</v>
@@ -1825,7 +1825,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G56" t="n">
-        <v>11.0573463439941</v>
+        <v>11.0573472976685</v>
       </c>
       <c r="H56" t="s">
         <v>8</v>
@@ -2007,7 +2007,7 @@
         <v>11.4499998092651</v>
       </c>
       <c r="G63" t="n">
-        <v>10.7293748855591</v>
+        <v>10.7293758392334</v>
       </c>
       <c r="H63" t="s">
         <v>8</v>
@@ -2033,7 +2033,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G64" t="n">
-        <v>10.682520866394</v>
+        <v>10.6825218200684</v>
       </c>
       <c r="H64" t="s">
         <v>8</v>
@@ -2059,7 +2059,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G65" t="n">
-        <v>10.682520866394</v>
+        <v>10.6825218200684</v>
       </c>
       <c r="H65" t="s">
         <v>8</v>
@@ -2085,7 +2085,7 @@
         <v>11.5500001907349</v>
       </c>
       <c r="G66" t="n">
-        <v>10.8230810165405</v>
+        <v>10.8230819702148</v>
       </c>
       <c r="H66" t="s">
         <v>8</v>
@@ -2137,7 +2137,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G68" t="n">
-        <v>10.682520866394</v>
+        <v>10.6825218200684</v>
       </c>
       <c r="H68" t="s">
         <v>8</v>
@@ -2163,7 +2163,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G69" t="n">
-        <v>10.682520866394</v>
+        <v>10.6825218200684</v>
       </c>
       <c r="H69" t="s">
         <v>8</v>
@@ -2215,7 +2215,7 @@
         <v>11.5</v>
       </c>
       <c r="G71" t="n">
-        <v>10.7762269973755</v>
+        <v>10.7762279510498</v>
       </c>
       <c r="H71" t="s">
         <v>8</v>
@@ -2241,7 +2241,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G72" t="n">
-        <v>10.682520866394</v>
+        <v>10.6825218200684</v>
       </c>
       <c r="H72" t="s">
         <v>8</v>
@@ -2397,7 +2397,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G78" t="n">
-        <v>11.0573463439941</v>
+        <v>11.0573472976685</v>
       </c>
       <c r="H78" t="s">
         <v>8</v>
@@ -2423,7 +2423,7 @@
         <v>11.5</v>
       </c>
       <c r="G79" t="n">
-        <v>10.7762269973755</v>
+        <v>10.7762279510498</v>
       </c>
       <c r="H79" t="s">
         <v>8</v>
@@ -2475,7 +2475,7 @@
         <v>11.5500001907349</v>
       </c>
       <c r="G81" t="n">
-        <v>10.8230810165405</v>
+        <v>10.8230819702148</v>
       </c>
       <c r="H81" t="s">
         <v>8</v>
@@ -2501,7 +2501,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G82" t="n">
-        <v>9.74545860290527</v>
+        <v>9.74545764923096</v>
       </c>
       <c r="H82" t="s">
         <v>8</v>
@@ -2657,7 +2657,7 @@
         <v>10.25</v>
       </c>
       <c r="G88" t="n">
-        <v>9.60489940643311</v>
+        <v>9.60489845275879</v>
       </c>
       <c r="H88" t="s">
         <v>8</v>
@@ -2683,7 +2683,7 @@
         <v>10.5500001907349</v>
       </c>
       <c r="G89" t="n">
-        <v>9.88601875305176</v>
+        <v>9.88601779937744</v>
       </c>
       <c r="H89" t="s">
         <v>8</v>
@@ -2709,7 +2709,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G90" t="n">
-        <v>9.55804634094238</v>
+        <v>9.55804538726807</v>
       </c>
       <c r="H90" t="s">
         <v>8</v>
@@ -2761,7 +2761,7 @@
         <v>9.92000007629395</v>
       </c>
       <c r="G92" t="n">
-        <v>9.29566860198975</v>
+        <v>9.29566764831543</v>
       </c>
       <c r="H92" t="s">
         <v>8</v>
@@ -2813,7 +2813,7 @@
         <v>9.73999977111816</v>
       </c>
       <c r="G94" t="n">
-        <v>9.12699699401855</v>
+        <v>9.12699604034424</v>
       </c>
       <c r="H94" t="s">
         <v>8</v>
@@ -2839,7 +2839,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G95" t="n">
-        <v>9.08951473236084</v>
+        <v>9.08951377868652</v>
       </c>
       <c r="H95" t="s">
         <v>8</v>
@@ -2865,7 +2865,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G96" t="n">
-        <v>9.08951473236084</v>
+        <v>9.08951377868652</v>
       </c>
       <c r="H96" t="s">
         <v>8</v>
@@ -2891,7 +2891,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G97" t="n">
-        <v>9.08951473236084</v>
+        <v>9.08951377868652</v>
       </c>
       <c r="H97" t="s">
         <v>8</v>
@@ -3073,7 +3073,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G104" t="n">
-        <v>8.62098217010498</v>
+        <v>8.6209831237793</v>
       </c>
       <c r="H104" t="s">
         <v>8</v>
@@ -3099,7 +3099,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G105" t="n">
-        <v>8.52727699279785</v>
+        <v>8.52727603912354</v>
       </c>
       <c r="H105" t="s">
         <v>8</v>
@@ -3125,7 +3125,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G106" t="n">
-        <v>8.62098217010498</v>
+        <v>8.6209831237793</v>
       </c>
       <c r="H106" t="s">
         <v>8</v>
@@ -3151,7 +3151,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G107" t="n">
-        <v>8.62098217010498</v>
+        <v>8.6209831237793</v>
       </c>
       <c r="H107" t="s">
         <v>8</v>
@@ -3229,7 +3229,7 @@
         <v>9.4399995803833</v>
       </c>
       <c r="G110" t="n">
-        <v>8.8458776473999</v>
+        <v>8.84587669372559</v>
       </c>
       <c r="H110" t="s">
         <v>8</v>
@@ -3255,7 +3255,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G111" t="n">
-        <v>9.08951473236084</v>
+        <v>9.08951377868652</v>
       </c>
       <c r="H111" t="s">
         <v>8</v>
@@ -3333,7 +3333,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G114" t="n">
-        <v>9.55804634094238</v>
+        <v>9.55804538726807</v>
       </c>
       <c r="H114" t="s">
         <v>8</v>
@@ -3359,7 +3359,7 @@
         <v>10</v>
       </c>
       <c r="G115" t="n">
-        <v>9.37063407897949</v>
+        <v>9.37063312530518</v>
       </c>
       <c r="H115" t="s">
         <v>8</v>
@@ -3385,7 +3385,7 @@
         <v>10.5500001907349</v>
       </c>
       <c r="G116" t="n">
-        <v>9.88601875305176</v>
+        <v>9.88601779937744</v>
       </c>
       <c r="H116" t="s">
         <v>8</v>
@@ -3411,7 +3411,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G117" t="n">
-        <v>9.74545860290527</v>
+        <v>9.74545764923096</v>
       </c>
       <c r="H117" t="s">
         <v>8</v>
@@ -3437,7 +3437,7 @@
         <v>10.5500001907349</v>
       </c>
       <c r="G118" t="n">
-        <v>9.88601875305176</v>
+        <v>9.88601779937744</v>
       </c>
       <c r="H118" t="s">
         <v>8</v>
@@ -3463,7 +3463,7 @@
         <v>10.5</v>
       </c>
       <c r="G119" t="n">
-        <v>9.83916568756104</v>
+        <v>9.83916473388672</v>
       </c>
       <c r="H119" t="s">
         <v>8</v>
@@ -3619,7 +3619,7 @@
         <v>9.57999992370605</v>
       </c>
       <c r="G125" t="n">
-        <v>8.97706699371338</v>
+        <v>8.97706604003906</v>
       </c>
       <c r="H125" t="s">
         <v>8</v>
@@ -3697,7 +3697,7 @@
         <v>9.88000011444092</v>
       </c>
       <c r="G128" t="n">
-        <v>9.25818634033203</v>
+        <v>9.25818538665771</v>
       </c>
       <c r="H128" t="s">
         <v>8</v>
@@ -3749,7 +3749,7 @@
         <v>9.92000007629395</v>
       </c>
       <c r="G130" t="n">
-        <v>9.29566860198975</v>
+        <v>9.29566764831543</v>
       </c>
       <c r="H130" t="s">
         <v>8</v>
@@ -3775,7 +3775,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G131" t="n">
-        <v>9.65175342559814</v>
+        <v>9.65175247192383</v>
       </c>
       <c r="H131" t="s">
         <v>8</v>
@@ -3801,7 +3801,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G132" t="n">
-        <v>9.65175342559814</v>
+        <v>9.65175247192383</v>
       </c>
       <c r="H132" t="s">
         <v>8</v>
@@ -3827,7 +3827,7 @@
         <v>9.97999954223633</v>
       </c>
       <c r="G133" t="n">
-        <v>9.35189247131348</v>
+        <v>9.35189056396484</v>
       </c>
       <c r="H133" t="s">
         <v>8</v>
@@ -3905,7 +3905,7 @@
         <v>10.5</v>
       </c>
       <c r="G136" t="n">
-        <v>9.83916568756104</v>
+        <v>9.83916473388672</v>
       </c>
       <c r="H136" t="s">
         <v>8</v>
@@ -3931,7 +3931,7 @@
         <v>10.5500001907349</v>
       </c>
       <c r="G137" t="n">
-        <v>9.88601875305176</v>
+        <v>9.88601779937744</v>
       </c>
       <c r="H137" t="s">
         <v>8</v>
@@ -3983,7 +3983,7 @@
         <v>10.5</v>
       </c>
       <c r="G139" t="n">
-        <v>9.83916568756104</v>
+        <v>9.83916473388672</v>
       </c>
       <c r="H139" t="s">
         <v>8</v>
@@ -4009,7 +4009,7 @@
         <v>10.5</v>
       </c>
       <c r="G140" t="n">
-        <v>9.83916568756104</v>
+        <v>9.83916473388672</v>
       </c>
       <c r="H140" t="s">
         <v>8</v>
@@ -4035,7 +4035,7 @@
         <v>10.5</v>
       </c>
       <c r="G141" t="n">
-        <v>9.83916568756104</v>
+        <v>9.83916473388672</v>
       </c>
       <c r="H141" t="s">
         <v>8</v>
@@ -4061,7 +4061,7 @@
         <v>10</v>
       </c>
       <c r="G142" t="n">
-        <v>9.37063407897949</v>
+        <v>9.37063312530518</v>
       </c>
       <c r="H142" t="s">
         <v>8</v>
@@ -4139,7 +4139,7 @@
         <v>9.5600004196167</v>
       </c>
       <c r="G145" t="n">
-        <v>8.95832538604736</v>
+        <v>8.95832633972168</v>
       </c>
       <c r="H145" t="s">
         <v>8</v>
@@ -4295,7 +4295,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G151" t="n">
-        <v>9.08951473236084</v>
+        <v>9.08951377868652</v>
       </c>
       <c r="H151" t="s">
         <v>8</v>
@@ -4321,7 +4321,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G152" t="n">
-        <v>9.08951473236084</v>
+        <v>9.08951377868652</v>
       </c>
       <c r="H152" t="s">
         <v>8</v>
@@ -4347,7 +4347,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G153" t="n">
-        <v>9.08951473236084</v>
+        <v>9.08951377868652</v>
       </c>
       <c r="H153" t="s">
         <v>8</v>
@@ -4399,7 +4399,7 @@
         <v>10</v>
       </c>
       <c r="G155" t="n">
-        <v>9.37063407897949</v>
+        <v>9.37063312530518</v>
       </c>
       <c r="H155" t="s">
         <v>8</v>
@@ -4425,7 +4425,7 @@
         <v>10</v>
       </c>
       <c r="G156" t="n">
-        <v>9.37063407897949</v>
+        <v>9.37063312530518</v>
       </c>
       <c r="H156" t="s">
         <v>8</v>
@@ -4451,7 +4451,7 @@
         <v>10</v>
       </c>
       <c r="G157" t="n">
-        <v>9.37063407897949</v>
+        <v>9.37063312530518</v>
       </c>
       <c r="H157" t="s">
         <v>8</v>
@@ -4477,7 +4477,7 @@
         <v>10</v>
       </c>
       <c r="G158" t="n">
-        <v>9.37063407897949</v>
+        <v>9.37063312530518</v>
       </c>
       <c r="H158" t="s">
         <v>8</v>
@@ -4503,7 +4503,7 @@
         <v>10</v>
       </c>
       <c r="G159" t="n">
-        <v>9.37063407897949</v>
+        <v>9.37063312530518</v>
       </c>
       <c r="H159" t="s">
         <v>8</v>
@@ -4529,7 +4529,7 @@
         <v>10</v>
       </c>
       <c r="G160" t="n">
-        <v>9.37063407897949</v>
+        <v>9.37063312530518</v>
       </c>
       <c r="H160" t="s">
         <v>8</v>
@@ -4555,7 +4555,7 @@
         <v>10</v>
       </c>
       <c r="G161" t="n">
-        <v>9.37063407897949</v>
+        <v>9.37063312530518</v>
       </c>
       <c r="H161" t="s">
         <v>8</v>
@@ -4581,7 +4581,7 @@
         <v>10</v>
       </c>
       <c r="G162" t="n">
-        <v>9.37063407897949</v>
+        <v>9.37063312530518</v>
       </c>
       <c r="H162" t="s">
         <v>8</v>
@@ -4633,7 +4633,7 @@
         <v>9.97999954223633</v>
       </c>
       <c r="G164" t="n">
-        <v>9.35189247131348</v>
+        <v>9.35189056396484</v>
       </c>
       <c r="H164" t="s">
         <v>8</v>
@@ -4711,7 +4711,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G167" t="n">
-        <v>9.08951473236084</v>
+        <v>9.08951377868652</v>
       </c>
       <c r="H167" t="s">
         <v>8</v>
@@ -4737,7 +4737,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G168" t="n">
-        <v>9.08951473236084</v>
+        <v>9.08951377868652</v>
       </c>
       <c r="H168" t="s">
         <v>8</v>
@@ -4763,7 +4763,7 @@
         <v>9.15999984741211</v>
       </c>
       <c r="G169" t="n">
-        <v>8.58350086212158</v>
+        <v>8.58349990844727</v>
       </c>
       <c r="H169" t="s">
         <v>8</v>
@@ -4841,7 +4841,7 @@
         <v>9.5600004196167</v>
       </c>
       <c r="G172" t="n">
-        <v>8.95832538604736</v>
+        <v>8.95832633972168</v>
       </c>
       <c r="H172" t="s">
         <v>8</v>
@@ -4893,7 +4893,7 @@
         <v>9.27999973297119</v>
       </c>
       <c r="G174" t="n">
-        <v>8.69594764709473</v>
+        <v>8.69594669342041</v>
       </c>
       <c r="H174" t="s">
         <v>8</v>
@@ -4919,7 +4919,7 @@
         <v>9.42000007629395</v>
       </c>
       <c r="G175" t="n">
-        <v>8.8271369934082</v>
+        <v>8.82713603973389</v>
       </c>
       <c r="H175" t="s">
         <v>8</v>
@@ -4945,7 +4945,7 @@
         <v>9.27999973297119</v>
       </c>
       <c r="G176" t="n">
-        <v>8.69594764709473</v>
+        <v>8.69594669342041</v>
       </c>
       <c r="H176" t="s">
         <v>8</v>
@@ -4971,7 +4971,7 @@
         <v>9.27999973297119</v>
       </c>
       <c r="G177" t="n">
-        <v>8.69594764709473</v>
+        <v>8.69594669342041</v>
       </c>
       <c r="H177" t="s">
         <v>8</v>
@@ -5127,7 +5127,7 @@
         <v>9.42000007629395</v>
       </c>
       <c r="G183" t="n">
-        <v>8.8271369934082</v>
+        <v>8.82713603973389</v>
       </c>
       <c r="H183" t="s">
         <v>8</v>
@@ -5153,7 +5153,7 @@
         <v>9.42000007629395</v>
       </c>
       <c r="G184" t="n">
-        <v>8.8271369934082</v>
+        <v>8.82713603973389</v>
       </c>
       <c r="H184" t="s">
         <v>8</v>
@@ -5231,7 +5231,7 @@
         <v>9.97999954223633</v>
       </c>
       <c r="G187" t="n">
-        <v>9.35189247131348</v>
+        <v>9.35189056396484</v>
       </c>
       <c r="H187" t="s">
         <v>8</v>
@@ -5257,7 +5257,7 @@
         <v>9.97999954223633</v>
       </c>
       <c r="G188" t="n">
-        <v>9.35189247131348</v>
+        <v>9.35189056396484</v>
       </c>
       <c r="H188" t="s">
         <v>8</v>
@@ -5413,7 +5413,7 @@
         <v>9.64000034332275</v>
       </c>
       <c r="G194" t="n">
-        <v>9.03329086303711</v>
+        <v>9.03328990936279</v>
       </c>
       <c r="H194" t="s">
         <v>8</v>
@@ -5595,7 +5595,7 @@
         <v>9</v>
       </c>
       <c r="G201" t="n">
-        <v>8.43356990814209</v>
+        <v>8.43356895446777</v>
       </c>
       <c r="H201" t="s">
         <v>8</v>
@@ -5621,7 +5621,7 @@
         <v>9</v>
       </c>
       <c r="G202" t="n">
-        <v>8.43356990814209</v>
+        <v>8.43356895446777</v>
       </c>
       <c r="H202" t="s">
         <v>8</v>
@@ -5647,7 +5647,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G203" t="n">
-        <v>8.2461576461792</v>
+        <v>8.24615669250488</v>
       </c>
       <c r="H203" t="s">
         <v>8</v>
@@ -5673,7 +5673,7 @@
         <v>9.0600004196167</v>
       </c>
       <c r="G204" t="n">
-        <v>8.48979473114014</v>
+        <v>8.48979377746582</v>
       </c>
       <c r="H204" t="s">
         <v>8</v>
@@ -5725,7 +5725,7 @@
         <v>9</v>
       </c>
       <c r="G206" t="n">
-        <v>8.43356990814209</v>
+        <v>8.43356895446777</v>
       </c>
       <c r="H206" t="s">
         <v>8</v>
@@ -5829,7 +5829,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G210" t="n">
-        <v>8.62098217010498</v>
+        <v>8.6209831237793</v>
       </c>
       <c r="H210" t="s">
         <v>8</v>
@@ -5855,7 +5855,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G211" t="n">
-        <v>8.62098217010498</v>
+        <v>8.6209831237793</v>
       </c>
       <c r="H211" t="s">
         <v>8</v>
@@ -5881,7 +5881,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G212" t="n">
-        <v>8.52727699279785</v>
+        <v>8.52727603912354</v>
       </c>
       <c r="H212" t="s">
         <v>8</v>
@@ -5907,7 +5907,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G213" t="n">
-        <v>8.52727699279785</v>
+        <v>8.52727603912354</v>
       </c>
       <c r="H213" t="s">
         <v>8</v>
@@ -5933,7 +5933,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G214" t="n">
-        <v>8.52727699279785</v>
+        <v>8.52727603912354</v>
       </c>
       <c r="H214" t="s">
         <v>8</v>
@@ -5959,7 +5959,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G215" t="n">
-        <v>8.52727699279785</v>
+        <v>8.52727603912354</v>
       </c>
       <c r="H215" t="s">
         <v>8</v>
@@ -5985,7 +5985,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G216" t="n">
-        <v>8.52727699279785</v>
+        <v>8.52727603912354</v>
       </c>
       <c r="H216" t="s">
         <v>8</v>
@@ -6011,7 +6011,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G217" t="n">
-        <v>8.52727699279785</v>
+        <v>8.52727603912354</v>
       </c>
       <c r="H217" t="s">
         <v>8</v>
@@ -6037,7 +6037,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G218" t="n">
-        <v>8.52727699279785</v>
+        <v>8.52727603912354</v>
       </c>
       <c r="H218" t="s">
         <v>8</v>
@@ -6063,7 +6063,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G219" t="n">
-        <v>8.52727699279785</v>
+        <v>8.52727603912354</v>
       </c>
       <c r="H219" t="s">
         <v>8</v>
@@ -6219,7 +6219,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G225" t="n">
-        <v>8.52727699279785</v>
+        <v>8.52727603912354</v>
       </c>
       <c r="H225" t="s">
         <v>8</v>
@@ -6245,7 +6245,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G226" t="n">
-        <v>8.52727699279785</v>
+        <v>8.52727603912354</v>
       </c>
       <c r="H226" t="s">
         <v>8</v>
@@ -6271,7 +6271,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G227" t="n">
-        <v>8.52727699279785</v>
+        <v>8.52727603912354</v>
       </c>
       <c r="H227" t="s">
         <v>8</v>
@@ -6297,7 +6297,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G228" t="n">
-        <v>8.52727699279785</v>
+        <v>8.52727603912354</v>
       </c>
       <c r="H228" t="s">
         <v>8</v>
@@ -6323,7 +6323,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G229" t="n">
-        <v>8.52727699279785</v>
+        <v>8.52727603912354</v>
       </c>
       <c r="H229" t="s">
         <v>8</v>
@@ -6349,7 +6349,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G230" t="n">
-        <v>8.52727699279785</v>
+        <v>8.52727603912354</v>
       </c>
       <c r="H230" t="s">
         <v>8</v>
@@ -6375,7 +6375,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G231" t="n">
-        <v>8.52727699279785</v>
+        <v>8.52727603912354</v>
       </c>
       <c r="H231" t="s">
         <v>8</v>
@@ -6401,7 +6401,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G232" t="n">
-        <v>8.52727699279785</v>
+        <v>8.52727603912354</v>
       </c>
       <c r="H232" t="s">
         <v>8</v>
@@ -6427,7 +6427,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G233" t="n">
-        <v>8.52727699279785</v>
+        <v>8.52727603912354</v>
       </c>
       <c r="H233" t="s">
         <v>8</v>
@@ -6479,7 +6479,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G235" t="n">
-        <v>8.2461576461792</v>
+        <v>8.24615669250488</v>
       </c>
       <c r="H235" t="s">
         <v>8</v>
@@ -6583,7 +6583,7 @@
         <v>8.73999977111816</v>
       </c>
       <c r="G239" t="n">
-        <v>8.18993377685547</v>
+        <v>8.18993282318115</v>
       </c>
       <c r="H239" t="s">
         <v>8</v>
@@ -6661,7 +6661,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G242" t="n">
-        <v>7.68391942977905</v>
+        <v>7.68391895294189</v>
       </c>
       <c r="H242" t="s">
         <v>8</v>
@@ -6713,7 +6713,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G244" t="n">
-        <v>7.59021329879761</v>
+        <v>7.59021282196045</v>
       </c>
       <c r="H244" t="s">
         <v>8</v>
@@ -6739,7 +6739,7 @@
         <v>8.0600004196167</v>
       </c>
       <c r="G245" t="n">
-        <v>7.55273103713989</v>
+        <v>7.55273056030273</v>
       </c>
       <c r="H245" t="s">
         <v>8</v>
@@ -6765,7 +6765,7 @@
         <v>8.0600004196167</v>
       </c>
       <c r="G246" t="n">
-        <v>7.55273103713989</v>
+        <v>7.55273056030273</v>
       </c>
       <c r="H246" t="s">
         <v>8</v>
@@ -6791,7 +6791,7 @@
         <v>8.0600004196167</v>
       </c>
       <c r="G247" t="n">
-        <v>7.55273103713989</v>
+        <v>7.55273056030273</v>
       </c>
       <c r="H247" t="s">
         <v>8</v>
@@ -6817,7 +6817,7 @@
         <v>8.0600004196167</v>
       </c>
       <c r="G248" t="n">
-        <v>7.55273103713989</v>
+        <v>7.55273056030273</v>
       </c>
       <c r="H248" t="s">
         <v>8</v>
@@ -6843,7 +6843,7 @@
         <v>8.03999996185303</v>
       </c>
       <c r="G249" t="n">
-        <v>7.53398942947388</v>
+        <v>7.53398895263672</v>
       </c>
       <c r="H249" t="s">
         <v>8</v>
@@ -6895,7 +6895,7 @@
         <v>8.23999977111816</v>
       </c>
       <c r="G251" t="n">
-        <v>7.72140169143677</v>
+        <v>7.72140121459961</v>
       </c>
       <c r="H251" t="s">
         <v>8</v>
@@ -6921,7 +6921,7 @@
         <v>8.26000022888184</v>
       </c>
       <c r="G252" t="n">
-        <v>7.74014377593994</v>
+        <v>7.74014282226562</v>
       </c>
       <c r="H252" t="s">
         <v>8</v>
@@ -6973,7 +6973,7 @@
         <v>8.03999996185303</v>
       </c>
       <c r="G254" t="n">
-        <v>7.53398942947388</v>
+        <v>7.53398895263672</v>
       </c>
       <c r="H254" t="s">
         <v>8</v>
@@ -7051,7 +7051,7 @@
         <v>7.55999994277954</v>
       </c>
       <c r="G257" t="n">
-        <v>7.08419847488403</v>
+        <v>7.08419895172119</v>
       </c>
       <c r="H257" t="s">
         <v>8</v>
@@ -7077,7 +7077,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G258" t="n">
-        <v>7.12168121337891</v>
+        <v>7.12168073654175</v>
       </c>
       <c r="H258" t="s">
         <v>8</v>
@@ -7129,7 +7129,7 @@
         <v>7.67999982833862</v>
       </c>
       <c r="G260" t="n">
-        <v>7.19664621353149</v>
+        <v>7.19664573669434</v>
       </c>
       <c r="H260" t="s">
         <v>8</v>
@@ -7155,7 +7155,7 @@
         <v>7.84000015258789</v>
       </c>
       <c r="G261" t="n">
-        <v>7.34657669067383</v>
+        <v>7.34657621383667</v>
       </c>
       <c r="H261" t="s">
         <v>8</v>
@@ -7207,7 +7207,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G263" t="n">
-        <v>7.40280055999756</v>
+        <v>7.4028000831604</v>
       </c>
       <c r="H263" t="s">
         <v>8</v>
@@ -7259,7 +7259,7 @@
         <v>7.48000001907349</v>
       </c>
       <c r="G265" t="n">
-        <v>7.0092339515686</v>
+        <v>7.00923347473145</v>
       </c>
       <c r="H265" t="s">
         <v>8</v>
@@ -7337,7 +7337,7 @@
         <v>7.48000001907349</v>
       </c>
       <c r="G268" t="n">
-        <v>7.0092339515686</v>
+        <v>7.00923347473145</v>
       </c>
       <c r="H268" t="s">
         <v>8</v>
@@ -7441,7 +7441,7 @@
         <v>8.53999996185303</v>
       </c>
       <c r="G272" t="n">
-        <v>8.00252151489258</v>
+        <v>8.00252056121826</v>
       </c>
       <c r="H272" t="s">
         <v>8</v>
@@ -7545,7 +7545,7 @@
         <v>9.11999988555908</v>
       </c>
       <c r="G276" t="n">
-        <v>8.54601764678955</v>
+        <v>8.54601669311523</v>
       </c>
       <c r="H276" t="s">
         <v>8</v>
@@ -7597,7 +7597,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G278" t="n">
-        <v>8.62098217010498</v>
+        <v>8.6209831237793</v>
       </c>
       <c r="H278" t="s">
         <v>8</v>
@@ -7623,7 +7623,7 @@
         <v>9.11999988555908</v>
       </c>
       <c r="G279" t="n">
-        <v>8.54601764678955</v>
+        <v>8.54601669311523</v>
       </c>
       <c r="H279" t="s">
         <v>8</v>
@@ -7649,7 +7649,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G280" t="n">
-        <v>8.52727699279785</v>
+        <v>8.52727603912354</v>
       </c>
       <c r="H280" t="s">
         <v>8</v>
@@ -7701,7 +7701,7 @@
         <v>8.92000007629395</v>
       </c>
       <c r="G282" t="n">
-        <v>8.35860443115234</v>
+        <v>8.35860538482666</v>
       </c>
       <c r="H282" t="s">
         <v>8</v>
@@ -7831,7 +7831,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G287" t="n">
-        <v>8.2461576461792</v>
+        <v>8.24615669250488</v>
       </c>
       <c r="H287" t="s">
         <v>8</v>
@@ -7883,7 +7883,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G289" t="n">
-        <v>8.52727699279785</v>
+        <v>8.52727603912354</v>
       </c>
       <c r="H289" t="s">
         <v>8</v>
@@ -7935,7 +7935,7 @@
         <v>9.11999988555908</v>
       </c>
       <c r="G291" t="n">
-        <v>8.54601764678955</v>
+        <v>8.54601669311523</v>
       </c>
       <c r="H291" t="s">
         <v>8</v>
@@ -7961,7 +7961,7 @@
         <v>9.11999988555908</v>
       </c>
       <c r="G292" t="n">
-        <v>8.54601764678955</v>
+        <v>8.54601669311523</v>
       </c>
       <c r="H292" t="s">
         <v>8</v>
@@ -8013,7 +8013,7 @@
         <v>9</v>
       </c>
       <c r="G294" t="n">
-        <v>8.43356990814209</v>
+        <v>8.43356895446777</v>
       </c>
       <c r="H294" t="s">
         <v>8</v>
@@ -8065,7 +8065,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G296" t="n">
-        <v>8.62098217010498</v>
+        <v>8.6209831237793</v>
       </c>
       <c r="H296" t="s">
         <v>8</v>
@@ -8143,7 +8143,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G299" t="n">
-        <v>8.52727699279785</v>
+        <v>8.52727603912354</v>
       </c>
       <c r="H299" t="s">
         <v>8</v>
@@ -8195,7 +8195,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G301" t="n">
-        <v>8.52727699279785</v>
+        <v>8.52727603912354</v>
       </c>
       <c r="H301" t="s">
         <v>8</v>
@@ -8221,7 +8221,7 @@
         <v>9</v>
       </c>
       <c r="G302" t="n">
-        <v>8.43356990814209</v>
+        <v>8.43356895446777</v>
       </c>
       <c r="H302" t="s">
         <v>8</v>
@@ -8247,7 +8247,7 @@
         <v>9</v>
       </c>
       <c r="G303" t="n">
-        <v>8.43356990814209</v>
+        <v>8.43356895446777</v>
       </c>
       <c r="H303" t="s">
         <v>8</v>
@@ -8299,7 +8299,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G305" t="n">
-        <v>8.2461576461792</v>
+        <v>8.24615669250488</v>
       </c>
       <c r="H305" t="s">
         <v>8</v>
@@ -8325,7 +8325,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G306" t="n">
-        <v>8.2461576461792</v>
+        <v>8.24615669250488</v>
       </c>
       <c r="H306" t="s">
         <v>8</v>
@@ -8351,7 +8351,7 @@
         <v>8.64000034332275</v>
       </c>
       <c r="G307" t="n">
-        <v>8.09622764587402</v>
+        <v>8.09622669219971</v>
       </c>
       <c r="H307" t="s">
         <v>8</v>
@@ -8403,7 +8403,7 @@
         <v>8.53999996185303</v>
       </c>
       <c r="G309" t="n">
-        <v>8.00252151489258</v>
+        <v>8.00252056121826</v>
       </c>
       <c r="H309" t="s">
         <v>8</v>
@@ -8429,7 +8429,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G310" t="n">
-        <v>8.2461576461792</v>
+        <v>8.24615669250488</v>
       </c>
       <c r="H310" t="s">
         <v>8</v>
@@ -8455,7 +8455,7 @@
         <v>8.47999954223633</v>
       </c>
       <c r="G311" t="n">
-        <v>7.94629669189453</v>
+        <v>7.94629621505737</v>
       </c>
       <c r="H311" t="s">
         <v>8</v>
@@ -8507,7 +8507,7 @@
         <v>8.61999988555908</v>
       </c>
       <c r="G313" t="n">
-        <v>8.07748508453369</v>
+        <v>8.07748603820801</v>
       </c>
       <c r="H313" t="s">
         <v>8</v>
@@ -8533,7 +8533,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G314" t="n">
-        <v>8.2461576461792</v>
+        <v>8.24615669250488</v>
       </c>
       <c r="H314" t="s">
         <v>8</v>
@@ -8585,7 +8585,7 @@
         <v>8.47999954223633</v>
       </c>
       <c r="G316" t="n">
-        <v>7.94629669189453</v>
+        <v>7.94629621505737</v>
       </c>
       <c r="H316" t="s">
         <v>8</v>
@@ -8637,7 +8637,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G318" t="n">
-        <v>8.2461576461792</v>
+        <v>8.24615669250488</v>
       </c>
       <c r="H318" t="s">
         <v>8</v>
@@ -8663,7 +8663,7 @@
         <v>8.47999954223633</v>
       </c>
       <c r="G319" t="n">
-        <v>7.94629669189453</v>
+        <v>7.94629621505737</v>
       </c>
       <c r="H319" t="s">
         <v>8</v>
@@ -8689,7 +8689,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G320" t="n">
-        <v>7.87133169174194</v>
+        <v>7.87133121490479</v>
       </c>
       <c r="H320" t="s">
         <v>8</v>
@@ -8845,7 +8845,7 @@
         <v>8.31999969482422</v>
       </c>
       <c r="G326" t="n">
-        <v>7.7963662147522</v>
+        <v>7.79636669158936</v>
       </c>
       <c r="H326" t="s">
         <v>8</v>
@@ -8897,7 +8897,7 @@
         <v>8.34000015258789</v>
       </c>
       <c r="G328" t="n">
-        <v>7.81510782241821</v>
+        <v>7.81510829925537</v>
       </c>
       <c r="H328" t="s">
         <v>8</v>
@@ -8923,7 +8923,7 @@
         <v>8.34000015258789</v>
       </c>
       <c r="G329" t="n">
-        <v>7.81510782241821</v>
+        <v>7.81510829925537</v>
       </c>
       <c r="H329" t="s">
         <v>8</v>
@@ -8949,7 +8949,7 @@
         <v>8.34000015258789</v>
       </c>
       <c r="G330" t="n">
-        <v>7.81510782241821</v>
+        <v>7.81510829925537</v>
       </c>
       <c r="H330" t="s">
         <v>8</v>
@@ -8975,7 +8975,7 @@
         <v>8.34000015258789</v>
       </c>
       <c r="G331" t="n">
-        <v>7.81510782241821</v>
+        <v>7.81510829925537</v>
       </c>
       <c r="H331" t="s">
         <v>8</v>
@@ -9001,7 +9001,7 @@
         <v>8.34000015258789</v>
       </c>
       <c r="G332" t="n">
-        <v>7.81510782241821</v>
+        <v>7.81510829925537</v>
       </c>
       <c r="H332" t="s">
         <v>8</v>
@@ -9105,7 +9105,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G336" t="n">
-        <v>8.2461576461792</v>
+        <v>8.24615669250488</v>
       </c>
       <c r="H336" t="s">
         <v>8</v>
@@ -9131,7 +9131,7 @@
         <v>9</v>
       </c>
       <c r="G337" t="n">
-        <v>8.43356990814209</v>
+        <v>8.43356895446777</v>
       </c>
       <c r="H337" t="s">
         <v>8</v>
@@ -9157,7 +9157,7 @@
         <v>9</v>
       </c>
       <c r="G338" t="n">
-        <v>8.43356990814209</v>
+        <v>8.43356895446777</v>
       </c>
       <c r="H338" t="s">
         <v>8</v>
@@ -9183,7 +9183,7 @@
         <v>9</v>
       </c>
       <c r="G339" t="n">
-        <v>8.43356990814209</v>
+        <v>8.43356895446777</v>
       </c>
       <c r="H339" t="s">
         <v>8</v>
@@ -9209,7 +9209,7 @@
         <v>9</v>
       </c>
       <c r="G340" t="n">
-        <v>8.43356990814209</v>
+        <v>8.43356895446777</v>
       </c>
       <c r="H340" t="s">
         <v>8</v>
@@ -9287,7 +9287,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G343" t="n">
-        <v>9.08951473236084</v>
+        <v>9.08951377868652</v>
       </c>
       <c r="H343" t="s">
         <v>8</v>
@@ -9339,7 +9339,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G345" t="n">
-        <v>9.08951473236084</v>
+        <v>9.08951377868652</v>
       </c>
       <c r="H345" t="s">
         <v>8</v>
@@ -9495,7 +9495,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G351" t="n">
-        <v>9.08951473236084</v>
+        <v>9.08951377868652</v>
       </c>
       <c r="H351" t="s">
         <v>8</v>
@@ -9703,7 +9703,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G359" t="n">
-        <v>9.0426607131958</v>
+        <v>9.04265975952148</v>
       </c>
       <c r="H359" t="s">
         <v>8</v>
@@ -9729,7 +9729,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G360" t="n">
-        <v>9.0426607131958</v>
+        <v>9.04265975952148</v>
       </c>
       <c r="H360" t="s">
         <v>8</v>
@@ -9807,7 +9807,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G363" t="n">
-        <v>9.0426607131958</v>
+        <v>9.04265975952148</v>
       </c>
       <c r="H363" t="s">
         <v>8</v>
@@ -9833,7 +9833,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G364" t="n">
-        <v>9.0426607131958</v>
+        <v>9.04265975952148</v>
       </c>
       <c r="H364" t="s">
         <v>8</v>
@@ -9859,7 +9859,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G365" t="n">
-        <v>9.0426607131958</v>
+        <v>9.04265975952148</v>
       </c>
       <c r="H365" t="s">
         <v>8</v>
@@ -10093,7 +10093,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G374" t="n">
-        <v>9.0426607131958</v>
+        <v>9.04265975952148</v>
       </c>
       <c r="H374" t="s">
         <v>8</v>
@@ -10119,7 +10119,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G375" t="n">
-        <v>9.30551815032959</v>
+        <v>9.30551719665527</v>
       </c>
       <c r="H375" t="s">
         <v>8</v>
@@ -10145,7 +10145,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G376" t="n">
-        <v>9.2575511932373</v>
+        <v>9.25755023956299</v>
       </c>
       <c r="H376" t="s">
         <v>8</v>
@@ -10197,7 +10197,7 @@
         <v>10</v>
       </c>
       <c r="G378" t="n">
-        <v>9.59331798553467</v>
+        <v>9.59331703186035</v>
       </c>
       <c r="H378" t="s">
         <v>8</v>
@@ -10535,7 +10535,7 @@
         <v>10</v>
       </c>
       <c r="G391" t="n">
-        <v>9.59331798553467</v>
+        <v>9.59331703186035</v>
       </c>
       <c r="H391" t="s">
         <v>8</v>
@@ -10665,7 +10665,7 @@
         <v>10</v>
       </c>
       <c r="G396" t="n">
-        <v>9.59331798553467</v>
+        <v>9.59331703186035</v>
       </c>
       <c r="H396" t="s">
         <v>8</v>
@@ -10691,7 +10691,7 @@
         <v>10</v>
       </c>
       <c r="G397" t="n">
-        <v>9.59331798553467</v>
+        <v>9.59331703186035</v>
       </c>
       <c r="H397" t="s">
         <v>8</v>
@@ -10743,7 +10743,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G399" t="n">
-        <v>9.30551815032959</v>
+        <v>9.30551719665527</v>
       </c>
       <c r="H399" t="s">
         <v>8</v>
@@ -10795,7 +10795,7 @@
         <v>9.35000038146973</v>
       </c>
       <c r="G401" t="n">
-        <v>8.96975231170654</v>
+        <v>8.96975135803223</v>
       </c>
       <c r="H401" t="s">
         <v>8</v>
@@ -11055,7 +11055,7 @@
         <v>10</v>
       </c>
       <c r="G411" t="n">
-        <v>9.59331798553467</v>
+        <v>9.59331703186035</v>
       </c>
       <c r="H411" t="s">
         <v>8</v>
@@ -11185,7 +11185,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G416" t="n">
-        <v>9.2575511932373</v>
+        <v>9.25755023956299</v>
       </c>
       <c r="H416" t="s">
         <v>8</v>
@@ -11211,7 +11211,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G417" t="n">
-        <v>9.2575511932373</v>
+        <v>9.25755023956299</v>
       </c>
       <c r="H417" t="s">
         <v>8</v>
@@ -11237,7 +11237,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G418" t="n">
-        <v>9.2575511932373</v>
+        <v>9.25755023956299</v>
       </c>
       <c r="H418" t="s">
         <v>8</v>
@@ -11263,7 +11263,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G419" t="n">
-        <v>9.30551815032959</v>
+        <v>9.30551719665527</v>
       </c>
       <c r="H419" t="s">
         <v>8</v>
@@ -11315,7 +11315,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G421" t="n">
-        <v>9.01771831512451</v>
+        <v>9.0177173614502</v>
       </c>
       <c r="H421" t="s">
         <v>8</v>
@@ -11367,7 +11367,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G423" t="n">
-        <v>9.2575511932373</v>
+        <v>9.25755023956299</v>
       </c>
       <c r="H423" t="s">
         <v>8</v>
@@ -11393,7 +11393,7 @@
         <v>9.35000038146973</v>
       </c>
       <c r="G424" t="n">
-        <v>8.96975231170654</v>
+        <v>8.96975135803223</v>
       </c>
       <c r="H424" t="s">
         <v>8</v>
@@ -11419,7 +11419,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G425" t="n">
-        <v>8.53805160522461</v>
+        <v>8.53805255889893</v>
       </c>
       <c r="H425" t="s">
         <v>8</v>
@@ -11523,7 +11523,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G429" t="n">
-        <v>9.2575511932373</v>
+        <v>9.25755023956299</v>
       </c>
       <c r="H429" t="s">
         <v>8</v>
@@ -11549,7 +11549,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G430" t="n">
-        <v>9.2575511932373</v>
+        <v>9.25755023956299</v>
       </c>
       <c r="H430" t="s">
         <v>8</v>
@@ -11601,7 +11601,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G432" t="n">
-        <v>9.01771831512451</v>
+        <v>9.0177173614502</v>
       </c>
       <c r="H432" t="s">
         <v>8</v>
@@ -11627,7 +11627,7 @@
         <v>9.35000038146973</v>
       </c>
       <c r="G433" t="n">
-        <v>8.96975231170654</v>
+        <v>8.96975135803223</v>
       </c>
       <c r="H433" t="s">
         <v>8</v>
@@ -11679,7 +11679,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G435" t="n">
-        <v>9.30551815032959</v>
+        <v>9.30551719665527</v>
       </c>
       <c r="H435" t="s">
         <v>8</v>
@@ -11705,7 +11705,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G436" t="n">
-        <v>9.2575511932373</v>
+        <v>9.25755023956299</v>
       </c>
       <c r="H436" t="s">
         <v>8</v>
@@ -11757,7 +11757,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G438" t="n">
-        <v>9.01771831512451</v>
+        <v>9.0177173614502</v>
       </c>
       <c r="H438" t="s">
         <v>8</v>
@@ -11783,7 +11783,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G439" t="n">
-        <v>9.30551815032959</v>
+        <v>9.30551719665527</v>
       </c>
       <c r="H439" t="s">
         <v>8</v>
@@ -11809,7 +11809,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G440" t="n">
-        <v>9.30551815032959</v>
+        <v>9.30551719665527</v>
       </c>
       <c r="H440" t="s">
         <v>8</v>
@@ -11835,7 +11835,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G441" t="n">
-        <v>9.30551815032959</v>
+        <v>9.30551719665527</v>
       </c>
       <c r="H441" t="s">
         <v>8</v>
@@ -11861,7 +11861,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G442" t="n">
-        <v>9.30551815032959</v>
+        <v>9.30551719665527</v>
       </c>
       <c r="H442" t="s">
         <v>8</v>
@@ -11939,7 +11939,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G445" t="n">
-        <v>9.01771831512451</v>
+        <v>9.0177173614502</v>
       </c>
       <c r="H445" t="s">
         <v>8</v>
@@ -11965,7 +11965,7 @@
         <v>9.44999980926514</v>
       </c>
       <c r="G446" t="n">
-        <v>9.0656852722168</v>
+        <v>9.06568431854248</v>
       </c>
       <c r="H446" t="s">
         <v>8</v>
@@ -11991,7 +11991,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G447" t="n">
-        <v>9.01771831512451</v>
+        <v>9.0177173614502</v>
       </c>
       <c r="H447" t="s">
         <v>8</v>
@@ -12017,7 +12017,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G448" t="n">
-        <v>8.82585144042969</v>
+        <v>8.825852394104</v>
       </c>
       <c r="H448" t="s">
         <v>8</v>
@@ -12173,7 +12173,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G454" t="n">
-        <v>8.82585144042969</v>
+        <v>8.825852394104</v>
       </c>
       <c r="H454" t="s">
         <v>8</v>
@@ -12199,7 +12199,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G455" t="n">
-        <v>8.82585144042969</v>
+        <v>8.825852394104</v>
       </c>
       <c r="H455" t="s">
         <v>8</v>
@@ -12225,7 +12225,7 @@
         <v>9.35000038146973</v>
       </c>
       <c r="G456" t="n">
-        <v>8.96975231170654</v>
+        <v>8.96975135803223</v>
       </c>
       <c r="H456" t="s">
         <v>8</v>
@@ -12407,7 +12407,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G463" t="n">
-        <v>8.53805160522461</v>
+        <v>8.53805255889893</v>
       </c>
       <c r="H463" t="s">
         <v>8</v>
@@ -12641,7 +12641,7 @@
         <v>7.75</v>
       </c>
       <c r="G472" t="n">
-        <v>7.43482112884521</v>
+        <v>7.43482065200806</v>
       </c>
       <c r="H472" t="s">
         <v>8</v>
@@ -12849,7 +12849,7 @@
         <v>7.5</v>
       </c>
       <c r="G480" t="n">
-        <v>7.19498777389526</v>
+        <v>7.19498825073242</v>
       </c>
       <c r="H480" t="s">
         <v>8</v>
@@ -12875,7 +12875,7 @@
         <v>7.34999990463257</v>
       </c>
       <c r="G481" t="n">
-        <v>7.05108785629272</v>
+        <v>7.05108833312988</v>
       </c>
       <c r="H481" t="s">
         <v>8</v>
@@ -12901,7 +12901,7 @@
         <v>7.34999990463257</v>
       </c>
       <c r="G482" t="n">
-        <v>7.05108785629272</v>
+        <v>7.05108833312988</v>
       </c>
       <c r="H482" t="s">
         <v>8</v>
@@ -12979,7 +12979,7 @@
         <v>7</v>
       </c>
       <c r="G485" t="n">
-        <v>6.71532201766968</v>
+        <v>6.71532249450684</v>
       </c>
       <c r="H485" t="s">
         <v>8</v>
@@ -13239,7 +13239,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G495" t="n">
-        <v>6.04379034042358</v>
+        <v>6.04378986358643</v>
       </c>
       <c r="H495" t="s">
         <v>8</v>
@@ -13499,7 +13499,7 @@
         <v>7</v>
       </c>
       <c r="G505" t="n">
-        <v>6.71532201766968</v>
+        <v>6.71532249450684</v>
       </c>
       <c r="H505" t="s">
         <v>8</v>
@@ -13551,7 +13551,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G507" t="n">
-        <v>6.81125497817993</v>
+        <v>6.81125545501709</v>
       </c>
       <c r="H507" t="s">
         <v>8</v>
@@ -13629,7 +13629,7 @@
         <v>7.75</v>
       </c>
       <c r="G510" t="n">
-        <v>7.43482112884521</v>
+        <v>7.43482065200806</v>
       </c>
       <c r="H510" t="s">
         <v>8</v>
@@ -14097,7 +14097,7 @@
         <v>7.34999990463257</v>
       </c>
       <c r="G528" t="n">
-        <v>7.05108785629272</v>
+        <v>7.05108833312988</v>
       </c>
       <c r="H528" t="s">
         <v>8</v>
@@ -14279,7 +14279,7 @@
         <v>7.5</v>
       </c>
       <c r="G535" t="n">
-        <v>7.19498777389526</v>
+        <v>7.19498825073242</v>
       </c>
       <c r="H535" t="s">
         <v>8</v>
@@ -14409,7 +14409,7 @@
         <v>7</v>
       </c>
       <c r="G540" t="n">
-        <v>6.71532201766968</v>
+        <v>6.71532249450684</v>
       </c>
       <c r="H540" t="s">
         <v>8</v>
@@ -14565,7 +14565,7 @@
         <v>6.94999980926514</v>
       </c>
       <c r="G546" t="n">
-        <v>6.66735506057739</v>
+        <v>6.66735553741455</v>
       </c>
       <c r="H546" t="s">
         <v>8</v>
@@ -14643,7 +14643,7 @@
         <v>7</v>
       </c>
       <c r="G549" t="n">
-        <v>6.71532201766968</v>
+        <v>6.71532249450684</v>
       </c>
       <c r="H549" t="s">
         <v>8</v>
@@ -14669,7 +14669,7 @@
         <v>6.94999980926514</v>
       </c>
       <c r="G550" t="n">
-        <v>6.66735506057739</v>
+        <v>6.66735553741455</v>
       </c>
       <c r="H550" t="s">
         <v>8</v>
@@ -14903,7 +14903,7 @@
         <v>7.75</v>
       </c>
       <c r="G559" t="n">
-        <v>7.43482112884521</v>
+        <v>7.43482065200806</v>
       </c>
       <c r="H559" t="s">
         <v>8</v>
@@ -15033,7 +15033,7 @@
         <v>7.75</v>
       </c>
       <c r="G564" t="n">
-        <v>7.43482112884521</v>
+        <v>7.43482065200806</v>
       </c>
       <c r="H564" t="s">
         <v>8</v>
@@ -15137,7 +15137,7 @@
         <v>7.75</v>
       </c>
       <c r="G568" t="n">
-        <v>7.43482112884521</v>
+        <v>7.43482065200806</v>
       </c>
       <c r="H568" t="s">
         <v>8</v>
@@ -15293,7 +15293,7 @@
         <v>8.14999961853027</v>
       </c>
       <c r="G574" t="n">
-        <v>7.81855344772339</v>
+        <v>7.81855297088623</v>
       </c>
       <c r="H574" t="s">
         <v>8</v>
@@ -15423,7 +15423,7 @@
         <v>7.5</v>
       </c>
       <c r="G579" t="n">
-        <v>7.19498777389526</v>
+        <v>7.19498825073242</v>
       </c>
       <c r="H579" t="s">
         <v>8</v>
@@ -15501,7 +15501,7 @@
         <v>8.25</v>
       </c>
       <c r="G582" t="n">
-        <v>7.91448736190796</v>
+        <v>7.91448640823364</v>
       </c>
       <c r="H582" t="s">
         <v>8</v>
@@ -15527,7 +15527,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G583" t="n">
-        <v>7.86652040481567</v>
+        <v>7.86651945114136</v>
       </c>
       <c r="H583" t="s">
         <v>8</v>
@@ -15579,7 +15579,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G585" t="n">
-        <v>7.86652040481567</v>
+        <v>7.86651945114136</v>
       </c>
       <c r="H585" t="s">
         <v>8</v>
@@ -15605,7 +15605,7 @@
         <v>7.75</v>
       </c>
       <c r="G586" t="n">
-        <v>7.43482112884521</v>
+        <v>7.43482065200806</v>
       </c>
       <c r="H586" t="s">
         <v>8</v>
@@ -15631,7 +15631,7 @@
         <v>7.75</v>
       </c>
       <c r="G587" t="n">
-        <v>7.43482112884521</v>
+        <v>7.43482065200806</v>
       </c>
       <c r="H587" t="s">
         <v>8</v>
@@ -15657,7 +15657,7 @@
         <v>7.75</v>
       </c>
       <c r="G588" t="n">
-        <v>7.43482112884521</v>
+        <v>7.43482065200806</v>
       </c>
       <c r="H588" t="s">
         <v>8</v>
@@ -15709,7 +15709,7 @@
         <v>7.75</v>
       </c>
       <c r="G590" t="n">
-        <v>7.43482112884521</v>
+        <v>7.43482065200806</v>
       </c>
       <c r="H590" t="s">
         <v>8</v>
@@ -15865,7 +15865,7 @@
         <v>6.94999980926514</v>
       </c>
       <c r="G596" t="n">
-        <v>6.66735506057739</v>
+        <v>6.66735553741455</v>
       </c>
       <c r="H596" t="s">
         <v>8</v>
@@ -15891,7 +15891,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G597" t="n">
-        <v>6.90718841552734</v>
+        <v>6.90718793869019</v>
       </c>
       <c r="H597" t="s">
         <v>8</v>
@@ -15917,7 +15917,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G598" t="n">
-        <v>6.90718841552734</v>
+        <v>6.90718793869019</v>
       </c>
       <c r="H598" t="s">
         <v>8</v>
@@ -15995,7 +15995,7 @@
         <v>7.34999990463257</v>
       </c>
       <c r="G601" t="n">
-        <v>7.05108785629272</v>
+        <v>7.05108833312988</v>
       </c>
       <c r="H601" t="s">
         <v>8</v>
@@ -16021,7 +16021,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G602" t="n">
-        <v>6.90718841552734</v>
+        <v>6.90718793869019</v>
       </c>
       <c r="H602" t="s">
         <v>8</v>
@@ -16073,7 +16073,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G604" t="n">
-        <v>6.81125497817993</v>
+        <v>6.81125545501709</v>
       </c>
       <c r="H604" t="s">
         <v>8</v>
@@ -25826,6 +25826,32 @@
         <v>11.3000001907349</v>
       </c>
       <c r="H979" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="980">
+      <c r="A980" s="1" t="n">
+        <v>46310.2916666667</v>
+      </c>
+      <c r="B980" t="n">
+        <v>900</v>
+      </c>
+      <c r="C980" t="n">
+        <v>11.3000001907349</v>
+      </c>
+      <c r="D980" t="n">
+        <v>11</v>
+      </c>
+      <c r="E980" t="n">
+        <v>11.1000003814697</v>
+      </c>
+      <c r="F980" t="n">
+        <v>11.3000001907349</v>
+      </c>
+      <c r="G980" t="n">
+        <v>11.3000001907349</v>
+      </c>
+      <c r="H980" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/RDUE.MI.xlsx
+++ b/data/RDUE.MI.xlsx
@@ -447,7 +447,7 @@
         <v>12.0500001907349</v>
       </c>
       <c r="G3" t="n">
-        <v>11.2916135787964</v>
+        <v>11.2916126251221</v>
       </c>
       <c r="H3" t="s">
         <v>8</v>
@@ -473,7 +473,7 @@
         <v>12.0600004196167</v>
       </c>
       <c r="G4" t="n">
-        <v>11.3009834289551</v>
+        <v>11.3009843826294</v>
       </c>
       <c r="H4" t="s">
         <v>8</v>
@@ -499,7 +499,7 @@
         <v>12.1499996185303</v>
       </c>
       <c r="G5" t="n">
-        <v>11.3853197097778</v>
+        <v>11.3853187561035</v>
       </c>
       <c r="H5" t="s">
         <v>8</v>
@@ -525,7 +525,7 @@
         <v>12.0539999008179</v>
       </c>
       <c r="G6" t="n">
-        <v>11.2953605651855</v>
+        <v>11.2953615188599</v>
       </c>
       <c r="H6" t="s">
         <v>8</v>
@@ -551,7 +551,7 @@
         <v>12.0900001525879</v>
       </c>
       <c r="G7" t="n">
-        <v>11.3290967941284</v>
+        <v>11.3290948867798</v>
       </c>
       <c r="H7" t="s">
         <v>8</v>
@@ -603,7 +603,7 @@
         <v>11.8599996566772</v>
       </c>
       <c r="G9" t="n">
-        <v>11.1135702133179</v>
+        <v>11.1135711669922</v>
       </c>
       <c r="H9" t="s">
         <v>8</v>
@@ -655,7 +655,7 @@
         <v>11.9180002212524</v>
       </c>
       <c r="G11" t="n">
-        <v>11.1679210662842</v>
+        <v>11.1679201126099</v>
       </c>
       <c r="H11" t="s">
         <v>8</v>
@@ -681,7 +681,7 @@
         <v>11.9899997711182</v>
       </c>
       <c r="G12" t="n">
-        <v>11.2353897094727</v>
+        <v>11.2353887557983</v>
       </c>
       <c r="H12" t="s">
         <v>8</v>
@@ -759,7 +759,7 @@
         <v>11.6199998855591</v>
       </c>
       <c r="G15" t="n">
-        <v>10.8886756896973</v>
+        <v>10.8886747360229</v>
       </c>
       <c r="H15" t="s">
         <v>8</v>
@@ -889,7 +889,7 @@
         <v>11.5900001525879</v>
       </c>
       <c r="G20" t="n">
-        <v>10.8605632781982</v>
+        <v>10.8605642318726</v>
       </c>
       <c r="H20" t="s">
         <v>8</v>
@@ -915,7 +915,7 @@
         <v>11.3800001144409</v>
       </c>
       <c r="G21" t="n">
-        <v>10.6637802124023</v>
+        <v>10.6637811660767</v>
       </c>
       <c r="H21" t="s">
         <v>8</v>
@@ -941,7 +941,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G22" t="n">
-        <v>10.6825218200684</v>
+        <v>10.682520866394</v>
       </c>
       <c r="H22" t="s">
         <v>8</v>
@@ -993,7 +993,7 @@
         <v>11.2600002288818</v>
       </c>
       <c r="G24" t="n">
-        <v>10.5513324737549</v>
+        <v>10.5513334274292</v>
       </c>
       <c r="H24" t="s">
         <v>8</v>
@@ -1045,7 +1045,7 @@
         <v>11.25</v>
       </c>
       <c r="G26" t="n">
-        <v>10.5419626235962</v>
+        <v>10.5419616699219</v>
       </c>
       <c r="H26" t="s">
         <v>8</v>
@@ -1071,7 +1071,7 @@
         <v>11.9840002059937</v>
       </c>
       <c r="G27" t="n">
-        <v>11.2297677993774</v>
+        <v>11.2297668457031</v>
       </c>
       <c r="H27" t="s">
         <v>8</v>
@@ -1097,7 +1097,7 @@
         <v>12.0100002288818</v>
       </c>
       <c r="G28" t="n">
-        <v>11.2541303634644</v>
+        <v>11.2541313171387</v>
       </c>
       <c r="H28" t="s">
         <v>8</v>
@@ -1175,7 +1175,7 @@
         <v>11.9799995422363</v>
       </c>
       <c r="G31" t="n">
-        <v>11.2260189056396</v>
+        <v>11.2260179519653</v>
       </c>
       <c r="H31" t="s">
         <v>8</v>
@@ -1253,7 +1253,7 @@
         <v>11.75</v>
       </c>
       <c r="G34" t="n">
-        <v>11.0104942321777</v>
+        <v>11.0104932785034</v>
       </c>
       <c r="H34" t="s">
         <v>8</v>
@@ -1357,7 +1357,7 @@
         <v>11.996000289917</v>
       </c>
       <c r="G38" t="n">
-        <v>11.2410125732422</v>
+        <v>11.2410116195679</v>
       </c>
       <c r="H38" t="s">
         <v>8</v>
@@ -1409,7 +1409,7 @@
         <v>11.9799995422363</v>
       </c>
       <c r="G40" t="n">
-        <v>11.2260189056396</v>
+        <v>11.2260179519653</v>
       </c>
       <c r="H40" t="s">
         <v>8</v>
@@ -1435,7 +1435,7 @@
         <v>11.9799995422363</v>
       </c>
       <c r="G41" t="n">
-        <v>11.2260189056396</v>
+        <v>11.2260179519653</v>
       </c>
       <c r="H41" t="s">
         <v>8</v>
@@ -1669,7 +1669,7 @@
         <v>11.5500001907349</v>
       </c>
       <c r="G50" t="n">
-        <v>10.8230819702148</v>
+        <v>10.8230810165405</v>
       </c>
       <c r="H50" t="s">
         <v>8</v>
@@ -1695,7 +1695,7 @@
         <v>11.5500001907349</v>
       </c>
       <c r="G51" t="n">
-        <v>10.8230819702148</v>
+        <v>10.8230810165405</v>
       </c>
       <c r="H51" t="s">
         <v>8</v>
@@ -1851,7 +1851,7 @@
         <v>11.75</v>
       </c>
       <c r="G57" t="n">
-        <v>11.0104942321777</v>
+        <v>11.0104932785034</v>
       </c>
       <c r="H57" t="s">
         <v>8</v>
@@ -1877,7 +1877,7 @@
         <v>11.75</v>
       </c>
       <c r="G58" t="n">
-        <v>11.0104942321777</v>
+        <v>11.0104932785034</v>
       </c>
       <c r="H58" t="s">
         <v>8</v>
@@ -1903,7 +1903,7 @@
         <v>11.75</v>
       </c>
       <c r="G59" t="n">
-        <v>11.0104942321777</v>
+        <v>11.0104932785034</v>
       </c>
       <c r="H59" t="s">
         <v>8</v>
@@ -1929,7 +1929,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G60" t="n">
-        <v>10.8699340820312</v>
+        <v>10.8699350357056</v>
       </c>
       <c r="H60" t="s">
         <v>8</v>
@@ -2007,7 +2007,7 @@
         <v>11.4499998092651</v>
       </c>
       <c r="G63" t="n">
-        <v>10.7293758392334</v>
+        <v>10.7293748855591</v>
       </c>
       <c r="H63" t="s">
         <v>8</v>
@@ -2033,7 +2033,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G64" t="n">
-        <v>10.6825218200684</v>
+        <v>10.682520866394</v>
       </c>
       <c r="H64" t="s">
         <v>8</v>
@@ -2059,7 +2059,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G65" t="n">
-        <v>10.6825218200684</v>
+        <v>10.682520866394</v>
       </c>
       <c r="H65" t="s">
         <v>8</v>
@@ -2085,7 +2085,7 @@
         <v>11.5500001907349</v>
       </c>
       <c r="G66" t="n">
-        <v>10.8230819702148</v>
+        <v>10.8230810165405</v>
       </c>
       <c r="H66" t="s">
         <v>8</v>
@@ -2137,7 +2137,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G68" t="n">
-        <v>10.6825218200684</v>
+        <v>10.682520866394</v>
       </c>
       <c r="H68" t="s">
         <v>8</v>
@@ -2163,7 +2163,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G69" t="n">
-        <v>10.6825218200684</v>
+        <v>10.682520866394</v>
       </c>
       <c r="H69" t="s">
         <v>8</v>
@@ -2241,7 +2241,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G72" t="n">
-        <v>10.6825218200684</v>
+        <v>10.682520866394</v>
       </c>
       <c r="H72" t="s">
         <v>8</v>
@@ -2267,7 +2267,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G73" t="n">
-        <v>10.8699340820312</v>
+        <v>10.8699350357056</v>
       </c>
       <c r="H73" t="s">
         <v>8</v>
@@ -2293,7 +2293,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G74" t="n">
-        <v>10.8699340820312</v>
+        <v>10.8699350357056</v>
       </c>
       <c r="H74" t="s">
         <v>8</v>
@@ -2319,7 +2319,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G75" t="n">
-        <v>10.8699340820312</v>
+        <v>10.8699350357056</v>
       </c>
       <c r="H75" t="s">
         <v>8</v>
@@ -2345,7 +2345,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G76" t="n">
-        <v>10.8699340820312</v>
+        <v>10.8699350357056</v>
       </c>
       <c r="H76" t="s">
         <v>8</v>
@@ -2475,7 +2475,7 @@
         <v>11.5500001907349</v>
       </c>
       <c r="G81" t="n">
-        <v>10.8230819702148</v>
+        <v>10.8230810165405</v>
       </c>
       <c r="H81" t="s">
         <v>8</v>
@@ -2501,7 +2501,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G82" t="n">
-        <v>9.74545764923096</v>
+        <v>9.74545860290527</v>
       </c>
       <c r="H82" t="s">
         <v>8</v>
@@ -2527,7 +2527,7 @@
         <v>10.0500001907349</v>
       </c>
       <c r="G83" t="n">
-        <v>9.4174861907959</v>
+        <v>9.41748714447021</v>
       </c>
       <c r="H83" t="s">
         <v>8</v>
@@ -2553,7 +2553,7 @@
         <v>10.0500001907349</v>
       </c>
       <c r="G84" t="n">
-        <v>9.4174861907959</v>
+        <v>9.41748714447021</v>
       </c>
       <c r="H84" t="s">
         <v>8</v>
@@ -2657,7 +2657,7 @@
         <v>10.25</v>
       </c>
       <c r="G88" t="n">
-        <v>9.60489845275879</v>
+        <v>9.60489940643311</v>
       </c>
       <c r="H88" t="s">
         <v>8</v>
@@ -2683,7 +2683,7 @@
         <v>10.5500001907349</v>
       </c>
       <c r="G89" t="n">
-        <v>9.88601779937744</v>
+        <v>9.88601875305176</v>
       </c>
       <c r="H89" t="s">
         <v>8</v>
@@ -2709,7 +2709,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G90" t="n">
-        <v>9.55804538726807</v>
+        <v>9.55804634094238</v>
       </c>
       <c r="H90" t="s">
         <v>8</v>
@@ -2735,7 +2735,7 @@
         <v>10.0500001907349</v>
       </c>
       <c r="G91" t="n">
-        <v>9.4174861907959</v>
+        <v>9.41748714447021</v>
       </c>
       <c r="H91" t="s">
         <v>8</v>
@@ -2787,7 +2787,7 @@
         <v>9.72000026702881</v>
       </c>
       <c r="G93" t="n">
-        <v>9.10825634002686</v>
+        <v>9.10825538635254</v>
       </c>
       <c r="H93" t="s">
         <v>8</v>
@@ -2917,7 +2917,7 @@
         <v>9.53999996185303</v>
       </c>
       <c r="G98" t="n">
-        <v>8.93958377838135</v>
+        <v>8.93958282470703</v>
       </c>
       <c r="H98" t="s">
         <v>8</v>
@@ -2943,7 +2943,7 @@
         <v>9.34000015258789</v>
       </c>
       <c r="G99" t="n">
-        <v>8.75217151641846</v>
+        <v>8.75217056274414</v>
       </c>
       <c r="H99" t="s">
         <v>8</v>
@@ -2969,7 +2969,7 @@
         <v>9.14000034332275</v>
       </c>
       <c r="G100" t="n">
-        <v>8.56475925445557</v>
+        <v>8.56475830078125</v>
       </c>
       <c r="H100" t="s">
         <v>8</v>
@@ -3073,7 +3073,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G104" t="n">
-        <v>8.6209831237793</v>
+        <v>8.62098217010498</v>
       </c>
       <c r="H104" t="s">
         <v>8</v>
@@ -3125,7 +3125,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G106" t="n">
-        <v>8.6209831237793</v>
+        <v>8.62098217010498</v>
       </c>
       <c r="H106" t="s">
         <v>8</v>
@@ -3151,7 +3151,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G107" t="n">
-        <v>8.6209831237793</v>
+        <v>8.62098217010498</v>
       </c>
       <c r="H107" t="s">
         <v>8</v>
@@ -3203,7 +3203,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G109" t="n">
-        <v>8.80839538574219</v>
+        <v>8.80839443206787</v>
       </c>
       <c r="H109" t="s">
         <v>8</v>
@@ -3333,7 +3333,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G114" t="n">
-        <v>9.55804538726807</v>
+        <v>9.55804634094238</v>
       </c>
       <c r="H114" t="s">
         <v>8</v>
@@ -3385,7 +3385,7 @@
         <v>10.5500001907349</v>
       </c>
       <c r="G116" t="n">
-        <v>9.88601779937744</v>
+        <v>9.88601875305176</v>
       </c>
       <c r="H116" t="s">
         <v>8</v>
@@ -3411,7 +3411,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G117" t="n">
-        <v>9.74545764923096</v>
+        <v>9.74545860290527</v>
       </c>
       <c r="H117" t="s">
         <v>8</v>
@@ -3437,7 +3437,7 @@
         <v>10.5500001907349</v>
       </c>
       <c r="G118" t="n">
-        <v>9.88601779937744</v>
+        <v>9.88601875305176</v>
       </c>
       <c r="H118" t="s">
         <v>8</v>
@@ -3619,7 +3619,7 @@
         <v>9.57999992370605</v>
       </c>
       <c r="G125" t="n">
-        <v>8.97706604003906</v>
+        <v>8.97706699371338</v>
       </c>
       <c r="H125" t="s">
         <v>8</v>
@@ -3697,7 +3697,7 @@
         <v>9.88000011444092</v>
       </c>
       <c r="G128" t="n">
-        <v>9.25818538665771</v>
+        <v>9.25818634033203</v>
       </c>
       <c r="H128" t="s">
         <v>8</v>
@@ -3723,7 +3723,7 @@
         <v>9.84000015258789</v>
       </c>
       <c r="G129" t="n">
-        <v>9.220703125</v>
+        <v>9.22070217132568</v>
       </c>
       <c r="H129" t="s">
         <v>8</v>
@@ -3827,7 +3827,7 @@
         <v>9.97999954223633</v>
       </c>
       <c r="G133" t="n">
-        <v>9.35189056396484</v>
+        <v>9.35189247131348</v>
       </c>
       <c r="H133" t="s">
         <v>8</v>
@@ -3931,7 +3931,7 @@
         <v>10.5500001907349</v>
       </c>
       <c r="G137" t="n">
-        <v>9.88601779937744</v>
+        <v>9.88601875305176</v>
       </c>
       <c r="H137" t="s">
         <v>8</v>
@@ -4139,7 +4139,7 @@
         <v>9.5600004196167</v>
       </c>
       <c r="G145" t="n">
-        <v>8.95832633972168</v>
+        <v>8.95832538604736</v>
       </c>
       <c r="H145" t="s">
         <v>8</v>
@@ -4217,7 +4217,7 @@
         <v>9.31999969482422</v>
       </c>
       <c r="G148" t="n">
-        <v>8.73342990875244</v>
+        <v>8.73342895507812</v>
       </c>
       <c r="H148" t="s">
         <v>8</v>
@@ -4633,7 +4633,7 @@
         <v>9.97999954223633</v>
       </c>
       <c r="G164" t="n">
-        <v>9.35189056396484</v>
+        <v>9.35189247131348</v>
       </c>
       <c r="H164" t="s">
         <v>8</v>
@@ -4763,7 +4763,7 @@
         <v>9.15999984741211</v>
       </c>
       <c r="G169" t="n">
-        <v>8.58349990844727</v>
+        <v>8.58350086212158</v>
       </c>
       <c r="H169" t="s">
         <v>8</v>
@@ -4815,7 +4815,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G171" t="n">
-        <v>8.80839538574219</v>
+        <v>8.80839443206787</v>
       </c>
       <c r="H171" t="s">
         <v>8</v>
@@ -4841,7 +4841,7 @@
         <v>9.5600004196167</v>
       </c>
       <c r="G172" t="n">
-        <v>8.95832633972168</v>
+        <v>8.95832538604736</v>
       </c>
       <c r="H172" t="s">
         <v>8</v>
@@ -4893,7 +4893,7 @@
         <v>9.27999973297119</v>
       </c>
       <c r="G174" t="n">
-        <v>8.69594669342041</v>
+        <v>8.69594764709473</v>
       </c>
       <c r="H174" t="s">
         <v>8</v>
@@ -4945,7 +4945,7 @@
         <v>9.27999973297119</v>
       </c>
       <c r="G176" t="n">
-        <v>8.69594669342041</v>
+        <v>8.69594764709473</v>
       </c>
       <c r="H176" t="s">
         <v>8</v>
@@ -4971,7 +4971,7 @@
         <v>9.27999973297119</v>
       </c>
       <c r="G177" t="n">
-        <v>8.69594669342041</v>
+        <v>8.69594764709473</v>
       </c>
       <c r="H177" t="s">
         <v>8</v>
@@ -5179,7 +5179,7 @@
         <v>9.72000026702881</v>
       </c>
       <c r="G185" t="n">
-        <v>9.10825634002686</v>
+        <v>9.10825538635254</v>
       </c>
       <c r="H185" t="s">
         <v>8</v>
@@ -5205,7 +5205,7 @@
         <v>9.84000015258789</v>
       </c>
       <c r="G186" t="n">
-        <v>9.220703125</v>
+        <v>9.22070217132568</v>
       </c>
       <c r="H186" t="s">
         <v>8</v>
@@ -5231,7 +5231,7 @@
         <v>9.97999954223633</v>
       </c>
       <c r="G187" t="n">
-        <v>9.35189056396484</v>
+        <v>9.35189247131348</v>
       </c>
       <c r="H187" t="s">
         <v>8</v>
@@ -5257,7 +5257,7 @@
         <v>9.97999954223633</v>
       </c>
       <c r="G188" t="n">
-        <v>9.35189056396484</v>
+        <v>9.35189247131348</v>
       </c>
       <c r="H188" t="s">
         <v>8</v>
@@ -5283,7 +5283,7 @@
         <v>9.61999988555908</v>
       </c>
       <c r="G189" t="n">
-        <v>9.01454925537109</v>
+        <v>9.01454830169678</v>
       </c>
       <c r="H189" t="s">
         <v>8</v>
@@ -5439,7 +5439,7 @@
         <v>9.53999996185303</v>
       </c>
       <c r="G195" t="n">
-        <v>8.93958377838135</v>
+        <v>8.93958282470703</v>
       </c>
       <c r="H195" t="s">
         <v>8</v>
@@ -5465,7 +5465,7 @@
         <v>9.53999996185303</v>
       </c>
       <c r="G196" t="n">
-        <v>8.93958377838135</v>
+        <v>8.93958282470703</v>
       </c>
       <c r="H196" t="s">
         <v>8</v>
@@ -5491,7 +5491,7 @@
         <v>9.53999996185303</v>
       </c>
       <c r="G197" t="n">
-        <v>8.93958377838135</v>
+        <v>8.93958282470703</v>
       </c>
       <c r="H197" t="s">
         <v>8</v>
@@ -5595,7 +5595,7 @@
         <v>9</v>
       </c>
       <c r="G201" t="n">
-        <v>8.43356895446777</v>
+        <v>8.43356990814209</v>
       </c>
       <c r="H201" t="s">
         <v>8</v>
@@ -5621,7 +5621,7 @@
         <v>9</v>
       </c>
       <c r="G202" t="n">
-        <v>8.43356895446777</v>
+        <v>8.43356990814209</v>
       </c>
       <c r="H202" t="s">
         <v>8</v>
@@ -5647,7 +5647,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G203" t="n">
-        <v>8.24615669250488</v>
+        <v>8.2461576461792</v>
       </c>
       <c r="H203" t="s">
         <v>8</v>
@@ -5673,7 +5673,7 @@
         <v>9.0600004196167</v>
       </c>
       <c r="G204" t="n">
-        <v>8.48979377746582</v>
+        <v>8.48979473114014</v>
       </c>
       <c r="H204" t="s">
         <v>8</v>
@@ -5725,7 +5725,7 @@
         <v>9</v>
       </c>
       <c r="G206" t="n">
-        <v>8.43356895446777</v>
+        <v>8.43356990814209</v>
       </c>
       <c r="H206" t="s">
         <v>8</v>
@@ -5829,7 +5829,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G210" t="n">
-        <v>8.6209831237793</v>
+        <v>8.62098217010498</v>
       </c>
       <c r="H210" t="s">
         <v>8</v>
@@ -5855,7 +5855,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G211" t="n">
-        <v>8.6209831237793</v>
+        <v>8.62098217010498</v>
       </c>
       <c r="H211" t="s">
         <v>8</v>
@@ -6479,7 +6479,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G235" t="n">
-        <v>8.24615669250488</v>
+        <v>8.2461576461792</v>
       </c>
       <c r="H235" t="s">
         <v>8</v>
@@ -6687,7 +6687,7 @@
         <v>8.15999984741211</v>
       </c>
       <c r="G243" t="n">
-        <v>7.64643669128418</v>
+        <v>7.64643621444702</v>
       </c>
       <c r="H243" t="s">
         <v>8</v>
@@ -6713,7 +6713,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G244" t="n">
-        <v>7.59021282196045</v>
+        <v>7.59021329879761</v>
       </c>
       <c r="H244" t="s">
         <v>8</v>
@@ -6843,7 +6843,7 @@
         <v>8.03999996185303</v>
       </c>
       <c r="G249" t="n">
-        <v>7.53398895263672</v>
+        <v>7.53398942947388</v>
       </c>
       <c r="H249" t="s">
         <v>8</v>
@@ -6895,7 +6895,7 @@
         <v>8.23999977111816</v>
       </c>
       <c r="G251" t="n">
-        <v>7.72140121459961</v>
+        <v>7.72140073776245</v>
       </c>
       <c r="H251" t="s">
         <v>8</v>
@@ -6921,7 +6921,7 @@
         <v>8.26000022888184</v>
       </c>
       <c r="G252" t="n">
-        <v>7.74014282226562</v>
+        <v>7.74014377593994</v>
       </c>
       <c r="H252" t="s">
         <v>8</v>
@@ -6973,7 +6973,7 @@
         <v>8.03999996185303</v>
       </c>
       <c r="G254" t="n">
-        <v>7.53398895263672</v>
+        <v>7.53398942947388</v>
       </c>
       <c r="H254" t="s">
         <v>8</v>
@@ -6999,7 +6999,7 @@
         <v>7.61999988555908</v>
       </c>
       <c r="G255" t="n">
-        <v>7.14042234420776</v>
+        <v>7.14042186737061</v>
       </c>
       <c r="H255" t="s">
         <v>8</v>
@@ -7025,7 +7025,7 @@
         <v>7.71999979019165</v>
       </c>
       <c r="G256" t="n">
-        <v>7.23412847518921</v>
+        <v>7.23412799835205</v>
       </c>
       <c r="H256" t="s">
         <v>8</v>
@@ -7051,7 +7051,7 @@
         <v>7.55999994277954</v>
       </c>
       <c r="G257" t="n">
-        <v>7.08419895172119</v>
+        <v>7.08419847488403</v>
       </c>
       <c r="H257" t="s">
         <v>8</v>
@@ -7077,7 +7077,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G258" t="n">
-        <v>7.12168073654175</v>
+        <v>7.12168121337891</v>
       </c>
       <c r="H258" t="s">
         <v>8</v>
@@ -7129,7 +7129,7 @@
         <v>7.67999982833862</v>
       </c>
       <c r="G260" t="n">
-        <v>7.19664573669434</v>
+        <v>7.19664621353149</v>
       </c>
       <c r="H260" t="s">
         <v>8</v>
@@ -7155,7 +7155,7 @@
         <v>7.84000015258789</v>
       </c>
       <c r="G261" t="n">
-        <v>7.34657621383667</v>
+        <v>7.34657669067383</v>
       </c>
       <c r="H261" t="s">
         <v>8</v>
@@ -7207,7 +7207,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G263" t="n">
-        <v>7.4028000831604</v>
+        <v>7.40280055999756</v>
       </c>
       <c r="H263" t="s">
         <v>8</v>
@@ -7259,7 +7259,7 @@
         <v>7.48000001907349</v>
       </c>
       <c r="G265" t="n">
-        <v>7.00923347473145</v>
+        <v>7.0092339515686</v>
       </c>
       <c r="H265" t="s">
         <v>8</v>
@@ -7285,7 +7285,7 @@
         <v>7.61999988555908</v>
       </c>
       <c r="G266" t="n">
-        <v>7.14042234420776</v>
+        <v>7.14042186737061</v>
       </c>
       <c r="H266" t="s">
         <v>8</v>
@@ -7337,7 +7337,7 @@
         <v>7.48000001907349</v>
       </c>
       <c r="G268" t="n">
-        <v>7.00923347473145</v>
+        <v>7.0092339515686</v>
       </c>
       <c r="H268" t="s">
         <v>8</v>
@@ -7389,7 +7389,7 @@
         <v>7.71999979019165</v>
       </c>
       <c r="G270" t="n">
-        <v>7.23412847518921</v>
+        <v>7.23412799835205</v>
       </c>
       <c r="H270" t="s">
         <v>8</v>
@@ -7415,7 +7415,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G271" t="n">
-        <v>7.7776255607605</v>
+        <v>7.77762603759766</v>
       </c>
       <c r="H271" t="s">
         <v>8</v>
@@ -7519,7 +7519,7 @@
         <v>9.14000034332275</v>
       </c>
       <c r="G275" t="n">
-        <v>8.56475925445557</v>
+        <v>8.56475830078125</v>
       </c>
       <c r="H275" t="s">
         <v>8</v>
@@ -7571,7 +7571,7 @@
         <v>9.14000034332275</v>
       </c>
       <c r="G277" t="n">
-        <v>8.56475925445557</v>
+        <v>8.56475830078125</v>
       </c>
       <c r="H277" t="s">
         <v>8</v>
@@ -7597,7 +7597,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G278" t="n">
-        <v>8.6209831237793</v>
+        <v>8.62098217010498</v>
       </c>
       <c r="H278" t="s">
         <v>8</v>
@@ -7701,7 +7701,7 @@
         <v>8.92000007629395</v>
       </c>
       <c r="G282" t="n">
-        <v>8.35860538482666</v>
+        <v>8.35860443115234</v>
       </c>
       <c r="H282" t="s">
         <v>8</v>
@@ -7753,7 +7753,7 @@
         <v>8.81999969482422</v>
       </c>
       <c r="G284" t="n">
-        <v>8.2648983001709</v>
+        <v>8.26489734649658</v>
       </c>
       <c r="H284" t="s">
         <v>8</v>
@@ -7831,7 +7831,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G287" t="n">
-        <v>8.24615669250488</v>
+        <v>8.2461576461792</v>
       </c>
       <c r="H287" t="s">
         <v>8</v>
@@ -8013,7 +8013,7 @@
         <v>9</v>
       </c>
       <c r="G294" t="n">
-        <v>8.43356895446777</v>
+        <v>8.43356990814209</v>
       </c>
       <c r="H294" t="s">
         <v>8</v>
@@ -8039,7 +8039,7 @@
         <v>9.14000034332275</v>
       </c>
       <c r="G295" t="n">
-        <v>8.56475925445557</v>
+        <v>8.56475830078125</v>
       </c>
       <c r="H295" t="s">
         <v>8</v>
@@ -8065,7 +8065,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G296" t="n">
-        <v>8.6209831237793</v>
+        <v>8.62098217010498</v>
       </c>
       <c r="H296" t="s">
         <v>8</v>
@@ -8091,7 +8091,7 @@
         <v>9.14000034332275</v>
       </c>
       <c r="G297" t="n">
-        <v>8.56475925445557</v>
+        <v>8.56475830078125</v>
       </c>
       <c r="H297" t="s">
         <v>8</v>
@@ -8117,7 +8117,7 @@
         <v>9.14000034332275</v>
       </c>
       <c r="G298" t="n">
-        <v>8.56475925445557</v>
+        <v>8.56475830078125</v>
       </c>
       <c r="H298" t="s">
         <v>8</v>
@@ -8221,7 +8221,7 @@
         <v>9</v>
       </c>
       <c r="G302" t="n">
-        <v>8.43356895446777</v>
+        <v>8.43356990814209</v>
       </c>
       <c r="H302" t="s">
         <v>8</v>
@@ -8247,7 +8247,7 @@
         <v>9</v>
       </c>
       <c r="G303" t="n">
-        <v>8.43356895446777</v>
+        <v>8.43356990814209</v>
       </c>
       <c r="H303" t="s">
         <v>8</v>
@@ -8299,7 +8299,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G305" t="n">
-        <v>8.24615669250488</v>
+        <v>8.2461576461792</v>
       </c>
       <c r="H305" t="s">
         <v>8</v>
@@ -8325,7 +8325,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G306" t="n">
-        <v>8.24615669250488</v>
+        <v>8.2461576461792</v>
       </c>
       <c r="H306" t="s">
         <v>8</v>
@@ -8351,7 +8351,7 @@
         <v>8.64000034332275</v>
       </c>
       <c r="G307" t="n">
-        <v>8.09622669219971</v>
+        <v>8.09622764587402</v>
       </c>
       <c r="H307" t="s">
         <v>8</v>
@@ -8429,7 +8429,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G310" t="n">
-        <v>8.24615669250488</v>
+        <v>8.2461576461792</v>
       </c>
       <c r="H310" t="s">
         <v>8</v>
@@ -8455,7 +8455,7 @@
         <v>8.47999954223633</v>
       </c>
       <c r="G311" t="n">
-        <v>7.94629621505737</v>
+        <v>7.94629669189453</v>
       </c>
       <c r="H311" t="s">
         <v>8</v>
@@ -8481,7 +8481,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G312" t="n">
-        <v>7.83384895324707</v>
+        <v>7.83384990692139</v>
       </c>
       <c r="H312" t="s">
         <v>8</v>
@@ -8507,7 +8507,7 @@
         <v>8.61999988555908</v>
       </c>
       <c r="G313" t="n">
-        <v>8.07748603820801</v>
+        <v>8.07748508453369</v>
       </c>
       <c r="H313" t="s">
         <v>8</v>
@@ -8533,7 +8533,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G314" t="n">
-        <v>8.24615669250488</v>
+        <v>8.2461576461792</v>
       </c>
       <c r="H314" t="s">
         <v>8</v>
@@ -8585,7 +8585,7 @@
         <v>8.47999954223633</v>
       </c>
       <c r="G316" t="n">
-        <v>7.94629621505737</v>
+        <v>7.94629669189453</v>
       </c>
       <c r="H316" t="s">
         <v>8</v>
@@ -8637,7 +8637,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G318" t="n">
-        <v>8.24615669250488</v>
+        <v>8.2461576461792</v>
       </c>
       <c r="H318" t="s">
         <v>8</v>
@@ -8663,7 +8663,7 @@
         <v>8.47999954223633</v>
       </c>
       <c r="G319" t="n">
-        <v>7.94629621505737</v>
+        <v>7.94629669189453</v>
       </c>
       <c r="H319" t="s">
         <v>8</v>
@@ -8689,7 +8689,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G320" t="n">
-        <v>7.87133121490479</v>
+        <v>7.87133169174194</v>
       </c>
       <c r="H320" t="s">
         <v>8</v>
@@ -8741,7 +8741,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G322" t="n">
-        <v>7.7776255607605</v>
+        <v>7.77762603759766</v>
       </c>
       <c r="H322" t="s">
         <v>8</v>
@@ -8767,7 +8767,7 @@
         <v>8.27999973297119</v>
       </c>
       <c r="G323" t="n">
-        <v>7.75888442993164</v>
+        <v>7.75888395309448</v>
       </c>
       <c r="H323" t="s">
         <v>8</v>
@@ -8793,7 +8793,7 @@
         <v>8.27999973297119</v>
       </c>
       <c r="G324" t="n">
-        <v>7.75888442993164</v>
+        <v>7.75888395309448</v>
       </c>
       <c r="H324" t="s">
         <v>8</v>
@@ -8819,7 +8819,7 @@
         <v>8.27999973297119</v>
       </c>
       <c r="G325" t="n">
-        <v>7.75888442993164</v>
+        <v>7.75888395309448</v>
       </c>
       <c r="H325" t="s">
         <v>8</v>
@@ -8845,7 +8845,7 @@
         <v>8.31999969482422</v>
       </c>
       <c r="G326" t="n">
-        <v>7.79636669158936</v>
+        <v>7.7963662147522</v>
       </c>
       <c r="H326" t="s">
         <v>8</v>
@@ -8871,7 +8871,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G327" t="n">
-        <v>7.7776255607605</v>
+        <v>7.77762603759766</v>
       </c>
       <c r="H327" t="s">
         <v>8</v>
@@ -8897,7 +8897,7 @@
         <v>8.34000015258789</v>
       </c>
       <c r="G328" t="n">
-        <v>7.81510829925537</v>
+        <v>7.81510782241821</v>
       </c>
       <c r="H328" t="s">
         <v>8</v>
@@ -8923,7 +8923,7 @@
         <v>8.34000015258789</v>
       </c>
       <c r="G329" t="n">
-        <v>7.81510829925537</v>
+        <v>7.81510782241821</v>
       </c>
       <c r="H329" t="s">
         <v>8</v>
@@ -8949,7 +8949,7 @@
         <v>8.34000015258789</v>
       </c>
       <c r="G330" t="n">
-        <v>7.81510829925537</v>
+        <v>7.81510782241821</v>
       </c>
       <c r="H330" t="s">
         <v>8</v>
@@ -8975,7 +8975,7 @@
         <v>8.34000015258789</v>
       </c>
       <c r="G331" t="n">
-        <v>7.81510829925537</v>
+        <v>7.81510782241821</v>
       </c>
       <c r="H331" t="s">
         <v>8</v>
@@ -9001,7 +9001,7 @@
         <v>8.34000015258789</v>
       </c>
       <c r="G332" t="n">
-        <v>7.81510829925537</v>
+        <v>7.81510782241821</v>
       </c>
       <c r="H332" t="s">
         <v>8</v>
@@ -9105,7 +9105,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G336" t="n">
-        <v>8.24615669250488</v>
+        <v>8.2461576461792</v>
       </c>
       <c r="H336" t="s">
         <v>8</v>
@@ -9131,7 +9131,7 @@
         <v>9</v>
       </c>
       <c r="G337" t="n">
-        <v>8.43356895446777</v>
+        <v>8.43356990814209</v>
       </c>
       <c r="H337" t="s">
         <v>8</v>
@@ -9157,7 +9157,7 @@
         <v>9</v>
       </c>
       <c r="G338" t="n">
-        <v>8.43356895446777</v>
+        <v>8.43356990814209</v>
       </c>
       <c r="H338" t="s">
         <v>8</v>
@@ -9183,7 +9183,7 @@
         <v>9</v>
       </c>
       <c r="G339" t="n">
-        <v>8.43356895446777</v>
+        <v>8.43356990814209</v>
       </c>
       <c r="H339" t="s">
         <v>8</v>
@@ -9209,7 +9209,7 @@
         <v>9</v>
       </c>
       <c r="G340" t="n">
-        <v>8.43356895446777</v>
+        <v>8.43356990814209</v>
       </c>
       <c r="H340" t="s">
         <v>8</v>
@@ -9261,7 +9261,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G342" t="n">
-        <v>8.80839538574219</v>
+        <v>8.80839443206787</v>
       </c>
       <c r="H342" t="s">
         <v>8</v>
@@ -9703,7 +9703,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G359" t="n">
-        <v>9.04265975952148</v>
+        <v>9.0426607131958</v>
       </c>
       <c r="H359" t="s">
         <v>8</v>
@@ -9729,7 +9729,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G360" t="n">
-        <v>9.04265975952148</v>
+        <v>9.0426607131958</v>
       </c>
       <c r="H360" t="s">
         <v>8</v>
@@ -9755,7 +9755,7 @@
         <v>9.75</v>
       </c>
       <c r="G361" t="n">
-        <v>9.13636684417725</v>
+        <v>9.13636779785156</v>
       </c>
       <c r="H361" t="s">
         <v>8</v>
@@ -9807,7 +9807,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G363" t="n">
-        <v>9.04265975952148</v>
+        <v>9.0426607131958</v>
       </c>
       <c r="H363" t="s">
         <v>8</v>
@@ -9833,7 +9833,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G364" t="n">
-        <v>9.04265975952148</v>
+        <v>9.0426607131958</v>
       </c>
       <c r="H364" t="s">
         <v>8</v>
@@ -9859,7 +9859,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G365" t="n">
-        <v>9.04265975952148</v>
+        <v>9.0426607131958</v>
       </c>
       <c r="H365" t="s">
         <v>8</v>
@@ -10015,7 +10015,7 @@
         <v>9.75</v>
       </c>
       <c r="G371" t="n">
-        <v>9.13636684417725</v>
+        <v>9.13636779785156</v>
       </c>
       <c r="H371" t="s">
         <v>8</v>
@@ -10041,7 +10041,7 @@
         <v>9.75</v>
       </c>
       <c r="G372" t="n">
-        <v>9.13636684417725</v>
+        <v>9.13636779785156</v>
       </c>
       <c r="H372" t="s">
         <v>8</v>
@@ -10093,7 +10093,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G374" t="n">
-        <v>9.04265975952148</v>
+        <v>9.0426607131958</v>
       </c>
       <c r="H374" t="s">
         <v>8</v>
@@ -10119,7 +10119,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G375" t="n">
-        <v>9.30551719665527</v>
+        <v>9.30551815032959</v>
       </c>
       <c r="H375" t="s">
         <v>8</v>
@@ -10145,7 +10145,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G376" t="n">
-        <v>9.25755023956299</v>
+        <v>9.2575511932373</v>
       </c>
       <c r="H376" t="s">
         <v>8</v>
@@ -10197,7 +10197,7 @@
         <v>10</v>
       </c>
       <c r="G378" t="n">
-        <v>9.59331703186035</v>
+        <v>9.59331798553467</v>
       </c>
       <c r="H378" t="s">
         <v>8</v>
@@ -10535,7 +10535,7 @@
         <v>10</v>
       </c>
       <c r="G391" t="n">
-        <v>9.59331703186035</v>
+        <v>9.59331798553467</v>
       </c>
       <c r="H391" t="s">
         <v>8</v>
@@ -10665,7 +10665,7 @@
         <v>10</v>
       </c>
       <c r="G396" t="n">
-        <v>9.59331703186035</v>
+        <v>9.59331798553467</v>
       </c>
       <c r="H396" t="s">
         <v>8</v>
@@ -10691,7 +10691,7 @@
         <v>10</v>
       </c>
       <c r="G397" t="n">
-        <v>9.59331703186035</v>
+        <v>9.59331798553467</v>
       </c>
       <c r="H397" t="s">
         <v>8</v>
@@ -10743,7 +10743,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G399" t="n">
-        <v>9.30551719665527</v>
+        <v>9.30551815032959</v>
       </c>
       <c r="H399" t="s">
         <v>8</v>
@@ -10795,7 +10795,7 @@
         <v>9.35000038146973</v>
       </c>
       <c r="G401" t="n">
-        <v>8.96975135803223</v>
+        <v>8.96975231170654</v>
       </c>
       <c r="H401" t="s">
         <v>8</v>
@@ -11055,7 +11055,7 @@
         <v>10</v>
       </c>
       <c r="G411" t="n">
-        <v>9.59331703186035</v>
+        <v>9.59331798553467</v>
       </c>
       <c r="H411" t="s">
         <v>8</v>
@@ -11185,7 +11185,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G416" t="n">
-        <v>9.25755023956299</v>
+        <v>9.2575511932373</v>
       </c>
       <c r="H416" t="s">
         <v>8</v>
@@ -11211,7 +11211,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G417" t="n">
-        <v>9.25755023956299</v>
+        <v>9.2575511932373</v>
       </c>
       <c r="H417" t="s">
         <v>8</v>
@@ -11237,7 +11237,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G418" t="n">
-        <v>9.25755023956299</v>
+        <v>9.2575511932373</v>
       </c>
       <c r="H418" t="s">
         <v>8</v>
@@ -11263,7 +11263,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G419" t="n">
-        <v>9.30551719665527</v>
+        <v>9.30551815032959</v>
       </c>
       <c r="H419" t="s">
         <v>8</v>
@@ -11315,7 +11315,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G421" t="n">
-        <v>9.0177173614502</v>
+        <v>9.01771831512451</v>
       </c>
       <c r="H421" t="s">
         <v>8</v>
@@ -11367,7 +11367,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G423" t="n">
-        <v>9.25755023956299</v>
+        <v>9.2575511932373</v>
       </c>
       <c r="H423" t="s">
         <v>8</v>
@@ -11393,7 +11393,7 @@
         <v>9.35000038146973</v>
       </c>
       <c r="G424" t="n">
-        <v>8.96975135803223</v>
+        <v>8.96975231170654</v>
       </c>
       <c r="H424" t="s">
         <v>8</v>
@@ -11419,7 +11419,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G425" t="n">
-        <v>8.53805255889893</v>
+        <v>8.53805160522461</v>
       </c>
       <c r="H425" t="s">
         <v>8</v>
@@ -11523,7 +11523,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G429" t="n">
-        <v>9.25755023956299</v>
+        <v>9.2575511932373</v>
       </c>
       <c r="H429" t="s">
         <v>8</v>
@@ -11549,7 +11549,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G430" t="n">
-        <v>9.25755023956299</v>
+        <v>9.2575511932373</v>
       </c>
       <c r="H430" t="s">
         <v>8</v>
@@ -11601,7 +11601,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G432" t="n">
-        <v>9.0177173614502</v>
+        <v>9.01771831512451</v>
       </c>
       <c r="H432" t="s">
         <v>8</v>
@@ -11627,7 +11627,7 @@
         <v>9.35000038146973</v>
       </c>
       <c r="G433" t="n">
-        <v>8.96975135803223</v>
+        <v>8.96975231170654</v>
       </c>
       <c r="H433" t="s">
         <v>8</v>
@@ -11679,7 +11679,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G435" t="n">
-        <v>9.30551719665527</v>
+        <v>9.30551815032959</v>
       </c>
       <c r="H435" t="s">
         <v>8</v>
@@ -11705,7 +11705,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G436" t="n">
-        <v>9.25755023956299</v>
+        <v>9.2575511932373</v>
       </c>
       <c r="H436" t="s">
         <v>8</v>
@@ -11757,7 +11757,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G438" t="n">
-        <v>9.0177173614502</v>
+        <v>9.01771831512451</v>
       </c>
       <c r="H438" t="s">
         <v>8</v>
@@ -11783,7 +11783,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G439" t="n">
-        <v>9.30551719665527</v>
+        <v>9.30551815032959</v>
       </c>
       <c r="H439" t="s">
         <v>8</v>
@@ -11809,7 +11809,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G440" t="n">
-        <v>9.30551719665527</v>
+        <v>9.30551815032959</v>
       </c>
       <c r="H440" t="s">
         <v>8</v>
@@ -11835,7 +11835,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G441" t="n">
-        <v>9.30551719665527</v>
+        <v>9.30551815032959</v>
       </c>
       <c r="H441" t="s">
         <v>8</v>
@@ -11861,7 +11861,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G442" t="n">
-        <v>9.30551719665527</v>
+        <v>9.30551815032959</v>
       </c>
       <c r="H442" t="s">
         <v>8</v>
@@ -11939,7 +11939,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G445" t="n">
-        <v>9.0177173614502</v>
+        <v>9.01771831512451</v>
       </c>
       <c r="H445" t="s">
         <v>8</v>
@@ -11965,7 +11965,7 @@
         <v>9.44999980926514</v>
       </c>
       <c r="G446" t="n">
-        <v>9.06568431854248</v>
+        <v>9.0656852722168</v>
       </c>
       <c r="H446" t="s">
         <v>8</v>
@@ -11991,7 +11991,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G447" t="n">
-        <v>9.0177173614502</v>
+        <v>9.01771831512451</v>
       </c>
       <c r="H447" t="s">
         <v>8</v>
@@ -12017,7 +12017,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G448" t="n">
-        <v>8.825852394104</v>
+        <v>8.82585144042969</v>
       </c>
       <c r="H448" t="s">
         <v>8</v>
@@ -12173,7 +12173,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G454" t="n">
-        <v>8.825852394104</v>
+        <v>8.82585144042969</v>
       </c>
       <c r="H454" t="s">
         <v>8</v>
@@ -12199,7 +12199,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G455" t="n">
-        <v>8.825852394104</v>
+        <v>8.82585144042969</v>
       </c>
       <c r="H455" t="s">
         <v>8</v>
@@ -12225,7 +12225,7 @@
         <v>9.35000038146973</v>
       </c>
       <c r="G456" t="n">
-        <v>8.96975135803223</v>
+        <v>8.96975231170654</v>
       </c>
       <c r="H456" t="s">
         <v>8</v>
@@ -12407,7 +12407,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G463" t="n">
-        <v>8.53805255889893</v>
+        <v>8.53805160522461</v>
       </c>
       <c r="H463" t="s">
         <v>8</v>
@@ -12641,7 +12641,7 @@
         <v>7.75</v>
       </c>
       <c r="G472" t="n">
-        <v>7.43482065200806</v>
+        <v>7.43482112884521</v>
       </c>
       <c r="H472" t="s">
         <v>8</v>
@@ -12849,7 +12849,7 @@
         <v>7.5</v>
       </c>
       <c r="G480" t="n">
-        <v>7.19498825073242</v>
+        <v>7.19498777389526</v>
       </c>
       <c r="H480" t="s">
         <v>8</v>
@@ -12875,7 +12875,7 @@
         <v>7.34999990463257</v>
       </c>
       <c r="G481" t="n">
-        <v>7.05108833312988</v>
+        <v>7.05108785629272</v>
       </c>
       <c r="H481" t="s">
         <v>8</v>
@@ -12901,7 +12901,7 @@
         <v>7.34999990463257</v>
       </c>
       <c r="G482" t="n">
-        <v>7.05108833312988</v>
+        <v>7.05108785629272</v>
       </c>
       <c r="H482" t="s">
         <v>8</v>
@@ -12979,7 +12979,7 @@
         <v>7</v>
       </c>
       <c r="G485" t="n">
-        <v>6.71532249450684</v>
+        <v>6.71532201766968</v>
       </c>
       <c r="H485" t="s">
         <v>8</v>
@@ -13239,7 +13239,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G495" t="n">
-        <v>6.04378986358643</v>
+        <v>6.04379034042358</v>
       </c>
       <c r="H495" t="s">
         <v>8</v>
@@ -13499,7 +13499,7 @@
         <v>7</v>
       </c>
       <c r="G505" t="n">
-        <v>6.71532249450684</v>
+        <v>6.71532201766968</v>
       </c>
       <c r="H505" t="s">
         <v>8</v>
@@ -13551,7 +13551,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G507" t="n">
-        <v>6.81125545501709</v>
+        <v>6.81125497817993</v>
       </c>
       <c r="H507" t="s">
         <v>8</v>
@@ -13629,7 +13629,7 @@
         <v>7.75</v>
       </c>
       <c r="G510" t="n">
-        <v>7.43482065200806</v>
+        <v>7.43482112884521</v>
       </c>
       <c r="H510" t="s">
         <v>8</v>
@@ -14097,7 +14097,7 @@
         <v>7.34999990463257</v>
       </c>
       <c r="G528" t="n">
-        <v>7.05108833312988</v>
+        <v>7.05108785629272</v>
       </c>
       <c r="H528" t="s">
         <v>8</v>
@@ -14279,7 +14279,7 @@
         <v>7.5</v>
       </c>
       <c r="G535" t="n">
-        <v>7.19498825073242</v>
+        <v>7.19498777389526</v>
       </c>
       <c r="H535" t="s">
         <v>8</v>
@@ -14409,7 +14409,7 @@
         <v>7</v>
       </c>
       <c r="G540" t="n">
-        <v>6.71532249450684</v>
+        <v>6.71532201766968</v>
       </c>
       <c r="H540" t="s">
         <v>8</v>
@@ -14565,7 +14565,7 @@
         <v>6.94999980926514</v>
       </c>
       <c r="G546" t="n">
-        <v>6.66735553741455</v>
+        <v>6.66735506057739</v>
       </c>
       <c r="H546" t="s">
         <v>8</v>
@@ -14643,7 +14643,7 @@
         <v>7</v>
       </c>
       <c r="G549" t="n">
-        <v>6.71532249450684</v>
+        <v>6.71532201766968</v>
       </c>
       <c r="H549" t="s">
         <v>8</v>
@@ -14669,7 +14669,7 @@
         <v>6.94999980926514</v>
       </c>
       <c r="G550" t="n">
-        <v>6.66735553741455</v>
+        <v>6.66735506057739</v>
       </c>
       <c r="H550" t="s">
         <v>8</v>
@@ -14903,7 +14903,7 @@
         <v>7.75</v>
       </c>
       <c r="G559" t="n">
-        <v>7.43482065200806</v>
+        <v>7.43482112884521</v>
       </c>
       <c r="H559" t="s">
         <v>8</v>
@@ -15033,7 +15033,7 @@
         <v>7.75</v>
       </c>
       <c r="G564" t="n">
-        <v>7.43482065200806</v>
+        <v>7.43482112884521</v>
       </c>
       <c r="H564" t="s">
         <v>8</v>
@@ -15137,7 +15137,7 @@
         <v>7.75</v>
       </c>
       <c r="G568" t="n">
-        <v>7.43482065200806</v>
+        <v>7.43482112884521</v>
       </c>
       <c r="H568" t="s">
         <v>8</v>
@@ -15293,7 +15293,7 @@
         <v>8.14999961853027</v>
       </c>
       <c r="G574" t="n">
-        <v>7.81855297088623</v>
+        <v>7.81855344772339</v>
       </c>
       <c r="H574" t="s">
         <v>8</v>
@@ -15423,7 +15423,7 @@
         <v>7.5</v>
       </c>
       <c r="G579" t="n">
-        <v>7.19498825073242</v>
+        <v>7.19498777389526</v>
       </c>
       <c r="H579" t="s">
         <v>8</v>
@@ -15501,7 +15501,7 @@
         <v>8.25</v>
       </c>
       <c r="G582" t="n">
-        <v>7.91448640823364</v>
+        <v>7.91448736190796</v>
       </c>
       <c r="H582" t="s">
         <v>8</v>
@@ -15527,7 +15527,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G583" t="n">
-        <v>7.86651945114136</v>
+        <v>7.86652040481567</v>
       </c>
       <c r="H583" t="s">
         <v>8</v>
@@ -15579,7 +15579,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G585" t="n">
-        <v>7.86651945114136</v>
+        <v>7.86652040481567</v>
       </c>
       <c r="H585" t="s">
         <v>8</v>
@@ -15605,7 +15605,7 @@
         <v>7.75</v>
       </c>
       <c r="G586" t="n">
-        <v>7.43482065200806</v>
+        <v>7.43482112884521</v>
       </c>
       <c r="H586" t="s">
         <v>8</v>
@@ -15631,7 +15631,7 @@
         <v>7.75</v>
       </c>
       <c r="G587" t="n">
-        <v>7.43482065200806</v>
+        <v>7.43482112884521</v>
       </c>
       <c r="H587" t="s">
         <v>8</v>
@@ -15657,7 +15657,7 @@
         <v>7.75</v>
       </c>
       <c r="G588" t="n">
-        <v>7.43482065200806</v>
+        <v>7.43482112884521</v>
       </c>
       <c r="H588" t="s">
         <v>8</v>
@@ -15709,7 +15709,7 @@
         <v>7.75</v>
       </c>
       <c r="G590" t="n">
-        <v>7.43482065200806</v>
+        <v>7.43482112884521</v>
       </c>
       <c r="H590" t="s">
         <v>8</v>
@@ -15865,7 +15865,7 @@
         <v>6.94999980926514</v>
       </c>
       <c r="G596" t="n">
-        <v>6.66735553741455</v>
+        <v>6.66735506057739</v>
       </c>
       <c r="H596" t="s">
         <v>8</v>
@@ -15891,7 +15891,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G597" t="n">
-        <v>6.90718793869019</v>
+        <v>6.90718841552734</v>
       </c>
       <c r="H597" t="s">
         <v>8</v>
@@ -15917,7 +15917,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G598" t="n">
-        <v>6.90718793869019</v>
+        <v>6.90718841552734</v>
       </c>
       <c r="H598" t="s">
         <v>8</v>
@@ -15995,7 +15995,7 @@
         <v>7.34999990463257</v>
       </c>
       <c r="G601" t="n">
-        <v>7.05108833312988</v>
+        <v>7.05108785629272</v>
       </c>
       <c r="H601" t="s">
         <v>8</v>
@@ -16021,7 +16021,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G602" t="n">
-        <v>6.90718793869019</v>
+        <v>6.90718841552734</v>
       </c>
       <c r="H602" t="s">
         <v>8</v>
@@ -16073,7 +16073,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G604" t="n">
-        <v>6.81125545501709</v>
+        <v>6.81125497817993</v>
       </c>
       <c r="H604" t="s">
         <v>8</v>
@@ -25852,6 +25852,32 @@
         <v>11.3000001907349</v>
       </c>
       <c r="H980" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="981">
+      <c r="A981" s="1" t="n">
+        <v>46311.2916666667</v>
+      </c>
+      <c r="B981" t="n">
+        <v>1500</v>
+      </c>
+      <c r="C981" t="n">
+        <v>11.3500003814697</v>
+      </c>
+      <c r="D981" t="n">
+        <v>11.1000003814697</v>
+      </c>
+      <c r="E981" t="n">
+        <v>11.3500003814697</v>
+      </c>
+      <c r="F981" t="n">
+        <v>11.3000001907349</v>
+      </c>
+      <c r="G981" t="n">
+        <v>11.3000001907349</v>
+      </c>
+      <c r="H981" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/RDUE.MI.xlsx
+++ b/data/RDUE.MI.xlsx
@@ -485,7 +485,7 @@
         <v>12.0600004196167</v>
       </c>
       <c r="G4" t="n">
-        <v>11.3009843826294</v>
+        <v>11.3009834289551</v>
       </c>
       <c r="H4" t="n">
         <v>2100</v>
@@ -514,7 +514,7 @@
         <v>12.1499996185303</v>
       </c>
       <c r="G5" t="n">
-        <v>11.3853187561035</v>
+        <v>11.3853197097778</v>
       </c>
       <c r="H5" t="n">
         <v>14000</v>
@@ -572,7 +572,7 @@
         <v>12.0900001525879</v>
       </c>
       <c r="G7" t="n">
-        <v>11.3290948867798</v>
+        <v>11.3290958404541</v>
       </c>
       <c r="H7" t="n">
         <v>1000</v>
@@ -688,7 +688,7 @@
         <v>11.9180002212524</v>
       </c>
       <c r="G11" t="n">
-        <v>11.1679201126099</v>
+        <v>11.1679210662842</v>
       </c>
       <c r="H11" t="n">
         <v>2300</v>
@@ -833,7 +833,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G16" t="n">
-        <v>11.0573463439941</v>
+        <v>11.0573472976685</v>
       </c>
       <c r="H16" t="n">
         <v>200</v>
@@ -862,7 +862,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G17" t="n">
-        <v>11.0573463439941</v>
+        <v>11.0573472976685</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
@@ -1094,7 +1094,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G25" t="n">
-        <v>10.5888147354126</v>
+        <v>10.5888156890869</v>
       </c>
       <c r="H25" t="n">
         <v>600</v>
@@ -1123,7 +1123,7 @@
         <v>11.25</v>
       </c>
       <c r="G26" t="n">
-        <v>10.5419616699219</v>
+        <v>10.5419626235962</v>
       </c>
       <c r="H26" t="n">
         <v>400</v>
@@ -1181,7 +1181,7 @@
         <v>12.0100002288818</v>
       </c>
       <c r="G28" t="n">
-        <v>11.2541313171387</v>
+        <v>11.2541303634644</v>
       </c>
       <c r="H28" t="n">
         <v>5900</v>
@@ -1210,7 +1210,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G29" t="n">
-        <v>11.3384656906128</v>
+        <v>11.3384666442871</v>
       </c>
       <c r="H29" t="n">
         <v>12200</v>
@@ -1384,7 +1384,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G35" t="n">
-        <v>11.0573463439941</v>
+        <v>11.0573472976685</v>
       </c>
       <c r="H35" t="n">
         <v>2200</v>
@@ -1413,7 +1413,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G36" t="n">
-        <v>11.0573463439941</v>
+        <v>11.0573472976685</v>
       </c>
       <c r="H36" t="n">
         <v>0</v>
@@ -1442,7 +1442,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G37" t="n">
-        <v>11.0573463439941</v>
+        <v>11.0573472976685</v>
       </c>
       <c r="H37" t="n">
         <v>3200</v>
@@ -1616,7 +1616,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G43" t="n">
-        <v>11.0573463439941</v>
+        <v>11.0573472976685</v>
       </c>
       <c r="H43" t="n">
         <v>4800</v>
@@ -1761,7 +1761,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G48" t="n">
-        <v>11.0573463439941</v>
+        <v>11.0573472976685</v>
       </c>
       <c r="H48" t="n">
         <v>1200</v>
@@ -1877,7 +1877,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G52" t="n">
-        <v>11.0573463439941</v>
+        <v>11.0573472976685</v>
       </c>
       <c r="H52" t="n">
         <v>100</v>
@@ -1935,7 +1935,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G54" t="n">
-        <v>11.0573463439941</v>
+        <v>11.0573472976685</v>
       </c>
       <c r="H54" t="n">
         <v>700</v>
@@ -1964,7 +1964,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G55" t="n">
-        <v>11.0573463439941</v>
+        <v>11.0573472976685</v>
       </c>
       <c r="H55" t="n">
         <v>100</v>
@@ -1993,7 +1993,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G56" t="n">
-        <v>11.0573463439941</v>
+        <v>11.0573472976685</v>
       </c>
       <c r="H56" t="n">
         <v>0</v>
@@ -2631,7 +2631,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G78" t="n">
-        <v>11.0573463439941</v>
+        <v>11.0573472976685</v>
       </c>
       <c r="H78" t="n">
         <v>2600</v>
@@ -2747,7 +2747,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G82" t="n">
-        <v>9.74545860290527</v>
+        <v>9.74545764923096</v>
       </c>
       <c r="H82" t="n">
         <v>13600</v>
@@ -2950,7 +2950,7 @@
         <v>10.5500001907349</v>
       </c>
       <c r="G89" t="n">
-        <v>9.88601875305176</v>
+        <v>9.88601779937744</v>
       </c>
       <c r="H89" t="n">
         <v>4400</v>
@@ -3124,7 +3124,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G95" t="n">
-        <v>9.08951473236084</v>
+        <v>9.08951377868652</v>
       </c>
       <c r="H95" t="n">
         <v>800</v>
@@ -3153,7 +3153,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G96" t="n">
-        <v>9.08951473236084</v>
+        <v>9.08951377868652</v>
       </c>
       <c r="H96" t="n">
         <v>0</v>
@@ -3182,7 +3182,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G97" t="n">
-        <v>9.08951473236084</v>
+        <v>9.08951377868652</v>
       </c>
       <c r="H97" t="n">
         <v>0</v>
@@ -3211,7 +3211,7 @@
         <v>9.53999996185303</v>
       </c>
       <c r="G98" t="n">
-        <v>8.93958377838135</v>
+        <v>8.93958473205566</v>
       </c>
       <c r="H98" t="n">
         <v>900</v>
@@ -3385,7 +3385,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G104" t="n">
-        <v>8.62098217010498</v>
+        <v>8.6209831237793</v>
       </c>
       <c r="H104" t="n">
         <v>1400</v>
@@ -3443,7 +3443,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G106" t="n">
-        <v>8.62098217010498</v>
+        <v>8.6209831237793</v>
       </c>
       <c r="H106" t="n">
         <v>200</v>
@@ -3472,7 +3472,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G107" t="n">
-        <v>8.62098217010498</v>
+        <v>8.6209831237793</v>
       </c>
       <c r="H107" t="n">
         <v>0</v>
@@ -3530,7 +3530,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G109" t="n">
-        <v>8.80839538574219</v>
+        <v>8.80839443206787</v>
       </c>
       <c r="H109" t="n">
         <v>300</v>
@@ -3588,7 +3588,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G111" t="n">
-        <v>9.08951473236084</v>
+        <v>9.08951377868652</v>
       </c>
       <c r="H111" t="n">
         <v>500</v>
@@ -3704,7 +3704,7 @@
         <v>10</v>
       </c>
       <c r="G115" t="n">
-        <v>9.37063407897949</v>
+        <v>9.37063312530518</v>
       </c>
       <c r="H115" t="n">
         <v>200</v>
@@ -3733,7 +3733,7 @@
         <v>10.5500001907349</v>
       </c>
       <c r="G116" t="n">
-        <v>9.88601875305176</v>
+        <v>9.88601779937744</v>
       </c>
       <c r="H116" t="n">
         <v>2700</v>
@@ -3762,7 +3762,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G117" t="n">
-        <v>9.74545860290527</v>
+        <v>9.74545764923096</v>
       </c>
       <c r="H117" t="n">
         <v>300</v>
@@ -3791,7 +3791,7 @@
         <v>10.5500001907349</v>
       </c>
       <c r="G118" t="n">
-        <v>9.88601875305176</v>
+        <v>9.88601779937744</v>
       </c>
       <c r="H118" t="n">
         <v>100</v>
@@ -3820,7 +3820,7 @@
         <v>10.5</v>
       </c>
       <c r="G119" t="n">
-        <v>9.83916568756104</v>
+        <v>9.83916473388672</v>
       </c>
       <c r="H119" t="n">
         <v>800</v>
@@ -3994,7 +3994,7 @@
         <v>9.57999992370605</v>
       </c>
       <c r="G125" t="n">
-        <v>8.97706699371338</v>
+        <v>8.97706604003906</v>
       </c>
       <c r="H125" t="n">
         <v>1400</v>
@@ -4081,7 +4081,7 @@
         <v>9.88000011444092</v>
       </c>
       <c r="G128" t="n">
-        <v>9.25818634033203</v>
+        <v>9.25818538665771</v>
       </c>
       <c r="H128" t="n">
         <v>2400</v>
@@ -4110,7 +4110,7 @@
         <v>9.84000015258789</v>
       </c>
       <c r="G129" t="n">
-        <v>9.220703125</v>
+        <v>9.22070407867432</v>
       </c>
       <c r="H129" t="n">
         <v>200</v>
@@ -4226,7 +4226,7 @@
         <v>9.97999954223633</v>
       </c>
       <c r="G133" t="n">
-        <v>9.35189247131348</v>
+        <v>9.35189151763916</v>
       </c>
       <c r="H133" t="n">
         <v>500</v>
@@ -4313,7 +4313,7 @@
         <v>10.5</v>
       </c>
       <c r="G136" t="n">
-        <v>9.83916568756104</v>
+        <v>9.83916473388672</v>
       </c>
       <c r="H136" t="n">
         <v>700</v>
@@ -4342,7 +4342,7 @@
         <v>10.5500001907349</v>
       </c>
       <c r="G137" t="n">
-        <v>9.88601875305176</v>
+        <v>9.88601779937744</v>
       </c>
       <c r="H137" t="n">
         <v>1000</v>
@@ -4371,7 +4371,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G138" t="n">
-        <v>10.0265769958496</v>
+        <v>10.0265779495239</v>
       </c>
       <c r="H138" t="n">
         <v>500</v>
@@ -4400,7 +4400,7 @@
         <v>10.5</v>
       </c>
       <c r="G139" t="n">
-        <v>9.83916568756104</v>
+        <v>9.83916473388672</v>
       </c>
       <c r="H139" t="n">
         <v>300</v>
@@ -4429,7 +4429,7 @@
         <v>10.5</v>
       </c>
       <c r="G140" t="n">
-        <v>9.83916568756104</v>
+        <v>9.83916473388672</v>
       </c>
       <c r="H140" t="n">
         <v>100</v>
@@ -4458,7 +4458,7 @@
         <v>10.5</v>
       </c>
       <c r="G141" t="n">
-        <v>9.83916568756104</v>
+        <v>9.83916473388672</v>
       </c>
       <c r="H141" t="n">
         <v>0</v>
@@ -4487,7 +4487,7 @@
         <v>10</v>
       </c>
       <c r="G142" t="n">
-        <v>9.37063407897949</v>
+        <v>9.37063312530518</v>
       </c>
       <c r="H142" t="n">
         <v>7600</v>
@@ -4545,7 +4545,7 @@
         <v>9.47999954223633</v>
       </c>
       <c r="G144" t="n">
-        <v>8.88335990905762</v>
+        <v>8.88336086273193</v>
       </c>
       <c r="H144" t="n">
         <v>1800</v>
@@ -4574,7 +4574,7 @@
         <v>9.5600004196167</v>
       </c>
       <c r="G145" t="n">
-        <v>8.95832538604736</v>
+        <v>8.95832633972168</v>
       </c>
       <c r="H145" t="n">
         <v>1400</v>
@@ -4748,7 +4748,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G151" t="n">
-        <v>9.08951473236084</v>
+        <v>9.08951377868652</v>
       </c>
       <c r="H151" t="n">
         <v>500</v>
@@ -4777,7 +4777,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G152" t="n">
-        <v>9.08951473236084</v>
+        <v>9.08951377868652</v>
       </c>
       <c r="H152" t="n">
         <v>0</v>
@@ -4806,7 +4806,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G153" t="n">
-        <v>9.08951473236084</v>
+        <v>9.08951377868652</v>
       </c>
       <c r="H153" t="n">
         <v>0</v>
@@ -4864,7 +4864,7 @@
         <v>10</v>
       </c>
       <c r="G155" t="n">
-        <v>9.37063407897949</v>
+        <v>9.37063312530518</v>
       </c>
       <c r="H155" t="n">
         <v>100</v>
@@ -4893,7 +4893,7 @@
         <v>10</v>
       </c>
       <c r="G156" t="n">
-        <v>9.37063407897949</v>
+        <v>9.37063312530518</v>
       </c>
       <c r="H156" t="n">
         <v>0</v>
@@ -4922,7 +4922,7 @@
         <v>10</v>
       </c>
       <c r="G157" t="n">
-        <v>9.37063407897949</v>
+        <v>9.37063312530518</v>
       </c>
       <c r="H157" t="n">
         <v>0</v>
@@ -4951,7 +4951,7 @@
         <v>10</v>
       </c>
       <c r="G158" t="n">
-        <v>9.37063407897949</v>
+        <v>9.37063312530518</v>
       </c>
       <c r="H158" t="n">
         <v>0</v>
@@ -4980,7 +4980,7 @@
         <v>10</v>
       </c>
       <c r="G159" t="n">
-        <v>9.37063407897949</v>
+        <v>9.37063312530518</v>
       </c>
       <c r="H159" t="n">
         <v>0</v>
@@ -5009,7 +5009,7 @@
         <v>10</v>
       </c>
       <c r="G160" t="n">
-        <v>9.37063407897949</v>
+        <v>9.37063312530518</v>
       </c>
       <c r="H160" t="n">
         <v>0</v>
@@ -5038,7 +5038,7 @@
         <v>10</v>
       </c>
       <c r="G161" t="n">
-        <v>9.37063407897949</v>
+        <v>9.37063312530518</v>
       </c>
       <c r="H161" t="n">
         <v>0</v>
@@ -5067,7 +5067,7 @@
         <v>10</v>
       </c>
       <c r="G162" t="n">
-        <v>9.37063407897949</v>
+        <v>9.37063312530518</v>
       </c>
       <c r="H162" t="n">
         <v>100</v>
@@ -5125,7 +5125,7 @@
         <v>9.97999954223633</v>
       </c>
       <c r="G164" t="n">
-        <v>9.35189247131348</v>
+        <v>9.35189151763916</v>
       </c>
       <c r="H164" t="n">
         <v>400</v>
@@ -5212,7 +5212,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G167" t="n">
-        <v>9.08951473236084</v>
+        <v>9.08951377868652</v>
       </c>
       <c r="H167" t="n">
         <v>1600</v>
@@ -5241,7 +5241,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G168" t="n">
-        <v>9.08951473236084</v>
+        <v>9.08951377868652</v>
       </c>
       <c r="H168" t="n">
         <v>5000</v>
@@ -5270,7 +5270,7 @@
         <v>9.15999984741211</v>
       </c>
       <c r="G169" t="n">
-        <v>8.58350086212158</v>
+        <v>8.58349990844727</v>
       </c>
       <c r="H169" t="n">
         <v>16200</v>
@@ -5328,7 +5328,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G171" t="n">
-        <v>8.80839538574219</v>
+        <v>8.80839443206787</v>
       </c>
       <c r="H171" t="n">
         <v>900</v>
@@ -5357,7 +5357,7 @@
         <v>9.5600004196167</v>
       </c>
       <c r="G172" t="n">
-        <v>8.95832538604736</v>
+        <v>8.95832633972168</v>
       </c>
       <c r="H172" t="n">
         <v>200</v>
@@ -5444,7 +5444,7 @@
         <v>9.42000007629395</v>
       </c>
       <c r="G175" t="n">
-        <v>8.8271369934082</v>
+        <v>8.82713603973389</v>
       </c>
       <c r="H175" t="n">
         <v>800</v>
@@ -5676,7 +5676,7 @@
         <v>9.42000007629395</v>
       </c>
       <c r="G183" t="n">
-        <v>8.8271369934082</v>
+        <v>8.82713603973389</v>
       </c>
       <c r="H183" t="n">
         <v>300</v>
@@ -5705,7 +5705,7 @@
         <v>9.42000007629395</v>
       </c>
       <c r="G184" t="n">
-        <v>8.8271369934082</v>
+        <v>8.82713603973389</v>
       </c>
       <c r="H184" t="n">
         <v>0</v>
@@ -5763,7 +5763,7 @@
         <v>9.84000015258789</v>
       </c>
       <c r="G186" t="n">
-        <v>9.220703125</v>
+        <v>9.22070407867432</v>
       </c>
       <c r="H186" t="n">
         <v>400</v>
@@ -5792,7 +5792,7 @@
         <v>9.97999954223633</v>
       </c>
       <c r="G187" t="n">
-        <v>9.35189247131348</v>
+        <v>9.35189151763916</v>
       </c>
       <c r="H187" t="n">
         <v>3900</v>
@@ -5821,7 +5821,7 @@
         <v>9.97999954223633</v>
       </c>
       <c r="G188" t="n">
-        <v>9.35189247131348</v>
+        <v>9.35189151763916</v>
       </c>
       <c r="H188" t="n">
         <v>300</v>
@@ -6024,7 +6024,7 @@
         <v>9.53999996185303</v>
       </c>
       <c r="G195" t="n">
-        <v>8.93958377838135</v>
+        <v>8.93958473205566</v>
       </c>
       <c r="H195" t="n">
         <v>600</v>
@@ -6053,7 +6053,7 @@
         <v>9.53999996185303</v>
       </c>
       <c r="G196" t="n">
-        <v>8.93958377838135</v>
+        <v>8.93958473205566</v>
       </c>
       <c r="H196" t="n">
         <v>0</v>
@@ -6082,7 +6082,7 @@
         <v>9.53999996185303</v>
       </c>
       <c r="G197" t="n">
-        <v>8.93958377838135</v>
+        <v>8.93958473205566</v>
       </c>
       <c r="H197" t="n">
         <v>0</v>
@@ -6169,7 +6169,7 @@
         <v>8.85999965667725</v>
       </c>
       <c r="G200" t="n">
-        <v>8.30238151550293</v>
+        <v>8.30238056182861</v>
       </c>
       <c r="H200" t="n">
         <v>12000</v>
@@ -6285,7 +6285,7 @@
         <v>9.0600004196167</v>
       </c>
       <c r="G204" t="n">
-        <v>8.48979473114014</v>
+        <v>8.48979377746582</v>
       </c>
       <c r="H204" t="n">
         <v>2200</v>
@@ -6314,7 +6314,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G205" t="n">
-        <v>8.33986282348633</v>
+        <v>8.33986377716064</v>
       </c>
       <c r="H205" t="n">
         <v>100</v>
@@ -6459,7 +6459,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G210" t="n">
-        <v>8.62098217010498</v>
+        <v>8.6209831237793</v>
       </c>
       <c r="H210" t="n">
         <v>100</v>
@@ -6488,7 +6488,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G211" t="n">
-        <v>8.62098217010498</v>
+        <v>8.6209831237793</v>
       </c>
       <c r="H211" t="n">
         <v>400</v>
@@ -6749,7 +6749,7 @@
         <v>8.9399995803833</v>
       </c>
       <c r="G220" t="n">
-        <v>8.37734508514404</v>
+        <v>8.37734603881836</v>
       </c>
       <c r="H220" t="n">
         <v>200</v>
@@ -6778,7 +6778,7 @@
         <v>8.9399995803833</v>
       </c>
       <c r="G221" t="n">
-        <v>8.37734508514404</v>
+        <v>8.37734603881836</v>
       </c>
       <c r="H221" t="n">
         <v>0</v>
@@ -6807,7 +6807,7 @@
         <v>8.9399995803833</v>
       </c>
       <c r="G222" t="n">
-        <v>8.37734508514404</v>
+        <v>8.37734603881836</v>
       </c>
       <c r="H222" t="n">
         <v>0</v>
@@ -6836,7 +6836,7 @@
         <v>8.9399995803833</v>
       </c>
       <c r="G223" t="n">
-        <v>8.37734508514404</v>
+        <v>8.37734603881836</v>
       </c>
       <c r="H223" t="n">
         <v>0</v>
@@ -6865,7 +6865,7 @@
         <v>8.9399995803833</v>
       </c>
       <c r="G224" t="n">
-        <v>8.37734508514404</v>
+        <v>8.37734603881836</v>
       </c>
       <c r="H224" t="n">
         <v>0</v>
@@ -7155,7 +7155,7 @@
         <v>8.9399995803833</v>
       </c>
       <c r="G234" t="n">
-        <v>8.37734508514404</v>
+        <v>8.37734603881836</v>
       </c>
       <c r="H234" t="n">
         <v>800</v>
@@ -7242,7 +7242,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G237" t="n">
-        <v>8.33986282348633</v>
+        <v>8.33986377716064</v>
       </c>
       <c r="H237" t="n">
         <v>9400</v>
@@ -7271,7 +7271,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G238" t="n">
-        <v>8.33986282348633</v>
+        <v>8.33986377716064</v>
       </c>
       <c r="H238" t="n">
         <v>300</v>
@@ -7387,7 +7387,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G242" t="n">
-        <v>7.68391942977905</v>
+        <v>7.68391847610474</v>
       </c>
       <c r="H242" t="n">
         <v>10000</v>
@@ -7474,7 +7474,7 @@
         <v>8.0600004196167</v>
       </c>
       <c r="G245" t="n">
-        <v>7.55273103713989</v>
+        <v>7.55273056030273</v>
       </c>
       <c r="H245" t="n">
         <v>500</v>
@@ -7503,7 +7503,7 @@
         <v>8.0600004196167</v>
       </c>
       <c r="G246" t="n">
-        <v>7.55273103713989</v>
+        <v>7.55273056030273</v>
       </c>
       <c r="H246" t="n">
         <v>2400</v>
@@ -7532,7 +7532,7 @@
         <v>8.0600004196167</v>
       </c>
       <c r="G247" t="n">
-        <v>7.55273103713989</v>
+        <v>7.55273056030273</v>
       </c>
       <c r="H247" t="n">
         <v>300</v>
@@ -7561,7 +7561,7 @@
         <v>8.0600004196167</v>
       </c>
       <c r="G248" t="n">
-        <v>7.55273103713989</v>
+        <v>7.55273056030273</v>
       </c>
       <c r="H248" t="n">
         <v>0</v>
@@ -7648,7 +7648,7 @@
         <v>8.23999977111816</v>
       </c>
       <c r="G251" t="n">
-        <v>7.72140169143677</v>
+        <v>7.72140121459961</v>
       </c>
       <c r="H251" t="n">
         <v>100</v>
@@ -7677,7 +7677,7 @@
         <v>8.26000022888184</v>
       </c>
       <c r="G252" t="n">
-        <v>7.74014377593994</v>
+        <v>7.74014282226562</v>
       </c>
       <c r="H252" t="n">
         <v>300</v>
@@ -7938,7 +7938,7 @@
         <v>7.84000015258789</v>
       </c>
       <c r="G261" t="n">
-        <v>7.34657669067383</v>
+        <v>7.34657621383667</v>
       </c>
       <c r="H261" t="n">
         <v>2200</v>
@@ -8054,7 +8054,7 @@
         <v>7.48000001907349</v>
       </c>
       <c r="G265" t="n">
-        <v>7.0092339515686</v>
+        <v>7.00923347473145</v>
       </c>
       <c r="H265" t="n">
         <v>10400</v>
@@ -8141,7 +8141,7 @@
         <v>7.48000001907349</v>
       </c>
       <c r="G268" t="n">
-        <v>7.0092339515686</v>
+        <v>7.00923347473145</v>
       </c>
       <c r="H268" t="n">
         <v>4100</v>
@@ -8257,7 +8257,7 @@
         <v>8.53999996185303</v>
       </c>
       <c r="G272" t="n">
-        <v>8.00252151489258</v>
+        <v>8.00252056121826</v>
       </c>
       <c r="H272" t="n">
         <v>9400</v>
@@ -8431,7 +8431,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G278" t="n">
-        <v>8.62098217010498</v>
+        <v>8.6209831237793</v>
       </c>
       <c r="H278" t="n">
         <v>300</v>
@@ -8547,7 +8547,7 @@
         <v>8.92000007629395</v>
       </c>
       <c r="G282" t="n">
-        <v>8.35860443115234</v>
+        <v>8.35860538482666</v>
       </c>
       <c r="H282" t="n">
         <v>200</v>
@@ -8576,7 +8576,7 @@
         <v>8.76000022888184</v>
       </c>
       <c r="G283" t="n">
-        <v>8.20867538452148</v>
+        <v>8.20867443084717</v>
       </c>
       <c r="H283" t="n">
         <v>2800</v>
@@ -8953,7 +8953,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G296" t="n">
-        <v>8.62098217010498</v>
+        <v>8.6209831237793</v>
       </c>
       <c r="H296" t="n">
         <v>1000</v>
@@ -9069,7 +9069,7 @@
         <v>8.9399995803833</v>
       </c>
       <c r="G300" t="n">
-        <v>8.37734508514404</v>
+        <v>8.37734603881836</v>
       </c>
       <c r="H300" t="n">
         <v>300</v>
@@ -9185,7 +9185,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G304" t="n">
-        <v>8.33986282348633</v>
+        <v>8.33986377716064</v>
       </c>
       <c r="H304" t="n">
         <v>300</v>
@@ -9330,7 +9330,7 @@
         <v>8.53999996185303</v>
       </c>
       <c r="G309" t="n">
-        <v>8.00252151489258</v>
+        <v>8.00252056121826</v>
       </c>
       <c r="H309" t="n">
         <v>2500</v>
@@ -9446,7 +9446,7 @@
         <v>8.61999988555908</v>
       </c>
       <c r="G313" t="n">
-        <v>8.07748508453369</v>
+        <v>8.07748603820801</v>
       </c>
       <c r="H313" t="n">
         <v>5400</v>
@@ -9823,7 +9823,7 @@
         <v>8.31999969482422</v>
       </c>
       <c r="G326" t="n">
-        <v>7.7963662147522</v>
+        <v>7.79636716842651</v>
       </c>
       <c r="H326" t="n">
         <v>3800</v>
@@ -10258,7 +10258,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G341" t="n">
-        <v>8.33986282348633</v>
+        <v>8.33986377716064</v>
       </c>
       <c r="H341" t="n">
         <v>3000</v>
@@ -10287,7 +10287,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G342" t="n">
-        <v>8.80839538574219</v>
+        <v>8.80839443206787</v>
       </c>
       <c r="H342" t="n">
         <v>10000</v>
@@ -10316,7 +10316,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G343" t="n">
-        <v>9.08951473236084</v>
+        <v>9.08951377868652</v>
       </c>
       <c r="H343" t="n">
         <v>10200</v>
@@ -10374,7 +10374,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G345" t="n">
-        <v>9.08951473236084</v>
+        <v>9.08951377868652</v>
       </c>
       <c r="H345" t="n">
         <v>4500</v>
@@ -10548,7 +10548,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G351" t="n">
-        <v>9.08951473236084</v>
+        <v>9.08951377868652</v>
       </c>
       <c r="H351" t="n">
         <v>800</v>
@@ -10780,7 +10780,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G359" t="n">
-        <v>9.0426607131958</v>
+        <v>9.04265975952148</v>
       </c>
       <c r="H359" t="n">
         <v>4000</v>
@@ -10809,7 +10809,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G360" t="n">
-        <v>9.0426607131958</v>
+        <v>9.04265975952148</v>
       </c>
       <c r="H360" t="n">
         <v>0</v>
@@ -10896,7 +10896,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G363" t="n">
-        <v>9.0426607131958</v>
+        <v>9.04265975952148</v>
       </c>
       <c r="H363" t="n">
         <v>100</v>
@@ -10925,7 +10925,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G364" t="n">
-        <v>9.0426607131958</v>
+        <v>9.04265975952148</v>
       </c>
       <c r="H364" t="n">
         <v>0</v>
@@ -10954,7 +10954,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G365" t="n">
-        <v>9.0426607131958</v>
+        <v>9.04265975952148</v>
       </c>
       <c r="H365" t="n">
         <v>300</v>
@@ -11215,7 +11215,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G374" t="n">
-        <v>9.0426607131958</v>
+        <v>9.04265975952148</v>
       </c>
       <c r="H374" t="n">
         <v>100</v>
@@ -11244,7 +11244,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G375" t="n">
-        <v>9.30551815032959</v>
+        <v>9.30551719665527</v>
       </c>
       <c r="H375" t="n">
         <v>600</v>
@@ -11273,7 +11273,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G376" t="n">
-        <v>9.2575511932373</v>
+        <v>9.25755023956299</v>
       </c>
       <c r="H376" t="n">
         <v>2500</v>
@@ -11331,7 +11331,7 @@
         <v>10</v>
       </c>
       <c r="G378" t="n">
-        <v>9.59331798553467</v>
+        <v>9.59331703186035</v>
       </c>
       <c r="H378" t="n">
         <v>7200</v>
@@ -11708,7 +11708,7 @@
         <v>10</v>
       </c>
       <c r="G391" t="n">
-        <v>9.59331798553467</v>
+        <v>9.59331703186035</v>
       </c>
       <c r="H391" t="n">
         <v>300</v>
@@ -11853,7 +11853,7 @@
         <v>10</v>
       </c>
       <c r="G396" t="n">
-        <v>9.59331798553467</v>
+        <v>9.59331703186035</v>
       </c>
       <c r="H396" t="n">
         <v>500</v>
@@ -11882,7 +11882,7 @@
         <v>10</v>
       </c>
       <c r="G397" t="n">
-        <v>9.59331798553467</v>
+        <v>9.59331703186035</v>
       </c>
       <c r="H397" t="n">
         <v>0</v>
@@ -11940,7 +11940,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G399" t="n">
-        <v>9.30551815032959</v>
+        <v>9.30551719665527</v>
       </c>
       <c r="H399" t="n">
         <v>1600</v>
@@ -11998,7 +11998,7 @@
         <v>9.35000038146973</v>
       </c>
       <c r="G401" t="n">
-        <v>8.96975231170654</v>
+        <v>8.96975135803223</v>
       </c>
       <c r="H401" t="n">
         <v>5200</v>
@@ -12288,7 +12288,7 @@
         <v>10</v>
       </c>
       <c r="G411" t="n">
-        <v>9.59331798553467</v>
+        <v>9.59331703186035</v>
       </c>
       <c r="H411" t="n">
         <v>600</v>
@@ -12433,7 +12433,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G416" t="n">
-        <v>9.2575511932373</v>
+        <v>9.25755023956299</v>
       </c>
       <c r="H416" t="n">
         <v>700</v>
@@ -12462,7 +12462,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G417" t="n">
-        <v>9.2575511932373</v>
+        <v>9.25755023956299</v>
       </c>
       <c r="H417" t="n">
         <v>0</v>
@@ -12491,7 +12491,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G418" t="n">
-        <v>9.2575511932373</v>
+        <v>9.25755023956299</v>
       </c>
       <c r="H418" t="n">
         <v>0</v>
@@ -12520,7 +12520,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G419" t="n">
-        <v>9.30551815032959</v>
+        <v>9.30551719665527</v>
       </c>
       <c r="H419" t="n">
         <v>1700</v>
@@ -12578,7 +12578,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G421" t="n">
-        <v>9.01771831512451</v>
+        <v>9.0177173614502</v>
       </c>
       <c r="H421" t="n">
         <v>100</v>
@@ -12636,7 +12636,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G423" t="n">
-        <v>9.2575511932373</v>
+        <v>9.25755023956299</v>
       </c>
       <c r="H423" t="n">
         <v>1100</v>
@@ -12665,7 +12665,7 @@
         <v>9.35000038146973</v>
       </c>
       <c r="G424" t="n">
-        <v>8.96975231170654</v>
+        <v>8.96975135803223</v>
       </c>
       <c r="H424" t="n">
         <v>500</v>
@@ -12694,7 +12694,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G425" t="n">
-        <v>8.53805160522461</v>
+        <v>8.53805255889893</v>
       </c>
       <c r="H425" t="n">
         <v>1300</v>
@@ -12810,7 +12810,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G429" t="n">
-        <v>9.2575511932373</v>
+        <v>9.25755023956299</v>
       </c>
       <c r="H429" t="n">
         <v>700</v>
@@ -12839,7 +12839,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G430" t="n">
-        <v>9.2575511932373</v>
+        <v>9.25755023956299</v>
       </c>
       <c r="H430" t="n">
         <v>0</v>
@@ -12897,7 +12897,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G432" t="n">
-        <v>9.01771831512451</v>
+        <v>9.0177173614502</v>
       </c>
       <c r="H432" t="n">
         <v>100</v>
@@ -12926,7 +12926,7 @@
         <v>9.35000038146973</v>
       </c>
       <c r="G433" t="n">
-        <v>8.96975231170654</v>
+        <v>8.96975135803223</v>
       </c>
       <c r="H433" t="n">
         <v>1200</v>
@@ -12984,7 +12984,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G435" t="n">
-        <v>9.30551815032959</v>
+        <v>9.30551719665527</v>
       </c>
       <c r="H435" t="n">
         <v>200</v>
@@ -13013,7 +13013,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G436" t="n">
-        <v>9.2575511932373</v>
+        <v>9.25755023956299</v>
       </c>
       <c r="H436" t="n">
         <v>400</v>
@@ -13071,7 +13071,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G438" t="n">
-        <v>9.01771831512451</v>
+        <v>9.0177173614502</v>
       </c>
       <c r="H438" t="n">
         <v>600</v>
@@ -13100,7 +13100,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G439" t="n">
-        <v>9.30551815032959</v>
+        <v>9.30551719665527</v>
       </c>
       <c r="H439" t="n">
         <v>200</v>
@@ -13129,7 +13129,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G440" t="n">
-        <v>9.30551815032959</v>
+        <v>9.30551719665527</v>
       </c>
       <c r="H440" t="n">
         <v>500</v>
@@ -13158,7 +13158,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G441" t="n">
-        <v>9.30551815032959</v>
+        <v>9.30551719665527</v>
       </c>
       <c r="H441" t="n">
         <v>600</v>
@@ -13187,7 +13187,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G442" t="n">
-        <v>9.30551815032959</v>
+        <v>9.30551719665527</v>
       </c>
       <c r="H442" t="n">
         <v>800</v>
@@ -13274,7 +13274,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G445" t="n">
-        <v>9.01771831512451</v>
+        <v>9.0177173614502</v>
       </c>
       <c r="H445" t="n">
         <v>4900</v>
@@ -13303,7 +13303,7 @@
         <v>9.44999980926514</v>
       </c>
       <c r="G446" t="n">
-        <v>9.0656852722168</v>
+        <v>9.06568431854248</v>
       </c>
       <c r="H446" t="n">
         <v>4900</v>
@@ -13332,7 +13332,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G447" t="n">
-        <v>9.01771831512451</v>
+        <v>9.0177173614502</v>
       </c>
       <c r="H447" t="n">
         <v>2000</v>
@@ -13361,7 +13361,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G448" t="n">
-        <v>8.82585144042969</v>
+        <v>8.825852394104</v>
       </c>
       <c r="H448" t="n">
         <v>1200</v>
@@ -13535,7 +13535,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G454" t="n">
-        <v>8.82585144042969</v>
+        <v>8.825852394104</v>
       </c>
       <c r="H454" t="n">
         <v>100</v>
@@ -13564,7 +13564,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G455" t="n">
-        <v>8.82585144042969</v>
+        <v>8.825852394104</v>
       </c>
       <c r="H455" t="n">
         <v>0</v>
@@ -13593,7 +13593,7 @@
         <v>9.35000038146973</v>
       </c>
       <c r="G456" t="n">
-        <v>8.96975231170654</v>
+        <v>8.96975135803223</v>
       </c>
       <c r="H456" t="n">
         <v>9000</v>
@@ -13796,7 +13796,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G463" t="n">
-        <v>8.53805160522461</v>
+        <v>8.53805255889893</v>
       </c>
       <c r="H463" t="n">
         <v>800</v>
@@ -14057,7 +14057,7 @@
         <v>7.75</v>
       </c>
       <c r="G472" t="n">
-        <v>7.43482112884521</v>
+        <v>7.43482065200806</v>
       </c>
       <c r="H472" t="n">
         <v>5500</v>
@@ -14289,7 +14289,7 @@
         <v>7.5</v>
       </c>
       <c r="G480" t="n">
-        <v>7.19498777389526</v>
+        <v>7.19498825073242</v>
       </c>
       <c r="H480" t="n">
         <v>1800</v>
@@ -14318,7 +14318,7 @@
         <v>7.34999990463257</v>
       </c>
       <c r="G481" t="n">
-        <v>7.05108785629272</v>
+        <v>7.05108833312988</v>
       </c>
       <c r="H481" t="n">
         <v>4200</v>
@@ -14347,7 +14347,7 @@
         <v>7.34999990463257</v>
       </c>
       <c r="G482" t="n">
-        <v>7.05108785629272</v>
+        <v>7.05108833312988</v>
       </c>
       <c r="H482" t="n">
         <v>7800</v>
@@ -14434,7 +14434,7 @@
         <v>7</v>
       </c>
       <c r="G485" t="n">
-        <v>6.71532201766968</v>
+        <v>6.71532249450684</v>
       </c>
       <c r="H485" t="n">
         <v>10100</v>
@@ -14724,7 +14724,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G495" t="n">
-        <v>6.04379034042358</v>
+        <v>6.04378986358643</v>
       </c>
       <c r="H495" t="n">
         <v>7900</v>
@@ -15014,7 +15014,7 @@
         <v>7</v>
       </c>
       <c r="G505" t="n">
-        <v>6.71532201766968</v>
+        <v>6.71532249450684</v>
       </c>
       <c r="H505" t="n">
         <v>13500</v>
@@ -15072,7 +15072,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G507" t="n">
-        <v>6.81125497817993</v>
+        <v>6.81125545501709</v>
       </c>
       <c r="H507" t="n">
         <v>3900</v>
@@ -15159,7 +15159,7 @@
         <v>7.75</v>
       </c>
       <c r="G510" t="n">
-        <v>7.43482112884521</v>
+        <v>7.43482065200806</v>
       </c>
       <c r="H510" t="n">
         <v>3700</v>
@@ -15681,7 +15681,7 @@
         <v>7.34999990463257</v>
       </c>
       <c r="G528" t="n">
-        <v>7.05108785629272</v>
+        <v>7.05108833312988</v>
       </c>
       <c r="H528" t="n">
         <v>4000</v>
@@ -15884,7 +15884,7 @@
         <v>7.5</v>
       </c>
       <c r="G535" t="n">
-        <v>7.19498777389526</v>
+        <v>7.19498825073242</v>
       </c>
       <c r="H535" t="n">
         <v>200</v>
@@ -16029,7 +16029,7 @@
         <v>7</v>
       </c>
       <c r="G540" t="n">
-        <v>6.71532201766968</v>
+        <v>6.71532249450684</v>
       </c>
       <c r="H540" t="n">
         <v>7000</v>
@@ -16203,7 +16203,7 @@
         <v>6.94999980926514</v>
       </c>
       <c r="G546" t="n">
-        <v>6.66735506057739</v>
+        <v>6.66735553741455</v>
       </c>
       <c r="H546" t="n">
         <v>2700</v>
@@ -16290,7 +16290,7 @@
         <v>7</v>
       </c>
       <c r="G549" t="n">
-        <v>6.71532201766968</v>
+        <v>6.71532249450684</v>
       </c>
       <c r="H549" t="n">
         <v>9500</v>
@@ -16319,7 +16319,7 @@
         <v>6.94999980926514</v>
       </c>
       <c r="G550" t="n">
-        <v>6.66735506057739</v>
+        <v>6.66735553741455</v>
       </c>
       <c r="H550" t="n">
         <v>16600</v>
@@ -16580,7 +16580,7 @@
         <v>7.75</v>
       </c>
       <c r="G559" t="n">
-        <v>7.43482112884521</v>
+        <v>7.43482065200806</v>
       </c>
       <c r="H559" t="n">
         <v>4000</v>
@@ -16725,7 +16725,7 @@
         <v>7.75</v>
       </c>
       <c r="G564" t="n">
-        <v>7.43482112884521</v>
+        <v>7.43482065200806</v>
       </c>
       <c r="H564" t="n">
         <v>700</v>
@@ -16841,7 +16841,7 @@
         <v>7.75</v>
       </c>
       <c r="G568" t="n">
-        <v>7.43482112884521</v>
+        <v>7.43482065200806</v>
       </c>
       <c r="H568" t="n">
         <v>6900</v>
@@ -17015,7 +17015,7 @@
         <v>8.14999961853027</v>
       </c>
       <c r="G574" t="n">
-        <v>7.81855344772339</v>
+        <v>7.81855297088623</v>
       </c>
       <c r="H574" t="n">
         <v>5200</v>
@@ -17160,7 +17160,7 @@
         <v>7.5</v>
       </c>
       <c r="G579" t="n">
-        <v>7.19498777389526</v>
+        <v>7.19498825073242</v>
       </c>
       <c r="H579" t="n">
         <v>3100</v>
@@ -17247,7 +17247,7 @@
         <v>8.25</v>
       </c>
       <c r="G582" t="n">
-        <v>7.91448736190796</v>
+        <v>7.91448640823364</v>
       </c>
       <c r="H582" t="n">
         <v>10200</v>
@@ -17276,7 +17276,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G583" t="n">
-        <v>7.86652040481567</v>
+        <v>7.86651945114136</v>
       </c>
       <c r="H583" t="n">
         <v>20900</v>
@@ -17334,7 +17334,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G585" t="n">
-        <v>7.86652040481567</v>
+        <v>7.86651945114136</v>
       </c>
       <c r="H585" t="n">
         <v>5700</v>
@@ -17363,7 +17363,7 @@
         <v>7.75</v>
       </c>
       <c r="G586" t="n">
-        <v>7.43482112884521</v>
+        <v>7.43482065200806</v>
       </c>
       <c r="H586" t="n">
         <v>8000</v>
@@ -17392,7 +17392,7 @@
         <v>7.75</v>
       </c>
       <c r="G587" t="n">
-        <v>7.43482112884521</v>
+        <v>7.43482065200806</v>
       </c>
       <c r="H587" t="n">
         <v>1500</v>
@@ -17421,7 +17421,7 @@
         <v>7.75</v>
       </c>
       <c r="G588" t="n">
-        <v>7.43482112884521</v>
+        <v>7.43482065200806</v>
       </c>
       <c r="H588" t="n">
         <v>100</v>
@@ -17479,7 +17479,7 @@
         <v>7.75</v>
       </c>
       <c r="G590" t="n">
-        <v>7.43482112884521</v>
+        <v>7.43482065200806</v>
       </c>
       <c r="H590" t="n">
         <v>2300</v>
@@ -17653,7 +17653,7 @@
         <v>6.94999980926514</v>
       </c>
       <c r="G596" t="n">
-        <v>6.66735506057739</v>
+        <v>6.66735553741455</v>
       </c>
       <c r="H596" t="n">
         <v>1100</v>
@@ -17682,7 +17682,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G597" t="n">
-        <v>6.90718841552734</v>
+        <v>6.90718793869019</v>
       </c>
       <c r="H597" t="n">
         <v>1200</v>
@@ -17711,7 +17711,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G598" t="n">
-        <v>6.90718841552734</v>
+        <v>6.90718793869019</v>
       </c>
       <c r="H598" t="n">
         <v>0</v>
@@ -17798,7 +17798,7 @@
         <v>7.34999990463257</v>
       </c>
       <c r="G601" t="n">
-        <v>7.05108785629272</v>
+        <v>7.05108833312988</v>
       </c>
       <c r="H601" t="n">
         <v>2100</v>
@@ -17827,7 +17827,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G602" t="n">
-        <v>6.90718841552734</v>
+        <v>6.90718793869019</v>
       </c>
       <c r="H602" t="n">
         <v>1600</v>
@@ -17885,7 +17885,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G604" t="n">
-        <v>6.81125497817993</v>
+        <v>6.81125545501709</v>
       </c>
       <c r="H604" t="n">
         <v>15300</v>
@@ -28824,6 +28824,64 @@
         <v>1500</v>
       </c>
       <c r="I981" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="982">
+      <c r="A982" t="s">
+        <v>9</v>
+      </c>
+      <c r="B982" s="1" t="n">
+        <v>46314.2916666667</v>
+      </c>
+      <c r="C982" t="n">
+        <v>11.4499998092651</v>
+      </c>
+      <c r="D982" t="n">
+        <v>11.4499998092651</v>
+      </c>
+      <c r="E982" t="n">
+        <v>10.8999996185303</v>
+      </c>
+      <c r="F982" t="n">
+        <v>11</v>
+      </c>
+      <c r="G982" t="n">
+        <v>11</v>
+      </c>
+      <c r="H982" t="n">
+        <v>1500</v>
+      </c>
+      <c r="I982" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="983">
+      <c r="A983" t="s">
+        <v>9</v>
+      </c>
+      <c r="B983" s="1" t="n">
+        <v>46315.2916666667</v>
+      </c>
+      <c r="C983" t="n">
+        <v>10.9499998092651</v>
+      </c>
+      <c r="D983" t="n">
+        <v>10.9499998092651</v>
+      </c>
+      <c r="E983" t="n">
+        <v>10.8999996185303</v>
+      </c>
+      <c r="F983" t="n">
+        <v>10.8500003814697</v>
+      </c>
+      <c r="G983" t="n">
+        <v>10.8500003814697</v>
+      </c>
+      <c r="H983" t="n">
+        <v>1300</v>
+      </c>
+      <c r="I983" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/RDUE.MI.xlsx
+++ b/data/RDUE.MI.xlsx
@@ -456,7 +456,7 @@
         <v>12.0500001907349</v>
       </c>
       <c r="G3" t="n">
-        <v>11.2916135787964</v>
+        <v>11.2916126251221</v>
       </c>
       <c r="H3" t="n">
         <v>19500</v>
@@ -485,7 +485,7 @@
         <v>12.0600004196167</v>
       </c>
       <c r="G4" t="n">
-        <v>11.3009834289551</v>
+        <v>11.3009843826294</v>
       </c>
       <c r="H4" t="n">
         <v>2100</v>
@@ -514,7 +514,7 @@
         <v>12.1499996185303</v>
       </c>
       <c r="G5" t="n">
-        <v>11.3853197097778</v>
+        <v>11.3853187561035</v>
       </c>
       <c r="H5" t="n">
         <v>14000</v>
@@ -543,7 +543,7 @@
         <v>12.0539999008179</v>
       </c>
       <c r="G6" t="n">
-        <v>11.2953605651855</v>
+        <v>11.2953615188599</v>
       </c>
       <c r="H6" t="n">
         <v>9400</v>
@@ -572,7 +572,7 @@
         <v>12.0900001525879</v>
       </c>
       <c r="G7" t="n">
-        <v>11.3290958404541</v>
+        <v>11.3290948867798</v>
       </c>
       <c r="H7" t="n">
         <v>1000</v>
@@ -630,7 +630,7 @@
         <v>11.8599996566772</v>
       </c>
       <c r="G9" t="n">
-        <v>11.1135702133179</v>
+        <v>11.1135711669922</v>
       </c>
       <c r="H9" t="n">
         <v>5700</v>
@@ -688,7 +688,7 @@
         <v>11.9180002212524</v>
       </c>
       <c r="G11" t="n">
-        <v>11.1679210662842</v>
+        <v>11.1679201126099</v>
       </c>
       <c r="H11" t="n">
         <v>2300</v>
@@ -746,7 +746,7 @@
         <v>11.8800001144409</v>
       </c>
       <c r="G13" t="n">
-        <v>11.1323118209839</v>
+        <v>11.1323127746582</v>
       </c>
       <c r="H13" t="n">
         <v>5200</v>
@@ -978,7 +978,7 @@
         <v>11.3800001144409</v>
       </c>
       <c r="G21" t="n">
-        <v>10.6637802124023</v>
+        <v>10.6637811660767</v>
       </c>
       <c r="H21" t="n">
         <v>3200</v>
@@ -1065,7 +1065,7 @@
         <v>11.2600002288818</v>
       </c>
       <c r="G24" t="n">
-        <v>10.5513324737549</v>
+        <v>10.5513334274292</v>
       </c>
       <c r="H24" t="n">
         <v>200</v>
@@ -1123,7 +1123,7 @@
         <v>11.25</v>
       </c>
       <c r="G26" t="n">
-        <v>10.5419626235962</v>
+        <v>10.5419616699219</v>
       </c>
       <c r="H26" t="n">
         <v>400</v>
@@ -1181,7 +1181,7 @@
         <v>12.0100002288818</v>
       </c>
       <c r="G28" t="n">
-        <v>11.2541303634644</v>
+        <v>11.2541313171387</v>
       </c>
       <c r="H28" t="n">
         <v>5900</v>
@@ -1239,7 +1239,7 @@
         <v>11.8800001144409</v>
       </c>
       <c r="G30" t="n">
-        <v>11.1323118209839</v>
+        <v>11.1323127746582</v>
       </c>
       <c r="H30" t="n">
         <v>3900</v>
@@ -1355,7 +1355,7 @@
         <v>11.75</v>
       </c>
       <c r="G34" t="n">
-        <v>11.0104942321777</v>
+        <v>11.0104932785034</v>
       </c>
       <c r="H34" t="n">
         <v>3400</v>
@@ -2022,7 +2022,7 @@
         <v>11.75</v>
       </c>
       <c r="G57" t="n">
-        <v>11.0104942321777</v>
+        <v>11.0104932785034</v>
       </c>
       <c r="H57" t="n">
         <v>200</v>
@@ -2051,7 +2051,7 @@
         <v>11.75</v>
       </c>
       <c r="G58" t="n">
-        <v>11.0104942321777</v>
+        <v>11.0104932785034</v>
       </c>
       <c r="H58" t="n">
         <v>500</v>
@@ -2080,7 +2080,7 @@
         <v>11.75</v>
       </c>
       <c r="G59" t="n">
-        <v>11.0104942321777</v>
+        <v>11.0104932785034</v>
       </c>
       <c r="H59" t="n">
         <v>0</v>
@@ -2109,7 +2109,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G60" t="n">
-        <v>10.8699340820312</v>
+        <v>10.8699350357056</v>
       </c>
       <c r="H60" t="n">
         <v>6000</v>
@@ -2428,7 +2428,7 @@
         <v>11.5</v>
       </c>
       <c r="G71" t="n">
-        <v>10.7762269973755</v>
+        <v>10.7762279510498</v>
       </c>
       <c r="H71" t="n">
         <v>500</v>
@@ -2486,7 +2486,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G73" t="n">
-        <v>10.8699340820312</v>
+        <v>10.8699350357056</v>
       </c>
       <c r="H73" t="n">
         <v>10000</v>
@@ -2515,7 +2515,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G74" t="n">
-        <v>10.8699340820312</v>
+        <v>10.8699350357056</v>
       </c>
       <c r="H74" t="n">
         <v>4200</v>
@@ -2544,7 +2544,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G75" t="n">
-        <v>10.8699340820312</v>
+        <v>10.8699350357056</v>
       </c>
       <c r="H75" t="n">
         <v>1100</v>
@@ -2573,7 +2573,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G76" t="n">
-        <v>10.8699340820312</v>
+        <v>10.8699350357056</v>
       </c>
       <c r="H76" t="n">
         <v>3300</v>
@@ -2660,7 +2660,7 @@
         <v>11.5</v>
       </c>
       <c r="G79" t="n">
-        <v>10.7762269973755</v>
+        <v>10.7762279510498</v>
       </c>
       <c r="H79" t="n">
         <v>2100</v>
@@ -2747,7 +2747,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G82" t="n">
-        <v>9.74545764923096</v>
+        <v>9.74545860290527</v>
       </c>
       <c r="H82" t="n">
         <v>13600</v>
@@ -2776,7 +2776,7 @@
         <v>10.0500001907349</v>
       </c>
       <c r="G83" t="n">
-        <v>9.4174861907959</v>
+        <v>9.41748714447021</v>
       </c>
       <c r="H83" t="n">
         <v>13500</v>
@@ -2805,7 +2805,7 @@
         <v>10.0500001907349</v>
       </c>
       <c r="G84" t="n">
-        <v>9.4174861907959</v>
+        <v>9.41748714447021</v>
       </c>
       <c r="H84" t="n">
         <v>16000</v>
@@ -2950,7 +2950,7 @@
         <v>10.5500001907349</v>
       </c>
       <c r="G89" t="n">
-        <v>9.88601779937744</v>
+        <v>9.88601875305176</v>
       </c>
       <c r="H89" t="n">
         <v>4400</v>
@@ -3008,7 +3008,7 @@
         <v>10.0500001907349</v>
       </c>
       <c r="G91" t="n">
-        <v>9.4174861907959</v>
+        <v>9.41748714447021</v>
       </c>
       <c r="H91" t="n">
         <v>1800</v>
@@ -3037,7 +3037,7 @@
         <v>9.92000007629395</v>
       </c>
       <c r="G92" t="n">
-        <v>9.29566860198975</v>
+        <v>9.29566764831543</v>
       </c>
       <c r="H92" t="n">
         <v>5200</v>
@@ -3066,7 +3066,7 @@
         <v>9.72000026702881</v>
       </c>
       <c r="G93" t="n">
-        <v>9.10825634002686</v>
+        <v>9.10825538635254</v>
       </c>
       <c r="H93" t="n">
         <v>3500</v>
@@ -3095,7 +3095,7 @@
         <v>9.73999977111816</v>
       </c>
       <c r="G94" t="n">
-        <v>9.12699699401855</v>
+        <v>9.12699604034424</v>
       </c>
       <c r="H94" t="n">
         <v>2000</v>
@@ -3211,7 +3211,7 @@
         <v>9.53999996185303</v>
       </c>
       <c r="G98" t="n">
-        <v>8.93958473205566</v>
+        <v>8.93958282470703</v>
       </c>
       <c r="H98" t="n">
         <v>900</v>
@@ -3240,7 +3240,7 @@
         <v>9.34000015258789</v>
       </c>
       <c r="G99" t="n">
-        <v>8.75217151641846</v>
+        <v>8.75217056274414</v>
       </c>
       <c r="H99" t="n">
         <v>600</v>
@@ -3269,7 +3269,7 @@
         <v>9.14000034332275</v>
       </c>
       <c r="G100" t="n">
-        <v>8.56475925445557</v>
+        <v>8.56475830078125</v>
       </c>
       <c r="H100" t="n">
         <v>800</v>
@@ -3385,7 +3385,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G104" t="n">
-        <v>8.6209831237793</v>
+        <v>8.62098217010498</v>
       </c>
       <c r="H104" t="n">
         <v>1400</v>
@@ -3414,7 +3414,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G105" t="n">
-        <v>8.52727699279785</v>
+        <v>8.52727603912354</v>
       </c>
       <c r="H105" t="n">
         <v>1300</v>
@@ -3443,7 +3443,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G106" t="n">
-        <v>8.6209831237793</v>
+        <v>8.62098217010498</v>
       </c>
       <c r="H106" t="n">
         <v>200</v>
@@ -3472,7 +3472,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G107" t="n">
-        <v>8.6209831237793</v>
+        <v>8.62098217010498</v>
       </c>
       <c r="H107" t="n">
         <v>0</v>
@@ -3559,7 +3559,7 @@
         <v>9.4399995803833</v>
       </c>
       <c r="G110" t="n">
-        <v>8.8458776473999</v>
+        <v>8.84587669372559</v>
       </c>
       <c r="H110" t="n">
         <v>200</v>
@@ -3733,7 +3733,7 @@
         <v>10.5500001907349</v>
       </c>
       <c r="G116" t="n">
-        <v>9.88601779937744</v>
+        <v>9.88601875305176</v>
       </c>
       <c r="H116" t="n">
         <v>2700</v>
@@ -3762,7 +3762,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G117" t="n">
-        <v>9.74545764923096</v>
+        <v>9.74545860290527</v>
       </c>
       <c r="H117" t="n">
         <v>300</v>
@@ -3791,7 +3791,7 @@
         <v>10.5500001907349</v>
       </c>
       <c r="G118" t="n">
-        <v>9.88601779937744</v>
+        <v>9.88601875305176</v>
       </c>
       <c r="H118" t="n">
         <v>100</v>
@@ -3994,7 +3994,7 @@
         <v>9.57999992370605</v>
       </c>
       <c r="G125" t="n">
-        <v>8.97706604003906</v>
+        <v>8.97706699371338</v>
       </c>
       <c r="H125" t="n">
         <v>1400</v>
@@ -4081,7 +4081,7 @@
         <v>9.88000011444092</v>
       </c>
       <c r="G128" t="n">
-        <v>9.25818538665771</v>
+        <v>9.25818634033203</v>
       </c>
       <c r="H128" t="n">
         <v>2400</v>
@@ -4110,7 +4110,7 @@
         <v>9.84000015258789</v>
       </c>
       <c r="G129" t="n">
-        <v>9.22070407867432</v>
+        <v>9.22070217132568</v>
       </c>
       <c r="H129" t="n">
         <v>200</v>
@@ -4139,7 +4139,7 @@
         <v>9.92000007629395</v>
       </c>
       <c r="G130" t="n">
-        <v>9.29566860198975</v>
+        <v>9.29566764831543</v>
       </c>
       <c r="H130" t="n">
         <v>200</v>
@@ -4168,7 +4168,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G131" t="n">
-        <v>9.65175342559814</v>
+        <v>9.65175247192383</v>
       </c>
       <c r="H131" t="n">
         <v>2700</v>
@@ -4197,7 +4197,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G132" t="n">
-        <v>9.65175342559814</v>
+        <v>9.65175247192383</v>
       </c>
       <c r="H132" t="n">
         <v>100</v>
@@ -4226,7 +4226,7 @@
         <v>9.97999954223633</v>
       </c>
       <c r="G133" t="n">
-        <v>9.35189151763916</v>
+        <v>9.35189247131348</v>
       </c>
       <c r="H133" t="n">
         <v>500</v>
@@ -4342,7 +4342,7 @@
         <v>10.5500001907349</v>
       </c>
       <c r="G137" t="n">
-        <v>9.88601779937744</v>
+        <v>9.88601875305176</v>
       </c>
       <c r="H137" t="n">
         <v>1000</v>
@@ -4545,7 +4545,7 @@
         <v>9.47999954223633</v>
       </c>
       <c r="G144" t="n">
-        <v>8.88336086273193</v>
+        <v>8.88335990905762</v>
       </c>
       <c r="H144" t="n">
         <v>1800</v>
@@ -4574,7 +4574,7 @@
         <v>9.5600004196167</v>
       </c>
       <c r="G145" t="n">
-        <v>8.95832633972168</v>
+        <v>8.95832538604736</v>
       </c>
       <c r="H145" t="n">
         <v>1400</v>
@@ -4661,7 +4661,7 @@
         <v>9.31999969482422</v>
       </c>
       <c r="G148" t="n">
-        <v>8.73342990875244</v>
+        <v>8.73342895507812</v>
       </c>
       <c r="H148" t="n">
         <v>1000</v>
@@ -5125,7 +5125,7 @@
         <v>9.97999954223633</v>
       </c>
       <c r="G164" t="n">
-        <v>9.35189151763916</v>
+        <v>9.35189247131348</v>
       </c>
       <c r="H164" t="n">
         <v>400</v>
@@ -5270,7 +5270,7 @@
         <v>9.15999984741211</v>
       </c>
       <c r="G169" t="n">
-        <v>8.58349990844727</v>
+        <v>8.58350086212158</v>
       </c>
       <c r="H169" t="n">
         <v>16200</v>
@@ -5357,7 +5357,7 @@
         <v>9.5600004196167</v>
       </c>
       <c r="G172" t="n">
-        <v>8.95832633972168</v>
+        <v>8.95832538604736</v>
       </c>
       <c r="H172" t="n">
         <v>200</v>
@@ -5734,7 +5734,7 @@
         <v>9.72000026702881</v>
       </c>
       <c r="G185" t="n">
-        <v>9.10825634002686</v>
+        <v>9.10825538635254</v>
       </c>
       <c r="H185" t="n">
         <v>1300</v>
@@ -5763,7 +5763,7 @@
         <v>9.84000015258789</v>
       </c>
       <c r="G186" t="n">
-        <v>9.22070407867432</v>
+        <v>9.22070217132568</v>
       </c>
       <c r="H186" t="n">
         <v>400</v>
@@ -5792,7 +5792,7 @@
         <v>9.97999954223633</v>
       </c>
       <c r="G187" t="n">
-        <v>9.35189151763916</v>
+        <v>9.35189247131348</v>
       </c>
       <c r="H187" t="n">
         <v>3900</v>
@@ -5821,7 +5821,7 @@
         <v>9.97999954223633</v>
       </c>
       <c r="G188" t="n">
-        <v>9.35189151763916</v>
+        <v>9.35189247131348</v>
       </c>
       <c r="H188" t="n">
         <v>300</v>
@@ -5850,7 +5850,7 @@
         <v>9.61999988555908</v>
       </c>
       <c r="G189" t="n">
-        <v>9.01454925537109</v>
+        <v>9.01454830169678</v>
       </c>
       <c r="H189" t="n">
         <v>1400</v>
@@ -5995,7 +5995,7 @@
         <v>9.64000034332275</v>
       </c>
       <c r="G194" t="n">
-        <v>9.03329086303711</v>
+        <v>9.03328990936279</v>
       </c>
       <c r="H194" t="n">
         <v>100</v>
@@ -6024,7 +6024,7 @@
         <v>9.53999996185303</v>
       </c>
       <c r="G195" t="n">
-        <v>8.93958473205566</v>
+        <v>8.93958282470703</v>
       </c>
       <c r="H195" t="n">
         <v>600</v>
@@ -6053,7 +6053,7 @@
         <v>9.53999996185303</v>
       </c>
       <c r="G196" t="n">
-        <v>8.93958473205566</v>
+        <v>8.93958282470703</v>
       </c>
       <c r="H196" t="n">
         <v>0</v>
@@ -6082,7 +6082,7 @@
         <v>9.53999996185303</v>
       </c>
       <c r="G197" t="n">
-        <v>8.93958473205566</v>
+        <v>8.93958282470703</v>
       </c>
       <c r="H197" t="n">
         <v>0</v>
@@ -6169,7 +6169,7 @@
         <v>8.85999965667725</v>
       </c>
       <c r="G200" t="n">
-        <v>8.30238056182861</v>
+        <v>8.30238151550293</v>
       </c>
       <c r="H200" t="n">
         <v>12000</v>
@@ -6285,7 +6285,7 @@
         <v>9.0600004196167</v>
       </c>
       <c r="G204" t="n">
-        <v>8.48979377746582</v>
+        <v>8.48979473114014</v>
       </c>
       <c r="H204" t="n">
         <v>2200</v>
@@ -6314,7 +6314,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G205" t="n">
-        <v>8.33986377716064</v>
+        <v>8.33986282348633</v>
       </c>
       <c r="H205" t="n">
         <v>100</v>
@@ -6459,7 +6459,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G210" t="n">
-        <v>8.6209831237793</v>
+        <v>8.62098217010498</v>
       </c>
       <c r="H210" t="n">
         <v>100</v>
@@ -6488,7 +6488,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G211" t="n">
-        <v>8.6209831237793</v>
+        <v>8.62098217010498</v>
       </c>
       <c r="H211" t="n">
         <v>400</v>
@@ -6517,7 +6517,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G212" t="n">
-        <v>8.52727699279785</v>
+        <v>8.52727603912354</v>
       </c>
       <c r="H212" t="n">
         <v>1500</v>
@@ -6546,7 +6546,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G213" t="n">
-        <v>8.52727699279785</v>
+        <v>8.52727603912354</v>
       </c>
       <c r="H213" t="n">
         <v>0</v>
@@ -6575,7 +6575,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G214" t="n">
-        <v>8.52727699279785</v>
+        <v>8.52727603912354</v>
       </c>
       <c r="H214" t="n">
         <v>0</v>
@@ -6604,7 +6604,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G215" t="n">
-        <v>8.52727699279785</v>
+        <v>8.52727603912354</v>
       </c>
       <c r="H215" t="n">
         <v>0</v>
@@ -6633,7 +6633,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G216" t="n">
-        <v>8.52727699279785</v>
+        <v>8.52727603912354</v>
       </c>
       <c r="H216" t="n">
         <v>300</v>
@@ -6662,7 +6662,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G217" t="n">
-        <v>8.52727699279785</v>
+        <v>8.52727603912354</v>
       </c>
       <c r="H217" t="n">
         <v>0</v>
@@ -6691,7 +6691,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G218" t="n">
-        <v>8.52727699279785</v>
+        <v>8.52727603912354</v>
       </c>
       <c r="H218" t="n">
         <v>0</v>
@@ -6720,7 +6720,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G219" t="n">
-        <v>8.52727699279785</v>
+        <v>8.52727603912354</v>
       </c>
       <c r="H219" t="n">
         <v>0</v>
@@ -6749,7 +6749,7 @@
         <v>8.9399995803833</v>
       </c>
       <c r="G220" t="n">
-        <v>8.37734603881836</v>
+        <v>8.37734508514404</v>
       </c>
       <c r="H220" t="n">
         <v>200</v>
@@ -6778,7 +6778,7 @@
         <v>8.9399995803833</v>
       </c>
       <c r="G221" t="n">
-        <v>8.37734603881836</v>
+        <v>8.37734508514404</v>
       </c>
       <c r="H221" t="n">
         <v>0</v>
@@ -6807,7 +6807,7 @@
         <v>8.9399995803833</v>
       </c>
       <c r="G222" t="n">
-        <v>8.37734603881836</v>
+        <v>8.37734508514404</v>
       </c>
       <c r="H222" t="n">
         <v>0</v>
@@ -6836,7 +6836,7 @@
         <v>8.9399995803833</v>
       </c>
       <c r="G223" t="n">
-        <v>8.37734603881836</v>
+        <v>8.37734508514404</v>
       </c>
       <c r="H223" t="n">
         <v>0</v>
@@ -6865,7 +6865,7 @@
         <v>8.9399995803833</v>
       </c>
       <c r="G224" t="n">
-        <v>8.37734603881836</v>
+        <v>8.37734508514404</v>
       </c>
       <c r="H224" t="n">
         <v>0</v>
@@ -6894,7 +6894,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G225" t="n">
-        <v>8.52727699279785</v>
+        <v>8.52727603912354</v>
       </c>
       <c r="H225" t="n">
         <v>300</v>
@@ -6923,7 +6923,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G226" t="n">
-        <v>8.52727699279785</v>
+        <v>8.52727603912354</v>
       </c>
       <c r="H226" t="n">
         <v>0</v>
@@ -6952,7 +6952,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G227" t="n">
-        <v>8.52727699279785</v>
+        <v>8.52727603912354</v>
       </c>
       <c r="H227" t="n">
         <v>900</v>
@@ -6981,7 +6981,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G228" t="n">
-        <v>8.52727699279785</v>
+        <v>8.52727603912354</v>
       </c>
       <c r="H228" t="n">
         <v>0</v>
@@ -7010,7 +7010,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G229" t="n">
-        <v>8.52727699279785</v>
+        <v>8.52727603912354</v>
       </c>
       <c r="H229" t="n">
         <v>0</v>
@@ -7039,7 +7039,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G230" t="n">
-        <v>8.52727699279785</v>
+        <v>8.52727603912354</v>
       </c>
       <c r="H230" t="n">
         <v>0</v>
@@ -7068,7 +7068,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G231" t="n">
-        <v>8.52727699279785</v>
+        <v>8.52727603912354</v>
       </c>
       <c r="H231" t="n">
         <v>0</v>
@@ -7097,7 +7097,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G232" t="n">
-        <v>8.52727699279785</v>
+        <v>8.52727603912354</v>
       </c>
       <c r="H232" t="n">
         <v>0</v>
@@ -7126,7 +7126,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G233" t="n">
-        <v>8.52727699279785</v>
+        <v>8.52727603912354</v>
       </c>
       <c r="H233" t="n">
         <v>0</v>
@@ -7155,7 +7155,7 @@
         <v>8.9399995803833</v>
       </c>
       <c r="G234" t="n">
-        <v>8.37734603881836</v>
+        <v>8.37734508514404</v>
       </c>
       <c r="H234" t="n">
         <v>800</v>
@@ -7242,7 +7242,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G237" t="n">
-        <v>8.33986377716064</v>
+        <v>8.33986282348633</v>
       </c>
       <c r="H237" t="n">
         <v>9400</v>
@@ -7271,7 +7271,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G238" t="n">
-        <v>8.33986377716064</v>
+        <v>8.33986282348633</v>
       </c>
       <c r="H238" t="n">
         <v>300</v>
@@ -7300,7 +7300,7 @@
         <v>8.73999977111816</v>
       </c>
       <c r="G239" t="n">
-        <v>8.18993377685547</v>
+        <v>8.18993282318115</v>
       </c>
       <c r="H239" t="n">
         <v>500</v>
@@ -7358,7 +7358,7 @@
         <v>8.42000007629395</v>
       </c>
       <c r="G241" t="n">
-        <v>7.8900728225708</v>
+        <v>7.89007329940796</v>
       </c>
       <c r="H241" t="n">
         <v>1500</v>
@@ -7387,7 +7387,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G242" t="n">
-        <v>7.68391847610474</v>
+        <v>7.68391895294189</v>
       </c>
       <c r="H242" t="n">
         <v>10000</v>
@@ -7416,7 +7416,7 @@
         <v>8.15999984741211</v>
       </c>
       <c r="G243" t="n">
-        <v>7.64643669128418</v>
+        <v>7.64643621444702</v>
       </c>
       <c r="H243" t="n">
         <v>28200</v>
@@ -7590,7 +7590,7 @@
         <v>8.03999996185303</v>
       </c>
       <c r="G249" t="n">
-        <v>7.53398895263672</v>
+        <v>7.53398942947388</v>
       </c>
       <c r="H249" t="n">
         <v>400</v>
@@ -7648,7 +7648,7 @@
         <v>8.23999977111816</v>
       </c>
       <c r="G251" t="n">
-        <v>7.72140121459961</v>
+        <v>7.72140073776245</v>
       </c>
       <c r="H251" t="n">
         <v>100</v>
@@ -7677,7 +7677,7 @@
         <v>8.26000022888184</v>
       </c>
       <c r="G252" t="n">
-        <v>7.74014282226562</v>
+        <v>7.74014377593994</v>
       </c>
       <c r="H252" t="n">
         <v>300</v>
@@ -7735,7 +7735,7 @@
         <v>8.03999996185303</v>
       </c>
       <c r="G254" t="n">
-        <v>7.53398895263672</v>
+        <v>7.53398942947388</v>
       </c>
       <c r="H254" t="n">
         <v>2500</v>
@@ -7764,7 +7764,7 @@
         <v>7.61999988555908</v>
       </c>
       <c r="G255" t="n">
-        <v>7.14042234420776</v>
+        <v>7.14042186737061</v>
       </c>
       <c r="H255" t="n">
         <v>13900</v>
@@ -7793,7 +7793,7 @@
         <v>7.71999979019165</v>
       </c>
       <c r="G256" t="n">
-        <v>7.23412847518921</v>
+        <v>7.23412799835205</v>
       </c>
       <c r="H256" t="n">
         <v>7300</v>
@@ -7938,7 +7938,7 @@
         <v>7.84000015258789</v>
       </c>
       <c r="G261" t="n">
-        <v>7.34657621383667</v>
+        <v>7.34657669067383</v>
       </c>
       <c r="H261" t="n">
         <v>2200</v>
@@ -8054,7 +8054,7 @@
         <v>7.48000001907349</v>
       </c>
       <c r="G265" t="n">
-        <v>7.00923347473145</v>
+        <v>7.0092339515686</v>
       </c>
       <c r="H265" t="n">
         <v>10400</v>
@@ -8083,7 +8083,7 @@
         <v>7.61999988555908</v>
       </c>
       <c r="G266" t="n">
-        <v>7.14042234420776</v>
+        <v>7.14042186737061</v>
       </c>
       <c r="H266" t="n">
         <v>600</v>
@@ -8141,7 +8141,7 @@
         <v>7.48000001907349</v>
       </c>
       <c r="G268" t="n">
-        <v>7.00923347473145</v>
+        <v>7.0092339515686</v>
       </c>
       <c r="H268" t="n">
         <v>4100</v>
@@ -8199,7 +8199,7 @@
         <v>7.71999979019165</v>
       </c>
       <c r="G270" t="n">
-        <v>7.23412847518921</v>
+        <v>7.23412799835205</v>
       </c>
       <c r="H270" t="n">
         <v>6600</v>
@@ -8228,7 +8228,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G271" t="n">
-        <v>7.7776255607605</v>
+        <v>7.77762603759766</v>
       </c>
       <c r="H271" t="n">
         <v>9100</v>
@@ -8344,7 +8344,7 @@
         <v>9.14000034332275</v>
       </c>
       <c r="G275" t="n">
-        <v>8.56475925445557</v>
+        <v>8.56475830078125</v>
       </c>
       <c r="H275" t="n">
         <v>4000</v>
@@ -8373,7 +8373,7 @@
         <v>9.11999988555908</v>
       </c>
       <c r="G276" t="n">
-        <v>8.54601764678955</v>
+        <v>8.54601669311523</v>
       </c>
       <c r="H276" t="n">
         <v>1600</v>
@@ -8402,7 +8402,7 @@
         <v>9.14000034332275</v>
       </c>
       <c r="G277" t="n">
-        <v>8.56475925445557</v>
+        <v>8.56475830078125</v>
       </c>
       <c r="H277" t="n">
         <v>600</v>
@@ -8431,7 +8431,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G278" t="n">
-        <v>8.6209831237793</v>
+        <v>8.62098217010498</v>
       </c>
       <c r="H278" t="n">
         <v>300</v>
@@ -8460,7 +8460,7 @@
         <v>9.11999988555908</v>
       </c>
       <c r="G279" t="n">
-        <v>8.54601764678955</v>
+        <v>8.54601669311523</v>
       </c>
       <c r="H279" t="n">
         <v>2000</v>
@@ -8489,7 +8489,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G280" t="n">
-        <v>8.52727699279785</v>
+        <v>8.52727603912354</v>
       </c>
       <c r="H280" t="n">
         <v>1100</v>
@@ -8547,7 +8547,7 @@
         <v>8.92000007629395</v>
       </c>
       <c r="G282" t="n">
-        <v>8.35860538482666</v>
+        <v>8.35860443115234</v>
       </c>
       <c r="H282" t="n">
         <v>200</v>
@@ -8576,7 +8576,7 @@
         <v>8.76000022888184</v>
       </c>
       <c r="G283" t="n">
-        <v>8.20867443084717</v>
+        <v>8.20867538452148</v>
       </c>
       <c r="H283" t="n">
         <v>2800</v>
@@ -8605,7 +8605,7 @@
         <v>8.81999969482422</v>
       </c>
       <c r="G284" t="n">
-        <v>8.2648983001709</v>
+        <v>8.26489734649658</v>
       </c>
       <c r="H284" t="n">
         <v>700</v>
@@ -8750,7 +8750,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G289" t="n">
-        <v>8.52727699279785</v>
+        <v>8.52727603912354</v>
       </c>
       <c r="H289" t="n">
         <v>2100</v>
@@ -8808,7 +8808,7 @@
         <v>9.11999988555908</v>
       </c>
       <c r="G291" t="n">
-        <v>8.54601764678955</v>
+        <v>8.54601669311523</v>
       </c>
       <c r="H291" t="n">
         <v>3400</v>
@@ -8837,7 +8837,7 @@
         <v>9.11999988555908</v>
       </c>
       <c r="G292" t="n">
-        <v>8.54601764678955</v>
+        <v>8.54601669311523</v>
       </c>
       <c r="H292" t="n">
         <v>2100</v>
@@ -8924,7 +8924,7 @@
         <v>9.14000034332275</v>
       </c>
       <c r="G295" t="n">
-        <v>8.56475925445557</v>
+        <v>8.56475830078125</v>
       </c>
       <c r="H295" t="n">
         <v>200</v>
@@ -8953,7 +8953,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G296" t="n">
-        <v>8.6209831237793</v>
+        <v>8.62098217010498</v>
       </c>
       <c r="H296" t="n">
         <v>1000</v>
@@ -8982,7 +8982,7 @@
         <v>9.14000034332275</v>
       </c>
       <c r="G297" t="n">
-        <v>8.56475925445557</v>
+        <v>8.56475830078125</v>
       </c>
       <c r="H297" t="n">
         <v>500</v>
@@ -9011,7 +9011,7 @@
         <v>9.14000034332275</v>
       </c>
       <c r="G298" t="n">
-        <v>8.56475925445557</v>
+        <v>8.56475830078125</v>
       </c>
       <c r="H298" t="n">
         <v>0</v>
@@ -9040,7 +9040,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G299" t="n">
-        <v>8.52727699279785</v>
+        <v>8.52727603912354</v>
       </c>
       <c r="H299" t="n">
         <v>700</v>
@@ -9069,7 +9069,7 @@
         <v>8.9399995803833</v>
       </c>
       <c r="G300" t="n">
-        <v>8.37734603881836</v>
+        <v>8.37734508514404</v>
       </c>
       <c r="H300" t="n">
         <v>300</v>
@@ -9098,7 +9098,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G301" t="n">
-        <v>8.52727699279785</v>
+        <v>8.52727603912354</v>
       </c>
       <c r="H301" t="n">
         <v>300</v>
@@ -9185,7 +9185,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G304" t="n">
-        <v>8.33986377716064</v>
+        <v>8.33986282348633</v>
       </c>
       <c r="H304" t="n">
         <v>300</v>
@@ -9417,7 +9417,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G312" t="n">
-        <v>7.83384895324707</v>
+        <v>7.83384990692139</v>
       </c>
       <c r="H312" t="n">
         <v>1100</v>
@@ -9446,7 +9446,7 @@
         <v>8.61999988555908</v>
       </c>
       <c r="G313" t="n">
-        <v>8.07748603820801</v>
+        <v>8.07748508453369</v>
       </c>
       <c r="H313" t="n">
         <v>5400</v>
@@ -9649,7 +9649,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G320" t="n">
-        <v>7.87133121490479</v>
+        <v>7.87133169174194</v>
       </c>
       <c r="H320" t="n">
         <v>1000</v>
@@ -9707,7 +9707,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G322" t="n">
-        <v>7.7776255607605</v>
+        <v>7.77762603759766</v>
       </c>
       <c r="H322" t="n">
         <v>3500</v>
@@ -9736,7 +9736,7 @@
         <v>8.27999973297119</v>
       </c>
       <c r="G323" t="n">
-        <v>7.75888442993164</v>
+        <v>7.75888395309448</v>
       </c>
       <c r="H323" t="n">
         <v>200</v>
@@ -9765,7 +9765,7 @@
         <v>8.27999973297119</v>
       </c>
       <c r="G324" t="n">
-        <v>7.75888442993164</v>
+        <v>7.75888395309448</v>
       </c>
       <c r="H324" t="n">
         <v>2000</v>
@@ -9794,7 +9794,7 @@
         <v>8.27999973297119</v>
       </c>
       <c r="G325" t="n">
-        <v>7.75888442993164</v>
+        <v>7.75888395309448</v>
       </c>
       <c r="H325" t="n">
         <v>6600</v>
@@ -9823,7 +9823,7 @@
         <v>8.31999969482422</v>
       </c>
       <c r="G326" t="n">
-        <v>7.79636716842651</v>
+        <v>7.7963662147522</v>
       </c>
       <c r="H326" t="n">
         <v>3800</v>
@@ -9852,7 +9852,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G327" t="n">
-        <v>7.7776255607605</v>
+        <v>7.77762603759766</v>
       </c>
       <c r="H327" t="n">
         <v>2400</v>
@@ -9881,7 +9881,7 @@
         <v>8.34000015258789</v>
       </c>
       <c r="G328" t="n">
-        <v>7.81510829925537</v>
+        <v>7.81510782241821</v>
       </c>
       <c r="H328" t="n">
         <v>2400</v>
@@ -9910,7 +9910,7 @@
         <v>8.34000015258789</v>
       </c>
       <c r="G329" t="n">
-        <v>7.81510829925537</v>
+        <v>7.81510782241821</v>
       </c>
       <c r="H329" t="n">
         <v>1700</v>
@@ -9939,7 +9939,7 @@
         <v>8.34000015258789</v>
       </c>
       <c r="G330" t="n">
-        <v>7.81510829925537</v>
+        <v>7.81510782241821</v>
       </c>
       <c r="H330" t="n">
         <v>800</v>
@@ -9968,7 +9968,7 @@
         <v>8.34000015258789</v>
       </c>
       <c r="G331" t="n">
-        <v>7.81510829925537</v>
+        <v>7.81510782241821</v>
       </c>
       <c r="H331" t="n">
         <v>1400</v>
@@ -9997,7 +9997,7 @@
         <v>8.34000015258789</v>
       </c>
       <c r="G332" t="n">
-        <v>7.81510829925537</v>
+        <v>7.81510782241821</v>
       </c>
       <c r="H332" t="n">
         <v>0</v>
@@ -10084,7 +10084,7 @@
         <v>8.42000007629395</v>
       </c>
       <c r="G335" t="n">
-        <v>7.8900728225708</v>
+        <v>7.89007329940796</v>
       </c>
       <c r="H335" t="n">
         <v>4600</v>
@@ -10258,7 +10258,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G341" t="n">
-        <v>8.33986377716064</v>
+        <v>8.33986282348633</v>
       </c>
       <c r="H341" t="n">
         <v>3000</v>
@@ -10780,7 +10780,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G359" t="n">
-        <v>9.04265975952148</v>
+        <v>9.0426607131958</v>
       </c>
       <c r="H359" t="n">
         <v>4000</v>
@@ -10809,7 +10809,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G360" t="n">
-        <v>9.04265975952148</v>
+        <v>9.0426607131958</v>
       </c>
       <c r="H360" t="n">
         <v>0</v>
@@ -10838,7 +10838,7 @@
         <v>9.75</v>
       </c>
       <c r="G361" t="n">
-        <v>9.13636684417725</v>
+        <v>9.13636779785156</v>
       </c>
       <c r="H361" t="n">
         <v>1500</v>
@@ -10896,7 +10896,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G363" t="n">
-        <v>9.04265975952148</v>
+        <v>9.0426607131958</v>
       </c>
       <c r="H363" t="n">
         <v>100</v>
@@ -10925,7 +10925,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G364" t="n">
-        <v>9.04265975952148</v>
+        <v>9.0426607131958</v>
       </c>
       <c r="H364" t="n">
         <v>0</v>
@@ -10954,7 +10954,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G365" t="n">
-        <v>9.04265975952148</v>
+        <v>9.0426607131958</v>
       </c>
       <c r="H365" t="n">
         <v>300</v>
@@ -11128,7 +11128,7 @@
         <v>9.75</v>
       </c>
       <c r="G371" t="n">
-        <v>9.13636684417725</v>
+        <v>9.13636779785156</v>
       </c>
       <c r="H371" t="n">
         <v>3600</v>
@@ -11157,7 +11157,7 @@
         <v>9.75</v>
       </c>
       <c r="G372" t="n">
-        <v>9.13636684417725</v>
+        <v>9.13636779785156</v>
       </c>
       <c r="H372" t="n">
         <v>100</v>
@@ -11215,7 +11215,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G374" t="n">
-        <v>9.04265975952148</v>
+        <v>9.0426607131958</v>
       </c>
       <c r="H374" t="n">
         <v>100</v>
@@ -11244,7 +11244,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G375" t="n">
-        <v>9.30551719665527</v>
+        <v>9.30551815032959</v>
       </c>
       <c r="H375" t="n">
         <v>600</v>
@@ -11273,7 +11273,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G376" t="n">
-        <v>9.25755023956299</v>
+        <v>9.2575511932373</v>
       </c>
       <c r="H376" t="n">
         <v>2500</v>
@@ -11331,7 +11331,7 @@
         <v>10</v>
       </c>
       <c r="G378" t="n">
-        <v>9.59331703186035</v>
+        <v>9.59331798553467</v>
       </c>
       <c r="H378" t="n">
         <v>7200</v>
@@ -11708,7 +11708,7 @@
         <v>10</v>
       </c>
       <c r="G391" t="n">
-        <v>9.59331703186035</v>
+        <v>9.59331798553467</v>
       </c>
       <c r="H391" t="n">
         <v>300</v>
@@ -11853,7 +11853,7 @@
         <v>10</v>
       </c>
       <c r="G396" t="n">
-        <v>9.59331703186035</v>
+        <v>9.59331798553467</v>
       </c>
       <c r="H396" t="n">
         <v>500</v>
@@ -11882,7 +11882,7 @@
         <v>10</v>
       </c>
       <c r="G397" t="n">
-        <v>9.59331703186035</v>
+        <v>9.59331798553467</v>
       </c>
       <c r="H397" t="n">
         <v>0</v>
@@ -11940,7 +11940,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G399" t="n">
-        <v>9.30551719665527</v>
+        <v>9.30551815032959</v>
       </c>
       <c r="H399" t="n">
         <v>1600</v>
@@ -11998,7 +11998,7 @@
         <v>9.35000038146973</v>
       </c>
       <c r="G401" t="n">
-        <v>8.96975135803223</v>
+        <v>8.96975231170654</v>
       </c>
       <c r="H401" t="n">
         <v>5200</v>
@@ -12288,7 +12288,7 @@
         <v>10</v>
       </c>
       <c r="G411" t="n">
-        <v>9.59331703186035</v>
+        <v>9.59331798553467</v>
       </c>
       <c r="H411" t="n">
         <v>600</v>
@@ -12433,7 +12433,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G416" t="n">
-        <v>9.25755023956299</v>
+        <v>9.2575511932373</v>
       </c>
       <c r="H416" t="n">
         <v>700</v>
@@ -12462,7 +12462,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G417" t="n">
-        <v>9.25755023956299</v>
+        <v>9.2575511932373</v>
       </c>
       <c r="H417" t="n">
         <v>0</v>
@@ -12491,7 +12491,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G418" t="n">
-        <v>9.25755023956299</v>
+        <v>9.2575511932373</v>
       </c>
       <c r="H418" t="n">
         <v>0</v>
@@ -12520,7 +12520,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G419" t="n">
-        <v>9.30551719665527</v>
+        <v>9.30551815032959</v>
       </c>
       <c r="H419" t="n">
         <v>1700</v>
@@ -12578,7 +12578,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G421" t="n">
-        <v>9.0177173614502</v>
+        <v>9.01771831512451</v>
       </c>
       <c r="H421" t="n">
         <v>100</v>
@@ -12636,7 +12636,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G423" t="n">
-        <v>9.25755023956299</v>
+        <v>9.2575511932373</v>
       </c>
       <c r="H423" t="n">
         <v>1100</v>
@@ -12665,7 +12665,7 @@
         <v>9.35000038146973</v>
       </c>
       <c r="G424" t="n">
-        <v>8.96975135803223</v>
+        <v>8.96975231170654</v>
       </c>
       <c r="H424" t="n">
         <v>500</v>
@@ -12694,7 +12694,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G425" t="n">
-        <v>8.53805255889893</v>
+        <v>8.53805160522461</v>
       </c>
       <c r="H425" t="n">
         <v>1300</v>
@@ -12810,7 +12810,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G429" t="n">
-        <v>9.25755023956299</v>
+        <v>9.2575511932373</v>
       </c>
       <c r="H429" t="n">
         <v>700</v>
@@ -12839,7 +12839,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G430" t="n">
-        <v>9.25755023956299</v>
+        <v>9.2575511932373</v>
       </c>
       <c r="H430" t="n">
         <v>0</v>
@@ -12897,7 +12897,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G432" t="n">
-        <v>9.0177173614502</v>
+        <v>9.01771831512451</v>
       </c>
       <c r="H432" t="n">
         <v>100</v>
@@ -12926,7 +12926,7 @@
         <v>9.35000038146973</v>
       </c>
       <c r="G433" t="n">
-        <v>8.96975135803223</v>
+        <v>8.96975231170654</v>
       </c>
       <c r="H433" t="n">
         <v>1200</v>
@@ -12984,7 +12984,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G435" t="n">
-        <v>9.30551719665527</v>
+        <v>9.30551815032959</v>
       </c>
       <c r="H435" t="n">
         <v>200</v>
@@ -13013,7 +13013,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G436" t="n">
-        <v>9.25755023956299</v>
+        <v>9.2575511932373</v>
       </c>
       <c r="H436" t="n">
         <v>400</v>
@@ -13071,7 +13071,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G438" t="n">
-        <v>9.0177173614502</v>
+        <v>9.01771831512451</v>
       </c>
       <c r="H438" t="n">
         <v>600</v>
@@ -13100,7 +13100,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G439" t="n">
-        <v>9.30551719665527</v>
+        <v>9.30551815032959</v>
       </c>
       <c r="H439" t="n">
         <v>200</v>
@@ -13129,7 +13129,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G440" t="n">
-        <v>9.30551719665527</v>
+        <v>9.30551815032959</v>
       </c>
       <c r="H440" t="n">
         <v>500</v>
@@ -13158,7 +13158,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G441" t="n">
-        <v>9.30551719665527</v>
+        <v>9.30551815032959</v>
       </c>
       <c r="H441" t="n">
         <v>600</v>
@@ -13187,7 +13187,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G442" t="n">
-        <v>9.30551719665527</v>
+        <v>9.30551815032959</v>
       </c>
       <c r="H442" t="n">
         <v>800</v>
@@ -13274,7 +13274,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G445" t="n">
-        <v>9.0177173614502</v>
+        <v>9.01771831512451</v>
       </c>
       <c r="H445" t="n">
         <v>4900</v>
@@ -13303,7 +13303,7 @@
         <v>9.44999980926514</v>
       </c>
       <c r="G446" t="n">
-        <v>9.06568431854248</v>
+        <v>9.0656852722168</v>
       </c>
       <c r="H446" t="n">
         <v>4900</v>
@@ -13332,7 +13332,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G447" t="n">
-        <v>9.0177173614502</v>
+        <v>9.01771831512451</v>
       </c>
       <c r="H447" t="n">
         <v>2000</v>
@@ -13361,7 +13361,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G448" t="n">
-        <v>8.825852394104</v>
+        <v>8.82585144042969</v>
       </c>
       <c r="H448" t="n">
         <v>1200</v>
@@ -13535,7 +13535,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G454" t="n">
-        <v>8.825852394104</v>
+        <v>8.82585144042969</v>
       </c>
       <c r="H454" t="n">
         <v>100</v>
@@ -13564,7 +13564,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G455" t="n">
-        <v>8.825852394104</v>
+        <v>8.82585144042969</v>
       </c>
       <c r="H455" t="n">
         <v>0</v>
@@ -13593,7 +13593,7 @@
         <v>9.35000038146973</v>
       </c>
       <c r="G456" t="n">
-        <v>8.96975135803223</v>
+        <v>8.96975231170654</v>
       </c>
       <c r="H456" t="n">
         <v>9000</v>
@@ -13796,7 +13796,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G463" t="n">
-        <v>8.53805255889893</v>
+        <v>8.53805160522461</v>
       </c>
       <c r="H463" t="n">
         <v>800</v>
@@ -14057,7 +14057,7 @@
         <v>7.75</v>
       </c>
       <c r="G472" t="n">
-        <v>7.43482065200806</v>
+        <v>7.43482112884521</v>
       </c>
       <c r="H472" t="n">
         <v>5500</v>
@@ -14289,7 +14289,7 @@
         <v>7.5</v>
       </c>
       <c r="G480" t="n">
-        <v>7.19498825073242</v>
+        <v>7.19498777389526</v>
       </c>
       <c r="H480" t="n">
         <v>1800</v>
@@ -14318,7 +14318,7 @@
         <v>7.34999990463257</v>
       </c>
       <c r="G481" t="n">
-        <v>7.05108833312988</v>
+        <v>7.05108785629272</v>
       </c>
       <c r="H481" t="n">
         <v>4200</v>
@@ -14347,7 +14347,7 @@
         <v>7.34999990463257</v>
       </c>
       <c r="G482" t="n">
-        <v>7.05108833312988</v>
+        <v>7.05108785629272</v>
       </c>
       <c r="H482" t="n">
         <v>7800</v>
@@ -14434,7 +14434,7 @@
         <v>7</v>
       </c>
       <c r="G485" t="n">
-        <v>6.71532249450684</v>
+        <v>6.71532201766968</v>
       </c>
       <c r="H485" t="n">
         <v>10100</v>
@@ -14724,7 +14724,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G495" t="n">
-        <v>6.04378986358643</v>
+        <v>6.04379034042358</v>
       </c>
       <c r="H495" t="n">
         <v>7900</v>
@@ -15014,7 +15014,7 @@
         <v>7</v>
       </c>
       <c r="G505" t="n">
-        <v>6.71532249450684</v>
+        <v>6.71532201766968</v>
       </c>
       <c r="H505" t="n">
         <v>13500</v>
@@ -15072,7 +15072,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G507" t="n">
-        <v>6.81125545501709</v>
+        <v>6.81125497817993</v>
       </c>
       <c r="H507" t="n">
         <v>3900</v>
@@ -15159,7 +15159,7 @@
         <v>7.75</v>
       </c>
       <c r="G510" t="n">
-        <v>7.43482065200806</v>
+        <v>7.43482112884521</v>
       </c>
       <c r="H510" t="n">
         <v>3700</v>
@@ -15681,7 +15681,7 @@
         <v>7.34999990463257</v>
       </c>
       <c r="G528" t="n">
-        <v>7.05108833312988</v>
+        <v>7.05108785629272</v>
       </c>
       <c r="H528" t="n">
         <v>4000</v>
@@ -15884,7 +15884,7 @@
         <v>7.5</v>
       </c>
       <c r="G535" t="n">
-        <v>7.19498825073242</v>
+        <v>7.19498777389526</v>
       </c>
       <c r="H535" t="n">
         <v>200</v>
@@ -16029,7 +16029,7 @@
         <v>7</v>
       </c>
       <c r="G540" t="n">
-        <v>6.71532249450684</v>
+        <v>6.71532201766968</v>
       </c>
       <c r="H540" t="n">
         <v>7000</v>
@@ -16203,7 +16203,7 @@
         <v>6.94999980926514</v>
       </c>
       <c r="G546" t="n">
-        <v>6.66735553741455</v>
+        <v>6.66735506057739</v>
       </c>
       <c r="H546" t="n">
         <v>2700</v>
@@ -16290,7 +16290,7 @@
         <v>7</v>
       </c>
       <c r="G549" t="n">
-        <v>6.71532249450684</v>
+        <v>6.71532201766968</v>
       </c>
       <c r="H549" t="n">
         <v>9500</v>
@@ -16319,7 +16319,7 @@
         <v>6.94999980926514</v>
       </c>
       <c r="G550" t="n">
-        <v>6.66735553741455</v>
+        <v>6.66735506057739</v>
       </c>
       <c r="H550" t="n">
         <v>16600</v>
@@ -16580,7 +16580,7 @@
         <v>7.75</v>
       </c>
       <c r="G559" t="n">
-        <v>7.43482065200806</v>
+        <v>7.43482112884521</v>
       </c>
       <c r="H559" t="n">
         <v>4000</v>
@@ -16725,7 +16725,7 @@
         <v>7.75</v>
       </c>
       <c r="G564" t="n">
-        <v>7.43482065200806</v>
+        <v>7.43482112884521</v>
       </c>
       <c r="H564" t="n">
         <v>700</v>
@@ -16841,7 +16841,7 @@
         <v>7.75</v>
       </c>
       <c r="G568" t="n">
-        <v>7.43482065200806</v>
+        <v>7.43482112884521</v>
       </c>
       <c r="H568" t="n">
         <v>6900</v>
@@ -17015,7 +17015,7 @@
         <v>8.14999961853027</v>
       </c>
       <c r="G574" t="n">
-        <v>7.81855297088623</v>
+        <v>7.81855344772339</v>
       </c>
       <c r="H574" t="n">
         <v>5200</v>
@@ -17160,7 +17160,7 @@
         <v>7.5</v>
       </c>
       <c r="G579" t="n">
-        <v>7.19498825073242</v>
+        <v>7.19498777389526</v>
       </c>
       <c r="H579" t="n">
         <v>3100</v>
@@ -17247,7 +17247,7 @@
         <v>8.25</v>
       </c>
       <c r="G582" t="n">
-        <v>7.91448640823364</v>
+        <v>7.91448736190796</v>
       </c>
       <c r="H582" t="n">
         <v>10200</v>
@@ -17276,7 +17276,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G583" t="n">
-        <v>7.86651945114136</v>
+        <v>7.86652040481567</v>
       </c>
       <c r="H583" t="n">
         <v>20900</v>
@@ -17334,7 +17334,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G585" t="n">
-        <v>7.86651945114136</v>
+        <v>7.86652040481567</v>
       </c>
       <c r="H585" t="n">
         <v>5700</v>
@@ -17363,7 +17363,7 @@
         <v>7.75</v>
       </c>
       <c r="G586" t="n">
-        <v>7.43482065200806</v>
+        <v>7.43482112884521</v>
       </c>
       <c r="H586" t="n">
         <v>8000</v>
@@ -17392,7 +17392,7 @@
         <v>7.75</v>
       </c>
       <c r="G587" t="n">
-        <v>7.43482065200806</v>
+        <v>7.43482112884521</v>
       </c>
       <c r="H587" t="n">
         <v>1500</v>
@@ -17421,7 +17421,7 @@
         <v>7.75</v>
       </c>
       <c r="G588" t="n">
-        <v>7.43482065200806</v>
+        <v>7.43482112884521</v>
       </c>
       <c r="H588" t="n">
         <v>100</v>
@@ -17479,7 +17479,7 @@
         <v>7.75</v>
       </c>
       <c r="G590" t="n">
-        <v>7.43482065200806</v>
+        <v>7.43482112884521</v>
       </c>
       <c r="H590" t="n">
         <v>2300</v>
@@ -17653,7 +17653,7 @@
         <v>6.94999980926514</v>
       </c>
       <c r="G596" t="n">
-        <v>6.66735553741455</v>
+        <v>6.66735506057739</v>
       </c>
       <c r="H596" t="n">
         <v>1100</v>
@@ -17682,7 +17682,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G597" t="n">
-        <v>6.90718793869019</v>
+        <v>6.90718841552734</v>
       </c>
       <c r="H597" t="n">
         <v>1200</v>
@@ -17711,7 +17711,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G598" t="n">
-        <v>6.90718793869019</v>
+        <v>6.90718841552734</v>
       </c>
       <c r="H598" t="n">
         <v>0</v>
@@ -17798,7 +17798,7 @@
         <v>7.34999990463257</v>
       </c>
       <c r="G601" t="n">
-        <v>7.05108833312988</v>
+        <v>7.05108785629272</v>
       </c>
       <c r="H601" t="n">
         <v>2100</v>
@@ -17827,7 +17827,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G602" t="n">
-        <v>6.90718793869019</v>
+        <v>6.90718841552734</v>
       </c>
       <c r="H602" t="n">
         <v>1600</v>
@@ -17885,7 +17885,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G604" t="n">
-        <v>6.81125545501709</v>
+        <v>6.81125497817993</v>
       </c>
       <c r="H604" t="n">
         <v>15300</v>
@@ -28870,7 +28870,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="E983" t="n">
-        <v>10.8999996185303</v>
+        <v>10.8500003814697</v>
       </c>
       <c r="F983" t="n">
         <v>10.8500003814697</v>
@@ -28882,6 +28882,35 @@
         <v>1300</v>
       </c>
       <c r="I983" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="984">
+      <c r="A984" t="s">
+        <v>9</v>
+      </c>
+      <c r="B984" s="1" t="n">
+        <v>46316.2916666667</v>
+      </c>
+      <c r="C984" t="n">
+        <v>10.8500003814697</v>
+      </c>
+      <c r="D984" t="n">
+        <v>10.8500003814697</v>
+      </c>
+      <c r="E984" t="n">
+        <v>10.8000001907349</v>
+      </c>
+      <c r="F984" t="n">
+        <v>10.8000001907349</v>
+      </c>
+      <c r="G984" t="n">
+        <v>10.8000001907349</v>
+      </c>
+      <c r="H984" t="n">
+        <v>600</v>
+      </c>
+      <c r="I984" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/RDUE.MI.xlsx
+++ b/data/RDUE.MI.xlsx
@@ -456,7 +456,7 @@
         <v>12.0500001907349</v>
       </c>
       <c r="G3" t="n">
-        <v>11.2916126251221</v>
+        <v>11.2916135787964</v>
       </c>
       <c r="H3" t="n">
         <v>19500</v>
@@ -543,7 +543,7 @@
         <v>12.0539999008179</v>
       </c>
       <c r="G6" t="n">
-        <v>11.2953615188599</v>
+        <v>11.2953605651855</v>
       </c>
       <c r="H6" t="n">
         <v>9400</v>
@@ -630,7 +630,7 @@
         <v>11.8599996566772</v>
       </c>
       <c r="G9" t="n">
-        <v>11.1135711669922</v>
+        <v>11.1135702133179</v>
       </c>
       <c r="H9" t="n">
         <v>5700</v>
@@ -746,7 +746,7 @@
         <v>11.8800001144409</v>
       </c>
       <c r="G13" t="n">
-        <v>11.1323127746582</v>
+        <v>11.1323118209839</v>
       </c>
       <c r="H13" t="n">
         <v>5200</v>
@@ -833,7 +833,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G16" t="n">
-        <v>11.0573472976685</v>
+        <v>11.0573463439941</v>
       </c>
       <c r="H16" t="n">
         <v>200</v>
@@ -862,7 +862,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G17" t="n">
-        <v>11.0573472976685</v>
+        <v>11.0573463439941</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
@@ -978,7 +978,7 @@
         <v>11.3800001144409</v>
       </c>
       <c r="G21" t="n">
-        <v>10.6637811660767</v>
+        <v>10.6637802124023</v>
       </c>
       <c r="H21" t="n">
         <v>3200</v>
@@ -1065,7 +1065,7 @@
         <v>11.2600002288818</v>
       </c>
       <c r="G24" t="n">
-        <v>10.5513334274292</v>
+        <v>10.5513324737549</v>
       </c>
       <c r="H24" t="n">
         <v>200</v>
@@ -1094,7 +1094,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G25" t="n">
-        <v>10.5888156890869</v>
+        <v>10.5888147354126</v>
       </c>
       <c r="H25" t="n">
         <v>600</v>
@@ -1210,7 +1210,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G29" t="n">
-        <v>11.3384666442871</v>
+        <v>11.3384656906128</v>
       </c>
       <c r="H29" t="n">
         <v>12200</v>
@@ -1239,7 +1239,7 @@
         <v>11.8800001144409</v>
       </c>
       <c r="G30" t="n">
-        <v>11.1323127746582</v>
+        <v>11.1323118209839</v>
       </c>
       <c r="H30" t="n">
         <v>3900</v>
@@ -1355,7 +1355,7 @@
         <v>11.75</v>
       </c>
       <c r="G34" t="n">
-        <v>11.0104932785034</v>
+        <v>11.0104942321777</v>
       </c>
       <c r="H34" t="n">
         <v>3400</v>
@@ -1384,7 +1384,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G35" t="n">
-        <v>11.0573472976685</v>
+        <v>11.0573463439941</v>
       </c>
       <c r="H35" t="n">
         <v>2200</v>
@@ -1413,7 +1413,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G36" t="n">
-        <v>11.0573472976685</v>
+        <v>11.0573463439941</v>
       </c>
       <c r="H36" t="n">
         <v>0</v>
@@ -1442,7 +1442,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G37" t="n">
-        <v>11.0573472976685</v>
+        <v>11.0573463439941</v>
       </c>
       <c r="H37" t="n">
         <v>3200</v>
@@ -1616,7 +1616,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G43" t="n">
-        <v>11.0573472976685</v>
+        <v>11.0573463439941</v>
       </c>
       <c r="H43" t="n">
         <v>4800</v>
@@ -1761,7 +1761,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G48" t="n">
-        <v>11.0573472976685</v>
+        <v>11.0573463439941</v>
       </c>
       <c r="H48" t="n">
         <v>1200</v>
@@ -1877,7 +1877,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G52" t="n">
-        <v>11.0573472976685</v>
+        <v>11.0573463439941</v>
       </c>
       <c r="H52" t="n">
         <v>100</v>
@@ -1935,7 +1935,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G54" t="n">
-        <v>11.0573472976685</v>
+        <v>11.0573463439941</v>
       </c>
       <c r="H54" t="n">
         <v>700</v>
@@ -1964,7 +1964,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G55" t="n">
-        <v>11.0573472976685</v>
+        <v>11.0573463439941</v>
       </c>
       <c r="H55" t="n">
         <v>100</v>
@@ -1993,7 +1993,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G56" t="n">
-        <v>11.0573472976685</v>
+        <v>11.0573463439941</v>
       </c>
       <c r="H56" t="n">
         <v>0</v>
@@ -2022,7 +2022,7 @@
         <v>11.75</v>
       </c>
       <c r="G57" t="n">
-        <v>11.0104932785034</v>
+        <v>11.0104942321777</v>
       </c>
       <c r="H57" t="n">
         <v>200</v>
@@ -2051,7 +2051,7 @@
         <v>11.75</v>
       </c>
       <c r="G58" t="n">
-        <v>11.0104932785034</v>
+        <v>11.0104942321777</v>
       </c>
       <c r="H58" t="n">
         <v>500</v>
@@ -2080,7 +2080,7 @@
         <v>11.75</v>
       </c>
       <c r="G59" t="n">
-        <v>11.0104932785034</v>
+        <v>11.0104942321777</v>
       </c>
       <c r="H59" t="n">
         <v>0</v>
@@ -2109,7 +2109,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G60" t="n">
-        <v>10.8699350357056</v>
+        <v>10.8699340820312</v>
       </c>
       <c r="H60" t="n">
         <v>6000</v>
@@ -2428,7 +2428,7 @@
         <v>11.5</v>
       </c>
       <c r="G71" t="n">
-        <v>10.7762279510498</v>
+        <v>10.7762269973755</v>
       </c>
       <c r="H71" t="n">
         <v>500</v>
@@ -2486,7 +2486,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G73" t="n">
-        <v>10.8699350357056</v>
+        <v>10.8699340820312</v>
       </c>
       <c r="H73" t="n">
         <v>10000</v>
@@ -2515,7 +2515,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G74" t="n">
-        <v>10.8699350357056</v>
+        <v>10.8699340820312</v>
       </c>
       <c r="H74" t="n">
         <v>4200</v>
@@ -2544,7 +2544,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G75" t="n">
-        <v>10.8699350357056</v>
+        <v>10.8699340820312</v>
       </c>
       <c r="H75" t="n">
         <v>1100</v>
@@ -2573,7 +2573,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G76" t="n">
-        <v>10.8699350357056</v>
+        <v>10.8699340820312</v>
       </c>
       <c r="H76" t="n">
         <v>3300</v>
@@ -2631,7 +2631,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G78" t="n">
-        <v>11.0573472976685</v>
+        <v>11.0573463439941</v>
       </c>
       <c r="H78" t="n">
         <v>2600</v>
@@ -2660,7 +2660,7 @@
         <v>11.5</v>
       </c>
       <c r="G79" t="n">
-        <v>10.7762279510498</v>
+        <v>10.7762269973755</v>
       </c>
       <c r="H79" t="n">
         <v>2100</v>
@@ -2776,7 +2776,7 @@
         <v>10.0500001907349</v>
       </c>
       <c r="G83" t="n">
-        <v>9.41748714447021</v>
+        <v>9.4174861907959</v>
       </c>
       <c r="H83" t="n">
         <v>13500</v>
@@ -2805,7 +2805,7 @@
         <v>10.0500001907349</v>
       </c>
       <c r="G84" t="n">
-        <v>9.41748714447021</v>
+        <v>9.4174861907959</v>
       </c>
       <c r="H84" t="n">
         <v>16000</v>
@@ -3008,7 +3008,7 @@
         <v>10.0500001907349</v>
       </c>
       <c r="G91" t="n">
-        <v>9.41748714447021</v>
+        <v>9.4174861907959</v>
       </c>
       <c r="H91" t="n">
         <v>1800</v>
@@ -3037,7 +3037,7 @@
         <v>9.92000007629395</v>
       </c>
       <c r="G92" t="n">
-        <v>9.29566764831543</v>
+        <v>9.29566860198975</v>
       </c>
       <c r="H92" t="n">
         <v>5200</v>
@@ -3066,7 +3066,7 @@
         <v>9.72000026702881</v>
       </c>
       <c r="G93" t="n">
-        <v>9.10825538635254</v>
+        <v>9.10825634002686</v>
       </c>
       <c r="H93" t="n">
         <v>3500</v>
@@ -3095,7 +3095,7 @@
         <v>9.73999977111816</v>
       </c>
       <c r="G94" t="n">
-        <v>9.12699604034424</v>
+        <v>9.12699699401855</v>
       </c>
       <c r="H94" t="n">
         <v>2000</v>
@@ -3124,7 +3124,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G95" t="n">
-        <v>9.08951377868652</v>
+        <v>9.08951473236084</v>
       </c>
       <c r="H95" t="n">
         <v>800</v>
@@ -3153,7 +3153,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G96" t="n">
-        <v>9.08951377868652</v>
+        <v>9.08951473236084</v>
       </c>
       <c r="H96" t="n">
         <v>0</v>
@@ -3182,7 +3182,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G97" t="n">
-        <v>9.08951377868652</v>
+        <v>9.08951473236084</v>
       </c>
       <c r="H97" t="n">
         <v>0</v>
@@ -3211,7 +3211,7 @@
         <v>9.53999996185303</v>
       </c>
       <c r="G98" t="n">
-        <v>8.93958282470703</v>
+        <v>8.93958377838135</v>
       </c>
       <c r="H98" t="n">
         <v>900</v>
@@ -3240,7 +3240,7 @@
         <v>9.34000015258789</v>
       </c>
       <c r="G99" t="n">
-        <v>8.75217056274414</v>
+        <v>8.75217151641846</v>
       </c>
       <c r="H99" t="n">
         <v>600</v>
@@ -3269,7 +3269,7 @@
         <v>9.14000034332275</v>
       </c>
       <c r="G100" t="n">
-        <v>8.56475830078125</v>
+        <v>8.56475925445557</v>
       </c>
       <c r="H100" t="n">
         <v>800</v>
@@ -3414,7 +3414,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G105" t="n">
-        <v>8.52727603912354</v>
+        <v>8.52727699279785</v>
       </c>
       <c r="H105" t="n">
         <v>1300</v>
@@ -3530,7 +3530,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G109" t="n">
-        <v>8.80839443206787</v>
+        <v>8.80839538574219</v>
       </c>
       <c r="H109" t="n">
         <v>300</v>
@@ -3559,7 +3559,7 @@
         <v>9.4399995803833</v>
       </c>
       <c r="G110" t="n">
-        <v>8.84587669372559</v>
+        <v>8.8458776473999</v>
       </c>
       <c r="H110" t="n">
         <v>200</v>
@@ -3588,7 +3588,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G111" t="n">
-        <v>9.08951377868652</v>
+        <v>9.08951473236084</v>
       </c>
       <c r="H111" t="n">
         <v>500</v>
@@ -3704,7 +3704,7 @@
         <v>10</v>
       </c>
       <c r="G115" t="n">
-        <v>9.37063312530518</v>
+        <v>9.37063407897949</v>
       </c>
       <c r="H115" t="n">
         <v>200</v>
@@ -3820,7 +3820,7 @@
         <v>10.5</v>
       </c>
       <c r="G119" t="n">
-        <v>9.83916473388672</v>
+        <v>9.83916568756104</v>
       </c>
       <c r="H119" t="n">
         <v>800</v>
@@ -4110,7 +4110,7 @@
         <v>9.84000015258789</v>
       </c>
       <c r="G129" t="n">
-        <v>9.22070217132568</v>
+        <v>9.220703125</v>
       </c>
       <c r="H129" t="n">
         <v>200</v>
@@ -4139,7 +4139,7 @@
         <v>9.92000007629395</v>
       </c>
       <c r="G130" t="n">
-        <v>9.29566764831543</v>
+        <v>9.29566860198975</v>
       </c>
       <c r="H130" t="n">
         <v>200</v>
@@ -4168,7 +4168,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G131" t="n">
-        <v>9.65175247192383</v>
+        <v>9.65175342559814</v>
       </c>
       <c r="H131" t="n">
         <v>2700</v>
@@ -4197,7 +4197,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G132" t="n">
-        <v>9.65175247192383</v>
+        <v>9.65175342559814</v>
       </c>
       <c r="H132" t="n">
         <v>100</v>
@@ -4313,7 +4313,7 @@
         <v>10.5</v>
       </c>
       <c r="G136" t="n">
-        <v>9.83916473388672</v>
+        <v>9.83916568756104</v>
       </c>
       <c r="H136" t="n">
         <v>700</v>
@@ -4400,7 +4400,7 @@
         <v>10.5</v>
       </c>
       <c r="G139" t="n">
-        <v>9.83916473388672</v>
+        <v>9.83916568756104</v>
       </c>
       <c r="H139" t="n">
         <v>300</v>
@@ -4429,7 +4429,7 @@
         <v>10.5</v>
       </c>
       <c r="G140" t="n">
-        <v>9.83916473388672</v>
+        <v>9.83916568756104</v>
       </c>
       <c r="H140" t="n">
         <v>100</v>
@@ -4458,7 +4458,7 @@
         <v>10.5</v>
       </c>
       <c r="G141" t="n">
-        <v>9.83916473388672</v>
+        <v>9.83916568756104</v>
       </c>
       <c r="H141" t="n">
         <v>0</v>
@@ -4487,7 +4487,7 @@
         <v>10</v>
       </c>
       <c r="G142" t="n">
-        <v>9.37063312530518</v>
+        <v>9.37063407897949</v>
       </c>
       <c r="H142" t="n">
         <v>7600</v>
@@ -4661,7 +4661,7 @@
         <v>9.31999969482422</v>
       </c>
       <c r="G148" t="n">
-        <v>8.73342895507812</v>
+        <v>8.73342990875244</v>
       </c>
       <c r="H148" t="n">
         <v>1000</v>
@@ -4748,7 +4748,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G151" t="n">
-        <v>9.08951377868652</v>
+        <v>9.08951473236084</v>
       </c>
       <c r="H151" t="n">
         <v>500</v>
@@ -4777,7 +4777,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G152" t="n">
-        <v>9.08951377868652</v>
+        <v>9.08951473236084</v>
       </c>
       <c r="H152" t="n">
         <v>0</v>
@@ -4806,7 +4806,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G153" t="n">
-        <v>9.08951377868652</v>
+        <v>9.08951473236084</v>
       </c>
       <c r="H153" t="n">
         <v>0</v>
@@ -4864,7 +4864,7 @@
         <v>10</v>
       </c>
       <c r="G155" t="n">
-        <v>9.37063312530518</v>
+        <v>9.37063407897949</v>
       </c>
       <c r="H155" t="n">
         <v>100</v>
@@ -4893,7 +4893,7 @@
         <v>10</v>
       </c>
       <c r="G156" t="n">
-        <v>9.37063312530518</v>
+        <v>9.37063407897949</v>
       </c>
       <c r="H156" t="n">
         <v>0</v>
@@ -4922,7 +4922,7 @@
         <v>10</v>
       </c>
       <c r="G157" t="n">
-        <v>9.37063312530518</v>
+        <v>9.37063407897949</v>
       </c>
       <c r="H157" t="n">
         <v>0</v>
@@ -4951,7 +4951,7 @@
         <v>10</v>
       </c>
       <c r="G158" t="n">
-        <v>9.37063312530518</v>
+        <v>9.37063407897949</v>
       </c>
       <c r="H158" t="n">
         <v>0</v>
@@ -4980,7 +4980,7 @@
         <v>10</v>
       </c>
       <c r="G159" t="n">
-        <v>9.37063312530518</v>
+        <v>9.37063407897949</v>
       </c>
       <c r="H159" t="n">
         <v>0</v>
@@ -5009,7 +5009,7 @@
         <v>10</v>
       </c>
       <c r="G160" t="n">
-        <v>9.37063312530518</v>
+        <v>9.37063407897949</v>
       </c>
       <c r="H160" t="n">
         <v>0</v>
@@ -5038,7 +5038,7 @@
         <v>10</v>
       </c>
       <c r="G161" t="n">
-        <v>9.37063312530518</v>
+        <v>9.37063407897949</v>
       </c>
       <c r="H161" t="n">
         <v>0</v>
@@ -5067,7 +5067,7 @@
         <v>10</v>
       </c>
       <c r="G162" t="n">
-        <v>9.37063312530518</v>
+        <v>9.37063407897949</v>
       </c>
       <c r="H162" t="n">
         <v>100</v>
@@ -5212,7 +5212,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G167" t="n">
-        <v>9.08951377868652</v>
+        <v>9.08951473236084</v>
       </c>
       <c r="H167" t="n">
         <v>1600</v>
@@ -5241,7 +5241,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G168" t="n">
-        <v>9.08951377868652</v>
+        <v>9.08951473236084</v>
       </c>
       <c r="H168" t="n">
         <v>5000</v>
@@ -5328,7 +5328,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G171" t="n">
-        <v>8.80839443206787</v>
+        <v>8.80839538574219</v>
       </c>
       <c r="H171" t="n">
         <v>900</v>
@@ -5444,7 +5444,7 @@
         <v>9.42000007629395</v>
       </c>
       <c r="G175" t="n">
-        <v>8.82713603973389</v>
+        <v>8.8271369934082</v>
       </c>
       <c r="H175" t="n">
         <v>800</v>
@@ -5676,7 +5676,7 @@
         <v>9.42000007629395</v>
       </c>
       <c r="G183" t="n">
-        <v>8.82713603973389</v>
+        <v>8.8271369934082</v>
       </c>
       <c r="H183" t="n">
         <v>300</v>
@@ -5705,7 +5705,7 @@
         <v>9.42000007629395</v>
       </c>
       <c r="G184" t="n">
-        <v>8.82713603973389</v>
+        <v>8.8271369934082</v>
       </c>
       <c r="H184" t="n">
         <v>0</v>
@@ -5734,7 +5734,7 @@
         <v>9.72000026702881</v>
       </c>
       <c r="G185" t="n">
-        <v>9.10825538635254</v>
+        <v>9.10825634002686</v>
       </c>
       <c r="H185" t="n">
         <v>1300</v>
@@ -5763,7 +5763,7 @@
         <v>9.84000015258789</v>
       </c>
       <c r="G186" t="n">
-        <v>9.22070217132568</v>
+        <v>9.220703125</v>
       </c>
       <c r="H186" t="n">
         <v>400</v>
@@ -5850,7 +5850,7 @@
         <v>9.61999988555908</v>
       </c>
       <c r="G189" t="n">
-        <v>9.01454830169678</v>
+        <v>9.01454925537109</v>
       </c>
       <c r="H189" t="n">
         <v>1400</v>
@@ -5995,7 +5995,7 @@
         <v>9.64000034332275</v>
       </c>
       <c r="G194" t="n">
-        <v>9.03328990936279</v>
+        <v>9.03329086303711</v>
       </c>
       <c r="H194" t="n">
         <v>100</v>
@@ -6024,7 +6024,7 @@
         <v>9.53999996185303</v>
       </c>
       <c r="G195" t="n">
-        <v>8.93958282470703</v>
+        <v>8.93958377838135</v>
       </c>
       <c r="H195" t="n">
         <v>600</v>
@@ -6053,7 +6053,7 @@
         <v>9.53999996185303</v>
       </c>
       <c r="G196" t="n">
-        <v>8.93958282470703</v>
+        <v>8.93958377838135</v>
       </c>
       <c r="H196" t="n">
         <v>0</v>
@@ -6082,7 +6082,7 @@
         <v>9.53999996185303</v>
       </c>
       <c r="G197" t="n">
-        <v>8.93958282470703</v>
+        <v>8.93958377838135</v>
       </c>
       <c r="H197" t="n">
         <v>0</v>
@@ -6517,7 +6517,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G212" t="n">
-        <v>8.52727603912354</v>
+        <v>8.52727699279785</v>
       </c>
       <c r="H212" t="n">
         <v>1500</v>
@@ -6546,7 +6546,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G213" t="n">
-        <v>8.52727603912354</v>
+        <v>8.52727699279785</v>
       </c>
       <c r="H213" t="n">
         <v>0</v>
@@ -6575,7 +6575,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G214" t="n">
-        <v>8.52727603912354</v>
+        <v>8.52727699279785</v>
       </c>
       <c r="H214" t="n">
         <v>0</v>
@@ -6604,7 +6604,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G215" t="n">
-        <v>8.52727603912354</v>
+        <v>8.52727699279785</v>
       </c>
       <c r="H215" t="n">
         <v>0</v>
@@ -6633,7 +6633,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G216" t="n">
-        <v>8.52727603912354</v>
+        <v>8.52727699279785</v>
       </c>
       <c r="H216" t="n">
         <v>300</v>
@@ -6662,7 +6662,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G217" t="n">
-        <v>8.52727603912354</v>
+        <v>8.52727699279785</v>
       </c>
       <c r="H217" t="n">
         <v>0</v>
@@ -6691,7 +6691,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G218" t="n">
-        <v>8.52727603912354</v>
+        <v>8.52727699279785</v>
       </c>
       <c r="H218" t="n">
         <v>0</v>
@@ -6720,7 +6720,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G219" t="n">
-        <v>8.52727603912354</v>
+        <v>8.52727699279785</v>
       </c>
       <c r="H219" t="n">
         <v>0</v>
@@ -6894,7 +6894,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G225" t="n">
-        <v>8.52727603912354</v>
+        <v>8.52727699279785</v>
       </c>
       <c r="H225" t="n">
         <v>300</v>
@@ -6923,7 +6923,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G226" t="n">
-        <v>8.52727603912354</v>
+        <v>8.52727699279785</v>
       </c>
       <c r="H226" t="n">
         <v>0</v>
@@ -6952,7 +6952,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G227" t="n">
-        <v>8.52727603912354</v>
+        <v>8.52727699279785</v>
       </c>
       <c r="H227" t="n">
         <v>900</v>
@@ -6981,7 +6981,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G228" t="n">
-        <v>8.52727603912354</v>
+        <v>8.52727699279785</v>
       </c>
       <c r="H228" t="n">
         <v>0</v>
@@ -7010,7 +7010,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G229" t="n">
-        <v>8.52727603912354</v>
+        <v>8.52727699279785</v>
       </c>
       <c r="H229" t="n">
         <v>0</v>
@@ -7039,7 +7039,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G230" t="n">
-        <v>8.52727603912354</v>
+        <v>8.52727699279785</v>
       </c>
       <c r="H230" t="n">
         <v>0</v>
@@ -7068,7 +7068,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G231" t="n">
-        <v>8.52727603912354</v>
+        <v>8.52727699279785</v>
       </c>
       <c r="H231" t="n">
         <v>0</v>
@@ -7097,7 +7097,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G232" t="n">
-        <v>8.52727603912354</v>
+        <v>8.52727699279785</v>
       </c>
       <c r="H232" t="n">
         <v>0</v>
@@ -7126,7 +7126,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G233" t="n">
-        <v>8.52727603912354</v>
+        <v>8.52727699279785</v>
       </c>
       <c r="H233" t="n">
         <v>0</v>
@@ -7300,7 +7300,7 @@
         <v>8.73999977111816</v>
       </c>
       <c r="G239" t="n">
-        <v>8.18993282318115</v>
+        <v>8.18993377685547</v>
       </c>
       <c r="H239" t="n">
         <v>500</v>
@@ -7387,7 +7387,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G242" t="n">
-        <v>7.68391895294189</v>
+        <v>7.68391942977905</v>
       </c>
       <c r="H242" t="n">
         <v>10000</v>
@@ -7416,7 +7416,7 @@
         <v>8.15999984741211</v>
       </c>
       <c r="G243" t="n">
-        <v>7.64643621444702</v>
+        <v>7.64643669128418</v>
       </c>
       <c r="H243" t="n">
         <v>28200</v>
@@ -7474,7 +7474,7 @@
         <v>8.0600004196167</v>
       </c>
       <c r="G245" t="n">
-        <v>7.55273056030273</v>
+        <v>7.55273103713989</v>
       </c>
       <c r="H245" t="n">
         <v>500</v>
@@ -7503,7 +7503,7 @@
         <v>8.0600004196167</v>
       </c>
       <c r="G246" t="n">
-        <v>7.55273056030273</v>
+        <v>7.55273103713989</v>
       </c>
       <c r="H246" t="n">
         <v>2400</v>
@@ -7532,7 +7532,7 @@
         <v>8.0600004196167</v>
       </c>
       <c r="G247" t="n">
-        <v>7.55273056030273</v>
+        <v>7.55273103713989</v>
       </c>
       <c r="H247" t="n">
         <v>300</v>
@@ -7561,7 +7561,7 @@
         <v>8.0600004196167</v>
       </c>
       <c r="G248" t="n">
-        <v>7.55273056030273</v>
+        <v>7.55273103713989</v>
       </c>
       <c r="H248" t="n">
         <v>0</v>
@@ -7648,7 +7648,7 @@
         <v>8.23999977111816</v>
       </c>
       <c r="G251" t="n">
-        <v>7.72140073776245</v>
+        <v>7.72140169143677</v>
       </c>
       <c r="H251" t="n">
         <v>100</v>
@@ -7764,7 +7764,7 @@
         <v>7.61999988555908</v>
       </c>
       <c r="G255" t="n">
-        <v>7.14042186737061</v>
+        <v>7.14042234420776</v>
       </c>
       <c r="H255" t="n">
         <v>13900</v>
@@ -7793,7 +7793,7 @@
         <v>7.71999979019165</v>
       </c>
       <c r="G256" t="n">
-        <v>7.23412799835205</v>
+        <v>7.23412847518921</v>
       </c>
       <c r="H256" t="n">
         <v>7300</v>
@@ -8083,7 +8083,7 @@
         <v>7.61999988555908</v>
       </c>
       <c r="G266" t="n">
-        <v>7.14042186737061</v>
+        <v>7.14042234420776</v>
       </c>
       <c r="H266" t="n">
         <v>600</v>
@@ -8199,7 +8199,7 @@
         <v>7.71999979019165</v>
       </c>
       <c r="G270" t="n">
-        <v>7.23412799835205</v>
+        <v>7.23412847518921</v>
       </c>
       <c r="H270" t="n">
         <v>6600</v>
@@ -8228,7 +8228,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G271" t="n">
-        <v>7.77762603759766</v>
+        <v>7.7776255607605</v>
       </c>
       <c r="H271" t="n">
         <v>9100</v>
@@ -8257,7 +8257,7 @@
         <v>8.53999996185303</v>
       </c>
       <c r="G272" t="n">
-        <v>8.00252056121826</v>
+        <v>8.00252151489258</v>
       </c>
       <c r="H272" t="n">
         <v>9400</v>
@@ -8344,7 +8344,7 @@
         <v>9.14000034332275</v>
       </c>
       <c r="G275" t="n">
-        <v>8.56475830078125</v>
+        <v>8.56475925445557</v>
       </c>
       <c r="H275" t="n">
         <v>4000</v>
@@ -8373,7 +8373,7 @@
         <v>9.11999988555908</v>
       </c>
       <c r="G276" t="n">
-        <v>8.54601669311523</v>
+        <v>8.54601764678955</v>
       </c>
       <c r="H276" t="n">
         <v>1600</v>
@@ -8402,7 +8402,7 @@
         <v>9.14000034332275</v>
       </c>
       <c r="G277" t="n">
-        <v>8.56475830078125</v>
+        <v>8.56475925445557</v>
       </c>
       <c r="H277" t="n">
         <v>600</v>
@@ -8460,7 +8460,7 @@
         <v>9.11999988555908</v>
       </c>
       <c r="G279" t="n">
-        <v>8.54601669311523</v>
+        <v>8.54601764678955</v>
       </c>
       <c r="H279" t="n">
         <v>2000</v>
@@ -8489,7 +8489,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G280" t="n">
-        <v>8.52727603912354</v>
+        <v>8.52727699279785</v>
       </c>
       <c r="H280" t="n">
         <v>1100</v>
@@ -8605,7 +8605,7 @@
         <v>8.81999969482422</v>
       </c>
       <c r="G284" t="n">
-        <v>8.26489734649658</v>
+        <v>8.2648983001709</v>
       </c>
       <c r="H284" t="n">
         <v>700</v>
@@ -8750,7 +8750,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G289" t="n">
-        <v>8.52727603912354</v>
+        <v>8.52727699279785</v>
       </c>
       <c r="H289" t="n">
         <v>2100</v>
@@ -8808,7 +8808,7 @@
         <v>9.11999988555908</v>
       </c>
       <c r="G291" t="n">
-        <v>8.54601669311523</v>
+        <v>8.54601764678955</v>
       </c>
       <c r="H291" t="n">
         <v>3400</v>
@@ -8837,7 +8837,7 @@
         <v>9.11999988555908</v>
       </c>
       <c r="G292" t="n">
-        <v>8.54601669311523</v>
+        <v>8.54601764678955</v>
       </c>
       <c r="H292" t="n">
         <v>2100</v>
@@ -8924,7 +8924,7 @@
         <v>9.14000034332275</v>
       </c>
       <c r="G295" t="n">
-        <v>8.56475830078125</v>
+        <v>8.56475925445557</v>
       </c>
       <c r="H295" t="n">
         <v>200</v>
@@ -8982,7 +8982,7 @@
         <v>9.14000034332275</v>
       </c>
       <c r="G297" t="n">
-        <v>8.56475830078125</v>
+        <v>8.56475925445557</v>
       </c>
       <c r="H297" t="n">
         <v>500</v>
@@ -9011,7 +9011,7 @@
         <v>9.14000034332275</v>
       </c>
       <c r="G298" t="n">
-        <v>8.56475830078125</v>
+        <v>8.56475925445557</v>
       </c>
       <c r="H298" t="n">
         <v>0</v>
@@ -9040,7 +9040,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G299" t="n">
-        <v>8.52727603912354</v>
+        <v>8.52727699279785</v>
       </c>
       <c r="H299" t="n">
         <v>700</v>
@@ -9098,7 +9098,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G301" t="n">
-        <v>8.52727603912354</v>
+        <v>8.52727699279785</v>
       </c>
       <c r="H301" t="n">
         <v>300</v>
@@ -9330,7 +9330,7 @@
         <v>8.53999996185303</v>
       </c>
       <c r="G309" t="n">
-        <v>8.00252056121826</v>
+        <v>8.00252151489258</v>
       </c>
       <c r="H309" t="n">
         <v>2500</v>
@@ -9417,7 +9417,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G312" t="n">
-        <v>7.83384990692139</v>
+        <v>7.83384895324707</v>
       </c>
       <c r="H312" t="n">
         <v>1100</v>
@@ -9707,7 +9707,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G322" t="n">
-        <v>7.77762603759766</v>
+        <v>7.7776255607605</v>
       </c>
       <c r="H322" t="n">
         <v>3500</v>
@@ -9736,7 +9736,7 @@
         <v>8.27999973297119</v>
       </c>
       <c r="G323" t="n">
-        <v>7.75888395309448</v>
+        <v>7.75888442993164</v>
       </c>
       <c r="H323" t="n">
         <v>200</v>
@@ -9765,7 +9765,7 @@
         <v>8.27999973297119</v>
       </c>
       <c r="G324" t="n">
-        <v>7.75888395309448</v>
+        <v>7.75888442993164</v>
       </c>
       <c r="H324" t="n">
         <v>2000</v>
@@ -9794,7 +9794,7 @@
         <v>8.27999973297119</v>
       </c>
       <c r="G325" t="n">
-        <v>7.75888395309448</v>
+        <v>7.75888442993164</v>
       </c>
       <c r="H325" t="n">
         <v>6600</v>
@@ -9852,7 +9852,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G327" t="n">
-        <v>7.77762603759766</v>
+        <v>7.7776255607605</v>
       </c>
       <c r="H327" t="n">
         <v>2400</v>
@@ -10287,7 +10287,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G342" t="n">
-        <v>8.80839443206787</v>
+        <v>8.80839538574219</v>
       </c>
       <c r="H342" t="n">
         <v>10000</v>
@@ -10316,7 +10316,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G343" t="n">
-        <v>9.08951377868652</v>
+        <v>9.08951473236084</v>
       </c>
       <c r="H343" t="n">
         <v>10200</v>
@@ -10374,7 +10374,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G345" t="n">
-        <v>9.08951377868652</v>
+        <v>9.08951473236084</v>
       </c>
       <c r="H345" t="n">
         <v>4500</v>
@@ -10548,7 +10548,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G351" t="n">
-        <v>9.08951377868652</v>
+        <v>9.08951473236084</v>
       </c>
       <c r="H351" t="n">
         <v>800</v>
@@ -10838,7 +10838,7 @@
         <v>9.75</v>
       </c>
       <c r="G361" t="n">
-        <v>9.13636779785156</v>
+        <v>9.13636684417725</v>
       </c>
       <c r="H361" t="n">
         <v>1500</v>
@@ -11128,7 +11128,7 @@
         <v>9.75</v>
       </c>
       <c r="G371" t="n">
-        <v>9.13636779785156</v>
+        <v>9.13636684417725</v>
       </c>
       <c r="H371" t="n">
         <v>3600</v>
@@ -11157,7 +11157,7 @@
         <v>9.75</v>
       </c>
       <c r="G372" t="n">
-        <v>9.13636779785156</v>
+        <v>9.13636684417725</v>
       </c>
       <c r="H372" t="n">
         <v>100</v>
@@ -28911,6 +28911,35 @@
         <v>600</v>
       </c>
       <c r="I984" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="985">
+      <c r="A985" t="s">
+        <v>9</v>
+      </c>
+      <c r="B985" s="1" t="n">
+        <v>46317.2916666667</v>
+      </c>
+      <c r="C985" t="n">
+        <v>10.9499998092651</v>
+      </c>
+      <c r="D985" t="n">
+        <v>10.9499998092651</v>
+      </c>
+      <c r="E985" t="n">
+        <v>10.4499998092651</v>
+      </c>
+      <c r="F985" t="n">
+        <v>10.4499998092651</v>
+      </c>
+      <c r="G985" t="n">
+        <v>10.4499998092651</v>
+      </c>
+      <c r="H985" t="n">
+        <v>8200</v>
+      </c>
+      <c r="I985" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/RDUE.MI.xlsx
+++ b/data/RDUE.MI.xlsx
@@ -543,7 +543,7 @@
         <v>12.0539999008179</v>
       </c>
       <c r="G6" t="n">
-        <v>11.2953605651855</v>
+        <v>11.2953615188599</v>
       </c>
       <c r="H6" t="n">
         <v>9400</v>
@@ -572,7 +572,7 @@
         <v>12.0900001525879</v>
       </c>
       <c r="G7" t="n">
-        <v>11.3290948867798</v>
+        <v>11.3290958404541</v>
       </c>
       <c r="H7" t="n">
         <v>1000</v>
@@ -688,7 +688,7 @@
         <v>11.9180002212524</v>
       </c>
       <c r="G11" t="n">
-        <v>11.1679201126099</v>
+        <v>11.1679210662842</v>
       </c>
       <c r="H11" t="n">
         <v>2300</v>
@@ -746,7 +746,7 @@
         <v>11.8800001144409</v>
       </c>
       <c r="G13" t="n">
-        <v>11.1323118209839</v>
+        <v>11.1323127746582</v>
       </c>
       <c r="H13" t="n">
         <v>5200</v>
@@ -804,7 +804,7 @@
         <v>11.6199998855591</v>
       </c>
       <c r="G15" t="n">
-        <v>10.8886747360229</v>
+        <v>10.8886756896973</v>
       </c>
       <c r="H15" t="n">
         <v>1900</v>
@@ -833,7 +833,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G16" t="n">
-        <v>11.0573463439941</v>
+        <v>11.0573472976685</v>
       </c>
       <c r="H16" t="n">
         <v>200</v>
@@ -862,7 +862,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G17" t="n">
-        <v>11.0573463439941</v>
+        <v>11.0573472976685</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
@@ -949,7 +949,7 @@
         <v>11.5900001525879</v>
       </c>
       <c r="G20" t="n">
-        <v>10.8605642318726</v>
+        <v>10.8605632781982</v>
       </c>
       <c r="H20" t="n">
         <v>800</v>
@@ -1007,7 +1007,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G22" t="n">
-        <v>10.682520866394</v>
+        <v>10.6825218200684</v>
       </c>
       <c r="H22" t="n">
         <v>600</v>
@@ -1065,7 +1065,7 @@
         <v>11.2600002288818</v>
       </c>
       <c r="G24" t="n">
-        <v>10.5513324737549</v>
+        <v>10.5513334274292</v>
       </c>
       <c r="H24" t="n">
         <v>200</v>
@@ -1094,7 +1094,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G25" t="n">
-        <v>10.5888147354126</v>
+        <v>10.5888156890869</v>
       </c>
       <c r="H25" t="n">
         <v>600</v>
@@ -1123,7 +1123,7 @@
         <v>11.25</v>
       </c>
       <c r="G26" t="n">
-        <v>10.5419616699219</v>
+        <v>10.5419626235962</v>
       </c>
       <c r="H26" t="n">
         <v>400</v>
@@ -1210,7 +1210,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G29" t="n">
-        <v>11.3384656906128</v>
+        <v>11.3384666442871</v>
       </c>
       <c r="H29" t="n">
         <v>12200</v>
@@ -1239,7 +1239,7 @@
         <v>11.8800001144409</v>
       </c>
       <c r="G30" t="n">
-        <v>11.1323118209839</v>
+        <v>11.1323127746582</v>
       </c>
       <c r="H30" t="n">
         <v>3900</v>
@@ -1268,7 +1268,7 @@
         <v>11.9799995422363</v>
       </c>
       <c r="G31" t="n">
-        <v>11.2260179519653</v>
+        <v>11.2260189056396</v>
       </c>
       <c r="H31" t="n">
         <v>200</v>
@@ -1355,7 +1355,7 @@
         <v>11.75</v>
       </c>
       <c r="G34" t="n">
-        <v>11.0104942321777</v>
+        <v>11.0104932785034</v>
       </c>
       <c r="H34" t="n">
         <v>3400</v>
@@ -1384,7 +1384,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G35" t="n">
-        <v>11.0573463439941</v>
+        <v>11.0573472976685</v>
       </c>
       <c r="H35" t="n">
         <v>2200</v>
@@ -1413,7 +1413,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G36" t="n">
-        <v>11.0573463439941</v>
+        <v>11.0573472976685</v>
       </c>
       <c r="H36" t="n">
         <v>0</v>
@@ -1442,7 +1442,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G37" t="n">
-        <v>11.0573463439941</v>
+        <v>11.0573472976685</v>
       </c>
       <c r="H37" t="n">
         <v>3200</v>
@@ -1500,7 +1500,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G39" t="n">
-        <v>11.1510524749756</v>
+        <v>11.1510534286499</v>
       </c>
       <c r="H39" t="n">
         <v>500</v>
@@ -1529,7 +1529,7 @@
         <v>11.9799995422363</v>
       </c>
       <c r="G40" t="n">
-        <v>11.2260179519653</v>
+        <v>11.2260189056396</v>
       </c>
       <c r="H40" t="n">
         <v>400</v>
@@ -1558,7 +1558,7 @@
         <v>11.9799995422363</v>
       </c>
       <c r="G41" t="n">
-        <v>11.2260179519653</v>
+        <v>11.2260189056396</v>
       </c>
       <c r="H41" t="n">
         <v>0</v>
@@ -1616,7 +1616,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G43" t="n">
-        <v>11.0573463439941</v>
+        <v>11.0573472976685</v>
       </c>
       <c r="H43" t="n">
         <v>4800</v>
@@ -1761,7 +1761,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G48" t="n">
-        <v>11.0573463439941</v>
+        <v>11.0573472976685</v>
       </c>
       <c r="H48" t="n">
         <v>1200</v>
@@ -1819,7 +1819,7 @@
         <v>11.5500001907349</v>
       </c>
       <c r="G50" t="n">
-        <v>10.8230810165405</v>
+        <v>10.8230819702148</v>
       </c>
       <c r="H50" t="n">
         <v>400</v>
@@ -1848,7 +1848,7 @@
         <v>11.5500001907349</v>
       </c>
       <c r="G51" t="n">
-        <v>10.8230810165405</v>
+        <v>10.8230819702148</v>
       </c>
       <c r="H51" t="n">
         <v>1700</v>
@@ -1877,7 +1877,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G52" t="n">
-        <v>11.0573463439941</v>
+        <v>11.0573472976685</v>
       </c>
       <c r="H52" t="n">
         <v>100</v>
@@ -1935,7 +1935,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G54" t="n">
-        <v>11.0573463439941</v>
+        <v>11.0573472976685</v>
       </c>
       <c r="H54" t="n">
         <v>700</v>
@@ -1964,7 +1964,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G55" t="n">
-        <v>11.0573463439941</v>
+        <v>11.0573472976685</v>
       </c>
       <c r="H55" t="n">
         <v>100</v>
@@ -1993,7 +1993,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G56" t="n">
-        <v>11.0573463439941</v>
+        <v>11.0573472976685</v>
       </c>
       <c r="H56" t="n">
         <v>0</v>
@@ -2022,7 +2022,7 @@
         <v>11.75</v>
       </c>
       <c r="G57" t="n">
-        <v>11.0104942321777</v>
+        <v>11.0104932785034</v>
       </c>
       <c r="H57" t="n">
         <v>200</v>
@@ -2051,7 +2051,7 @@
         <v>11.75</v>
       </c>
       <c r="G58" t="n">
-        <v>11.0104942321777</v>
+        <v>11.0104932785034</v>
       </c>
       <c r="H58" t="n">
         <v>500</v>
@@ -2080,7 +2080,7 @@
         <v>11.75</v>
       </c>
       <c r="G59" t="n">
-        <v>11.0104942321777</v>
+        <v>11.0104932785034</v>
       </c>
       <c r="H59" t="n">
         <v>0</v>
@@ -2225,7 +2225,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G64" t="n">
-        <v>10.682520866394</v>
+        <v>10.6825218200684</v>
       </c>
       <c r="H64" t="n">
         <v>2900</v>
@@ -2254,7 +2254,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G65" t="n">
-        <v>10.682520866394</v>
+        <v>10.6825218200684</v>
       </c>
       <c r="H65" t="n">
         <v>500</v>
@@ -2283,7 +2283,7 @@
         <v>11.5500001907349</v>
       </c>
       <c r="G66" t="n">
-        <v>10.8230810165405</v>
+        <v>10.8230819702148</v>
       </c>
       <c r="H66" t="n">
         <v>4100</v>
@@ -2341,7 +2341,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G68" t="n">
-        <v>10.682520866394</v>
+        <v>10.6825218200684</v>
       </c>
       <c r="H68" t="n">
         <v>700</v>
@@ -2370,7 +2370,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G69" t="n">
-        <v>10.682520866394</v>
+        <v>10.6825218200684</v>
       </c>
       <c r="H69" t="n">
         <v>0</v>
@@ -2428,7 +2428,7 @@
         <v>11.5</v>
       </c>
       <c r="G71" t="n">
-        <v>10.7762269973755</v>
+        <v>10.7762289047241</v>
       </c>
       <c r="H71" t="n">
         <v>500</v>
@@ -2457,7 +2457,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G72" t="n">
-        <v>10.682520866394</v>
+        <v>10.6825218200684</v>
       </c>
       <c r="H72" t="n">
         <v>3100</v>
@@ -2631,7 +2631,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G78" t="n">
-        <v>11.0573463439941</v>
+        <v>11.0573472976685</v>
       </c>
       <c r="H78" t="n">
         <v>2600</v>
@@ -2660,7 +2660,7 @@
         <v>11.5</v>
       </c>
       <c r="G79" t="n">
-        <v>10.7762269973755</v>
+        <v>10.7762289047241</v>
       </c>
       <c r="H79" t="n">
         <v>2100</v>
@@ -2718,7 +2718,7 @@
         <v>11.5500001907349</v>
       </c>
       <c r="G81" t="n">
-        <v>10.8230810165405</v>
+        <v>10.8230819702148</v>
       </c>
       <c r="H81" t="n">
         <v>800</v>
@@ -2747,7 +2747,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G82" t="n">
-        <v>9.74545860290527</v>
+        <v>9.74545764923096</v>
       </c>
       <c r="H82" t="n">
         <v>13600</v>
@@ -2776,7 +2776,7 @@
         <v>10.0500001907349</v>
       </c>
       <c r="G83" t="n">
-        <v>9.4174861907959</v>
+        <v>9.41748714447021</v>
       </c>
       <c r="H83" t="n">
         <v>13500</v>
@@ -2805,7 +2805,7 @@
         <v>10.0500001907349</v>
       </c>
       <c r="G84" t="n">
-        <v>9.4174861907959</v>
+        <v>9.41748714447021</v>
       </c>
       <c r="H84" t="n">
         <v>16000</v>
@@ -2921,7 +2921,7 @@
         <v>10.25</v>
       </c>
       <c r="G88" t="n">
-        <v>9.60489940643311</v>
+        <v>9.60489845275879</v>
       </c>
       <c r="H88" t="n">
         <v>1800</v>
@@ -2950,7 +2950,7 @@
         <v>10.5500001907349</v>
       </c>
       <c r="G89" t="n">
-        <v>9.88601875305176</v>
+        <v>9.88601779937744</v>
       </c>
       <c r="H89" t="n">
         <v>4400</v>
@@ -2979,7 +2979,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G90" t="n">
-        <v>9.55804634094238</v>
+        <v>9.55804538726807</v>
       </c>
       <c r="H90" t="n">
         <v>600</v>
@@ -3008,7 +3008,7 @@
         <v>10.0500001907349</v>
       </c>
       <c r="G91" t="n">
-        <v>9.4174861907959</v>
+        <v>9.41748714447021</v>
       </c>
       <c r="H91" t="n">
         <v>1800</v>
@@ -3037,7 +3037,7 @@
         <v>9.92000007629395</v>
       </c>
       <c r="G92" t="n">
-        <v>9.29566860198975</v>
+        <v>9.29566764831543</v>
       </c>
       <c r="H92" t="n">
         <v>5200</v>
@@ -3095,7 +3095,7 @@
         <v>9.73999977111816</v>
       </c>
       <c r="G94" t="n">
-        <v>9.12699699401855</v>
+        <v>9.12699604034424</v>
       </c>
       <c r="H94" t="n">
         <v>2000</v>
@@ -3124,7 +3124,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G95" t="n">
-        <v>9.08951473236084</v>
+        <v>9.08951377868652</v>
       </c>
       <c r="H95" t="n">
         <v>800</v>
@@ -3153,7 +3153,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G96" t="n">
-        <v>9.08951473236084</v>
+        <v>9.08951377868652</v>
       </c>
       <c r="H96" t="n">
         <v>0</v>
@@ -3182,7 +3182,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G97" t="n">
-        <v>9.08951473236084</v>
+        <v>9.08951377868652</v>
       </c>
       <c r="H97" t="n">
         <v>0</v>
@@ -3414,7 +3414,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G105" t="n">
-        <v>8.52727699279785</v>
+        <v>8.52727603912354</v>
       </c>
       <c r="H105" t="n">
         <v>1300</v>
@@ -3559,7 +3559,7 @@
         <v>9.4399995803833</v>
       </c>
       <c r="G110" t="n">
-        <v>8.8458776473999</v>
+        <v>8.84587669372559</v>
       </c>
       <c r="H110" t="n">
         <v>200</v>
@@ -3588,7 +3588,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G111" t="n">
-        <v>9.08951473236084</v>
+        <v>9.08951377868652</v>
       </c>
       <c r="H111" t="n">
         <v>500</v>
@@ -3646,7 +3646,7 @@
         <v>9.76000022888184</v>
       </c>
       <c r="G113" t="n">
-        <v>9.14573764801025</v>
+        <v>9.14573860168457</v>
       </c>
       <c r="H113" t="n">
         <v>800</v>
@@ -3675,7 +3675,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G114" t="n">
-        <v>9.55804634094238</v>
+        <v>9.55804538726807</v>
       </c>
       <c r="H114" t="n">
         <v>7600</v>
@@ -3704,7 +3704,7 @@
         <v>10</v>
       </c>
       <c r="G115" t="n">
-        <v>9.37063407897949</v>
+        <v>9.37063312530518</v>
       </c>
       <c r="H115" t="n">
         <v>200</v>
@@ -3733,7 +3733,7 @@
         <v>10.5500001907349</v>
       </c>
       <c r="G116" t="n">
-        <v>9.88601875305176</v>
+        <v>9.88601779937744</v>
       </c>
       <c r="H116" t="n">
         <v>2700</v>
@@ -3762,7 +3762,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G117" t="n">
-        <v>9.74545860290527</v>
+        <v>9.74545764923096</v>
       </c>
       <c r="H117" t="n">
         <v>300</v>
@@ -3791,7 +3791,7 @@
         <v>10.5500001907349</v>
       </c>
       <c r="G118" t="n">
-        <v>9.88601875305176</v>
+        <v>9.88601779937744</v>
       </c>
       <c r="H118" t="n">
         <v>100</v>
@@ -3820,7 +3820,7 @@
         <v>10.5</v>
       </c>
       <c r="G119" t="n">
-        <v>9.83916568756104</v>
+        <v>9.83916473388672</v>
       </c>
       <c r="H119" t="n">
         <v>800</v>
@@ -4023,7 +4023,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G126" t="n">
-        <v>8.99580860137939</v>
+        <v>8.99580764770508</v>
       </c>
       <c r="H126" t="n">
         <v>5200</v>
@@ -4052,7 +4052,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G127" t="n">
-        <v>8.99580860137939</v>
+        <v>8.99580764770508</v>
       </c>
       <c r="H127" t="n">
         <v>300</v>
@@ -4139,7 +4139,7 @@
         <v>9.92000007629395</v>
       </c>
       <c r="G130" t="n">
-        <v>9.29566860198975</v>
+        <v>9.29566764831543</v>
       </c>
       <c r="H130" t="n">
         <v>200</v>
@@ -4168,7 +4168,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G131" t="n">
-        <v>9.65175342559814</v>
+        <v>9.65175151824951</v>
       </c>
       <c r="H131" t="n">
         <v>2700</v>
@@ -4197,7 +4197,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G132" t="n">
-        <v>9.65175342559814</v>
+        <v>9.65175151824951</v>
       </c>
       <c r="H132" t="n">
         <v>100</v>
@@ -4226,7 +4226,7 @@
         <v>9.97999954223633</v>
       </c>
       <c r="G133" t="n">
-        <v>9.35189247131348</v>
+        <v>9.35189151763916</v>
       </c>
       <c r="H133" t="n">
         <v>500</v>
@@ -4313,7 +4313,7 @@
         <v>10.5</v>
       </c>
       <c r="G136" t="n">
-        <v>9.83916568756104</v>
+        <v>9.83916473388672</v>
       </c>
       <c r="H136" t="n">
         <v>700</v>
@@ -4342,7 +4342,7 @@
         <v>10.5500001907349</v>
       </c>
       <c r="G137" t="n">
-        <v>9.88601875305176</v>
+        <v>9.88601779937744</v>
       </c>
       <c r="H137" t="n">
         <v>1000</v>
@@ -4400,7 +4400,7 @@
         <v>10.5</v>
       </c>
       <c r="G139" t="n">
-        <v>9.83916568756104</v>
+        <v>9.83916473388672</v>
       </c>
       <c r="H139" t="n">
         <v>300</v>
@@ -4429,7 +4429,7 @@
         <v>10.5</v>
       </c>
       <c r="G140" t="n">
-        <v>9.83916568756104</v>
+        <v>9.83916473388672</v>
       </c>
       <c r="H140" t="n">
         <v>100</v>
@@ -4458,7 +4458,7 @@
         <v>10.5</v>
       </c>
       <c r="G141" t="n">
-        <v>9.83916568756104</v>
+        <v>9.83916473388672</v>
       </c>
       <c r="H141" t="n">
         <v>0</v>
@@ -4487,7 +4487,7 @@
         <v>10</v>
       </c>
       <c r="G142" t="n">
-        <v>9.37063407897949</v>
+        <v>9.37063312530518</v>
       </c>
       <c r="H142" t="n">
         <v>7600</v>
@@ -4574,7 +4574,7 @@
         <v>9.5600004196167</v>
       </c>
       <c r="G145" t="n">
-        <v>8.95832538604736</v>
+        <v>8.95832633972168</v>
       </c>
       <c r="H145" t="n">
         <v>1400</v>
@@ -4603,7 +4603,7 @@
         <v>9.5</v>
       </c>
       <c r="G146" t="n">
-        <v>8.90210151672363</v>
+        <v>8.90210056304932</v>
       </c>
       <c r="H146" t="n">
         <v>2600</v>
@@ -4632,7 +4632,7 @@
         <v>9.5</v>
       </c>
       <c r="G147" t="n">
-        <v>8.90210151672363</v>
+        <v>8.90210056304932</v>
       </c>
       <c r="H147" t="n">
         <v>0</v>
@@ -4690,7 +4690,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G149" t="n">
-        <v>8.99580860137939</v>
+        <v>8.99580764770508</v>
       </c>
       <c r="H149" t="n">
         <v>4300</v>
@@ -4719,7 +4719,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G150" t="n">
-        <v>8.99580860137939</v>
+        <v>8.99580764770508</v>
       </c>
       <c r="H150" t="n">
         <v>0</v>
@@ -4748,7 +4748,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G151" t="n">
-        <v>9.08951473236084</v>
+        <v>9.08951377868652</v>
       </c>
       <c r="H151" t="n">
         <v>500</v>
@@ -4777,7 +4777,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G152" t="n">
-        <v>9.08951473236084</v>
+        <v>9.08951377868652</v>
       </c>
       <c r="H152" t="n">
         <v>0</v>
@@ -4806,7 +4806,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G153" t="n">
-        <v>9.08951473236084</v>
+        <v>9.08951377868652</v>
       </c>
       <c r="H153" t="n">
         <v>0</v>
@@ -4864,7 +4864,7 @@
         <v>10</v>
       </c>
       <c r="G155" t="n">
-        <v>9.37063407897949</v>
+        <v>9.37063312530518</v>
       </c>
       <c r="H155" t="n">
         <v>100</v>
@@ -4893,7 +4893,7 @@
         <v>10</v>
       </c>
       <c r="G156" t="n">
-        <v>9.37063407897949</v>
+        <v>9.37063312530518</v>
       </c>
       <c r="H156" t="n">
         <v>0</v>
@@ -4922,7 +4922,7 @@
         <v>10</v>
       </c>
       <c r="G157" t="n">
-        <v>9.37063407897949</v>
+        <v>9.37063312530518</v>
       </c>
       <c r="H157" t="n">
         <v>0</v>
@@ -4951,7 +4951,7 @@
         <v>10</v>
       </c>
       <c r="G158" t="n">
-        <v>9.37063407897949</v>
+        <v>9.37063312530518</v>
       </c>
       <c r="H158" t="n">
         <v>0</v>
@@ -4980,7 +4980,7 @@
         <v>10</v>
       </c>
       <c r="G159" t="n">
-        <v>9.37063407897949</v>
+        <v>9.37063312530518</v>
       </c>
       <c r="H159" t="n">
         <v>0</v>
@@ -5009,7 +5009,7 @@
         <v>10</v>
       </c>
       <c r="G160" t="n">
-        <v>9.37063407897949</v>
+        <v>9.37063312530518</v>
       </c>
       <c r="H160" t="n">
         <v>0</v>
@@ -5038,7 +5038,7 @@
         <v>10</v>
       </c>
       <c r="G161" t="n">
-        <v>9.37063407897949</v>
+        <v>9.37063312530518</v>
       </c>
       <c r="H161" t="n">
         <v>0</v>
@@ -5067,7 +5067,7 @@
         <v>10</v>
       </c>
       <c r="G162" t="n">
-        <v>9.37063407897949</v>
+        <v>9.37063312530518</v>
       </c>
       <c r="H162" t="n">
         <v>100</v>
@@ -5125,7 +5125,7 @@
         <v>9.97999954223633</v>
       </c>
       <c r="G164" t="n">
-        <v>9.35189247131348</v>
+        <v>9.35189151763916</v>
       </c>
       <c r="H164" t="n">
         <v>400</v>
@@ -5154,7 +5154,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G165" t="n">
-        <v>9.27692699432373</v>
+        <v>9.27692604064941</v>
       </c>
       <c r="H165" t="n">
         <v>300</v>
@@ -5183,7 +5183,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G166" t="n">
-        <v>9.27692699432373</v>
+        <v>9.27692604064941</v>
       </c>
       <c r="H166" t="n">
         <v>100</v>
@@ -5212,7 +5212,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G167" t="n">
-        <v>9.08951473236084</v>
+        <v>9.08951377868652</v>
       </c>
       <c r="H167" t="n">
         <v>1600</v>
@@ -5241,7 +5241,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G168" t="n">
-        <v>9.08951473236084</v>
+        <v>9.08951377868652</v>
       </c>
       <c r="H168" t="n">
         <v>5000</v>
@@ -5270,7 +5270,7 @@
         <v>9.15999984741211</v>
       </c>
       <c r="G169" t="n">
-        <v>8.58350086212158</v>
+        <v>8.58349990844727</v>
       </c>
       <c r="H169" t="n">
         <v>16200</v>
@@ -5299,7 +5299,7 @@
         <v>9.5</v>
       </c>
       <c r="G170" t="n">
-        <v>8.90210151672363</v>
+        <v>8.90210056304932</v>
       </c>
       <c r="H170" t="n">
         <v>2200</v>
@@ -5357,7 +5357,7 @@
         <v>9.5600004196167</v>
       </c>
       <c r="G172" t="n">
-        <v>8.95832538604736</v>
+        <v>8.95832633972168</v>
       </c>
       <c r="H172" t="n">
         <v>200</v>
@@ -5386,7 +5386,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G173" t="n">
-        <v>9.27692699432373</v>
+        <v>9.27692604064941</v>
       </c>
       <c r="H173" t="n">
         <v>300</v>
@@ -5415,7 +5415,7 @@
         <v>9.27999973297119</v>
       </c>
       <c r="G174" t="n">
-        <v>8.69594764709473</v>
+        <v>8.69594669342041</v>
       </c>
       <c r="H174" t="n">
         <v>8500</v>
@@ -5444,7 +5444,7 @@
         <v>9.42000007629395</v>
       </c>
       <c r="G175" t="n">
-        <v>8.8271369934082</v>
+        <v>8.82713603973389</v>
       </c>
       <c r="H175" t="n">
         <v>800</v>
@@ -5473,7 +5473,7 @@
         <v>9.27999973297119</v>
       </c>
       <c r="G176" t="n">
-        <v>8.69594764709473</v>
+        <v>8.69594669342041</v>
       </c>
       <c r="H176" t="n">
         <v>1400</v>
@@ -5502,7 +5502,7 @@
         <v>9.27999973297119</v>
       </c>
       <c r="G177" t="n">
-        <v>8.69594764709473</v>
+        <v>8.69594669342041</v>
       </c>
       <c r="H177" t="n">
         <v>0</v>
@@ -5676,7 +5676,7 @@
         <v>9.42000007629395</v>
       </c>
       <c r="G183" t="n">
-        <v>8.8271369934082</v>
+        <v>8.82713603973389</v>
       </c>
       <c r="H183" t="n">
         <v>300</v>
@@ -5705,7 +5705,7 @@
         <v>9.42000007629395</v>
       </c>
       <c r="G184" t="n">
-        <v>8.8271369934082</v>
+        <v>8.82713603973389</v>
       </c>
       <c r="H184" t="n">
         <v>0</v>
@@ -5792,7 +5792,7 @@
         <v>9.97999954223633</v>
       </c>
       <c r="G187" t="n">
-        <v>9.35189247131348</v>
+        <v>9.35189151763916</v>
       </c>
       <c r="H187" t="n">
         <v>3900</v>
@@ -5821,7 +5821,7 @@
         <v>9.97999954223633</v>
       </c>
       <c r="G188" t="n">
-        <v>9.35189247131348</v>
+        <v>9.35189151763916</v>
       </c>
       <c r="H188" t="n">
         <v>300</v>
@@ -5995,7 +5995,7 @@
         <v>9.64000034332275</v>
       </c>
       <c r="G194" t="n">
-        <v>9.03329086303711</v>
+        <v>9.03328990936279</v>
       </c>
       <c r="H194" t="n">
         <v>100</v>
@@ -6111,7 +6111,7 @@
         <v>9.5</v>
       </c>
       <c r="G198" t="n">
-        <v>8.90210151672363</v>
+        <v>8.90210056304932</v>
       </c>
       <c r="H198" t="n">
         <v>2100</v>
@@ -6256,7 +6256,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G203" t="n">
-        <v>8.2461576461792</v>
+        <v>8.24615669250488</v>
       </c>
       <c r="H203" t="n">
         <v>2500</v>
@@ -6285,7 +6285,7 @@
         <v>9.0600004196167</v>
       </c>
       <c r="G204" t="n">
-        <v>8.48979473114014</v>
+        <v>8.48979377746582</v>
       </c>
       <c r="H204" t="n">
         <v>2200</v>
@@ -6517,7 +6517,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G212" t="n">
-        <v>8.52727699279785</v>
+        <v>8.52727603912354</v>
       </c>
       <c r="H212" t="n">
         <v>1500</v>
@@ -6546,7 +6546,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G213" t="n">
-        <v>8.52727699279785</v>
+        <v>8.52727603912354</v>
       </c>
       <c r="H213" t="n">
         <v>0</v>
@@ -6575,7 +6575,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G214" t="n">
-        <v>8.52727699279785</v>
+        <v>8.52727603912354</v>
       </c>
       <c r="H214" t="n">
         <v>0</v>
@@ -6604,7 +6604,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G215" t="n">
-        <v>8.52727699279785</v>
+        <v>8.52727603912354</v>
       </c>
       <c r="H215" t="n">
         <v>0</v>
@@ -6633,7 +6633,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G216" t="n">
-        <v>8.52727699279785</v>
+        <v>8.52727603912354</v>
       </c>
       <c r="H216" t="n">
         <v>300</v>
@@ -6662,7 +6662,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G217" t="n">
-        <v>8.52727699279785</v>
+        <v>8.52727603912354</v>
       </c>
       <c r="H217" t="n">
         <v>0</v>
@@ -6691,7 +6691,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G218" t="n">
-        <v>8.52727699279785</v>
+        <v>8.52727603912354</v>
       </c>
       <c r="H218" t="n">
         <v>0</v>
@@ -6720,7 +6720,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G219" t="n">
-        <v>8.52727699279785</v>
+        <v>8.52727603912354</v>
       </c>
       <c r="H219" t="n">
         <v>0</v>
@@ -6894,7 +6894,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G225" t="n">
-        <v>8.52727699279785</v>
+        <v>8.52727603912354</v>
       </c>
       <c r="H225" t="n">
         <v>300</v>
@@ -6923,7 +6923,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G226" t="n">
-        <v>8.52727699279785</v>
+        <v>8.52727603912354</v>
       </c>
       <c r="H226" t="n">
         <v>0</v>
@@ -6952,7 +6952,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G227" t="n">
-        <v>8.52727699279785</v>
+        <v>8.52727603912354</v>
       </c>
       <c r="H227" t="n">
         <v>900</v>
@@ -6981,7 +6981,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G228" t="n">
-        <v>8.52727699279785</v>
+        <v>8.52727603912354</v>
       </c>
       <c r="H228" t="n">
         <v>0</v>
@@ -7010,7 +7010,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G229" t="n">
-        <v>8.52727699279785</v>
+        <v>8.52727603912354</v>
       </c>
       <c r="H229" t="n">
         <v>0</v>
@@ -7039,7 +7039,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G230" t="n">
-        <v>8.52727699279785</v>
+        <v>8.52727603912354</v>
       </c>
       <c r="H230" t="n">
         <v>0</v>
@@ -7068,7 +7068,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G231" t="n">
-        <v>8.52727699279785</v>
+        <v>8.52727603912354</v>
       </c>
       <c r="H231" t="n">
         <v>0</v>
@@ -7097,7 +7097,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G232" t="n">
-        <v>8.52727699279785</v>
+        <v>8.52727603912354</v>
       </c>
       <c r="H232" t="n">
         <v>0</v>
@@ -7126,7 +7126,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G233" t="n">
-        <v>8.52727699279785</v>
+        <v>8.52727603912354</v>
       </c>
       <c r="H233" t="n">
         <v>0</v>
@@ -7184,7 +7184,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G235" t="n">
-        <v>8.2461576461792</v>
+        <v>8.24615669250488</v>
       </c>
       <c r="H235" t="n">
         <v>1000</v>
@@ -7300,7 +7300,7 @@
         <v>8.73999977111816</v>
       </c>
       <c r="G239" t="n">
-        <v>8.18993377685547</v>
+        <v>8.18993282318115</v>
       </c>
       <c r="H239" t="n">
         <v>500</v>
@@ -7329,7 +7329,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G240" t="n">
-        <v>8.05874443054199</v>
+        <v>8.05874538421631</v>
       </c>
       <c r="H240" t="n">
         <v>400</v>
@@ -7387,7 +7387,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G242" t="n">
-        <v>7.68391942977905</v>
+        <v>7.68391895294189</v>
       </c>
       <c r="H242" t="n">
         <v>10000</v>
@@ -7416,7 +7416,7 @@
         <v>8.15999984741211</v>
       </c>
       <c r="G243" t="n">
-        <v>7.64643669128418</v>
+        <v>7.64643621444702</v>
       </c>
       <c r="H243" t="n">
         <v>28200</v>
@@ -7474,7 +7474,7 @@
         <v>8.0600004196167</v>
       </c>
       <c r="G245" t="n">
-        <v>7.55273103713989</v>
+        <v>7.55273056030273</v>
       </c>
       <c r="H245" t="n">
         <v>500</v>
@@ -7503,7 +7503,7 @@
         <v>8.0600004196167</v>
       </c>
       <c r="G246" t="n">
-        <v>7.55273103713989</v>
+        <v>7.55273056030273</v>
       </c>
       <c r="H246" t="n">
         <v>2400</v>
@@ -7532,7 +7532,7 @@
         <v>8.0600004196167</v>
       </c>
       <c r="G247" t="n">
-        <v>7.55273103713989</v>
+        <v>7.55273056030273</v>
       </c>
       <c r="H247" t="n">
         <v>300</v>
@@ -7561,7 +7561,7 @@
         <v>8.0600004196167</v>
       </c>
       <c r="G248" t="n">
-        <v>7.55273103713989</v>
+        <v>7.55273056030273</v>
       </c>
       <c r="H248" t="n">
         <v>0</v>
@@ -7648,7 +7648,7 @@
         <v>8.23999977111816</v>
       </c>
       <c r="G251" t="n">
-        <v>7.72140169143677</v>
+        <v>7.72140121459961</v>
       </c>
       <c r="H251" t="n">
         <v>100</v>
@@ -7764,7 +7764,7 @@
         <v>7.61999988555908</v>
       </c>
       <c r="G255" t="n">
-        <v>7.14042234420776</v>
+        <v>7.14042186737061</v>
       </c>
       <c r="H255" t="n">
         <v>13900</v>
@@ -7851,7 +7851,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G258" t="n">
-        <v>7.12168121337891</v>
+        <v>7.12168073654175</v>
       </c>
       <c r="H258" t="n">
         <v>4500</v>
@@ -7996,7 +7996,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G263" t="n">
-        <v>7.40280055999756</v>
+        <v>7.4028000831604</v>
       </c>
       <c r="H263" t="n">
         <v>2900</v>
@@ -8083,7 +8083,7 @@
         <v>7.61999988555908</v>
       </c>
       <c r="G266" t="n">
-        <v>7.14042234420776</v>
+        <v>7.14042186737061</v>
       </c>
       <c r="H266" t="n">
         <v>600</v>
@@ -8257,7 +8257,7 @@
         <v>8.53999996185303</v>
       </c>
       <c r="G272" t="n">
-        <v>8.00252151489258</v>
+        <v>8.00252056121826</v>
       </c>
       <c r="H272" t="n">
         <v>9400</v>
@@ -8373,7 +8373,7 @@
         <v>9.11999988555908</v>
       </c>
       <c r="G276" t="n">
-        <v>8.54601764678955</v>
+        <v>8.54601669311523</v>
       </c>
       <c r="H276" t="n">
         <v>1600</v>
@@ -8460,7 +8460,7 @@
         <v>9.11999988555908</v>
       </c>
       <c r="G279" t="n">
-        <v>8.54601764678955</v>
+        <v>8.54601669311523</v>
       </c>
       <c r="H279" t="n">
         <v>2000</v>
@@ -8489,7 +8489,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G280" t="n">
-        <v>8.52727699279785</v>
+        <v>8.52727603912354</v>
       </c>
       <c r="H280" t="n">
         <v>1100</v>
@@ -8547,7 +8547,7 @@
         <v>8.92000007629395</v>
       </c>
       <c r="G282" t="n">
-        <v>8.35860443115234</v>
+        <v>8.35860538482666</v>
       </c>
       <c r="H282" t="n">
         <v>200</v>
@@ -8692,7 +8692,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G287" t="n">
-        <v>8.2461576461792</v>
+        <v>8.24615669250488</v>
       </c>
       <c r="H287" t="n">
         <v>200</v>
@@ -8750,7 +8750,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G289" t="n">
-        <v>8.52727699279785</v>
+        <v>8.52727603912354</v>
       </c>
       <c r="H289" t="n">
         <v>2100</v>
@@ -8808,7 +8808,7 @@
         <v>9.11999988555908</v>
       </c>
       <c r="G291" t="n">
-        <v>8.54601764678955</v>
+        <v>8.54601669311523</v>
       </c>
       <c r="H291" t="n">
         <v>3400</v>
@@ -8837,7 +8837,7 @@
         <v>9.11999988555908</v>
       </c>
       <c r="G292" t="n">
-        <v>8.54601764678955</v>
+        <v>8.54601669311523</v>
       </c>
       <c r="H292" t="n">
         <v>2100</v>
@@ -9040,7 +9040,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G299" t="n">
-        <v>8.52727699279785</v>
+        <v>8.52727603912354</v>
       </c>
       <c r="H299" t="n">
         <v>700</v>
@@ -9098,7 +9098,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G301" t="n">
-        <v>8.52727699279785</v>
+        <v>8.52727603912354</v>
       </c>
       <c r="H301" t="n">
         <v>300</v>
@@ -9214,7 +9214,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G305" t="n">
-        <v>8.2461576461792</v>
+        <v>8.24615669250488</v>
       </c>
       <c r="H305" t="n">
         <v>1700</v>
@@ -9243,7 +9243,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G306" t="n">
-        <v>8.2461576461792</v>
+        <v>8.24615669250488</v>
       </c>
       <c r="H306" t="n">
         <v>0</v>
@@ -9272,7 +9272,7 @@
         <v>8.64000034332275</v>
       </c>
       <c r="G307" t="n">
-        <v>8.09622764587402</v>
+        <v>8.09622669219971</v>
       </c>
       <c r="H307" t="n">
         <v>1600</v>
@@ -9301,7 +9301,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G308" t="n">
-        <v>8.05874443054199</v>
+        <v>8.05874538421631</v>
       </c>
       <c r="H308" t="n">
         <v>100</v>
@@ -9330,7 +9330,7 @@
         <v>8.53999996185303</v>
       </c>
       <c r="G309" t="n">
-        <v>8.00252151489258</v>
+        <v>8.00252056121826</v>
       </c>
       <c r="H309" t="n">
         <v>2500</v>
@@ -9359,7 +9359,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G310" t="n">
-        <v>8.2461576461792</v>
+        <v>8.24615669250488</v>
       </c>
       <c r="H310" t="n">
         <v>1000</v>
@@ -9388,7 +9388,7 @@
         <v>8.47999954223633</v>
       </c>
       <c r="G311" t="n">
-        <v>7.94629669189453</v>
+        <v>7.94629621505737</v>
       </c>
       <c r="H311" t="n">
         <v>4000</v>
@@ -9417,7 +9417,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G312" t="n">
-        <v>7.83384895324707</v>
+        <v>7.83384943008423</v>
       </c>
       <c r="H312" t="n">
         <v>1100</v>
@@ -9475,7 +9475,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G314" t="n">
-        <v>8.2461576461792</v>
+        <v>8.24615669250488</v>
       </c>
       <c r="H314" t="n">
         <v>1600</v>
@@ -9533,7 +9533,7 @@
         <v>8.47999954223633</v>
       </c>
       <c r="G316" t="n">
-        <v>7.94629669189453</v>
+        <v>7.94629621505737</v>
       </c>
       <c r="H316" t="n">
         <v>2000</v>
@@ -9591,7 +9591,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G318" t="n">
-        <v>8.2461576461792</v>
+        <v>8.24615669250488</v>
       </c>
       <c r="H318" t="n">
         <v>1600</v>
@@ -9620,7 +9620,7 @@
         <v>8.47999954223633</v>
       </c>
       <c r="G319" t="n">
-        <v>7.94629669189453</v>
+        <v>7.94629621505737</v>
       </c>
       <c r="H319" t="n">
         <v>1300</v>
@@ -9649,7 +9649,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G320" t="n">
-        <v>7.87133169174194</v>
+        <v>7.87133121490479</v>
       </c>
       <c r="H320" t="n">
         <v>1000</v>
@@ -10113,7 +10113,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G336" t="n">
-        <v>8.2461576461792</v>
+        <v>8.24615669250488</v>
       </c>
       <c r="H336" t="n">
         <v>7500</v>
@@ -10316,7 +10316,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G343" t="n">
-        <v>9.08951473236084</v>
+        <v>9.08951377868652</v>
       </c>
       <c r="H343" t="n">
         <v>10200</v>
@@ -10345,7 +10345,7 @@
         <v>9.5</v>
       </c>
       <c r="G344" t="n">
-        <v>8.90210151672363</v>
+        <v>8.90210056304932</v>
       </c>
       <c r="H344" t="n">
         <v>4500</v>
@@ -10374,7 +10374,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G345" t="n">
-        <v>9.08951473236084</v>
+        <v>9.08951377868652</v>
       </c>
       <c r="H345" t="n">
         <v>4500</v>
@@ -10432,7 +10432,7 @@
         <v>9.5</v>
       </c>
       <c r="G347" t="n">
-        <v>8.90210151672363</v>
+        <v>8.90210056304932</v>
       </c>
       <c r="H347" t="n">
         <v>5000</v>
@@ -10461,7 +10461,7 @@
         <v>9.5</v>
       </c>
       <c r="G348" t="n">
-        <v>8.90210151672363</v>
+        <v>8.90210056304932</v>
       </c>
       <c r="H348" t="n">
         <v>0</v>
@@ -10519,7 +10519,7 @@
         <v>9.5</v>
       </c>
       <c r="G350" t="n">
-        <v>8.90210151672363</v>
+        <v>8.90210056304932</v>
       </c>
       <c r="H350" t="n">
         <v>2800</v>
@@ -10548,7 +10548,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G351" t="n">
-        <v>9.08951473236084</v>
+        <v>9.08951377868652</v>
       </c>
       <c r="H351" t="n">
         <v>800</v>
@@ -10577,7 +10577,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G352" t="n">
-        <v>8.99580860137939</v>
+        <v>8.99580764770508</v>
       </c>
       <c r="H352" t="n">
         <v>1900</v>
@@ -10606,7 +10606,7 @@
         <v>9.5</v>
       </c>
       <c r="G353" t="n">
-        <v>8.90210151672363</v>
+        <v>8.90210056304932</v>
       </c>
       <c r="H353" t="n">
         <v>2900</v>
@@ -10635,7 +10635,7 @@
         <v>9.5</v>
       </c>
       <c r="G354" t="n">
-        <v>8.90210151672363</v>
+        <v>8.90210056304932</v>
       </c>
       <c r="H354" t="n">
         <v>0</v>
@@ -10664,7 +10664,7 @@
         <v>9.5</v>
       </c>
       <c r="G355" t="n">
-        <v>8.90210151672363</v>
+        <v>8.90210056304932</v>
       </c>
       <c r="H355" t="n">
         <v>1700</v>
@@ -10693,7 +10693,7 @@
         <v>9.5</v>
       </c>
       <c r="G356" t="n">
-        <v>8.90210151672363</v>
+        <v>8.90210056304932</v>
       </c>
       <c r="H356" t="n">
         <v>0</v>
@@ -10722,7 +10722,7 @@
         <v>9.5</v>
       </c>
       <c r="G357" t="n">
-        <v>8.90210151672363</v>
+        <v>8.90210056304932</v>
       </c>
       <c r="H357" t="n">
         <v>0</v>
@@ -10867,7 +10867,7 @@
         <v>9.5</v>
       </c>
       <c r="G362" t="n">
-        <v>8.90210151672363</v>
+        <v>8.90210056304932</v>
       </c>
       <c r="H362" t="n">
         <v>5500</v>
@@ -11099,7 +11099,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G370" t="n">
-        <v>9.27692699432373</v>
+        <v>9.27692604064941</v>
       </c>
       <c r="H370" t="n">
         <v>2100</v>
@@ -11244,7 +11244,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G375" t="n">
-        <v>9.30551815032959</v>
+        <v>9.30551719665527</v>
       </c>
       <c r="H375" t="n">
         <v>600</v>
@@ -11273,7 +11273,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G376" t="n">
-        <v>9.2575511932373</v>
+        <v>9.25755023956299</v>
       </c>
       <c r="H376" t="n">
         <v>2500</v>
@@ -11331,7 +11331,7 @@
         <v>10</v>
       </c>
       <c r="G378" t="n">
-        <v>9.59331798553467</v>
+        <v>9.59331703186035</v>
       </c>
       <c r="H378" t="n">
         <v>7200</v>
@@ -11708,7 +11708,7 @@
         <v>10</v>
       </c>
       <c r="G391" t="n">
-        <v>9.59331798553467</v>
+        <v>9.59331703186035</v>
       </c>
       <c r="H391" t="n">
         <v>300</v>
@@ -11853,7 +11853,7 @@
         <v>10</v>
       </c>
       <c r="G396" t="n">
-        <v>9.59331798553467</v>
+        <v>9.59331703186035</v>
       </c>
       <c r="H396" t="n">
         <v>500</v>
@@ -11882,7 +11882,7 @@
         <v>10</v>
       </c>
       <c r="G397" t="n">
-        <v>9.59331798553467</v>
+        <v>9.59331703186035</v>
       </c>
       <c r="H397" t="n">
         <v>0</v>
@@ -11940,7 +11940,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G399" t="n">
-        <v>9.30551815032959</v>
+        <v>9.30551719665527</v>
       </c>
       <c r="H399" t="n">
         <v>1600</v>
@@ -11998,7 +11998,7 @@
         <v>9.35000038146973</v>
       </c>
       <c r="G401" t="n">
-        <v>8.96975231170654</v>
+        <v>8.96975135803223</v>
       </c>
       <c r="H401" t="n">
         <v>5200</v>
@@ -12288,7 +12288,7 @@
         <v>10</v>
       </c>
       <c r="G411" t="n">
-        <v>9.59331798553467</v>
+        <v>9.59331703186035</v>
       </c>
       <c r="H411" t="n">
         <v>600</v>
@@ -12433,7 +12433,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G416" t="n">
-        <v>9.2575511932373</v>
+        <v>9.25755023956299</v>
       </c>
       <c r="H416" t="n">
         <v>700</v>
@@ -12462,7 +12462,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G417" t="n">
-        <v>9.2575511932373</v>
+        <v>9.25755023956299</v>
       </c>
       <c r="H417" t="n">
         <v>0</v>
@@ -12491,7 +12491,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G418" t="n">
-        <v>9.2575511932373</v>
+        <v>9.25755023956299</v>
       </c>
       <c r="H418" t="n">
         <v>0</v>
@@ -12520,7 +12520,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G419" t="n">
-        <v>9.30551815032959</v>
+        <v>9.30551719665527</v>
       </c>
       <c r="H419" t="n">
         <v>1700</v>
@@ -12578,7 +12578,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G421" t="n">
-        <v>9.01771831512451</v>
+        <v>9.0177173614502</v>
       </c>
       <c r="H421" t="n">
         <v>100</v>
@@ -12636,7 +12636,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G423" t="n">
-        <v>9.2575511932373</v>
+        <v>9.25755023956299</v>
       </c>
       <c r="H423" t="n">
         <v>1100</v>
@@ -12665,7 +12665,7 @@
         <v>9.35000038146973</v>
       </c>
       <c r="G424" t="n">
-        <v>8.96975231170654</v>
+        <v>8.96975135803223</v>
       </c>
       <c r="H424" t="n">
         <v>500</v>
@@ -12694,7 +12694,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G425" t="n">
-        <v>8.53805160522461</v>
+        <v>8.53805255889893</v>
       </c>
       <c r="H425" t="n">
         <v>1300</v>
@@ -12810,7 +12810,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G429" t="n">
-        <v>9.2575511932373</v>
+        <v>9.25755023956299</v>
       </c>
       <c r="H429" t="n">
         <v>700</v>
@@ -12839,7 +12839,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G430" t="n">
-        <v>9.2575511932373</v>
+        <v>9.25755023956299</v>
       </c>
       <c r="H430" t="n">
         <v>0</v>
@@ -12897,7 +12897,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G432" t="n">
-        <v>9.01771831512451</v>
+        <v>9.0177173614502</v>
       </c>
       <c r="H432" t="n">
         <v>100</v>
@@ -12926,7 +12926,7 @@
         <v>9.35000038146973</v>
       </c>
       <c r="G433" t="n">
-        <v>8.96975231170654</v>
+        <v>8.96975135803223</v>
       </c>
       <c r="H433" t="n">
         <v>1200</v>
@@ -12984,7 +12984,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G435" t="n">
-        <v>9.30551815032959</v>
+        <v>9.30551719665527</v>
       </c>
       <c r="H435" t="n">
         <v>200</v>
@@ -13013,7 +13013,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G436" t="n">
-        <v>9.2575511932373</v>
+        <v>9.25755023956299</v>
       </c>
       <c r="H436" t="n">
         <v>400</v>
@@ -13071,7 +13071,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G438" t="n">
-        <v>9.01771831512451</v>
+        <v>9.0177173614502</v>
       </c>
       <c r="H438" t="n">
         <v>600</v>
@@ -13100,7 +13100,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G439" t="n">
-        <v>9.30551815032959</v>
+        <v>9.30551719665527</v>
       </c>
       <c r="H439" t="n">
         <v>200</v>
@@ -13129,7 +13129,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G440" t="n">
-        <v>9.30551815032959</v>
+        <v>9.30551719665527</v>
       </c>
       <c r="H440" t="n">
         <v>500</v>
@@ -13158,7 +13158,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G441" t="n">
-        <v>9.30551815032959</v>
+        <v>9.30551719665527</v>
       </c>
       <c r="H441" t="n">
         <v>600</v>
@@ -13187,7 +13187,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G442" t="n">
-        <v>9.30551815032959</v>
+        <v>9.30551719665527</v>
       </c>
       <c r="H442" t="n">
         <v>800</v>
@@ -13274,7 +13274,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G445" t="n">
-        <v>9.01771831512451</v>
+        <v>9.0177173614502</v>
       </c>
       <c r="H445" t="n">
         <v>4900</v>
@@ -13303,7 +13303,7 @@
         <v>9.44999980926514</v>
       </c>
       <c r="G446" t="n">
-        <v>9.0656852722168</v>
+        <v>9.06568431854248</v>
       </c>
       <c r="H446" t="n">
         <v>4900</v>
@@ -13332,7 +13332,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G447" t="n">
-        <v>9.01771831512451</v>
+        <v>9.0177173614502</v>
       </c>
       <c r="H447" t="n">
         <v>2000</v>
@@ -13361,7 +13361,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G448" t="n">
-        <v>8.82585144042969</v>
+        <v>8.825852394104</v>
       </c>
       <c r="H448" t="n">
         <v>1200</v>
@@ -13535,7 +13535,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G454" t="n">
-        <v>8.82585144042969</v>
+        <v>8.825852394104</v>
       </c>
       <c r="H454" t="n">
         <v>100</v>
@@ -13564,7 +13564,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G455" t="n">
-        <v>8.82585144042969</v>
+        <v>8.825852394104</v>
       </c>
       <c r="H455" t="n">
         <v>0</v>
@@ -13593,7 +13593,7 @@
         <v>9.35000038146973</v>
       </c>
       <c r="G456" t="n">
-        <v>8.96975231170654</v>
+        <v>8.96975135803223</v>
       </c>
       <c r="H456" t="n">
         <v>9000</v>
@@ -13796,7 +13796,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G463" t="n">
-        <v>8.53805160522461</v>
+        <v>8.53805255889893</v>
       </c>
       <c r="H463" t="n">
         <v>800</v>
@@ -14057,7 +14057,7 @@
         <v>7.75</v>
       </c>
       <c r="G472" t="n">
-        <v>7.43482112884521</v>
+        <v>7.43482065200806</v>
       </c>
       <c r="H472" t="n">
         <v>5500</v>
@@ -14289,7 +14289,7 @@
         <v>7.5</v>
       </c>
       <c r="G480" t="n">
-        <v>7.19498777389526</v>
+        <v>7.19498825073242</v>
       </c>
       <c r="H480" t="n">
         <v>1800</v>
@@ -14318,7 +14318,7 @@
         <v>7.34999990463257</v>
       </c>
       <c r="G481" t="n">
-        <v>7.05108785629272</v>
+        <v>7.05108833312988</v>
       </c>
       <c r="H481" t="n">
         <v>4200</v>
@@ -14347,7 +14347,7 @@
         <v>7.34999990463257</v>
       </c>
       <c r="G482" t="n">
-        <v>7.05108785629272</v>
+        <v>7.05108833312988</v>
       </c>
       <c r="H482" t="n">
         <v>7800</v>
@@ -14434,7 +14434,7 @@
         <v>7</v>
       </c>
       <c r="G485" t="n">
-        <v>6.71532201766968</v>
+        <v>6.71532249450684</v>
       </c>
       <c r="H485" t="n">
         <v>10100</v>
@@ -14724,7 +14724,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G495" t="n">
-        <v>6.04379034042358</v>
+        <v>6.04378986358643</v>
       </c>
       <c r="H495" t="n">
         <v>7900</v>
@@ -15014,7 +15014,7 @@
         <v>7</v>
       </c>
       <c r="G505" t="n">
-        <v>6.71532201766968</v>
+        <v>6.71532249450684</v>
       </c>
       <c r="H505" t="n">
         <v>13500</v>
@@ -15072,7 +15072,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G507" t="n">
-        <v>6.81125497817993</v>
+        <v>6.81125545501709</v>
       </c>
       <c r="H507" t="n">
         <v>3900</v>
@@ -15159,7 +15159,7 @@
         <v>7.75</v>
       </c>
       <c r="G510" t="n">
-        <v>7.43482112884521</v>
+        <v>7.43482065200806</v>
       </c>
       <c r="H510" t="n">
         <v>3700</v>
@@ -15681,7 +15681,7 @@
         <v>7.34999990463257</v>
       </c>
       <c r="G528" t="n">
-        <v>7.05108785629272</v>
+        <v>7.05108833312988</v>
       </c>
       <c r="H528" t="n">
         <v>4000</v>
@@ -15884,7 +15884,7 @@
         <v>7.5</v>
       </c>
       <c r="G535" t="n">
-        <v>7.19498777389526</v>
+        <v>7.19498825073242</v>
       </c>
       <c r="H535" t="n">
         <v>200</v>
@@ -16029,7 +16029,7 @@
         <v>7</v>
       </c>
       <c r="G540" t="n">
-        <v>6.71532201766968</v>
+        <v>6.71532249450684</v>
       </c>
       <c r="H540" t="n">
         <v>7000</v>
@@ -16203,7 +16203,7 @@
         <v>6.94999980926514</v>
       </c>
       <c r="G546" t="n">
-        <v>6.66735506057739</v>
+        <v>6.66735553741455</v>
       </c>
       <c r="H546" t="n">
         <v>2700</v>
@@ -16290,7 +16290,7 @@
         <v>7</v>
       </c>
       <c r="G549" t="n">
-        <v>6.71532201766968</v>
+        <v>6.71532249450684</v>
       </c>
       <c r="H549" t="n">
         <v>9500</v>
@@ -16319,7 +16319,7 @@
         <v>6.94999980926514</v>
       </c>
       <c r="G550" t="n">
-        <v>6.66735506057739</v>
+        <v>6.66735553741455</v>
       </c>
       <c r="H550" t="n">
         <v>16600</v>
@@ -16580,7 +16580,7 @@
         <v>7.75</v>
       </c>
       <c r="G559" t="n">
-        <v>7.43482112884521</v>
+        <v>7.43482065200806</v>
       </c>
       <c r="H559" t="n">
         <v>4000</v>
@@ -16725,7 +16725,7 @@
         <v>7.75</v>
       </c>
       <c r="G564" t="n">
-        <v>7.43482112884521</v>
+        <v>7.43482065200806</v>
       </c>
       <c r="H564" t="n">
         <v>700</v>
@@ -16841,7 +16841,7 @@
         <v>7.75</v>
       </c>
       <c r="G568" t="n">
-        <v>7.43482112884521</v>
+        <v>7.43482065200806</v>
       </c>
       <c r="H568" t="n">
         <v>6900</v>
@@ -17015,7 +17015,7 @@
         <v>8.14999961853027</v>
       </c>
       <c r="G574" t="n">
-        <v>7.81855344772339</v>
+        <v>7.81855297088623</v>
       </c>
       <c r="H574" t="n">
         <v>5200</v>
@@ -17160,7 +17160,7 @@
         <v>7.5</v>
       </c>
       <c r="G579" t="n">
-        <v>7.19498777389526</v>
+        <v>7.19498825073242</v>
       </c>
       <c r="H579" t="n">
         <v>3100</v>
@@ -17247,7 +17247,7 @@
         <v>8.25</v>
       </c>
       <c r="G582" t="n">
-        <v>7.91448736190796</v>
+        <v>7.91448640823364</v>
       </c>
       <c r="H582" t="n">
         <v>10200</v>
@@ -17276,7 +17276,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G583" t="n">
-        <v>7.86652040481567</v>
+        <v>7.86651945114136</v>
       </c>
       <c r="H583" t="n">
         <v>20900</v>
@@ -17334,7 +17334,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G585" t="n">
-        <v>7.86652040481567</v>
+        <v>7.86651945114136</v>
       </c>
       <c r="H585" t="n">
         <v>5700</v>
@@ -17363,7 +17363,7 @@
         <v>7.75</v>
       </c>
       <c r="G586" t="n">
-        <v>7.43482112884521</v>
+        <v>7.43482065200806</v>
       </c>
       <c r="H586" t="n">
         <v>8000</v>
@@ -17392,7 +17392,7 @@
         <v>7.75</v>
       </c>
       <c r="G587" t="n">
-        <v>7.43482112884521</v>
+        <v>7.43482065200806</v>
       </c>
       <c r="H587" t="n">
         <v>1500</v>
@@ -17421,7 +17421,7 @@
         <v>7.75</v>
       </c>
       <c r="G588" t="n">
-        <v>7.43482112884521</v>
+        <v>7.43482065200806</v>
       </c>
       <c r="H588" t="n">
         <v>100</v>
@@ -17479,7 +17479,7 @@
         <v>7.75</v>
       </c>
       <c r="G590" t="n">
-        <v>7.43482112884521</v>
+        <v>7.43482065200806</v>
       </c>
       <c r="H590" t="n">
         <v>2300</v>
@@ -17653,7 +17653,7 @@
         <v>6.94999980926514</v>
       </c>
       <c r="G596" t="n">
-        <v>6.66735506057739</v>
+        <v>6.66735553741455</v>
       </c>
       <c r="H596" t="n">
         <v>1100</v>
@@ -17682,7 +17682,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G597" t="n">
-        <v>6.90718841552734</v>
+        <v>6.90718793869019</v>
       </c>
       <c r="H597" t="n">
         <v>1200</v>
@@ -17711,7 +17711,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G598" t="n">
-        <v>6.90718841552734</v>
+        <v>6.90718793869019</v>
       </c>
       <c r="H598" t="n">
         <v>0</v>
@@ -17798,7 +17798,7 @@
         <v>7.34999990463257</v>
       </c>
       <c r="G601" t="n">
-        <v>7.05108785629272</v>
+        <v>7.05108833312988</v>
       </c>
       <c r="H601" t="n">
         <v>2100</v>
@@ -17827,7 +17827,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G602" t="n">
-        <v>6.90718841552734</v>
+        <v>6.90718793869019</v>
       </c>
       <c r="H602" t="n">
         <v>1600</v>
@@ -17885,7 +17885,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G604" t="n">
-        <v>6.81125497817993</v>
+        <v>6.81125545501709</v>
       </c>
       <c r="H604" t="n">
         <v>15300</v>
@@ -28940,6 +28940,35 @@
         <v>8200</v>
       </c>
       <c r="I985" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="986">
+      <c r="A986" t="s">
+        <v>9</v>
+      </c>
+      <c r="B986" s="1" t="n">
+        <v>46318.2916666667</v>
+      </c>
+      <c r="C986" t="n">
+        <v>10.6000003814697</v>
+      </c>
+      <c r="D986" t="n">
+        <v>10.6000003814697</v>
+      </c>
+      <c r="E986" t="n">
+        <v>10.6000003814697</v>
+      </c>
+      <c r="F986" t="n">
+        <v>10.6000003814697</v>
+      </c>
+      <c r="G986" t="n">
+        <v>10.6000003814697</v>
+      </c>
+      <c r="H986" t="n">
+        <v>200</v>
+      </c>
+      <c r="I986" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/RDUE.MI.xlsx
+++ b/data/RDUE.MI.xlsx
@@ -543,7 +543,7 @@
         <v>12.0539999008179</v>
       </c>
       <c r="G6" t="n">
-        <v>11.2953615188599</v>
+        <v>11.2953605651855</v>
       </c>
       <c r="H6" t="n">
         <v>9400</v>
@@ -572,7 +572,7 @@
         <v>12.0900001525879</v>
       </c>
       <c r="G7" t="n">
-        <v>11.3290958404541</v>
+        <v>11.3290948867798</v>
       </c>
       <c r="H7" t="n">
         <v>1000</v>
@@ -688,7 +688,7 @@
         <v>11.9180002212524</v>
       </c>
       <c r="G11" t="n">
-        <v>11.1679210662842</v>
+        <v>11.1679201126099</v>
       </c>
       <c r="H11" t="n">
         <v>2300</v>
@@ -746,7 +746,7 @@
         <v>11.8800001144409</v>
       </c>
       <c r="G13" t="n">
-        <v>11.1323127746582</v>
+        <v>11.1323118209839</v>
       </c>
       <c r="H13" t="n">
         <v>5200</v>
@@ -804,7 +804,7 @@
         <v>11.6199998855591</v>
       </c>
       <c r="G15" t="n">
-        <v>10.8886756896973</v>
+        <v>10.8886747360229</v>
       </c>
       <c r="H15" t="n">
         <v>1900</v>
@@ -833,7 +833,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G16" t="n">
-        <v>11.0573472976685</v>
+        <v>11.0573463439941</v>
       </c>
       <c r="H16" t="n">
         <v>200</v>
@@ -862,7 +862,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G17" t="n">
-        <v>11.0573472976685</v>
+        <v>11.0573463439941</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
@@ -949,7 +949,7 @@
         <v>11.5900001525879</v>
       </c>
       <c r="G20" t="n">
-        <v>10.8605632781982</v>
+        <v>10.8605642318726</v>
       </c>
       <c r="H20" t="n">
         <v>800</v>
@@ -1007,7 +1007,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G22" t="n">
-        <v>10.6825218200684</v>
+        <v>10.682520866394</v>
       </c>
       <c r="H22" t="n">
         <v>600</v>
@@ -1065,7 +1065,7 @@
         <v>11.2600002288818</v>
       </c>
       <c r="G24" t="n">
-        <v>10.5513334274292</v>
+        <v>10.5513324737549</v>
       </c>
       <c r="H24" t="n">
         <v>200</v>
@@ -1094,7 +1094,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G25" t="n">
-        <v>10.5888156890869</v>
+        <v>10.5888147354126</v>
       </c>
       <c r="H25" t="n">
         <v>600</v>
@@ -1123,7 +1123,7 @@
         <v>11.25</v>
       </c>
       <c r="G26" t="n">
-        <v>10.5419626235962</v>
+        <v>10.5419616699219</v>
       </c>
       <c r="H26" t="n">
         <v>400</v>
@@ -1210,7 +1210,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G29" t="n">
-        <v>11.3384666442871</v>
+        <v>11.3384656906128</v>
       </c>
       <c r="H29" t="n">
         <v>12200</v>
@@ -1239,7 +1239,7 @@
         <v>11.8800001144409</v>
       </c>
       <c r="G30" t="n">
-        <v>11.1323127746582</v>
+        <v>11.1323118209839</v>
       </c>
       <c r="H30" t="n">
         <v>3900</v>
@@ -1268,7 +1268,7 @@
         <v>11.9799995422363</v>
       </c>
       <c r="G31" t="n">
-        <v>11.2260189056396</v>
+        <v>11.2260179519653</v>
       </c>
       <c r="H31" t="n">
         <v>200</v>
@@ -1355,7 +1355,7 @@
         <v>11.75</v>
       </c>
       <c r="G34" t="n">
-        <v>11.0104932785034</v>
+        <v>11.0104942321777</v>
       </c>
       <c r="H34" t="n">
         <v>3400</v>
@@ -1384,7 +1384,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G35" t="n">
-        <v>11.0573472976685</v>
+        <v>11.0573463439941</v>
       </c>
       <c r="H35" t="n">
         <v>2200</v>
@@ -1413,7 +1413,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G36" t="n">
-        <v>11.0573472976685</v>
+        <v>11.0573463439941</v>
       </c>
       <c r="H36" t="n">
         <v>0</v>
@@ -1442,7 +1442,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G37" t="n">
-        <v>11.0573472976685</v>
+        <v>11.0573463439941</v>
       </c>
       <c r="H37" t="n">
         <v>3200</v>
@@ -1500,7 +1500,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G39" t="n">
-        <v>11.1510534286499</v>
+        <v>11.1510524749756</v>
       </c>
       <c r="H39" t="n">
         <v>500</v>
@@ -1529,7 +1529,7 @@
         <v>11.9799995422363</v>
       </c>
       <c r="G40" t="n">
-        <v>11.2260189056396</v>
+        <v>11.2260179519653</v>
       </c>
       <c r="H40" t="n">
         <v>400</v>
@@ -1558,7 +1558,7 @@
         <v>11.9799995422363</v>
       </c>
       <c r="G41" t="n">
-        <v>11.2260189056396</v>
+        <v>11.2260179519653</v>
       </c>
       <c r="H41" t="n">
         <v>0</v>
@@ -1616,7 +1616,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G43" t="n">
-        <v>11.0573472976685</v>
+        <v>11.0573463439941</v>
       </c>
       <c r="H43" t="n">
         <v>4800</v>
@@ -1761,7 +1761,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G48" t="n">
-        <v>11.0573472976685</v>
+        <v>11.0573463439941</v>
       </c>
       <c r="H48" t="n">
         <v>1200</v>
@@ -1819,7 +1819,7 @@
         <v>11.5500001907349</v>
       </c>
       <c r="G50" t="n">
-        <v>10.8230819702148</v>
+        <v>10.8230810165405</v>
       </c>
       <c r="H50" t="n">
         <v>400</v>
@@ -1848,7 +1848,7 @@
         <v>11.5500001907349</v>
       </c>
       <c r="G51" t="n">
-        <v>10.8230819702148</v>
+        <v>10.8230810165405</v>
       </c>
       <c r="H51" t="n">
         <v>1700</v>
@@ -1877,7 +1877,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G52" t="n">
-        <v>11.0573472976685</v>
+        <v>11.0573463439941</v>
       </c>
       <c r="H52" t="n">
         <v>100</v>
@@ -1935,7 +1935,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G54" t="n">
-        <v>11.0573472976685</v>
+        <v>11.0573463439941</v>
       </c>
       <c r="H54" t="n">
         <v>700</v>
@@ -1964,7 +1964,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G55" t="n">
-        <v>11.0573472976685</v>
+        <v>11.0573463439941</v>
       </c>
       <c r="H55" t="n">
         <v>100</v>
@@ -1993,7 +1993,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G56" t="n">
-        <v>11.0573472976685</v>
+        <v>11.0573463439941</v>
       </c>
       <c r="H56" t="n">
         <v>0</v>
@@ -2022,7 +2022,7 @@
         <v>11.75</v>
       </c>
       <c r="G57" t="n">
-        <v>11.0104932785034</v>
+        <v>11.0104942321777</v>
       </c>
       <c r="H57" t="n">
         <v>200</v>
@@ -2051,7 +2051,7 @@
         <v>11.75</v>
       </c>
       <c r="G58" t="n">
-        <v>11.0104932785034</v>
+        <v>11.0104942321777</v>
       </c>
       <c r="H58" t="n">
         <v>500</v>
@@ -2080,7 +2080,7 @@
         <v>11.75</v>
       </c>
       <c r="G59" t="n">
-        <v>11.0104932785034</v>
+        <v>11.0104942321777</v>
       </c>
       <c r="H59" t="n">
         <v>0</v>
@@ -2225,7 +2225,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G64" t="n">
-        <v>10.6825218200684</v>
+        <v>10.682520866394</v>
       </c>
       <c r="H64" t="n">
         <v>2900</v>
@@ -2254,7 +2254,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G65" t="n">
-        <v>10.6825218200684</v>
+        <v>10.682520866394</v>
       </c>
       <c r="H65" t="n">
         <v>500</v>
@@ -2283,7 +2283,7 @@
         <v>11.5500001907349</v>
       </c>
       <c r="G66" t="n">
-        <v>10.8230819702148</v>
+        <v>10.8230810165405</v>
       </c>
       <c r="H66" t="n">
         <v>4100</v>
@@ -2341,7 +2341,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G68" t="n">
-        <v>10.6825218200684</v>
+        <v>10.682520866394</v>
       </c>
       <c r="H68" t="n">
         <v>700</v>
@@ -2370,7 +2370,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G69" t="n">
-        <v>10.6825218200684</v>
+        <v>10.682520866394</v>
       </c>
       <c r="H69" t="n">
         <v>0</v>
@@ -2428,7 +2428,7 @@
         <v>11.5</v>
       </c>
       <c r="G71" t="n">
-        <v>10.7762289047241</v>
+        <v>10.7762269973755</v>
       </c>
       <c r="H71" t="n">
         <v>500</v>
@@ -2457,7 +2457,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G72" t="n">
-        <v>10.6825218200684</v>
+        <v>10.682520866394</v>
       </c>
       <c r="H72" t="n">
         <v>3100</v>
@@ -2631,7 +2631,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G78" t="n">
-        <v>11.0573472976685</v>
+        <v>11.0573463439941</v>
       </c>
       <c r="H78" t="n">
         <v>2600</v>
@@ -2660,7 +2660,7 @@
         <v>11.5</v>
       </c>
       <c r="G79" t="n">
-        <v>10.7762289047241</v>
+        <v>10.7762269973755</v>
       </c>
       <c r="H79" t="n">
         <v>2100</v>
@@ -2718,7 +2718,7 @@
         <v>11.5500001907349</v>
       </c>
       <c r="G81" t="n">
-        <v>10.8230819702148</v>
+        <v>10.8230810165405</v>
       </c>
       <c r="H81" t="n">
         <v>800</v>
@@ -2747,7 +2747,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G82" t="n">
-        <v>9.74545764923096</v>
+        <v>9.74545860290527</v>
       </c>
       <c r="H82" t="n">
         <v>13600</v>
@@ -2776,7 +2776,7 @@
         <v>10.0500001907349</v>
       </c>
       <c r="G83" t="n">
-        <v>9.41748714447021</v>
+        <v>9.4174861907959</v>
       </c>
       <c r="H83" t="n">
         <v>13500</v>
@@ -2805,7 +2805,7 @@
         <v>10.0500001907349</v>
       </c>
       <c r="G84" t="n">
-        <v>9.41748714447021</v>
+        <v>9.4174861907959</v>
       </c>
       <c r="H84" t="n">
         <v>16000</v>
@@ -2921,7 +2921,7 @@
         <v>10.25</v>
       </c>
       <c r="G88" t="n">
-        <v>9.60489845275879</v>
+        <v>9.60489940643311</v>
       </c>
       <c r="H88" t="n">
         <v>1800</v>
@@ -2950,7 +2950,7 @@
         <v>10.5500001907349</v>
       </c>
       <c r="G89" t="n">
-        <v>9.88601779937744</v>
+        <v>9.88601875305176</v>
       </c>
       <c r="H89" t="n">
         <v>4400</v>
@@ -2979,7 +2979,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G90" t="n">
-        <v>9.55804538726807</v>
+        <v>9.55804634094238</v>
       </c>
       <c r="H90" t="n">
         <v>600</v>
@@ -3008,7 +3008,7 @@
         <v>10.0500001907349</v>
       </c>
       <c r="G91" t="n">
-        <v>9.41748714447021</v>
+        <v>9.4174861907959</v>
       </c>
       <c r="H91" t="n">
         <v>1800</v>
@@ -3037,7 +3037,7 @@
         <v>9.92000007629395</v>
       </c>
       <c r="G92" t="n">
-        <v>9.29566764831543</v>
+        <v>9.29566860198975</v>
       </c>
       <c r="H92" t="n">
         <v>5200</v>
@@ -3095,7 +3095,7 @@
         <v>9.73999977111816</v>
       </c>
       <c r="G94" t="n">
-        <v>9.12699604034424</v>
+        <v>9.12699699401855</v>
       </c>
       <c r="H94" t="n">
         <v>2000</v>
@@ -3124,7 +3124,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G95" t="n">
-        <v>9.08951377868652</v>
+        <v>9.08951473236084</v>
       </c>
       <c r="H95" t="n">
         <v>800</v>
@@ -3153,7 +3153,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G96" t="n">
-        <v>9.08951377868652</v>
+        <v>9.08951473236084</v>
       </c>
       <c r="H96" t="n">
         <v>0</v>
@@ -3182,7 +3182,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G97" t="n">
-        <v>9.08951377868652</v>
+        <v>9.08951473236084</v>
       </c>
       <c r="H97" t="n">
         <v>0</v>
@@ -3414,7 +3414,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G105" t="n">
-        <v>8.52727603912354</v>
+        <v>8.52727699279785</v>
       </c>
       <c r="H105" t="n">
         <v>1300</v>
@@ -3559,7 +3559,7 @@
         <v>9.4399995803833</v>
       </c>
       <c r="G110" t="n">
-        <v>8.84587669372559</v>
+        <v>8.8458776473999</v>
       </c>
       <c r="H110" t="n">
         <v>200</v>
@@ -3588,7 +3588,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G111" t="n">
-        <v>9.08951377868652</v>
+        <v>9.08951473236084</v>
       </c>
       <c r="H111" t="n">
         <v>500</v>
@@ -3646,7 +3646,7 @@
         <v>9.76000022888184</v>
       </c>
       <c r="G113" t="n">
-        <v>9.14573860168457</v>
+        <v>9.14573764801025</v>
       </c>
       <c r="H113" t="n">
         <v>800</v>
@@ -3675,7 +3675,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G114" t="n">
-        <v>9.55804538726807</v>
+        <v>9.55804634094238</v>
       </c>
       <c r="H114" t="n">
         <v>7600</v>
@@ -3704,7 +3704,7 @@
         <v>10</v>
       </c>
       <c r="G115" t="n">
-        <v>9.37063312530518</v>
+        <v>9.37063407897949</v>
       </c>
       <c r="H115" t="n">
         <v>200</v>
@@ -3733,7 +3733,7 @@
         <v>10.5500001907349</v>
       </c>
       <c r="G116" t="n">
-        <v>9.88601779937744</v>
+        <v>9.88601875305176</v>
       </c>
       <c r="H116" t="n">
         <v>2700</v>
@@ -3762,7 +3762,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G117" t="n">
-        <v>9.74545764923096</v>
+        <v>9.74545860290527</v>
       </c>
       <c r="H117" t="n">
         <v>300</v>
@@ -3791,7 +3791,7 @@
         <v>10.5500001907349</v>
       </c>
       <c r="G118" t="n">
-        <v>9.88601779937744</v>
+        <v>9.88601875305176</v>
       </c>
       <c r="H118" t="n">
         <v>100</v>
@@ -3820,7 +3820,7 @@
         <v>10.5</v>
       </c>
       <c r="G119" t="n">
-        <v>9.83916473388672</v>
+        <v>9.83916568756104</v>
       </c>
       <c r="H119" t="n">
         <v>800</v>
@@ -4023,7 +4023,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G126" t="n">
-        <v>8.99580764770508</v>
+        <v>8.99580860137939</v>
       </c>
       <c r="H126" t="n">
         <v>5200</v>
@@ -4052,7 +4052,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G127" t="n">
-        <v>8.99580764770508</v>
+        <v>8.99580860137939</v>
       </c>
       <c r="H127" t="n">
         <v>300</v>
@@ -4139,7 +4139,7 @@
         <v>9.92000007629395</v>
       </c>
       <c r="G130" t="n">
-        <v>9.29566764831543</v>
+        <v>9.29566860198975</v>
       </c>
       <c r="H130" t="n">
         <v>200</v>
@@ -4168,7 +4168,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G131" t="n">
-        <v>9.65175151824951</v>
+        <v>9.65175342559814</v>
       </c>
       <c r="H131" t="n">
         <v>2700</v>
@@ -4197,7 +4197,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G132" t="n">
-        <v>9.65175151824951</v>
+        <v>9.65175342559814</v>
       </c>
       <c r="H132" t="n">
         <v>100</v>
@@ -4226,7 +4226,7 @@
         <v>9.97999954223633</v>
       </c>
       <c r="G133" t="n">
-        <v>9.35189151763916</v>
+        <v>9.35189247131348</v>
       </c>
       <c r="H133" t="n">
         <v>500</v>
@@ -4313,7 +4313,7 @@
         <v>10.5</v>
       </c>
       <c r="G136" t="n">
-        <v>9.83916473388672</v>
+        <v>9.83916568756104</v>
       </c>
       <c r="H136" t="n">
         <v>700</v>
@@ -4342,7 +4342,7 @@
         <v>10.5500001907349</v>
       </c>
       <c r="G137" t="n">
-        <v>9.88601779937744</v>
+        <v>9.88601875305176</v>
       </c>
       <c r="H137" t="n">
         <v>1000</v>
@@ -4400,7 +4400,7 @@
         <v>10.5</v>
       </c>
       <c r="G139" t="n">
-        <v>9.83916473388672</v>
+        <v>9.83916568756104</v>
       </c>
       <c r="H139" t="n">
         <v>300</v>
@@ -4429,7 +4429,7 @@
         <v>10.5</v>
       </c>
       <c r="G140" t="n">
-        <v>9.83916473388672</v>
+        <v>9.83916568756104</v>
       </c>
       <c r="H140" t="n">
         <v>100</v>
@@ -4458,7 +4458,7 @@
         <v>10.5</v>
       </c>
       <c r="G141" t="n">
-        <v>9.83916473388672</v>
+        <v>9.83916568756104</v>
       </c>
       <c r="H141" t="n">
         <v>0</v>
@@ -4487,7 +4487,7 @@
         <v>10</v>
       </c>
       <c r="G142" t="n">
-        <v>9.37063312530518</v>
+        <v>9.37063407897949</v>
       </c>
       <c r="H142" t="n">
         <v>7600</v>
@@ -4574,7 +4574,7 @@
         <v>9.5600004196167</v>
       </c>
       <c r="G145" t="n">
-        <v>8.95832633972168</v>
+        <v>8.95832538604736</v>
       </c>
       <c r="H145" t="n">
         <v>1400</v>
@@ -4603,7 +4603,7 @@
         <v>9.5</v>
       </c>
       <c r="G146" t="n">
-        <v>8.90210056304932</v>
+        <v>8.90210151672363</v>
       </c>
       <c r="H146" t="n">
         <v>2600</v>
@@ -4632,7 +4632,7 @@
         <v>9.5</v>
       </c>
       <c r="G147" t="n">
-        <v>8.90210056304932</v>
+        <v>8.90210151672363</v>
       </c>
       <c r="H147" t="n">
         <v>0</v>
@@ -4690,7 +4690,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G149" t="n">
-        <v>8.99580764770508</v>
+        <v>8.99580860137939</v>
       </c>
       <c r="H149" t="n">
         <v>4300</v>
@@ -4719,7 +4719,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G150" t="n">
-        <v>8.99580764770508</v>
+        <v>8.99580860137939</v>
       </c>
       <c r="H150" t="n">
         <v>0</v>
@@ -4748,7 +4748,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G151" t="n">
-        <v>9.08951377868652</v>
+        <v>9.08951473236084</v>
       </c>
       <c r="H151" t="n">
         <v>500</v>
@@ -4777,7 +4777,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G152" t="n">
-        <v>9.08951377868652</v>
+        <v>9.08951473236084</v>
       </c>
       <c r="H152" t="n">
         <v>0</v>
@@ -4806,7 +4806,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G153" t="n">
-        <v>9.08951377868652</v>
+        <v>9.08951473236084</v>
       </c>
       <c r="H153" t="n">
         <v>0</v>
@@ -4864,7 +4864,7 @@
         <v>10</v>
       </c>
       <c r="G155" t="n">
-        <v>9.37063312530518</v>
+        <v>9.37063407897949</v>
       </c>
       <c r="H155" t="n">
         <v>100</v>
@@ -4893,7 +4893,7 @@
         <v>10</v>
       </c>
       <c r="G156" t="n">
-        <v>9.37063312530518</v>
+        <v>9.37063407897949</v>
       </c>
       <c r="H156" t="n">
         <v>0</v>
@@ -4922,7 +4922,7 @@
         <v>10</v>
       </c>
       <c r="G157" t="n">
-        <v>9.37063312530518</v>
+        <v>9.37063407897949</v>
       </c>
       <c r="H157" t="n">
         <v>0</v>
@@ -4951,7 +4951,7 @@
         <v>10</v>
       </c>
       <c r="G158" t="n">
-        <v>9.37063312530518</v>
+        <v>9.37063407897949</v>
       </c>
       <c r="H158" t="n">
         <v>0</v>
@@ -4980,7 +4980,7 @@
         <v>10</v>
       </c>
       <c r="G159" t="n">
-        <v>9.37063312530518</v>
+        <v>9.37063407897949</v>
       </c>
       <c r="H159" t="n">
         <v>0</v>
@@ -5009,7 +5009,7 @@
         <v>10</v>
       </c>
       <c r="G160" t="n">
-        <v>9.37063312530518</v>
+        <v>9.37063407897949</v>
       </c>
       <c r="H160" t="n">
         <v>0</v>
@@ -5038,7 +5038,7 @@
         <v>10</v>
       </c>
       <c r="G161" t="n">
-        <v>9.37063312530518</v>
+        <v>9.37063407897949</v>
       </c>
       <c r="H161" t="n">
         <v>0</v>
@@ -5067,7 +5067,7 @@
         <v>10</v>
       </c>
       <c r="G162" t="n">
-        <v>9.37063312530518</v>
+        <v>9.37063407897949</v>
       </c>
       <c r="H162" t="n">
         <v>100</v>
@@ -5125,7 +5125,7 @@
         <v>9.97999954223633</v>
       </c>
       <c r="G164" t="n">
-        <v>9.35189151763916</v>
+        <v>9.35189247131348</v>
       </c>
       <c r="H164" t="n">
         <v>400</v>
@@ -5154,7 +5154,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G165" t="n">
-        <v>9.27692604064941</v>
+        <v>9.27692699432373</v>
       </c>
       <c r="H165" t="n">
         <v>300</v>
@@ -5183,7 +5183,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G166" t="n">
-        <v>9.27692604064941</v>
+        <v>9.27692699432373</v>
       </c>
       <c r="H166" t="n">
         <v>100</v>
@@ -5212,7 +5212,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G167" t="n">
-        <v>9.08951377868652</v>
+        <v>9.08951473236084</v>
       </c>
       <c r="H167" t="n">
         <v>1600</v>
@@ -5241,7 +5241,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G168" t="n">
-        <v>9.08951377868652</v>
+        <v>9.08951473236084</v>
       </c>
       <c r="H168" t="n">
         <v>5000</v>
@@ -5270,7 +5270,7 @@
         <v>9.15999984741211</v>
       </c>
       <c r="G169" t="n">
-        <v>8.58349990844727</v>
+        <v>8.58350086212158</v>
       </c>
       <c r="H169" t="n">
         <v>16200</v>
@@ -5299,7 +5299,7 @@
         <v>9.5</v>
       </c>
       <c r="G170" t="n">
-        <v>8.90210056304932</v>
+        <v>8.90210151672363</v>
       </c>
       <c r="H170" t="n">
         <v>2200</v>
@@ -5357,7 +5357,7 @@
         <v>9.5600004196167</v>
       </c>
       <c r="G172" t="n">
-        <v>8.95832633972168</v>
+        <v>8.95832538604736</v>
       </c>
       <c r="H172" t="n">
         <v>200</v>
@@ -5386,7 +5386,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G173" t="n">
-        <v>9.27692604064941</v>
+        <v>9.27692699432373</v>
       </c>
       <c r="H173" t="n">
         <v>300</v>
@@ -5415,7 +5415,7 @@
         <v>9.27999973297119</v>
       </c>
       <c r="G174" t="n">
-        <v>8.69594669342041</v>
+        <v>8.69594764709473</v>
       </c>
       <c r="H174" t="n">
         <v>8500</v>
@@ -5444,7 +5444,7 @@
         <v>9.42000007629395</v>
       </c>
       <c r="G175" t="n">
-        <v>8.82713603973389</v>
+        <v>8.8271369934082</v>
       </c>
       <c r="H175" t="n">
         <v>800</v>
@@ -5473,7 +5473,7 @@
         <v>9.27999973297119</v>
       </c>
       <c r="G176" t="n">
-        <v>8.69594669342041</v>
+        <v>8.69594764709473</v>
       </c>
       <c r="H176" t="n">
         <v>1400</v>
@@ -5502,7 +5502,7 @@
         <v>9.27999973297119</v>
       </c>
       <c r="G177" t="n">
-        <v>8.69594669342041</v>
+        <v>8.69594764709473</v>
       </c>
       <c r="H177" t="n">
         <v>0</v>
@@ -5676,7 +5676,7 @@
         <v>9.42000007629395</v>
       </c>
       <c r="G183" t="n">
-        <v>8.82713603973389</v>
+        <v>8.8271369934082</v>
       </c>
       <c r="H183" t="n">
         <v>300</v>
@@ -5705,7 +5705,7 @@
         <v>9.42000007629395</v>
       </c>
       <c r="G184" t="n">
-        <v>8.82713603973389</v>
+        <v>8.8271369934082</v>
       </c>
       <c r="H184" t="n">
         <v>0</v>
@@ -5792,7 +5792,7 @@
         <v>9.97999954223633</v>
       </c>
       <c r="G187" t="n">
-        <v>9.35189151763916</v>
+        <v>9.35189247131348</v>
       </c>
       <c r="H187" t="n">
         <v>3900</v>
@@ -5821,7 +5821,7 @@
         <v>9.97999954223633</v>
       </c>
       <c r="G188" t="n">
-        <v>9.35189151763916</v>
+        <v>9.35189247131348</v>
       </c>
       <c r="H188" t="n">
         <v>300</v>
@@ -5995,7 +5995,7 @@
         <v>9.64000034332275</v>
       </c>
       <c r="G194" t="n">
-        <v>9.03328990936279</v>
+        <v>9.03329086303711</v>
       </c>
       <c r="H194" t="n">
         <v>100</v>
@@ -6111,7 +6111,7 @@
         <v>9.5</v>
       </c>
       <c r="G198" t="n">
-        <v>8.90210056304932</v>
+        <v>8.90210151672363</v>
       </c>
       <c r="H198" t="n">
         <v>2100</v>
@@ -6256,7 +6256,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G203" t="n">
-        <v>8.24615669250488</v>
+        <v>8.2461576461792</v>
       </c>
       <c r="H203" t="n">
         <v>2500</v>
@@ -6285,7 +6285,7 @@
         <v>9.0600004196167</v>
       </c>
       <c r="G204" t="n">
-        <v>8.48979377746582</v>
+        <v>8.48979473114014</v>
       </c>
       <c r="H204" t="n">
         <v>2200</v>
@@ -6517,7 +6517,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G212" t="n">
-        <v>8.52727603912354</v>
+        <v>8.52727699279785</v>
       </c>
       <c r="H212" t="n">
         <v>1500</v>
@@ -6546,7 +6546,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G213" t="n">
-        <v>8.52727603912354</v>
+        <v>8.52727699279785</v>
       </c>
       <c r="H213" t="n">
         <v>0</v>
@@ -6575,7 +6575,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G214" t="n">
-        <v>8.52727603912354</v>
+        <v>8.52727699279785</v>
       </c>
       <c r="H214" t="n">
         <v>0</v>
@@ -6604,7 +6604,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G215" t="n">
-        <v>8.52727603912354</v>
+        <v>8.52727699279785</v>
       </c>
       <c r="H215" t="n">
         <v>0</v>
@@ -6633,7 +6633,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G216" t="n">
-        <v>8.52727603912354</v>
+        <v>8.52727699279785</v>
       </c>
       <c r="H216" t="n">
         <v>300</v>
@@ -6662,7 +6662,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G217" t="n">
-        <v>8.52727603912354</v>
+        <v>8.52727699279785</v>
       </c>
       <c r="H217" t="n">
         <v>0</v>
@@ -6691,7 +6691,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G218" t="n">
-        <v>8.52727603912354</v>
+        <v>8.52727699279785</v>
       </c>
       <c r="H218" t="n">
         <v>0</v>
@@ -6720,7 +6720,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G219" t="n">
-        <v>8.52727603912354</v>
+        <v>8.52727699279785</v>
       </c>
       <c r="H219" t="n">
         <v>0</v>
@@ -6894,7 +6894,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G225" t="n">
-        <v>8.52727603912354</v>
+        <v>8.52727699279785</v>
       </c>
       <c r="H225" t="n">
         <v>300</v>
@@ -6923,7 +6923,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G226" t="n">
-        <v>8.52727603912354</v>
+        <v>8.52727699279785</v>
       </c>
       <c r="H226" t="n">
         <v>0</v>
@@ -6952,7 +6952,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G227" t="n">
-        <v>8.52727603912354</v>
+        <v>8.52727699279785</v>
       </c>
       <c r="H227" t="n">
         <v>900</v>
@@ -6981,7 +6981,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G228" t="n">
-        <v>8.52727603912354</v>
+        <v>8.52727699279785</v>
       </c>
       <c r="H228" t="n">
         <v>0</v>
@@ -7010,7 +7010,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G229" t="n">
-        <v>8.52727603912354</v>
+        <v>8.52727699279785</v>
       </c>
       <c r="H229" t="n">
         <v>0</v>
@@ -7039,7 +7039,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G230" t="n">
-        <v>8.52727603912354</v>
+        <v>8.52727699279785</v>
       </c>
       <c r="H230" t="n">
         <v>0</v>
@@ -7068,7 +7068,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G231" t="n">
-        <v>8.52727603912354</v>
+        <v>8.52727699279785</v>
       </c>
       <c r="H231" t="n">
         <v>0</v>
@@ -7097,7 +7097,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G232" t="n">
-        <v>8.52727603912354</v>
+        <v>8.52727699279785</v>
       </c>
       <c r="H232" t="n">
         <v>0</v>
@@ -7126,7 +7126,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G233" t="n">
-        <v>8.52727603912354</v>
+        <v>8.52727699279785</v>
       </c>
       <c r="H233" t="n">
         <v>0</v>
@@ -7184,7 +7184,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G235" t="n">
-        <v>8.24615669250488</v>
+        <v>8.2461576461792</v>
       </c>
       <c r="H235" t="n">
         <v>1000</v>
@@ -7300,7 +7300,7 @@
         <v>8.73999977111816</v>
       </c>
       <c r="G239" t="n">
-        <v>8.18993282318115</v>
+        <v>8.18993377685547</v>
       </c>
       <c r="H239" t="n">
         <v>500</v>
@@ -7329,7 +7329,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G240" t="n">
-        <v>8.05874538421631</v>
+        <v>8.05874443054199</v>
       </c>
       <c r="H240" t="n">
         <v>400</v>
@@ -7387,7 +7387,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G242" t="n">
-        <v>7.68391895294189</v>
+        <v>7.68391942977905</v>
       </c>
       <c r="H242" t="n">
         <v>10000</v>
@@ -7416,7 +7416,7 @@
         <v>8.15999984741211</v>
       </c>
       <c r="G243" t="n">
-        <v>7.64643621444702</v>
+        <v>7.64643669128418</v>
       </c>
       <c r="H243" t="n">
         <v>28200</v>
@@ -7474,7 +7474,7 @@
         <v>8.0600004196167</v>
       </c>
       <c r="G245" t="n">
-        <v>7.55273056030273</v>
+        <v>7.55273103713989</v>
       </c>
       <c r="H245" t="n">
         <v>500</v>
@@ -7503,7 +7503,7 @@
         <v>8.0600004196167</v>
       </c>
       <c r="G246" t="n">
-        <v>7.55273056030273</v>
+        <v>7.55273103713989</v>
       </c>
       <c r="H246" t="n">
         <v>2400</v>
@@ -7532,7 +7532,7 @@
         <v>8.0600004196167</v>
       </c>
       <c r="G247" t="n">
-        <v>7.55273056030273</v>
+        <v>7.55273103713989</v>
       </c>
       <c r="H247" t="n">
         <v>300</v>
@@ -7561,7 +7561,7 @@
         <v>8.0600004196167</v>
       </c>
       <c r="G248" t="n">
-        <v>7.55273056030273</v>
+        <v>7.55273103713989</v>
       </c>
       <c r="H248" t="n">
         <v>0</v>
@@ -7648,7 +7648,7 @@
         <v>8.23999977111816</v>
       </c>
       <c r="G251" t="n">
-        <v>7.72140121459961</v>
+        <v>7.72140169143677</v>
       </c>
       <c r="H251" t="n">
         <v>100</v>
@@ -7764,7 +7764,7 @@
         <v>7.61999988555908</v>
       </c>
       <c r="G255" t="n">
-        <v>7.14042186737061</v>
+        <v>7.14042234420776</v>
       </c>
       <c r="H255" t="n">
         <v>13900</v>
@@ -7851,7 +7851,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G258" t="n">
-        <v>7.12168073654175</v>
+        <v>7.12168121337891</v>
       </c>
       <c r="H258" t="n">
         <v>4500</v>
@@ -7996,7 +7996,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G263" t="n">
-        <v>7.4028000831604</v>
+        <v>7.40280055999756</v>
       </c>
       <c r="H263" t="n">
         <v>2900</v>
@@ -8083,7 +8083,7 @@
         <v>7.61999988555908</v>
       </c>
       <c r="G266" t="n">
-        <v>7.14042186737061</v>
+        <v>7.14042234420776</v>
       </c>
       <c r="H266" t="n">
         <v>600</v>
@@ -8257,7 +8257,7 @@
         <v>8.53999996185303</v>
       </c>
       <c r="G272" t="n">
-        <v>8.00252056121826</v>
+        <v>8.00252151489258</v>
       </c>
       <c r="H272" t="n">
         <v>9400</v>
@@ -8373,7 +8373,7 @@
         <v>9.11999988555908</v>
       </c>
       <c r="G276" t="n">
-        <v>8.54601669311523</v>
+        <v>8.54601764678955</v>
       </c>
       <c r="H276" t="n">
         <v>1600</v>
@@ -8460,7 +8460,7 @@
         <v>9.11999988555908</v>
       </c>
       <c r="G279" t="n">
-        <v>8.54601669311523</v>
+        <v>8.54601764678955</v>
       </c>
       <c r="H279" t="n">
         <v>2000</v>
@@ -8489,7 +8489,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G280" t="n">
-        <v>8.52727603912354</v>
+        <v>8.52727699279785</v>
       </c>
       <c r="H280" t="n">
         <v>1100</v>
@@ -8547,7 +8547,7 @@
         <v>8.92000007629395</v>
       </c>
       <c r="G282" t="n">
-        <v>8.35860538482666</v>
+        <v>8.35860443115234</v>
       </c>
       <c r="H282" t="n">
         <v>200</v>
@@ -8692,7 +8692,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G287" t="n">
-        <v>8.24615669250488</v>
+        <v>8.2461576461792</v>
       </c>
       <c r="H287" t="n">
         <v>200</v>
@@ -8750,7 +8750,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G289" t="n">
-        <v>8.52727603912354</v>
+        <v>8.52727699279785</v>
       </c>
       <c r="H289" t="n">
         <v>2100</v>
@@ -8808,7 +8808,7 @@
         <v>9.11999988555908</v>
       </c>
       <c r="G291" t="n">
-        <v>8.54601669311523</v>
+        <v>8.54601764678955</v>
       </c>
       <c r="H291" t="n">
         <v>3400</v>
@@ -8837,7 +8837,7 @@
         <v>9.11999988555908</v>
       </c>
       <c r="G292" t="n">
-        <v>8.54601669311523</v>
+        <v>8.54601764678955</v>
       </c>
       <c r="H292" t="n">
         <v>2100</v>
@@ -9040,7 +9040,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G299" t="n">
-        <v>8.52727603912354</v>
+        <v>8.52727699279785</v>
       </c>
       <c r="H299" t="n">
         <v>700</v>
@@ -9098,7 +9098,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G301" t="n">
-        <v>8.52727603912354</v>
+        <v>8.52727699279785</v>
       </c>
       <c r="H301" t="n">
         <v>300</v>
@@ -9214,7 +9214,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G305" t="n">
-        <v>8.24615669250488</v>
+        <v>8.2461576461792</v>
       </c>
       <c r="H305" t="n">
         <v>1700</v>
@@ -9243,7 +9243,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G306" t="n">
-        <v>8.24615669250488</v>
+        <v>8.2461576461792</v>
       </c>
       <c r="H306" t="n">
         <v>0</v>
@@ -9272,7 +9272,7 @@
         <v>8.64000034332275</v>
       </c>
       <c r="G307" t="n">
-        <v>8.09622669219971</v>
+        <v>8.09622764587402</v>
       </c>
       <c r="H307" t="n">
         <v>1600</v>
@@ -9301,7 +9301,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G308" t="n">
-        <v>8.05874538421631</v>
+        <v>8.05874443054199</v>
       </c>
       <c r="H308" t="n">
         <v>100</v>
@@ -9330,7 +9330,7 @@
         <v>8.53999996185303</v>
       </c>
       <c r="G309" t="n">
-        <v>8.00252056121826</v>
+        <v>8.00252151489258</v>
       </c>
       <c r="H309" t="n">
         <v>2500</v>
@@ -9359,7 +9359,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G310" t="n">
-        <v>8.24615669250488</v>
+        <v>8.2461576461792</v>
       </c>
       <c r="H310" t="n">
         <v>1000</v>
@@ -9388,7 +9388,7 @@
         <v>8.47999954223633</v>
       </c>
       <c r="G311" t="n">
-        <v>7.94629621505737</v>
+        <v>7.94629669189453</v>
       </c>
       <c r="H311" t="n">
         <v>4000</v>
@@ -9417,7 +9417,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G312" t="n">
-        <v>7.83384943008423</v>
+        <v>7.83384895324707</v>
       </c>
       <c r="H312" t="n">
         <v>1100</v>
@@ -9475,7 +9475,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G314" t="n">
-        <v>8.24615669250488</v>
+        <v>8.2461576461792</v>
       </c>
       <c r="H314" t="n">
         <v>1600</v>
@@ -9533,7 +9533,7 @@
         <v>8.47999954223633</v>
       </c>
       <c r="G316" t="n">
-        <v>7.94629621505737</v>
+        <v>7.94629669189453</v>
       </c>
       <c r="H316" t="n">
         <v>2000</v>
@@ -9591,7 +9591,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G318" t="n">
-        <v>8.24615669250488</v>
+        <v>8.2461576461792</v>
       </c>
       <c r="H318" t="n">
         <v>1600</v>
@@ -9620,7 +9620,7 @@
         <v>8.47999954223633</v>
       </c>
       <c r="G319" t="n">
-        <v>7.94629621505737</v>
+        <v>7.94629669189453</v>
       </c>
       <c r="H319" t="n">
         <v>1300</v>
@@ -9649,7 +9649,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G320" t="n">
-        <v>7.87133121490479</v>
+        <v>7.87133169174194</v>
       </c>
       <c r="H320" t="n">
         <v>1000</v>
@@ -10113,7 +10113,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G336" t="n">
-        <v>8.24615669250488</v>
+        <v>8.2461576461792</v>
       </c>
       <c r="H336" t="n">
         <v>7500</v>
@@ -10316,7 +10316,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G343" t="n">
-        <v>9.08951377868652</v>
+        <v>9.08951473236084</v>
       </c>
       <c r="H343" t="n">
         <v>10200</v>
@@ -10345,7 +10345,7 @@
         <v>9.5</v>
       </c>
       <c r="G344" t="n">
-        <v>8.90210056304932</v>
+        <v>8.90210151672363</v>
       </c>
       <c r="H344" t="n">
         <v>4500</v>
@@ -10374,7 +10374,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G345" t="n">
-        <v>9.08951377868652</v>
+        <v>9.08951473236084</v>
       </c>
       <c r="H345" t="n">
         <v>4500</v>
@@ -10432,7 +10432,7 @@
         <v>9.5</v>
       </c>
       <c r="G347" t="n">
-        <v>8.90210056304932</v>
+        <v>8.90210151672363</v>
       </c>
       <c r="H347" t="n">
         <v>5000</v>
@@ -10461,7 +10461,7 @@
         <v>9.5</v>
       </c>
       <c r="G348" t="n">
-        <v>8.90210056304932</v>
+        <v>8.90210151672363</v>
       </c>
       <c r="H348" t="n">
         <v>0</v>
@@ -10519,7 +10519,7 @@
         <v>9.5</v>
       </c>
       <c r="G350" t="n">
-        <v>8.90210056304932</v>
+        <v>8.90210151672363</v>
       </c>
       <c r="H350" t="n">
         <v>2800</v>
@@ -10548,7 +10548,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G351" t="n">
-        <v>9.08951377868652</v>
+        <v>9.08951473236084</v>
       </c>
       <c r="H351" t="n">
         <v>800</v>
@@ -10577,7 +10577,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G352" t="n">
-        <v>8.99580764770508</v>
+        <v>8.99580860137939</v>
       </c>
       <c r="H352" t="n">
         <v>1900</v>
@@ -10606,7 +10606,7 @@
         <v>9.5</v>
       </c>
       <c r="G353" t="n">
-        <v>8.90210056304932</v>
+        <v>8.90210151672363</v>
       </c>
       <c r="H353" t="n">
         <v>2900</v>
@@ -10635,7 +10635,7 @@
         <v>9.5</v>
       </c>
       <c r="G354" t="n">
-        <v>8.90210056304932</v>
+        <v>8.90210151672363</v>
       </c>
       <c r="H354" t="n">
         <v>0</v>
@@ -10664,7 +10664,7 @@
         <v>9.5</v>
       </c>
       <c r="G355" t="n">
-        <v>8.90210056304932</v>
+        <v>8.90210151672363</v>
       </c>
       <c r="H355" t="n">
         <v>1700</v>
@@ -10693,7 +10693,7 @@
         <v>9.5</v>
       </c>
       <c r="G356" t="n">
-        <v>8.90210056304932</v>
+        <v>8.90210151672363</v>
       </c>
       <c r="H356" t="n">
         <v>0</v>
@@ -10722,7 +10722,7 @@
         <v>9.5</v>
       </c>
       <c r="G357" t="n">
-        <v>8.90210056304932</v>
+        <v>8.90210151672363</v>
       </c>
       <c r="H357" t="n">
         <v>0</v>
@@ -10867,7 +10867,7 @@
         <v>9.5</v>
       </c>
       <c r="G362" t="n">
-        <v>8.90210056304932</v>
+        <v>8.90210151672363</v>
       </c>
       <c r="H362" t="n">
         <v>5500</v>
@@ -11099,7 +11099,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G370" t="n">
-        <v>9.27692604064941</v>
+        <v>9.27692699432373</v>
       </c>
       <c r="H370" t="n">
         <v>2100</v>
@@ -11244,7 +11244,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G375" t="n">
-        <v>9.30551719665527</v>
+        <v>9.30551815032959</v>
       </c>
       <c r="H375" t="n">
         <v>600</v>
@@ -11273,7 +11273,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G376" t="n">
-        <v>9.25755023956299</v>
+        <v>9.2575511932373</v>
       </c>
       <c r="H376" t="n">
         <v>2500</v>
@@ -11331,7 +11331,7 @@
         <v>10</v>
       </c>
       <c r="G378" t="n">
-        <v>9.59331703186035</v>
+        <v>9.59331798553467</v>
       </c>
       <c r="H378" t="n">
         <v>7200</v>
@@ -11708,7 +11708,7 @@
         <v>10</v>
       </c>
       <c r="G391" t="n">
-        <v>9.59331703186035</v>
+        <v>9.59331798553467</v>
       </c>
       <c r="H391" t="n">
         <v>300</v>
@@ -11853,7 +11853,7 @@
         <v>10</v>
       </c>
       <c r="G396" t="n">
-        <v>9.59331703186035</v>
+        <v>9.59331798553467</v>
       </c>
       <c r="H396" t="n">
         <v>500</v>
@@ -11882,7 +11882,7 @@
         <v>10</v>
       </c>
       <c r="G397" t="n">
-        <v>9.59331703186035</v>
+        <v>9.59331798553467</v>
       </c>
       <c r="H397" t="n">
         <v>0</v>
@@ -11940,7 +11940,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G399" t="n">
-        <v>9.30551719665527</v>
+        <v>9.30551815032959</v>
       </c>
       <c r="H399" t="n">
         <v>1600</v>
@@ -11998,7 +11998,7 @@
         <v>9.35000038146973</v>
       </c>
       <c r="G401" t="n">
-        <v>8.96975135803223</v>
+        <v>8.96975231170654</v>
       </c>
       <c r="H401" t="n">
         <v>5200</v>
@@ -12288,7 +12288,7 @@
         <v>10</v>
       </c>
       <c r="G411" t="n">
-        <v>9.59331703186035</v>
+        <v>9.59331798553467</v>
       </c>
       <c r="H411" t="n">
         <v>600</v>
@@ -12433,7 +12433,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G416" t="n">
-        <v>9.25755023956299</v>
+        <v>9.2575511932373</v>
       </c>
       <c r="H416" t="n">
         <v>700</v>
@@ -12462,7 +12462,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G417" t="n">
-        <v>9.25755023956299</v>
+        <v>9.2575511932373</v>
       </c>
       <c r="H417" t="n">
         <v>0</v>
@@ -12491,7 +12491,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G418" t="n">
-        <v>9.25755023956299</v>
+        <v>9.2575511932373</v>
       </c>
       <c r="H418" t="n">
         <v>0</v>
@@ -12520,7 +12520,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G419" t="n">
-        <v>9.30551719665527</v>
+        <v>9.30551815032959</v>
       </c>
       <c r="H419" t="n">
         <v>1700</v>
@@ -12578,7 +12578,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G421" t="n">
-        <v>9.0177173614502</v>
+        <v>9.01771831512451</v>
       </c>
       <c r="H421" t="n">
         <v>100</v>
@@ -12636,7 +12636,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G423" t="n">
-        <v>9.25755023956299</v>
+        <v>9.2575511932373</v>
       </c>
       <c r="H423" t="n">
         <v>1100</v>
@@ -12665,7 +12665,7 @@
         <v>9.35000038146973</v>
       </c>
       <c r="G424" t="n">
-        <v>8.96975135803223</v>
+        <v>8.96975231170654</v>
       </c>
       <c r="H424" t="n">
         <v>500</v>
@@ -12694,7 +12694,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G425" t="n">
-        <v>8.53805255889893</v>
+        <v>8.53805160522461</v>
       </c>
       <c r="H425" t="n">
         <v>1300</v>
@@ -12810,7 +12810,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G429" t="n">
-        <v>9.25755023956299</v>
+        <v>9.2575511932373</v>
       </c>
       <c r="H429" t="n">
         <v>700</v>
@@ -12839,7 +12839,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G430" t="n">
-        <v>9.25755023956299</v>
+        <v>9.2575511932373</v>
       </c>
       <c r="H430" t="n">
         <v>0</v>
@@ -12897,7 +12897,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G432" t="n">
-        <v>9.0177173614502</v>
+        <v>9.01771831512451</v>
       </c>
       <c r="H432" t="n">
         <v>100</v>
@@ -12926,7 +12926,7 @@
         <v>9.35000038146973</v>
       </c>
       <c r="G433" t="n">
-        <v>8.96975135803223</v>
+        <v>8.96975231170654</v>
       </c>
       <c r="H433" t="n">
         <v>1200</v>
@@ -12984,7 +12984,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G435" t="n">
-        <v>9.30551719665527</v>
+        <v>9.30551815032959</v>
       </c>
       <c r="H435" t="n">
         <v>200</v>
@@ -13013,7 +13013,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G436" t="n">
-        <v>9.25755023956299</v>
+        <v>9.2575511932373</v>
       </c>
       <c r="H436" t="n">
         <v>400</v>
@@ -13071,7 +13071,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G438" t="n">
-        <v>9.0177173614502</v>
+        <v>9.01771831512451</v>
       </c>
       <c r="H438" t="n">
         <v>600</v>
@@ -13100,7 +13100,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G439" t="n">
-        <v>9.30551719665527</v>
+        <v>9.30551815032959</v>
       </c>
       <c r="H439" t="n">
         <v>200</v>
@@ -13129,7 +13129,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G440" t="n">
-        <v>9.30551719665527</v>
+        <v>9.30551815032959</v>
       </c>
       <c r="H440" t="n">
         <v>500</v>
@@ -13158,7 +13158,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G441" t="n">
-        <v>9.30551719665527</v>
+        <v>9.30551815032959</v>
       </c>
       <c r="H441" t="n">
         <v>600</v>
@@ -13187,7 +13187,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G442" t="n">
-        <v>9.30551719665527</v>
+        <v>9.30551815032959</v>
       </c>
       <c r="H442" t="n">
         <v>800</v>
@@ -13274,7 +13274,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G445" t="n">
-        <v>9.0177173614502</v>
+        <v>9.01771831512451</v>
       </c>
       <c r="H445" t="n">
         <v>4900</v>
@@ -13303,7 +13303,7 @@
         <v>9.44999980926514</v>
       </c>
       <c r="G446" t="n">
-        <v>9.06568431854248</v>
+        <v>9.0656852722168</v>
       </c>
       <c r="H446" t="n">
         <v>4900</v>
@@ -13332,7 +13332,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G447" t="n">
-        <v>9.0177173614502</v>
+        <v>9.01771831512451</v>
       </c>
       <c r="H447" t="n">
         <v>2000</v>
@@ -13361,7 +13361,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G448" t="n">
-        <v>8.825852394104</v>
+        <v>8.82585144042969</v>
       </c>
       <c r="H448" t="n">
         <v>1200</v>
@@ -13535,7 +13535,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G454" t="n">
-        <v>8.825852394104</v>
+        <v>8.82585144042969</v>
       </c>
       <c r="H454" t="n">
         <v>100</v>
@@ -13564,7 +13564,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G455" t="n">
-        <v>8.825852394104</v>
+        <v>8.82585144042969</v>
       </c>
       <c r="H455" t="n">
         <v>0</v>
@@ -13593,7 +13593,7 @@
         <v>9.35000038146973</v>
       </c>
       <c r="G456" t="n">
-        <v>8.96975135803223</v>
+        <v>8.96975231170654</v>
       </c>
       <c r="H456" t="n">
         <v>9000</v>
@@ -13796,7 +13796,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G463" t="n">
-        <v>8.53805255889893</v>
+        <v>8.53805160522461</v>
       </c>
       <c r="H463" t="n">
         <v>800</v>
@@ -14057,7 +14057,7 @@
         <v>7.75</v>
       </c>
       <c r="G472" t="n">
-        <v>7.43482065200806</v>
+        <v>7.43482112884521</v>
       </c>
       <c r="H472" t="n">
         <v>5500</v>
@@ -14289,7 +14289,7 @@
         <v>7.5</v>
       </c>
       <c r="G480" t="n">
-        <v>7.19498825073242</v>
+        <v>7.19498777389526</v>
       </c>
       <c r="H480" t="n">
         <v>1800</v>
@@ -14318,7 +14318,7 @@
         <v>7.34999990463257</v>
       </c>
       <c r="G481" t="n">
-        <v>7.05108833312988</v>
+        <v>7.05108785629272</v>
       </c>
       <c r="H481" t="n">
         <v>4200</v>
@@ -14347,7 +14347,7 @@
         <v>7.34999990463257</v>
       </c>
       <c r="G482" t="n">
-        <v>7.05108833312988</v>
+        <v>7.05108785629272</v>
       </c>
       <c r="H482" t="n">
         <v>7800</v>
@@ -14434,7 +14434,7 @@
         <v>7</v>
       </c>
       <c r="G485" t="n">
-        <v>6.71532249450684</v>
+        <v>6.71532201766968</v>
       </c>
       <c r="H485" t="n">
         <v>10100</v>
@@ -14724,7 +14724,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G495" t="n">
-        <v>6.04378986358643</v>
+        <v>6.04379034042358</v>
       </c>
       <c r="H495" t="n">
         <v>7900</v>
@@ -15014,7 +15014,7 @@
         <v>7</v>
       </c>
       <c r="G505" t="n">
-        <v>6.71532249450684</v>
+        <v>6.71532201766968</v>
       </c>
       <c r="H505" t="n">
         <v>13500</v>
@@ -15072,7 +15072,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G507" t="n">
-        <v>6.81125545501709</v>
+        <v>6.81125497817993</v>
       </c>
       <c r="H507" t="n">
         <v>3900</v>
@@ -15159,7 +15159,7 @@
         <v>7.75</v>
       </c>
       <c r="G510" t="n">
-        <v>7.43482065200806</v>
+        <v>7.43482112884521</v>
       </c>
       <c r="H510" t="n">
         <v>3700</v>
@@ -15681,7 +15681,7 @@
         <v>7.34999990463257</v>
       </c>
       <c r="G528" t="n">
-        <v>7.05108833312988</v>
+        <v>7.05108785629272</v>
       </c>
       <c r="H528" t="n">
         <v>4000</v>
@@ -15884,7 +15884,7 @@
         <v>7.5</v>
       </c>
       <c r="G535" t="n">
-        <v>7.19498825073242</v>
+        <v>7.19498777389526</v>
       </c>
       <c r="H535" t="n">
         <v>200</v>
@@ -16029,7 +16029,7 @@
         <v>7</v>
       </c>
       <c r="G540" t="n">
-        <v>6.71532249450684</v>
+        <v>6.71532201766968</v>
       </c>
       <c r="H540" t="n">
         <v>7000</v>
@@ -16203,7 +16203,7 @@
         <v>6.94999980926514</v>
       </c>
       <c r="G546" t="n">
-        <v>6.66735553741455</v>
+        <v>6.66735506057739</v>
       </c>
       <c r="H546" t="n">
         <v>2700</v>
@@ -16290,7 +16290,7 @@
         <v>7</v>
       </c>
       <c r="G549" t="n">
-        <v>6.71532249450684</v>
+        <v>6.71532201766968</v>
       </c>
       <c r="H549" t="n">
         <v>9500</v>
@@ -16319,7 +16319,7 @@
         <v>6.94999980926514</v>
       </c>
       <c r="G550" t="n">
-        <v>6.66735553741455</v>
+        <v>6.66735506057739</v>
       </c>
       <c r="H550" t="n">
         <v>16600</v>
@@ -16580,7 +16580,7 @@
         <v>7.75</v>
       </c>
       <c r="G559" t="n">
-        <v>7.43482065200806</v>
+        <v>7.43482112884521</v>
       </c>
       <c r="H559" t="n">
         <v>4000</v>
@@ -16725,7 +16725,7 @@
         <v>7.75</v>
       </c>
       <c r="G564" t="n">
-        <v>7.43482065200806</v>
+        <v>7.43482112884521</v>
       </c>
       <c r="H564" t="n">
         <v>700</v>
@@ -16841,7 +16841,7 @@
         <v>7.75</v>
       </c>
       <c r="G568" t="n">
-        <v>7.43482065200806</v>
+        <v>7.43482112884521</v>
       </c>
       <c r="H568" t="n">
         <v>6900</v>
@@ -17015,7 +17015,7 @@
         <v>8.14999961853027</v>
       </c>
       <c r="G574" t="n">
-        <v>7.81855297088623</v>
+        <v>7.81855344772339</v>
       </c>
       <c r="H574" t="n">
         <v>5200</v>
@@ -17160,7 +17160,7 @@
         <v>7.5</v>
       </c>
       <c r="G579" t="n">
-        <v>7.19498825073242</v>
+        <v>7.19498777389526</v>
       </c>
       <c r="H579" t="n">
         <v>3100</v>
@@ -17247,7 +17247,7 @@
         <v>8.25</v>
       </c>
       <c r="G582" t="n">
-        <v>7.91448640823364</v>
+        <v>7.91448736190796</v>
       </c>
       <c r="H582" t="n">
         <v>10200</v>
@@ -17276,7 +17276,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G583" t="n">
-        <v>7.86651945114136</v>
+        <v>7.86652040481567</v>
       </c>
       <c r="H583" t="n">
         <v>20900</v>
@@ -17334,7 +17334,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G585" t="n">
-        <v>7.86651945114136</v>
+        <v>7.86652040481567</v>
       </c>
       <c r="H585" t="n">
         <v>5700</v>
@@ -17363,7 +17363,7 @@
         <v>7.75</v>
       </c>
       <c r="G586" t="n">
-        <v>7.43482065200806</v>
+        <v>7.43482112884521</v>
       </c>
       <c r="H586" t="n">
         <v>8000</v>
@@ -17392,7 +17392,7 @@
         <v>7.75</v>
       </c>
       <c r="G587" t="n">
-        <v>7.43482065200806</v>
+        <v>7.43482112884521</v>
       </c>
       <c r="H587" t="n">
         <v>1500</v>
@@ -17421,7 +17421,7 @@
         <v>7.75</v>
       </c>
       <c r="G588" t="n">
-        <v>7.43482065200806</v>
+        <v>7.43482112884521</v>
       </c>
       <c r="H588" t="n">
         <v>100</v>
@@ -17479,7 +17479,7 @@
         <v>7.75</v>
       </c>
       <c r="G590" t="n">
-        <v>7.43482065200806</v>
+        <v>7.43482112884521</v>
       </c>
       <c r="H590" t="n">
         <v>2300</v>
@@ -17653,7 +17653,7 @@
         <v>6.94999980926514</v>
       </c>
       <c r="G596" t="n">
-        <v>6.66735553741455</v>
+        <v>6.66735506057739</v>
       </c>
       <c r="H596" t="n">
         <v>1100</v>
@@ -17682,7 +17682,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G597" t="n">
-        <v>6.90718793869019</v>
+        <v>6.90718841552734</v>
       </c>
       <c r="H597" t="n">
         <v>1200</v>
@@ -17711,7 +17711,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G598" t="n">
-        <v>6.90718793869019</v>
+        <v>6.90718841552734</v>
       </c>
       <c r="H598" t="n">
         <v>0</v>
@@ -17798,7 +17798,7 @@
         <v>7.34999990463257</v>
       </c>
       <c r="G601" t="n">
-        <v>7.05108833312988</v>
+        <v>7.05108785629272</v>
       </c>
       <c r="H601" t="n">
         <v>2100</v>
@@ -17827,7 +17827,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G602" t="n">
-        <v>6.90718793869019</v>
+        <v>6.90718841552734</v>
       </c>
       <c r="H602" t="n">
         <v>1600</v>
@@ -17885,7 +17885,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G604" t="n">
-        <v>6.81125545501709</v>
+        <v>6.81125497817993</v>
       </c>
       <c r="H604" t="n">
         <v>15300</v>
@@ -28969,6 +28969,35 @@
         <v>200</v>
       </c>
       <c r="I986" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="987">
+      <c r="A987" t="s">
+        <v>9</v>
+      </c>
+      <c r="B987" s="1" t="n">
+        <v>46321.3333333333</v>
+      </c>
+      <c r="C987" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="D987" t="n">
+        <v>10.6000003814697</v>
+      </c>
+      <c r="E987" t="n">
+        <v>10.1999998092651</v>
+      </c>
+      <c r="F987" t="n">
+        <v>10.6000003814697</v>
+      </c>
+      <c r="G987" t="n">
+        <v>10.6000003814697</v>
+      </c>
+      <c r="H987" t="n">
+        <v>2300</v>
+      </c>
+      <c r="I987" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/RDUE.MI.xlsx
+++ b/data/RDUE.MI.xlsx
@@ -456,7 +456,7 @@
         <v>12.0500001907349</v>
       </c>
       <c r="G3" t="n">
-        <v>11.2916135787964</v>
+        <v>11.2916126251221</v>
       </c>
       <c r="H3" t="n">
         <v>19500</v>
@@ -543,7 +543,7 @@
         <v>12.0539999008179</v>
       </c>
       <c r="G6" t="n">
-        <v>11.2953605651855</v>
+        <v>11.2953615188599</v>
       </c>
       <c r="H6" t="n">
         <v>9400</v>
@@ -630,7 +630,7 @@
         <v>11.8599996566772</v>
       </c>
       <c r="G9" t="n">
-        <v>11.1135702133179</v>
+        <v>11.1135711669922</v>
       </c>
       <c r="H9" t="n">
         <v>5700</v>
@@ -746,7 +746,7 @@
         <v>11.8800001144409</v>
       </c>
       <c r="G13" t="n">
-        <v>11.1323118209839</v>
+        <v>11.1323127746582</v>
       </c>
       <c r="H13" t="n">
         <v>5200</v>
@@ -833,7 +833,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G16" t="n">
-        <v>11.0573463439941</v>
+        <v>11.0573472976685</v>
       </c>
       <c r="H16" t="n">
         <v>200</v>
@@ -862,7 +862,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G17" t="n">
-        <v>11.0573463439941</v>
+        <v>11.0573472976685</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
@@ -978,7 +978,7 @@
         <v>11.3800001144409</v>
       </c>
       <c r="G21" t="n">
-        <v>10.6637802124023</v>
+        <v>10.6637811660767</v>
       </c>
       <c r="H21" t="n">
         <v>3200</v>
@@ -1065,7 +1065,7 @@
         <v>11.2600002288818</v>
       </c>
       <c r="G24" t="n">
-        <v>10.5513324737549</v>
+        <v>10.5513334274292</v>
       </c>
       <c r="H24" t="n">
         <v>200</v>
@@ -1094,7 +1094,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G25" t="n">
-        <v>10.5888147354126</v>
+        <v>10.5888156890869</v>
       </c>
       <c r="H25" t="n">
         <v>600</v>
@@ -1210,7 +1210,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G29" t="n">
-        <v>11.3384656906128</v>
+        <v>11.3384666442871</v>
       </c>
       <c r="H29" t="n">
         <v>12200</v>
@@ -1239,7 +1239,7 @@
         <v>11.8800001144409</v>
       </c>
       <c r="G30" t="n">
-        <v>11.1323118209839</v>
+        <v>11.1323127746582</v>
       </c>
       <c r="H30" t="n">
         <v>3900</v>
@@ -1355,7 +1355,7 @@
         <v>11.75</v>
       </c>
       <c r="G34" t="n">
-        <v>11.0104942321777</v>
+        <v>11.0104932785034</v>
       </c>
       <c r="H34" t="n">
         <v>3400</v>
@@ -1384,7 +1384,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G35" t="n">
-        <v>11.0573463439941</v>
+        <v>11.0573472976685</v>
       </c>
       <c r="H35" t="n">
         <v>2200</v>
@@ -1413,7 +1413,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G36" t="n">
-        <v>11.0573463439941</v>
+        <v>11.0573472976685</v>
       </c>
       <c r="H36" t="n">
         <v>0</v>
@@ -1442,7 +1442,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G37" t="n">
-        <v>11.0573463439941</v>
+        <v>11.0573472976685</v>
       </c>
       <c r="H37" t="n">
         <v>3200</v>
@@ -1616,7 +1616,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G43" t="n">
-        <v>11.0573463439941</v>
+        <v>11.0573472976685</v>
       </c>
       <c r="H43" t="n">
         <v>4800</v>
@@ -1761,7 +1761,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G48" t="n">
-        <v>11.0573463439941</v>
+        <v>11.0573472976685</v>
       </c>
       <c r="H48" t="n">
         <v>1200</v>
@@ -1877,7 +1877,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G52" t="n">
-        <v>11.0573463439941</v>
+        <v>11.0573472976685</v>
       </c>
       <c r="H52" t="n">
         <v>100</v>
@@ -1935,7 +1935,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G54" t="n">
-        <v>11.0573463439941</v>
+        <v>11.0573472976685</v>
       </c>
       <c r="H54" t="n">
         <v>700</v>
@@ -1964,7 +1964,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G55" t="n">
-        <v>11.0573463439941</v>
+        <v>11.0573472976685</v>
       </c>
       <c r="H55" t="n">
         <v>100</v>
@@ -1993,7 +1993,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G56" t="n">
-        <v>11.0573463439941</v>
+        <v>11.0573472976685</v>
       </c>
       <c r="H56" t="n">
         <v>0</v>
@@ -2022,7 +2022,7 @@
         <v>11.75</v>
       </c>
       <c r="G57" t="n">
-        <v>11.0104942321777</v>
+        <v>11.0104932785034</v>
       </c>
       <c r="H57" t="n">
         <v>200</v>
@@ -2051,7 +2051,7 @@
         <v>11.75</v>
       </c>
       <c r="G58" t="n">
-        <v>11.0104942321777</v>
+        <v>11.0104932785034</v>
       </c>
       <c r="H58" t="n">
         <v>500</v>
@@ -2080,7 +2080,7 @@
         <v>11.75</v>
       </c>
       <c r="G59" t="n">
-        <v>11.0104942321777</v>
+        <v>11.0104932785034</v>
       </c>
       <c r="H59" t="n">
         <v>0</v>
@@ -2109,7 +2109,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G60" t="n">
-        <v>10.8699340820312</v>
+        <v>10.8699350357056</v>
       </c>
       <c r="H60" t="n">
         <v>6000</v>
@@ -2428,7 +2428,7 @@
         <v>11.5</v>
       </c>
       <c r="G71" t="n">
-        <v>10.7762269973755</v>
+        <v>10.7762279510498</v>
       </c>
       <c r="H71" t="n">
         <v>500</v>
@@ -2486,7 +2486,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G73" t="n">
-        <v>10.8699340820312</v>
+        <v>10.8699350357056</v>
       </c>
       <c r="H73" t="n">
         <v>10000</v>
@@ -2515,7 +2515,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G74" t="n">
-        <v>10.8699340820312</v>
+        <v>10.8699350357056</v>
       </c>
       <c r="H74" t="n">
         <v>4200</v>
@@ -2544,7 +2544,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G75" t="n">
-        <v>10.8699340820312</v>
+        <v>10.8699350357056</v>
       </c>
       <c r="H75" t="n">
         <v>1100</v>
@@ -2573,7 +2573,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G76" t="n">
-        <v>10.8699340820312</v>
+        <v>10.8699350357056</v>
       </c>
       <c r="H76" t="n">
         <v>3300</v>
@@ -2631,7 +2631,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G78" t="n">
-        <v>11.0573463439941</v>
+        <v>11.0573472976685</v>
       </c>
       <c r="H78" t="n">
         <v>2600</v>
@@ -2660,7 +2660,7 @@
         <v>11.5</v>
       </c>
       <c r="G79" t="n">
-        <v>10.7762269973755</v>
+        <v>10.7762279510498</v>
       </c>
       <c r="H79" t="n">
         <v>2100</v>
@@ -2776,7 +2776,7 @@
         <v>10.0500001907349</v>
       </c>
       <c r="G83" t="n">
-        <v>9.4174861907959</v>
+        <v>9.41748714447021</v>
       </c>
       <c r="H83" t="n">
         <v>13500</v>
@@ -2805,7 +2805,7 @@
         <v>10.0500001907349</v>
       </c>
       <c r="G84" t="n">
-        <v>9.4174861907959</v>
+        <v>9.41748714447021</v>
       </c>
       <c r="H84" t="n">
         <v>16000</v>
@@ -3008,7 +3008,7 @@
         <v>10.0500001907349</v>
       </c>
       <c r="G91" t="n">
-        <v>9.4174861907959</v>
+        <v>9.41748714447021</v>
       </c>
       <c r="H91" t="n">
         <v>1800</v>
@@ -3037,7 +3037,7 @@
         <v>9.92000007629395</v>
       </c>
       <c r="G92" t="n">
-        <v>9.29566860198975</v>
+        <v>9.29566764831543</v>
       </c>
       <c r="H92" t="n">
         <v>5200</v>
@@ -3066,7 +3066,7 @@
         <v>9.72000026702881</v>
       </c>
       <c r="G93" t="n">
-        <v>9.10825634002686</v>
+        <v>9.10825538635254</v>
       </c>
       <c r="H93" t="n">
         <v>3500</v>
@@ -3095,7 +3095,7 @@
         <v>9.73999977111816</v>
       </c>
       <c r="G94" t="n">
-        <v>9.12699699401855</v>
+        <v>9.12699604034424</v>
       </c>
       <c r="H94" t="n">
         <v>2000</v>
@@ -3124,7 +3124,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G95" t="n">
-        <v>9.08951473236084</v>
+        <v>9.08951377868652</v>
       </c>
       <c r="H95" t="n">
         <v>800</v>
@@ -3153,7 +3153,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G96" t="n">
-        <v>9.08951473236084</v>
+        <v>9.08951377868652</v>
       </c>
       <c r="H96" t="n">
         <v>0</v>
@@ -3182,7 +3182,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G97" t="n">
-        <v>9.08951473236084</v>
+        <v>9.08951377868652</v>
       </c>
       <c r="H97" t="n">
         <v>0</v>
@@ -3211,7 +3211,7 @@
         <v>9.53999996185303</v>
       </c>
       <c r="G98" t="n">
-        <v>8.93958377838135</v>
+        <v>8.93958282470703</v>
       </c>
       <c r="H98" t="n">
         <v>900</v>
@@ -3240,7 +3240,7 @@
         <v>9.34000015258789</v>
       </c>
       <c r="G99" t="n">
-        <v>8.75217151641846</v>
+        <v>8.75217056274414</v>
       </c>
       <c r="H99" t="n">
         <v>600</v>
@@ -3269,7 +3269,7 @@
         <v>9.14000034332275</v>
       </c>
       <c r="G100" t="n">
-        <v>8.56475925445557</v>
+        <v>8.56475830078125</v>
       </c>
       <c r="H100" t="n">
         <v>800</v>
@@ -3414,7 +3414,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G105" t="n">
-        <v>8.52727699279785</v>
+        <v>8.52727603912354</v>
       </c>
       <c r="H105" t="n">
         <v>1300</v>
@@ -3530,7 +3530,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G109" t="n">
-        <v>8.80839538574219</v>
+        <v>8.80839443206787</v>
       </c>
       <c r="H109" t="n">
         <v>300</v>
@@ -3559,7 +3559,7 @@
         <v>9.4399995803833</v>
       </c>
       <c r="G110" t="n">
-        <v>8.8458776473999</v>
+        <v>8.84587669372559</v>
       </c>
       <c r="H110" t="n">
         <v>200</v>
@@ -3588,7 +3588,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G111" t="n">
-        <v>9.08951473236084</v>
+        <v>9.08951377868652</v>
       </c>
       <c r="H111" t="n">
         <v>500</v>
@@ -3704,7 +3704,7 @@
         <v>10</v>
       </c>
       <c r="G115" t="n">
-        <v>9.37063407897949</v>
+        <v>9.37063312530518</v>
       </c>
       <c r="H115" t="n">
         <v>200</v>
@@ -3820,7 +3820,7 @@
         <v>10.5</v>
       </c>
       <c r="G119" t="n">
-        <v>9.83916568756104</v>
+        <v>9.83916473388672</v>
       </c>
       <c r="H119" t="n">
         <v>800</v>
@@ -4110,7 +4110,7 @@
         <v>9.84000015258789</v>
       </c>
       <c r="G129" t="n">
-        <v>9.220703125</v>
+        <v>9.22070217132568</v>
       </c>
       <c r="H129" t="n">
         <v>200</v>
@@ -4139,7 +4139,7 @@
         <v>9.92000007629395</v>
       </c>
       <c r="G130" t="n">
-        <v>9.29566860198975</v>
+        <v>9.29566764831543</v>
       </c>
       <c r="H130" t="n">
         <v>200</v>
@@ -4168,7 +4168,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G131" t="n">
-        <v>9.65175342559814</v>
+        <v>9.65175247192383</v>
       </c>
       <c r="H131" t="n">
         <v>2700</v>
@@ -4197,7 +4197,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G132" t="n">
-        <v>9.65175342559814</v>
+        <v>9.65175247192383</v>
       </c>
       <c r="H132" t="n">
         <v>100</v>
@@ -4313,7 +4313,7 @@
         <v>10.5</v>
       </c>
       <c r="G136" t="n">
-        <v>9.83916568756104</v>
+        <v>9.83916473388672</v>
       </c>
       <c r="H136" t="n">
         <v>700</v>
@@ -4400,7 +4400,7 @@
         <v>10.5</v>
       </c>
       <c r="G139" t="n">
-        <v>9.83916568756104</v>
+        <v>9.83916473388672</v>
       </c>
       <c r="H139" t="n">
         <v>300</v>
@@ -4429,7 +4429,7 @@
         <v>10.5</v>
       </c>
       <c r="G140" t="n">
-        <v>9.83916568756104</v>
+        <v>9.83916473388672</v>
       </c>
       <c r="H140" t="n">
         <v>100</v>
@@ -4458,7 +4458,7 @@
         <v>10.5</v>
       </c>
       <c r="G141" t="n">
-        <v>9.83916568756104</v>
+        <v>9.83916473388672</v>
       </c>
       <c r="H141" t="n">
         <v>0</v>
@@ -4487,7 +4487,7 @@
         <v>10</v>
       </c>
       <c r="G142" t="n">
-        <v>9.37063407897949</v>
+        <v>9.37063312530518</v>
       </c>
       <c r="H142" t="n">
         <v>7600</v>
@@ -4661,7 +4661,7 @@
         <v>9.31999969482422</v>
       </c>
       <c r="G148" t="n">
-        <v>8.73342990875244</v>
+        <v>8.73342895507812</v>
       </c>
       <c r="H148" t="n">
         <v>1000</v>
@@ -4748,7 +4748,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G151" t="n">
-        <v>9.08951473236084</v>
+        <v>9.08951377868652</v>
       </c>
       <c r="H151" t="n">
         <v>500</v>
@@ -4777,7 +4777,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G152" t="n">
-        <v>9.08951473236084</v>
+        <v>9.08951377868652</v>
       </c>
       <c r="H152" t="n">
         <v>0</v>
@@ -4806,7 +4806,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G153" t="n">
-        <v>9.08951473236084</v>
+        <v>9.08951377868652</v>
       </c>
       <c r="H153" t="n">
         <v>0</v>
@@ -4864,7 +4864,7 @@
         <v>10</v>
       </c>
       <c r="G155" t="n">
-        <v>9.37063407897949</v>
+        <v>9.37063312530518</v>
       </c>
       <c r="H155" t="n">
         <v>100</v>
@@ -4893,7 +4893,7 @@
         <v>10</v>
       </c>
       <c r="G156" t="n">
-        <v>9.37063407897949</v>
+        <v>9.37063312530518</v>
       </c>
       <c r="H156" t="n">
         <v>0</v>
@@ -4922,7 +4922,7 @@
         <v>10</v>
       </c>
       <c r="G157" t="n">
-        <v>9.37063407897949</v>
+        <v>9.37063312530518</v>
       </c>
       <c r="H157" t="n">
         <v>0</v>
@@ -4951,7 +4951,7 @@
         <v>10</v>
       </c>
       <c r="G158" t="n">
-        <v>9.37063407897949</v>
+        <v>9.37063312530518</v>
       </c>
       <c r="H158" t="n">
         <v>0</v>
@@ -4980,7 +4980,7 @@
         <v>10</v>
       </c>
       <c r="G159" t="n">
-        <v>9.37063407897949</v>
+        <v>9.37063312530518</v>
       </c>
       <c r="H159" t="n">
         <v>0</v>
@@ -5009,7 +5009,7 @@
         <v>10</v>
       </c>
       <c r="G160" t="n">
-        <v>9.37063407897949</v>
+        <v>9.37063312530518</v>
       </c>
       <c r="H160" t="n">
         <v>0</v>
@@ -5038,7 +5038,7 @@
         <v>10</v>
       </c>
       <c r="G161" t="n">
-        <v>9.37063407897949</v>
+        <v>9.37063312530518</v>
       </c>
       <c r="H161" t="n">
         <v>0</v>
@@ -5067,7 +5067,7 @@
         <v>10</v>
       </c>
       <c r="G162" t="n">
-        <v>9.37063407897949</v>
+        <v>9.37063312530518</v>
       </c>
       <c r="H162" t="n">
         <v>100</v>
@@ -5212,7 +5212,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G167" t="n">
-        <v>9.08951473236084</v>
+        <v>9.08951377868652</v>
       </c>
       <c r="H167" t="n">
         <v>1600</v>
@@ -5241,7 +5241,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G168" t="n">
-        <v>9.08951473236084</v>
+        <v>9.08951377868652</v>
       </c>
       <c r="H168" t="n">
         <v>5000</v>
@@ -5328,7 +5328,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G171" t="n">
-        <v>8.80839538574219</v>
+        <v>8.80839443206787</v>
       </c>
       <c r="H171" t="n">
         <v>900</v>
@@ -5444,7 +5444,7 @@
         <v>9.42000007629395</v>
       </c>
       <c r="G175" t="n">
-        <v>8.8271369934082</v>
+        <v>8.82713603973389</v>
       </c>
       <c r="H175" t="n">
         <v>800</v>
@@ -5676,7 +5676,7 @@
         <v>9.42000007629395</v>
       </c>
       <c r="G183" t="n">
-        <v>8.8271369934082</v>
+        <v>8.82713603973389</v>
       </c>
       <c r="H183" t="n">
         <v>300</v>
@@ -5705,7 +5705,7 @@
         <v>9.42000007629395</v>
       </c>
       <c r="G184" t="n">
-        <v>8.8271369934082</v>
+        <v>8.82713603973389</v>
       </c>
       <c r="H184" t="n">
         <v>0</v>
@@ -5734,7 +5734,7 @@
         <v>9.72000026702881</v>
       </c>
       <c r="G185" t="n">
-        <v>9.10825634002686</v>
+        <v>9.10825538635254</v>
       </c>
       <c r="H185" t="n">
         <v>1300</v>
@@ -5763,7 +5763,7 @@
         <v>9.84000015258789</v>
       </c>
       <c r="G186" t="n">
-        <v>9.220703125</v>
+        <v>9.22070217132568</v>
       </c>
       <c r="H186" t="n">
         <v>400</v>
@@ -5850,7 +5850,7 @@
         <v>9.61999988555908</v>
       </c>
       <c r="G189" t="n">
-        <v>9.01454925537109</v>
+        <v>9.01454830169678</v>
       </c>
       <c r="H189" t="n">
         <v>1400</v>
@@ -5995,7 +5995,7 @@
         <v>9.64000034332275</v>
       </c>
       <c r="G194" t="n">
-        <v>9.03329086303711</v>
+        <v>9.03328990936279</v>
       </c>
       <c r="H194" t="n">
         <v>100</v>
@@ -6024,7 +6024,7 @@
         <v>9.53999996185303</v>
       </c>
       <c r="G195" t="n">
-        <v>8.93958377838135</v>
+        <v>8.93958282470703</v>
       </c>
       <c r="H195" t="n">
         <v>600</v>
@@ -6053,7 +6053,7 @@
         <v>9.53999996185303</v>
       </c>
       <c r="G196" t="n">
-        <v>8.93958377838135</v>
+        <v>8.93958282470703</v>
       </c>
       <c r="H196" t="n">
         <v>0</v>
@@ -6082,7 +6082,7 @@
         <v>9.53999996185303</v>
       </c>
       <c r="G197" t="n">
-        <v>8.93958377838135</v>
+        <v>8.93958282470703</v>
       </c>
       <c r="H197" t="n">
         <v>0</v>
@@ -6517,7 +6517,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G212" t="n">
-        <v>8.52727699279785</v>
+        <v>8.52727603912354</v>
       </c>
       <c r="H212" t="n">
         <v>1500</v>
@@ -6546,7 +6546,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G213" t="n">
-        <v>8.52727699279785</v>
+        <v>8.52727603912354</v>
       </c>
       <c r="H213" t="n">
         <v>0</v>
@@ -6575,7 +6575,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G214" t="n">
-        <v>8.52727699279785</v>
+        <v>8.52727603912354</v>
       </c>
       <c r="H214" t="n">
         <v>0</v>
@@ -6604,7 +6604,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G215" t="n">
-        <v>8.52727699279785</v>
+        <v>8.52727603912354</v>
       </c>
       <c r="H215" t="n">
         <v>0</v>
@@ -6633,7 +6633,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G216" t="n">
-        <v>8.52727699279785</v>
+        <v>8.52727603912354</v>
       </c>
       <c r="H216" t="n">
         <v>300</v>
@@ -6662,7 +6662,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G217" t="n">
-        <v>8.52727699279785</v>
+        <v>8.52727603912354</v>
       </c>
       <c r="H217" t="n">
         <v>0</v>
@@ -6691,7 +6691,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G218" t="n">
-        <v>8.52727699279785</v>
+        <v>8.52727603912354</v>
       </c>
       <c r="H218" t="n">
         <v>0</v>
@@ -6720,7 +6720,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G219" t="n">
-        <v>8.52727699279785</v>
+        <v>8.52727603912354</v>
       </c>
       <c r="H219" t="n">
         <v>0</v>
@@ -6894,7 +6894,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G225" t="n">
-        <v>8.52727699279785</v>
+        <v>8.52727603912354</v>
       </c>
       <c r="H225" t="n">
         <v>300</v>
@@ -6923,7 +6923,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G226" t="n">
-        <v>8.52727699279785</v>
+        <v>8.52727603912354</v>
       </c>
       <c r="H226" t="n">
         <v>0</v>
@@ -6952,7 +6952,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G227" t="n">
-        <v>8.52727699279785</v>
+        <v>8.52727603912354</v>
       </c>
       <c r="H227" t="n">
         <v>900</v>
@@ -6981,7 +6981,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G228" t="n">
-        <v>8.52727699279785</v>
+        <v>8.52727603912354</v>
       </c>
       <c r="H228" t="n">
         <v>0</v>
@@ -7010,7 +7010,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G229" t="n">
-        <v>8.52727699279785</v>
+        <v>8.52727603912354</v>
       </c>
       <c r="H229" t="n">
         <v>0</v>
@@ -7039,7 +7039,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G230" t="n">
-        <v>8.52727699279785</v>
+        <v>8.52727603912354</v>
       </c>
       <c r="H230" t="n">
         <v>0</v>
@@ -7068,7 +7068,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G231" t="n">
-        <v>8.52727699279785</v>
+        <v>8.52727603912354</v>
       </c>
       <c r="H231" t="n">
         <v>0</v>
@@ -7097,7 +7097,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G232" t="n">
-        <v>8.52727699279785</v>
+        <v>8.52727603912354</v>
       </c>
       <c r="H232" t="n">
         <v>0</v>
@@ -7126,7 +7126,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G233" t="n">
-        <v>8.52727699279785</v>
+        <v>8.52727603912354</v>
       </c>
       <c r="H233" t="n">
         <v>0</v>
@@ -7300,7 +7300,7 @@
         <v>8.73999977111816</v>
       </c>
       <c r="G239" t="n">
-        <v>8.18993377685547</v>
+        <v>8.18993282318115</v>
       </c>
       <c r="H239" t="n">
         <v>500</v>
@@ -7387,7 +7387,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G242" t="n">
-        <v>7.68391942977905</v>
+        <v>7.68391895294189</v>
       </c>
       <c r="H242" t="n">
         <v>10000</v>
@@ -7416,7 +7416,7 @@
         <v>8.15999984741211</v>
       </c>
       <c r="G243" t="n">
-        <v>7.64643669128418</v>
+        <v>7.64643621444702</v>
       </c>
       <c r="H243" t="n">
         <v>28200</v>
@@ -7474,7 +7474,7 @@
         <v>8.0600004196167</v>
       </c>
       <c r="G245" t="n">
-        <v>7.55273103713989</v>
+        <v>7.55273056030273</v>
       </c>
       <c r="H245" t="n">
         <v>500</v>
@@ -7503,7 +7503,7 @@
         <v>8.0600004196167</v>
       </c>
       <c r="G246" t="n">
-        <v>7.55273103713989</v>
+        <v>7.55273056030273</v>
       </c>
       <c r="H246" t="n">
         <v>2400</v>
@@ -7532,7 +7532,7 @@
         <v>8.0600004196167</v>
       </c>
       <c r="G247" t="n">
-        <v>7.55273103713989</v>
+        <v>7.55273056030273</v>
       </c>
       <c r="H247" t="n">
         <v>300</v>
@@ -7561,7 +7561,7 @@
         <v>8.0600004196167</v>
       </c>
       <c r="G248" t="n">
-        <v>7.55273103713989</v>
+        <v>7.55273056030273</v>
       </c>
       <c r="H248" t="n">
         <v>0</v>
@@ -7648,7 +7648,7 @@
         <v>8.23999977111816</v>
       </c>
       <c r="G251" t="n">
-        <v>7.72140169143677</v>
+        <v>7.72140073776245</v>
       </c>
       <c r="H251" t="n">
         <v>100</v>
@@ -7764,7 +7764,7 @@
         <v>7.61999988555908</v>
       </c>
       <c r="G255" t="n">
-        <v>7.14042234420776</v>
+        <v>7.14042186737061</v>
       </c>
       <c r="H255" t="n">
         <v>13900</v>
@@ -7793,7 +7793,7 @@
         <v>7.71999979019165</v>
       </c>
       <c r="G256" t="n">
-        <v>7.23412847518921</v>
+        <v>7.23412799835205</v>
       </c>
       <c r="H256" t="n">
         <v>7300</v>
@@ -8083,7 +8083,7 @@
         <v>7.61999988555908</v>
       </c>
       <c r="G266" t="n">
-        <v>7.14042234420776</v>
+        <v>7.14042186737061</v>
       </c>
       <c r="H266" t="n">
         <v>600</v>
@@ -8199,7 +8199,7 @@
         <v>7.71999979019165</v>
       </c>
       <c r="G270" t="n">
-        <v>7.23412847518921</v>
+        <v>7.23412799835205</v>
       </c>
       <c r="H270" t="n">
         <v>6600</v>
@@ -8228,7 +8228,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G271" t="n">
-        <v>7.7776255607605</v>
+        <v>7.77762603759766</v>
       </c>
       <c r="H271" t="n">
         <v>9100</v>
@@ -8257,7 +8257,7 @@
         <v>8.53999996185303</v>
       </c>
       <c r="G272" t="n">
-        <v>8.00252151489258</v>
+        <v>8.00252056121826</v>
       </c>
       <c r="H272" t="n">
         <v>9400</v>
@@ -8344,7 +8344,7 @@
         <v>9.14000034332275</v>
       </c>
       <c r="G275" t="n">
-        <v>8.56475925445557</v>
+        <v>8.56475830078125</v>
       </c>
       <c r="H275" t="n">
         <v>4000</v>
@@ -8373,7 +8373,7 @@
         <v>9.11999988555908</v>
       </c>
       <c r="G276" t="n">
-        <v>8.54601764678955</v>
+        <v>8.54601669311523</v>
       </c>
       <c r="H276" t="n">
         <v>1600</v>
@@ -8402,7 +8402,7 @@
         <v>9.14000034332275</v>
       </c>
       <c r="G277" t="n">
-        <v>8.56475925445557</v>
+        <v>8.56475830078125</v>
       </c>
       <c r="H277" t="n">
         <v>600</v>
@@ -8460,7 +8460,7 @@
         <v>9.11999988555908</v>
       </c>
       <c r="G279" t="n">
-        <v>8.54601764678955</v>
+        <v>8.54601669311523</v>
       </c>
       <c r="H279" t="n">
         <v>2000</v>
@@ -8489,7 +8489,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G280" t="n">
-        <v>8.52727699279785</v>
+        <v>8.52727603912354</v>
       </c>
       <c r="H280" t="n">
         <v>1100</v>
@@ -8605,7 +8605,7 @@
         <v>8.81999969482422</v>
       </c>
       <c r="G284" t="n">
-        <v>8.2648983001709</v>
+        <v>8.26489734649658</v>
       </c>
       <c r="H284" t="n">
         <v>700</v>
@@ -8750,7 +8750,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G289" t="n">
-        <v>8.52727699279785</v>
+        <v>8.52727603912354</v>
       </c>
       <c r="H289" t="n">
         <v>2100</v>
@@ -8808,7 +8808,7 @@
         <v>9.11999988555908</v>
       </c>
       <c r="G291" t="n">
-        <v>8.54601764678955</v>
+        <v>8.54601669311523</v>
       </c>
       <c r="H291" t="n">
         <v>3400</v>
@@ -8837,7 +8837,7 @@
         <v>9.11999988555908</v>
       </c>
       <c r="G292" t="n">
-        <v>8.54601764678955</v>
+        <v>8.54601669311523</v>
       </c>
       <c r="H292" t="n">
         <v>2100</v>
@@ -8924,7 +8924,7 @@
         <v>9.14000034332275</v>
       </c>
       <c r="G295" t="n">
-        <v>8.56475925445557</v>
+        <v>8.56475830078125</v>
       </c>
       <c r="H295" t="n">
         <v>200</v>
@@ -8982,7 +8982,7 @@
         <v>9.14000034332275</v>
       </c>
       <c r="G297" t="n">
-        <v>8.56475925445557</v>
+        <v>8.56475830078125</v>
       </c>
       <c r="H297" t="n">
         <v>500</v>
@@ -9011,7 +9011,7 @@
         <v>9.14000034332275</v>
       </c>
       <c r="G298" t="n">
-        <v>8.56475925445557</v>
+        <v>8.56475830078125</v>
       </c>
       <c r="H298" t="n">
         <v>0</v>
@@ -9040,7 +9040,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G299" t="n">
-        <v>8.52727699279785</v>
+        <v>8.52727603912354</v>
       </c>
       <c r="H299" t="n">
         <v>700</v>
@@ -9098,7 +9098,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G301" t="n">
-        <v>8.52727699279785</v>
+        <v>8.52727603912354</v>
       </c>
       <c r="H301" t="n">
         <v>300</v>
@@ -9330,7 +9330,7 @@
         <v>8.53999996185303</v>
       </c>
       <c r="G309" t="n">
-        <v>8.00252151489258</v>
+        <v>8.00252056121826</v>
       </c>
       <c r="H309" t="n">
         <v>2500</v>
@@ -9417,7 +9417,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G312" t="n">
-        <v>7.83384895324707</v>
+        <v>7.83384990692139</v>
       </c>
       <c r="H312" t="n">
         <v>1100</v>
@@ -9707,7 +9707,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G322" t="n">
-        <v>7.7776255607605</v>
+        <v>7.77762603759766</v>
       </c>
       <c r="H322" t="n">
         <v>3500</v>
@@ -9736,7 +9736,7 @@
         <v>8.27999973297119</v>
       </c>
       <c r="G323" t="n">
-        <v>7.75888442993164</v>
+        <v>7.75888395309448</v>
       </c>
       <c r="H323" t="n">
         <v>200</v>
@@ -9765,7 +9765,7 @@
         <v>8.27999973297119</v>
       </c>
       <c r="G324" t="n">
-        <v>7.75888442993164</v>
+        <v>7.75888395309448</v>
       </c>
       <c r="H324" t="n">
         <v>2000</v>
@@ -9794,7 +9794,7 @@
         <v>8.27999973297119</v>
       </c>
       <c r="G325" t="n">
-        <v>7.75888442993164</v>
+        <v>7.75888395309448</v>
       </c>
       <c r="H325" t="n">
         <v>6600</v>
@@ -9852,7 +9852,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G327" t="n">
-        <v>7.7776255607605</v>
+        <v>7.77762603759766</v>
       </c>
       <c r="H327" t="n">
         <v>2400</v>
@@ -10287,7 +10287,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G342" t="n">
-        <v>8.80839538574219</v>
+        <v>8.80839443206787</v>
       </c>
       <c r="H342" t="n">
         <v>10000</v>
@@ -10316,7 +10316,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G343" t="n">
-        <v>9.08951473236084</v>
+        <v>9.08951377868652</v>
       </c>
       <c r="H343" t="n">
         <v>10200</v>
@@ -10374,7 +10374,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G345" t="n">
-        <v>9.08951473236084</v>
+        <v>9.08951377868652</v>
       </c>
       <c r="H345" t="n">
         <v>4500</v>
@@ -10548,7 +10548,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G351" t="n">
-        <v>9.08951473236084</v>
+        <v>9.08951377868652</v>
       </c>
       <c r="H351" t="n">
         <v>800</v>
@@ -10838,7 +10838,7 @@
         <v>9.75</v>
       </c>
       <c r="G361" t="n">
-        <v>9.13636684417725</v>
+        <v>9.13636779785156</v>
       </c>
       <c r="H361" t="n">
         <v>1500</v>
@@ -11128,7 +11128,7 @@
         <v>9.75</v>
       </c>
       <c r="G371" t="n">
-        <v>9.13636684417725</v>
+        <v>9.13636779785156</v>
       </c>
       <c r="H371" t="n">
         <v>3600</v>
@@ -11157,7 +11157,7 @@
         <v>9.75</v>
       </c>
       <c r="G372" t="n">
-        <v>9.13636684417725</v>
+        <v>9.13636779785156</v>
       </c>
       <c r="H372" t="n">
         <v>100</v>
@@ -28998,6 +28998,35 @@
         <v>2300</v>
       </c>
       <c r="I987" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="988">
+      <c r="A988" t="s">
+        <v>9</v>
+      </c>
+      <c r="B988" s="1" t="n">
+        <v>46322.3333333333</v>
+      </c>
+      <c r="C988" t="n">
+        <v>10.5500001907349</v>
+      </c>
+      <c r="D988" t="n">
+        <v>10.6000003814697</v>
+      </c>
+      <c r="E988" t="n">
+        <v>10.3000001907349</v>
+      </c>
+      <c r="F988" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="G988" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="H988" t="n">
+        <v>1600</v>
+      </c>
+      <c r="I988" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/RDUE.MI.xlsx
+++ b/data/RDUE.MI.xlsx
@@ -456,7 +456,7 @@
         <v>12.0500001907349</v>
       </c>
       <c r="G3" t="n">
-        <v>11.2916126251221</v>
+        <v>11.2916135787964</v>
       </c>
       <c r="H3" t="n">
         <v>19500</v>
@@ -485,7 +485,7 @@
         <v>12.0600004196167</v>
       </c>
       <c r="G4" t="n">
-        <v>11.3009843826294</v>
+        <v>11.3009834289551</v>
       </c>
       <c r="H4" t="n">
         <v>2100</v>
@@ -514,7 +514,7 @@
         <v>12.1499996185303</v>
       </c>
       <c r="G5" t="n">
-        <v>11.3853187561035</v>
+        <v>11.3853197097778</v>
       </c>
       <c r="H5" t="n">
         <v>14000</v>
@@ -543,7 +543,7 @@
         <v>12.0539999008179</v>
       </c>
       <c r="G6" t="n">
-        <v>11.2953615188599</v>
+        <v>11.2953605651855</v>
       </c>
       <c r="H6" t="n">
         <v>9400</v>
@@ -572,7 +572,7 @@
         <v>12.0900001525879</v>
       </c>
       <c r="G7" t="n">
-        <v>11.3290948867798</v>
+        <v>11.3290958404541</v>
       </c>
       <c r="H7" t="n">
         <v>1000</v>
@@ -630,7 +630,7 @@
         <v>11.8599996566772</v>
       </c>
       <c r="G9" t="n">
-        <v>11.1135711669922</v>
+        <v>11.1135702133179</v>
       </c>
       <c r="H9" t="n">
         <v>5700</v>
@@ -688,7 +688,7 @@
         <v>11.9180002212524</v>
       </c>
       <c r="G11" t="n">
-        <v>11.1679201126099</v>
+        <v>11.1679210662842</v>
       </c>
       <c r="H11" t="n">
         <v>2300</v>
@@ -746,7 +746,7 @@
         <v>11.8800001144409</v>
       </c>
       <c r="G13" t="n">
-        <v>11.1323127746582</v>
+        <v>11.1323118209839</v>
       </c>
       <c r="H13" t="n">
         <v>5200</v>
@@ -978,7 +978,7 @@
         <v>11.3800001144409</v>
       </c>
       <c r="G21" t="n">
-        <v>10.6637811660767</v>
+        <v>10.6637802124023</v>
       </c>
       <c r="H21" t="n">
         <v>3200</v>
@@ -1065,7 +1065,7 @@
         <v>11.2600002288818</v>
       </c>
       <c r="G24" t="n">
-        <v>10.5513334274292</v>
+        <v>10.5513324737549</v>
       </c>
       <c r="H24" t="n">
         <v>200</v>
@@ -1123,7 +1123,7 @@
         <v>11.25</v>
       </c>
       <c r="G26" t="n">
-        <v>10.5419616699219</v>
+        <v>10.5419626235962</v>
       </c>
       <c r="H26" t="n">
         <v>400</v>
@@ -1181,7 +1181,7 @@
         <v>12.0100002288818</v>
       </c>
       <c r="G28" t="n">
-        <v>11.2541313171387</v>
+        <v>11.2541303634644</v>
       </c>
       <c r="H28" t="n">
         <v>5900</v>
@@ -1239,7 +1239,7 @@
         <v>11.8800001144409</v>
       </c>
       <c r="G30" t="n">
-        <v>11.1323127746582</v>
+        <v>11.1323118209839</v>
       </c>
       <c r="H30" t="n">
         <v>3900</v>
@@ -1355,7 +1355,7 @@
         <v>11.75</v>
       </c>
       <c r="G34" t="n">
-        <v>11.0104932785034</v>
+        <v>11.0104942321777</v>
       </c>
       <c r="H34" t="n">
         <v>3400</v>
@@ -2022,7 +2022,7 @@
         <v>11.75</v>
       </c>
       <c r="G57" t="n">
-        <v>11.0104932785034</v>
+        <v>11.0104942321777</v>
       </c>
       <c r="H57" t="n">
         <v>200</v>
@@ -2051,7 +2051,7 @@
         <v>11.75</v>
       </c>
       <c r="G58" t="n">
-        <v>11.0104932785034</v>
+        <v>11.0104942321777</v>
       </c>
       <c r="H58" t="n">
         <v>500</v>
@@ -2080,7 +2080,7 @@
         <v>11.75</v>
       </c>
       <c r="G59" t="n">
-        <v>11.0104932785034</v>
+        <v>11.0104942321777</v>
       </c>
       <c r="H59" t="n">
         <v>0</v>
@@ -2109,7 +2109,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G60" t="n">
-        <v>10.8699350357056</v>
+        <v>10.8699340820312</v>
       </c>
       <c r="H60" t="n">
         <v>6000</v>
@@ -2428,7 +2428,7 @@
         <v>11.5</v>
       </c>
       <c r="G71" t="n">
-        <v>10.7762279510498</v>
+        <v>10.7762269973755</v>
       </c>
       <c r="H71" t="n">
         <v>500</v>
@@ -2486,7 +2486,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G73" t="n">
-        <v>10.8699350357056</v>
+        <v>10.8699340820312</v>
       </c>
       <c r="H73" t="n">
         <v>10000</v>
@@ -2515,7 +2515,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G74" t="n">
-        <v>10.8699350357056</v>
+        <v>10.8699340820312</v>
       </c>
       <c r="H74" t="n">
         <v>4200</v>
@@ -2544,7 +2544,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G75" t="n">
-        <v>10.8699350357056</v>
+        <v>10.8699340820312</v>
       </c>
       <c r="H75" t="n">
         <v>1100</v>
@@ -2573,7 +2573,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G76" t="n">
-        <v>10.8699350357056</v>
+        <v>10.8699340820312</v>
       </c>
       <c r="H76" t="n">
         <v>3300</v>
@@ -2660,7 +2660,7 @@
         <v>11.5</v>
       </c>
       <c r="G79" t="n">
-        <v>10.7762279510498</v>
+        <v>10.7762269973755</v>
       </c>
       <c r="H79" t="n">
         <v>2100</v>
@@ -2747,7 +2747,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G82" t="n">
-        <v>9.74545860290527</v>
+        <v>9.74545764923096</v>
       </c>
       <c r="H82" t="n">
         <v>13600</v>
@@ -2776,7 +2776,7 @@
         <v>10.0500001907349</v>
       </c>
       <c r="G83" t="n">
-        <v>9.41748714447021</v>
+        <v>9.4174861907959</v>
       </c>
       <c r="H83" t="n">
         <v>13500</v>
@@ -2805,7 +2805,7 @@
         <v>10.0500001907349</v>
       </c>
       <c r="G84" t="n">
-        <v>9.41748714447021</v>
+        <v>9.4174861907959</v>
       </c>
       <c r="H84" t="n">
         <v>16000</v>
@@ -2950,7 +2950,7 @@
         <v>10.5500001907349</v>
       </c>
       <c r="G89" t="n">
-        <v>9.88601875305176</v>
+        <v>9.88601779937744</v>
       </c>
       <c r="H89" t="n">
         <v>4400</v>
@@ -3008,7 +3008,7 @@
         <v>10.0500001907349</v>
       </c>
       <c r="G91" t="n">
-        <v>9.41748714447021</v>
+        <v>9.4174861907959</v>
       </c>
       <c r="H91" t="n">
         <v>1800</v>
@@ -3037,7 +3037,7 @@
         <v>9.92000007629395</v>
       </c>
       <c r="G92" t="n">
-        <v>9.29566764831543</v>
+        <v>9.29566860198975</v>
       </c>
       <c r="H92" t="n">
         <v>5200</v>
@@ -3066,7 +3066,7 @@
         <v>9.72000026702881</v>
       </c>
       <c r="G93" t="n">
-        <v>9.10825538635254</v>
+        <v>9.10825634002686</v>
       </c>
       <c r="H93" t="n">
         <v>3500</v>
@@ -3095,7 +3095,7 @@
         <v>9.73999977111816</v>
       </c>
       <c r="G94" t="n">
-        <v>9.12699604034424</v>
+        <v>9.12699699401855</v>
       </c>
       <c r="H94" t="n">
         <v>2000</v>
@@ -3211,7 +3211,7 @@
         <v>9.53999996185303</v>
       </c>
       <c r="G98" t="n">
-        <v>8.93958282470703</v>
+        <v>8.93958473205566</v>
       </c>
       <c r="H98" t="n">
         <v>900</v>
@@ -3240,7 +3240,7 @@
         <v>9.34000015258789</v>
       </c>
       <c r="G99" t="n">
-        <v>8.75217056274414</v>
+        <v>8.75217151641846</v>
       </c>
       <c r="H99" t="n">
         <v>600</v>
@@ -3269,7 +3269,7 @@
         <v>9.14000034332275</v>
       </c>
       <c r="G100" t="n">
-        <v>8.56475830078125</v>
+        <v>8.56475925445557</v>
       </c>
       <c r="H100" t="n">
         <v>800</v>
@@ -3385,7 +3385,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G104" t="n">
-        <v>8.62098217010498</v>
+        <v>8.6209831237793</v>
       </c>
       <c r="H104" t="n">
         <v>1400</v>
@@ -3414,7 +3414,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G105" t="n">
-        <v>8.52727603912354</v>
+        <v>8.52727699279785</v>
       </c>
       <c r="H105" t="n">
         <v>1300</v>
@@ -3443,7 +3443,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G106" t="n">
-        <v>8.62098217010498</v>
+        <v>8.6209831237793</v>
       </c>
       <c r="H106" t="n">
         <v>200</v>
@@ -3472,7 +3472,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G107" t="n">
-        <v>8.62098217010498</v>
+        <v>8.6209831237793</v>
       </c>
       <c r="H107" t="n">
         <v>0</v>
@@ -3559,7 +3559,7 @@
         <v>9.4399995803833</v>
       </c>
       <c r="G110" t="n">
-        <v>8.84587669372559</v>
+        <v>8.8458776473999</v>
       </c>
       <c r="H110" t="n">
         <v>200</v>
@@ -3733,7 +3733,7 @@
         <v>10.5500001907349</v>
       </c>
       <c r="G116" t="n">
-        <v>9.88601875305176</v>
+        <v>9.88601779937744</v>
       </c>
       <c r="H116" t="n">
         <v>2700</v>
@@ -3762,7 +3762,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G117" t="n">
-        <v>9.74545860290527</v>
+        <v>9.74545764923096</v>
       </c>
       <c r="H117" t="n">
         <v>300</v>
@@ -3791,7 +3791,7 @@
         <v>10.5500001907349</v>
       </c>
       <c r="G118" t="n">
-        <v>9.88601875305176</v>
+        <v>9.88601779937744</v>
       </c>
       <c r="H118" t="n">
         <v>100</v>
@@ -3994,7 +3994,7 @@
         <v>9.57999992370605</v>
       </c>
       <c r="G125" t="n">
-        <v>8.97706699371338</v>
+        <v>8.97706604003906</v>
       </c>
       <c r="H125" t="n">
         <v>1400</v>
@@ -4081,7 +4081,7 @@
         <v>9.88000011444092</v>
       </c>
       <c r="G128" t="n">
-        <v>9.25818634033203</v>
+        <v>9.25818538665771</v>
       </c>
       <c r="H128" t="n">
         <v>2400</v>
@@ -4110,7 +4110,7 @@
         <v>9.84000015258789</v>
       </c>
       <c r="G129" t="n">
-        <v>9.22070217132568</v>
+        <v>9.22070407867432</v>
       </c>
       <c r="H129" t="n">
         <v>200</v>
@@ -4139,7 +4139,7 @@
         <v>9.92000007629395</v>
       </c>
       <c r="G130" t="n">
-        <v>9.29566764831543</v>
+        <v>9.29566860198975</v>
       </c>
       <c r="H130" t="n">
         <v>200</v>
@@ -4168,7 +4168,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G131" t="n">
-        <v>9.65175247192383</v>
+        <v>9.65175342559814</v>
       </c>
       <c r="H131" t="n">
         <v>2700</v>
@@ -4197,7 +4197,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G132" t="n">
-        <v>9.65175247192383</v>
+        <v>9.65175342559814</v>
       </c>
       <c r="H132" t="n">
         <v>100</v>
@@ -4226,7 +4226,7 @@
         <v>9.97999954223633</v>
       </c>
       <c r="G133" t="n">
-        <v>9.35189247131348</v>
+        <v>9.35189151763916</v>
       </c>
       <c r="H133" t="n">
         <v>500</v>
@@ -4342,7 +4342,7 @@
         <v>10.5500001907349</v>
       </c>
       <c r="G137" t="n">
-        <v>9.88601875305176</v>
+        <v>9.88601779937744</v>
       </c>
       <c r="H137" t="n">
         <v>1000</v>
@@ -4545,7 +4545,7 @@
         <v>9.47999954223633</v>
       </c>
       <c r="G144" t="n">
-        <v>8.88335990905762</v>
+        <v>8.88336086273193</v>
       </c>
       <c r="H144" t="n">
         <v>1800</v>
@@ -4574,7 +4574,7 @@
         <v>9.5600004196167</v>
       </c>
       <c r="G145" t="n">
-        <v>8.95832538604736</v>
+        <v>8.95832633972168</v>
       </c>
       <c r="H145" t="n">
         <v>1400</v>
@@ -4661,7 +4661,7 @@
         <v>9.31999969482422</v>
       </c>
       <c r="G148" t="n">
-        <v>8.73342895507812</v>
+        <v>8.73342990875244</v>
       </c>
       <c r="H148" t="n">
         <v>1000</v>
@@ -5125,7 +5125,7 @@
         <v>9.97999954223633</v>
       </c>
       <c r="G164" t="n">
-        <v>9.35189247131348</v>
+        <v>9.35189151763916</v>
       </c>
       <c r="H164" t="n">
         <v>400</v>
@@ -5270,7 +5270,7 @@
         <v>9.15999984741211</v>
       </c>
       <c r="G169" t="n">
-        <v>8.58350086212158</v>
+        <v>8.58349990844727</v>
       </c>
       <c r="H169" t="n">
         <v>16200</v>
@@ -5357,7 +5357,7 @@
         <v>9.5600004196167</v>
       </c>
       <c r="G172" t="n">
-        <v>8.95832538604736</v>
+        <v>8.95832633972168</v>
       </c>
       <c r="H172" t="n">
         <v>200</v>
@@ -5734,7 +5734,7 @@
         <v>9.72000026702881</v>
       </c>
       <c r="G185" t="n">
-        <v>9.10825538635254</v>
+        <v>9.10825634002686</v>
       </c>
       <c r="H185" t="n">
         <v>1300</v>
@@ -5763,7 +5763,7 @@
         <v>9.84000015258789</v>
       </c>
       <c r="G186" t="n">
-        <v>9.22070217132568</v>
+        <v>9.22070407867432</v>
       </c>
       <c r="H186" t="n">
         <v>400</v>
@@ -5792,7 +5792,7 @@
         <v>9.97999954223633</v>
       </c>
       <c r="G187" t="n">
-        <v>9.35189247131348</v>
+        <v>9.35189151763916</v>
       </c>
       <c r="H187" t="n">
         <v>3900</v>
@@ -5821,7 +5821,7 @@
         <v>9.97999954223633</v>
       </c>
       <c r="G188" t="n">
-        <v>9.35189247131348</v>
+        <v>9.35189151763916</v>
       </c>
       <c r="H188" t="n">
         <v>300</v>
@@ -5850,7 +5850,7 @@
         <v>9.61999988555908</v>
       </c>
       <c r="G189" t="n">
-        <v>9.01454830169678</v>
+        <v>9.01454925537109</v>
       </c>
       <c r="H189" t="n">
         <v>1400</v>
@@ -5995,7 +5995,7 @@
         <v>9.64000034332275</v>
       </c>
       <c r="G194" t="n">
-        <v>9.03328990936279</v>
+        <v>9.03329086303711</v>
       </c>
       <c r="H194" t="n">
         <v>100</v>
@@ -6024,7 +6024,7 @@
         <v>9.53999996185303</v>
       </c>
       <c r="G195" t="n">
-        <v>8.93958282470703</v>
+        <v>8.93958473205566</v>
       </c>
       <c r="H195" t="n">
         <v>600</v>
@@ -6053,7 +6053,7 @@
         <v>9.53999996185303</v>
       </c>
       <c r="G196" t="n">
-        <v>8.93958282470703</v>
+        <v>8.93958473205566</v>
       </c>
       <c r="H196" t="n">
         <v>0</v>
@@ -6082,7 +6082,7 @@
         <v>9.53999996185303</v>
       </c>
       <c r="G197" t="n">
-        <v>8.93958282470703</v>
+        <v>8.93958473205566</v>
       </c>
       <c r="H197" t="n">
         <v>0</v>
@@ -6169,7 +6169,7 @@
         <v>8.85999965667725</v>
       </c>
       <c r="G200" t="n">
-        <v>8.30238151550293</v>
+        <v>8.30238056182861</v>
       </c>
       <c r="H200" t="n">
         <v>12000</v>
@@ -6285,7 +6285,7 @@
         <v>9.0600004196167</v>
       </c>
       <c r="G204" t="n">
-        <v>8.48979473114014</v>
+        <v>8.48979377746582</v>
       </c>
       <c r="H204" t="n">
         <v>2200</v>
@@ -6314,7 +6314,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G205" t="n">
-        <v>8.33986282348633</v>
+        <v>8.33986377716064</v>
       </c>
       <c r="H205" t="n">
         <v>100</v>
@@ -6459,7 +6459,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G210" t="n">
-        <v>8.62098217010498</v>
+        <v>8.6209831237793</v>
       </c>
       <c r="H210" t="n">
         <v>100</v>
@@ -6488,7 +6488,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G211" t="n">
-        <v>8.62098217010498</v>
+        <v>8.6209831237793</v>
       </c>
       <c r="H211" t="n">
         <v>400</v>
@@ -6517,7 +6517,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G212" t="n">
-        <v>8.52727603912354</v>
+        <v>8.52727699279785</v>
       </c>
       <c r="H212" t="n">
         <v>1500</v>
@@ -6546,7 +6546,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G213" t="n">
-        <v>8.52727603912354</v>
+        <v>8.52727699279785</v>
       </c>
       <c r="H213" t="n">
         <v>0</v>
@@ -6575,7 +6575,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G214" t="n">
-        <v>8.52727603912354</v>
+        <v>8.52727699279785</v>
       </c>
       <c r="H214" t="n">
         <v>0</v>
@@ -6604,7 +6604,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G215" t="n">
-        <v>8.52727603912354</v>
+        <v>8.52727699279785</v>
       </c>
       <c r="H215" t="n">
         <v>0</v>
@@ -6633,7 +6633,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G216" t="n">
-        <v>8.52727603912354</v>
+        <v>8.52727699279785</v>
       </c>
       <c r="H216" t="n">
         <v>300</v>
@@ -6662,7 +6662,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G217" t="n">
-        <v>8.52727603912354</v>
+        <v>8.52727699279785</v>
       </c>
       <c r="H217" t="n">
         <v>0</v>
@@ -6691,7 +6691,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G218" t="n">
-        <v>8.52727603912354</v>
+        <v>8.52727699279785</v>
       </c>
       <c r="H218" t="n">
         <v>0</v>
@@ -6720,7 +6720,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G219" t="n">
-        <v>8.52727603912354</v>
+        <v>8.52727699279785</v>
       </c>
       <c r="H219" t="n">
         <v>0</v>
@@ -6749,7 +6749,7 @@
         <v>8.9399995803833</v>
       </c>
       <c r="G220" t="n">
-        <v>8.37734508514404</v>
+        <v>8.37734603881836</v>
       </c>
       <c r="H220" t="n">
         <v>200</v>
@@ -6778,7 +6778,7 @@
         <v>8.9399995803833</v>
       </c>
       <c r="G221" t="n">
-        <v>8.37734508514404</v>
+        <v>8.37734603881836</v>
       </c>
       <c r="H221" t="n">
         <v>0</v>
@@ -6807,7 +6807,7 @@
         <v>8.9399995803833</v>
       </c>
       <c r="G222" t="n">
-        <v>8.37734508514404</v>
+        <v>8.37734603881836</v>
       </c>
       <c r="H222" t="n">
         <v>0</v>
@@ -6836,7 +6836,7 @@
         <v>8.9399995803833</v>
       </c>
       <c r="G223" t="n">
-        <v>8.37734508514404</v>
+        <v>8.37734603881836</v>
       </c>
       <c r="H223" t="n">
         <v>0</v>
@@ -6865,7 +6865,7 @@
         <v>8.9399995803833</v>
       </c>
       <c r="G224" t="n">
-        <v>8.37734508514404</v>
+        <v>8.37734603881836</v>
       </c>
       <c r="H224" t="n">
         <v>0</v>
@@ -6894,7 +6894,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G225" t="n">
-        <v>8.52727603912354</v>
+        <v>8.52727699279785</v>
       </c>
       <c r="H225" t="n">
         <v>300</v>
@@ -6923,7 +6923,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G226" t="n">
-        <v>8.52727603912354</v>
+        <v>8.52727699279785</v>
       </c>
       <c r="H226" t="n">
         <v>0</v>
@@ -6952,7 +6952,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G227" t="n">
-        <v>8.52727603912354</v>
+        <v>8.52727699279785</v>
       </c>
       <c r="H227" t="n">
         <v>900</v>
@@ -6981,7 +6981,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G228" t="n">
-        <v>8.52727603912354</v>
+        <v>8.52727699279785</v>
       </c>
       <c r="H228" t="n">
         <v>0</v>
@@ -7010,7 +7010,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G229" t="n">
-        <v>8.52727603912354</v>
+        <v>8.52727699279785</v>
       </c>
       <c r="H229" t="n">
         <v>0</v>
@@ -7039,7 +7039,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G230" t="n">
-        <v>8.52727603912354</v>
+        <v>8.52727699279785</v>
       </c>
       <c r="H230" t="n">
         <v>0</v>
@@ -7068,7 +7068,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G231" t="n">
-        <v>8.52727603912354</v>
+        <v>8.52727699279785</v>
       </c>
       <c r="H231" t="n">
         <v>0</v>
@@ -7097,7 +7097,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G232" t="n">
-        <v>8.52727603912354</v>
+        <v>8.52727699279785</v>
       </c>
       <c r="H232" t="n">
         <v>0</v>
@@ -7126,7 +7126,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G233" t="n">
-        <v>8.52727603912354</v>
+        <v>8.52727699279785</v>
       </c>
       <c r="H233" t="n">
         <v>0</v>
@@ -7155,7 +7155,7 @@
         <v>8.9399995803833</v>
       </c>
       <c r="G234" t="n">
-        <v>8.37734508514404</v>
+        <v>8.37734603881836</v>
       </c>
       <c r="H234" t="n">
         <v>800</v>
@@ -7242,7 +7242,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G237" t="n">
-        <v>8.33986282348633</v>
+        <v>8.33986377716064</v>
       </c>
       <c r="H237" t="n">
         <v>9400</v>
@@ -7271,7 +7271,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G238" t="n">
-        <v>8.33986282348633</v>
+        <v>8.33986377716064</v>
       </c>
       <c r="H238" t="n">
         <v>300</v>
@@ -7300,7 +7300,7 @@
         <v>8.73999977111816</v>
       </c>
       <c r="G239" t="n">
-        <v>8.18993282318115</v>
+        <v>8.18993377685547</v>
       </c>
       <c r="H239" t="n">
         <v>500</v>
@@ -7358,7 +7358,7 @@
         <v>8.42000007629395</v>
       </c>
       <c r="G241" t="n">
-        <v>7.89007329940796</v>
+        <v>7.8900728225708</v>
       </c>
       <c r="H241" t="n">
         <v>1500</v>
@@ -7387,7 +7387,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G242" t="n">
-        <v>7.68391895294189</v>
+        <v>7.68391847610474</v>
       </c>
       <c r="H242" t="n">
         <v>10000</v>
@@ -7416,7 +7416,7 @@
         <v>8.15999984741211</v>
       </c>
       <c r="G243" t="n">
-        <v>7.64643621444702</v>
+        <v>7.64643669128418</v>
       </c>
       <c r="H243" t="n">
         <v>28200</v>
@@ -7590,7 +7590,7 @@
         <v>8.03999996185303</v>
       </c>
       <c r="G249" t="n">
-        <v>7.53398942947388</v>
+        <v>7.53398895263672</v>
       </c>
       <c r="H249" t="n">
         <v>400</v>
@@ -7648,7 +7648,7 @@
         <v>8.23999977111816</v>
       </c>
       <c r="G251" t="n">
-        <v>7.72140073776245</v>
+        <v>7.72140121459961</v>
       </c>
       <c r="H251" t="n">
         <v>100</v>
@@ -7677,7 +7677,7 @@
         <v>8.26000022888184</v>
       </c>
       <c r="G252" t="n">
-        <v>7.74014377593994</v>
+        <v>7.74014282226562</v>
       </c>
       <c r="H252" t="n">
         <v>300</v>
@@ -7735,7 +7735,7 @@
         <v>8.03999996185303</v>
       </c>
       <c r="G254" t="n">
-        <v>7.53398942947388</v>
+        <v>7.53398895263672</v>
       </c>
       <c r="H254" t="n">
         <v>2500</v>
@@ -7764,7 +7764,7 @@
         <v>7.61999988555908</v>
       </c>
       <c r="G255" t="n">
-        <v>7.14042186737061</v>
+        <v>7.14042234420776</v>
       </c>
       <c r="H255" t="n">
         <v>13900</v>
@@ -7793,7 +7793,7 @@
         <v>7.71999979019165</v>
       </c>
       <c r="G256" t="n">
-        <v>7.23412799835205</v>
+        <v>7.23412847518921</v>
       </c>
       <c r="H256" t="n">
         <v>7300</v>
@@ -7938,7 +7938,7 @@
         <v>7.84000015258789</v>
       </c>
       <c r="G261" t="n">
-        <v>7.34657669067383</v>
+        <v>7.34657621383667</v>
       </c>
       <c r="H261" t="n">
         <v>2200</v>
@@ -8054,7 +8054,7 @@
         <v>7.48000001907349</v>
       </c>
       <c r="G265" t="n">
-        <v>7.0092339515686</v>
+        <v>7.00923347473145</v>
       </c>
       <c r="H265" t="n">
         <v>10400</v>
@@ -8083,7 +8083,7 @@
         <v>7.61999988555908</v>
       </c>
       <c r="G266" t="n">
-        <v>7.14042186737061</v>
+        <v>7.14042234420776</v>
       </c>
       <c r="H266" t="n">
         <v>600</v>
@@ -8141,7 +8141,7 @@
         <v>7.48000001907349</v>
       </c>
       <c r="G268" t="n">
-        <v>7.0092339515686</v>
+        <v>7.00923347473145</v>
       </c>
       <c r="H268" t="n">
         <v>4100</v>
@@ -8199,7 +8199,7 @@
         <v>7.71999979019165</v>
       </c>
       <c r="G270" t="n">
-        <v>7.23412799835205</v>
+        <v>7.23412847518921</v>
       </c>
       <c r="H270" t="n">
         <v>6600</v>
@@ -8228,7 +8228,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G271" t="n">
-        <v>7.77762603759766</v>
+        <v>7.7776255607605</v>
       </c>
       <c r="H271" t="n">
         <v>9100</v>
@@ -8344,7 +8344,7 @@
         <v>9.14000034332275</v>
       </c>
       <c r="G275" t="n">
-        <v>8.56475830078125</v>
+        <v>8.56475925445557</v>
       </c>
       <c r="H275" t="n">
         <v>4000</v>
@@ -8373,7 +8373,7 @@
         <v>9.11999988555908</v>
       </c>
       <c r="G276" t="n">
-        <v>8.54601669311523</v>
+        <v>8.54601764678955</v>
       </c>
       <c r="H276" t="n">
         <v>1600</v>
@@ -8402,7 +8402,7 @@
         <v>9.14000034332275</v>
       </c>
       <c r="G277" t="n">
-        <v>8.56475830078125</v>
+        <v>8.56475925445557</v>
       </c>
       <c r="H277" t="n">
         <v>600</v>
@@ -8431,7 +8431,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G278" t="n">
-        <v>8.62098217010498</v>
+        <v>8.6209831237793</v>
       </c>
       <c r="H278" t="n">
         <v>300</v>
@@ -8460,7 +8460,7 @@
         <v>9.11999988555908</v>
       </c>
       <c r="G279" t="n">
-        <v>8.54601669311523</v>
+        <v>8.54601764678955</v>
       </c>
       <c r="H279" t="n">
         <v>2000</v>
@@ -8489,7 +8489,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G280" t="n">
-        <v>8.52727603912354</v>
+        <v>8.52727699279785</v>
       </c>
       <c r="H280" t="n">
         <v>1100</v>
@@ -8547,7 +8547,7 @@
         <v>8.92000007629395</v>
       </c>
       <c r="G282" t="n">
-        <v>8.35860443115234</v>
+        <v>8.35860538482666</v>
       </c>
       <c r="H282" t="n">
         <v>200</v>
@@ -8576,7 +8576,7 @@
         <v>8.76000022888184</v>
       </c>
       <c r="G283" t="n">
-        <v>8.20867538452148</v>
+        <v>8.20867443084717</v>
       </c>
       <c r="H283" t="n">
         <v>2800</v>
@@ -8605,7 +8605,7 @@
         <v>8.81999969482422</v>
       </c>
       <c r="G284" t="n">
-        <v>8.26489734649658</v>
+        <v>8.2648983001709</v>
       </c>
       <c r="H284" t="n">
         <v>700</v>
@@ -8750,7 +8750,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G289" t="n">
-        <v>8.52727603912354</v>
+        <v>8.52727699279785</v>
       </c>
       <c r="H289" t="n">
         <v>2100</v>
@@ -8808,7 +8808,7 @@
         <v>9.11999988555908</v>
       </c>
       <c r="G291" t="n">
-        <v>8.54601669311523</v>
+        <v>8.54601764678955</v>
       </c>
       <c r="H291" t="n">
         <v>3400</v>
@@ -8837,7 +8837,7 @@
         <v>9.11999988555908</v>
       </c>
       <c r="G292" t="n">
-        <v>8.54601669311523</v>
+        <v>8.54601764678955</v>
       </c>
       <c r="H292" t="n">
         <v>2100</v>
@@ -8924,7 +8924,7 @@
         <v>9.14000034332275</v>
       </c>
       <c r="G295" t="n">
-        <v>8.56475830078125</v>
+        <v>8.56475925445557</v>
       </c>
       <c r="H295" t="n">
         <v>200</v>
@@ -8953,7 +8953,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G296" t="n">
-        <v>8.62098217010498</v>
+        <v>8.6209831237793</v>
       </c>
       <c r="H296" t="n">
         <v>1000</v>
@@ -8982,7 +8982,7 @@
         <v>9.14000034332275</v>
       </c>
       <c r="G297" t="n">
-        <v>8.56475830078125</v>
+        <v>8.56475925445557</v>
       </c>
       <c r="H297" t="n">
         <v>500</v>
@@ -9011,7 +9011,7 @@
         <v>9.14000034332275</v>
       </c>
       <c r="G298" t="n">
-        <v>8.56475830078125</v>
+        <v>8.56475925445557</v>
       </c>
       <c r="H298" t="n">
         <v>0</v>
@@ -9040,7 +9040,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G299" t="n">
-        <v>8.52727603912354</v>
+        <v>8.52727699279785</v>
       </c>
       <c r="H299" t="n">
         <v>700</v>
@@ -9069,7 +9069,7 @@
         <v>8.9399995803833</v>
       </c>
       <c r="G300" t="n">
-        <v>8.37734508514404</v>
+        <v>8.37734603881836</v>
       </c>
       <c r="H300" t="n">
         <v>300</v>
@@ -9098,7 +9098,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G301" t="n">
-        <v>8.52727603912354</v>
+        <v>8.52727699279785</v>
       </c>
       <c r="H301" t="n">
         <v>300</v>
@@ -9185,7 +9185,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G304" t="n">
-        <v>8.33986282348633</v>
+        <v>8.33986377716064</v>
       </c>
       <c r="H304" t="n">
         <v>300</v>
@@ -9417,7 +9417,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G312" t="n">
-        <v>7.83384990692139</v>
+        <v>7.83384895324707</v>
       </c>
       <c r="H312" t="n">
         <v>1100</v>
@@ -9446,7 +9446,7 @@
         <v>8.61999988555908</v>
       </c>
       <c r="G313" t="n">
-        <v>8.07748508453369</v>
+        <v>8.07748603820801</v>
       </c>
       <c r="H313" t="n">
         <v>5400</v>
@@ -9649,7 +9649,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G320" t="n">
-        <v>7.87133169174194</v>
+        <v>7.87133121490479</v>
       </c>
       <c r="H320" t="n">
         <v>1000</v>
@@ -9707,7 +9707,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G322" t="n">
-        <v>7.77762603759766</v>
+        <v>7.7776255607605</v>
       </c>
       <c r="H322" t="n">
         <v>3500</v>
@@ -9736,7 +9736,7 @@
         <v>8.27999973297119</v>
       </c>
       <c r="G323" t="n">
-        <v>7.75888395309448</v>
+        <v>7.75888442993164</v>
       </c>
       <c r="H323" t="n">
         <v>200</v>
@@ -9765,7 +9765,7 @@
         <v>8.27999973297119</v>
       </c>
       <c r="G324" t="n">
-        <v>7.75888395309448</v>
+        <v>7.75888442993164</v>
       </c>
       <c r="H324" t="n">
         <v>2000</v>
@@ -9794,7 +9794,7 @@
         <v>8.27999973297119</v>
       </c>
       <c r="G325" t="n">
-        <v>7.75888395309448</v>
+        <v>7.75888442993164</v>
       </c>
       <c r="H325" t="n">
         <v>6600</v>
@@ -9823,7 +9823,7 @@
         <v>8.31999969482422</v>
       </c>
       <c r="G326" t="n">
-        <v>7.7963662147522</v>
+        <v>7.79636716842651</v>
       </c>
       <c r="H326" t="n">
         <v>3800</v>
@@ -9852,7 +9852,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G327" t="n">
-        <v>7.77762603759766</v>
+        <v>7.7776255607605</v>
       </c>
       <c r="H327" t="n">
         <v>2400</v>
@@ -9881,7 +9881,7 @@
         <v>8.34000015258789</v>
       </c>
       <c r="G328" t="n">
-        <v>7.81510782241821</v>
+        <v>7.81510829925537</v>
       </c>
       <c r="H328" t="n">
         <v>2400</v>
@@ -9910,7 +9910,7 @@
         <v>8.34000015258789</v>
       </c>
       <c r="G329" t="n">
-        <v>7.81510782241821</v>
+        <v>7.81510829925537</v>
       </c>
       <c r="H329" t="n">
         <v>1700</v>
@@ -9939,7 +9939,7 @@
         <v>8.34000015258789</v>
       </c>
       <c r="G330" t="n">
-        <v>7.81510782241821</v>
+        <v>7.81510829925537</v>
       </c>
       <c r="H330" t="n">
         <v>800</v>
@@ -9968,7 +9968,7 @@
         <v>8.34000015258789</v>
       </c>
       <c r="G331" t="n">
-        <v>7.81510782241821</v>
+        <v>7.81510829925537</v>
       </c>
       <c r="H331" t="n">
         <v>1400</v>
@@ -9997,7 +9997,7 @@
         <v>8.34000015258789</v>
       </c>
       <c r="G332" t="n">
-        <v>7.81510782241821</v>
+        <v>7.81510829925537</v>
       </c>
       <c r="H332" t="n">
         <v>0</v>
@@ -10084,7 +10084,7 @@
         <v>8.42000007629395</v>
       </c>
       <c r="G335" t="n">
-        <v>7.89007329940796</v>
+        <v>7.8900728225708</v>
       </c>
       <c r="H335" t="n">
         <v>4600</v>
@@ -10258,7 +10258,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G341" t="n">
-        <v>8.33986282348633</v>
+        <v>8.33986377716064</v>
       </c>
       <c r="H341" t="n">
         <v>3000</v>
@@ -10780,7 +10780,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G359" t="n">
-        <v>9.0426607131958</v>
+        <v>9.04265975952148</v>
       </c>
       <c r="H359" t="n">
         <v>4000</v>
@@ -10809,7 +10809,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G360" t="n">
-        <v>9.0426607131958</v>
+        <v>9.04265975952148</v>
       </c>
       <c r="H360" t="n">
         <v>0</v>
@@ -10838,7 +10838,7 @@
         <v>9.75</v>
       </c>
       <c r="G361" t="n">
-        <v>9.13636779785156</v>
+        <v>9.13636684417725</v>
       </c>
       <c r="H361" t="n">
         <v>1500</v>
@@ -10896,7 +10896,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G363" t="n">
-        <v>9.0426607131958</v>
+        <v>9.04265975952148</v>
       </c>
       <c r="H363" t="n">
         <v>100</v>
@@ -10925,7 +10925,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G364" t="n">
-        <v>9.0426607131958</v>
+        <v>9.04265975952148</v>
       </c>
       <c r="H364" t="n">
         <v>0</v>
@@ -10954,7 +10954,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G365" t="n">
-        <v>9.0426607131958</v>
+        <v>9.04265975952148</v>
       </c>
       <c r="H365" t="n">
         <v>300</v>
@@ -11128,7 +11128,7 @@
         <v>9.75</v>
       </c>
       <c r="G371" t="n">
-        <v>9.13636779785156</v>
+        <v>9.13636684417725</v>
       </c>
       <c r="H371" t="n">
         <v>3600</v>
@@ -11157,7 +11157,7 @@
         <v>9.75</v>
       </c>
       <c r="G372" t="n">
-        <v>9.13636779785156</v>
+        <v>9.13636684417725</v>
       </c>
       <c r="H372" t="n">
         <v>100</v>
@@ -11215,7 +11215,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G374" t="n">
-        <v>9.0426607131958</v>
+        <v>9.04265975952148</v>
       </c>
       <c r="H374" t="n">
         <v>100</v>
@@ -11244,7 +11244,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G375" t="n">
-        <v>9.30551815032959</v>
+        <v>9.30551719665527</v>
       </c>
       <c r="H375" t="n">
         <v>600</v>
@@ -11273,7 +11273,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G376" t="n">
-        <v>9.2575511932373</v>
+        <v>9.25755023956299</v>
       </c>
       <c r="H376" t="n">
         <v>2500</v>
@@ -11331,7 +11331,7 @@
         <v>10</v>
       </c>
       <c r="G378" t="n">
-        <v>9.59331798553467</v>
+        <v>9.59331703186035</v>
       </c>
       <c r="H378" t="n">
         <v>7200</v>
@@ -11708,7 +11708,7 @@
         <v>10</v>
       </c>
       <c r="G391" t="n">
-        <v>9.59331798553467</v>
+        <v>9.59331703186035</v>
       </c>
       <c r="H391" t="n">
         <v>300</v>
@@ -11853,7 +11853,7 @@
         <v>10</v>
       </c>
       <c r="G396" t="n">
-        <v>9.59331798553467</v>
+        <v>9.59331703186035</v>
       </c>
       <c r="H396" t="n">
         <v>500</v>
@@ -11882,7 +11882,7 @@
         <v>10</v>
       </c>
       <c r="G397" t="n">
-        <v>9.59331798553467</v>
+        <v>9.59331703186035</v>
       </c>
       <c r="H397" t="n">
         <v>0</v>
@@ -11940,7 +11940,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G399" t="n">
-        <v>9.30551815032959</v>
+        <v>9.30551719665527</v>
       </c>
       <c r="H399" t="n">
         <v>1600</v>
@@ -11998,7 +11998,7 @@
         <v>9.35000038146973</v>
       </c>
       <c r="G401" t="n">
-        <v>8.96975231170654</v>
+        <v>8.96975135803223</v>
       </c>
       <c r="H401" t="n">
         <v>5200</v>
@@ -12288,7 +12288,7 @@
         <v>10</v>
       </c>
       <c r="G411" t="n">
-        <v>9.59331798553467</v>
+        <v>9.59331703186035</v>
       </c>
       <c r="H411" t="n">
         <v>600</v>
@@ -12433,7 +12433,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G416" t="n">
-        <v>9.2575511932373</v>
+        <v>9.25755023956299</v>
       </c>
       <c r="H416" t="n">
         <v>700</v>
@@ -12462,7 +12462,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G417" t="n">
-        <v>9.2575511932373</v>
+        <v>9.25755023956299</v>
       </c>
       <c r="H417" t="n">
         <v>0</v>
@@ -12491,7 +12491,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G418" t="n">
-        <v>9.2575511932373</v>
+        <v>9.25755023956299</v>
       </c>
       <c r="H418" t="n">
         <v>0</v>
@@ -12520,7 +12520,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G419" t="n">
-        <v>9.30551815032959</v>
+        <v>9.30551719665527</v>
       </c>
       <c r="H419" t="n">
         <v>1700</v>
@@ -12578,7 +12578,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G421" t="n">
-        <v>9.01771831512451</v>
+        <v>9.0177173614502</v>
       </c>
       <c r="H421" t="n">
         <v>100</v>
@@ -12636,7 +12636,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G423" t="n">
-        <v>9.2575511932373</v>
+        <v>9.25755023956299</v>
       </c>
       <c r="H423" t="n">
         <v>1100</v>
@@ -12665,7 +12665,7 @@
         <v>9.35000038146973</v>
       </c>
       <c r="G424" t="n">
-        <v>8.96975231170654</v>
+        <v>8.96975135803223</v>
       </c>
       <c r="H424" t="n">
         <v>500</v>
@@ -12694,7 +12694,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G425" t="n">
-        <v>8.53805160522461</v>
+        <v>8.53805255889893</v>
       </c>
       <c r="H425" t="n">
         <v>1300</v>
@@ -12810,7 +12810,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G429" t="n">
-        <v>9.2575511932373</v>
+        <v>9.25755023956299</v>
       </c>
       <c r="H429" t="n">
         <v>700</v>
@@ -12839,7 +12839,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G430" t="n">
-        <v>9.2575511932373</v>
+        <v>9.25755023956299</v>
       </c>
       <c r="H430" t="n">
         <v>0</v>
@@ -12897,7 +12897,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G432" t="n">
-        <v>9.01771831512451</v>
+        <v>9.0177173614502</v>
       </c>
       <c r="H432" t="n">
         <v>100</v>
@@ -12926,7 +12926,7 @@
         <v>9.35000038146973</v>
       </c>
       <c r="G433" t="n">
-        <v>8.96975231170654</v>
+        <v>8.96975135803223</v>
       </c>
       <c r="H433" t="n">
         <v>1200</v>
@@ -12984,7 +12984,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G435" t="n">
-        <v>9.30551815032959</v>
+        <v>9.30551719665527</v>
       </c>
       <c r="H435" t="n">
         <v>200</v>
@@ -13013,7 +13013,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G436" t="n">
-        <v>9.2575511932373</v>
+        <v>9.25755023956299</v>
       </c>
       <c r="H436" t="n">
         <v>400</v>
@@ -13071,7 +13071,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G438" t="n">
-        <v>9.01771831512451</v>
+        <v>9.0177173614502</v>
       </c>
       <c r="H438" t="n">
         <v>600</v>
@@ -13100,7 +13100,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G439" t="n">
-        <v>9.30551815032959</v>
+        <v>9.30551719665527</v>
       </c>
       <c r="H439" t="n">
         <v>200</v>
@@ -13129,7 +13129,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G440" t="n">
-        <v>9.30551815032959</v>
+        <v>9.30551719665527</v>
       </c>
       <c r="H440" t="n">
         <v>500</v>
@@ -13158,7 +13158,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G441" t="n">
-        <v>9.30551815032959</v>
+        <v>9.30551719665527</v>
       </c>
       <c r="H441" t="n">
         <v>600</v>
@@ -13187,7 +13187,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G442" t="n">
-        <v>9.30551815032959</v>
+        <v>9.30551719665527</v>
       </c>
       <c r="H442" t="n">
         <v>800</v>
@@ -13274,7 +13274,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G445" t="n">
-        <v>9.01771831512451</v>
+        <v>9.0177173614502</v>
       </c>
       <c r="H445" t="n">
         <v>4900</v>
@@ -13303,7 +13303,7 @@
         <v>9.44999980926514</v>
       </c>
       <c r="G446" t="n">
-        <v>9.0656852722168</v>
+        <v>9.06568431854248</v>
       </c>
       <c r="H446" t="n">
         <v>4900</v>
@@ -13332,7 +13332,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G447" t="n">
-        <v>9.01771831512451</v>
+        <v>9.0177173614502</v>
       </c>
       <c r="H447" t="n">
         <v>2000</v>
@@ -13361,7 +13361,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G448" t="n">
-        <v>8.82585144042969</v>
+        <v>8.825852394104</v>
       </c>
       <c r="H448" t="n">
         <v>1200</v>
@@ -13535,7 +13535,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G454" t="n">
-        <v>8.82585144042969</v>
+        <v>8.825852394104</v>
       </c>
       <c r="H454" t="n">
         <v>100</v>
@@ -13564,7 +13564,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G455" t="n">
-        <v>8.82585144042969</v>
+        <v>8.825852394104</v>
       </c>
       <c r="H455" t="n">
         <v>0</v>
@@ -13593,7 +13593,7 @@
         <v>9.35000038146973</v>
       </c>
       <c r="G456" t="n">
-        <v>8.96975231170654</v>
+        <v>8.96975135803223</v>
       </c>
       <c r="H456" t="n">
         <v>9000</v>
@@ -13796,7 +13796,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G463" t="n">
-        <v>8.53805160522461</v>
+        <v>8.53805255889893</v>
       </c>
       <c r="H463" t="n">
         <v>800</v>
@@ -14057,7 +14057,7 @@
         <v>7.75</v>
       </c>
       <c r="G472" t="n">
-        <v>7.43482112884521</v>
+        <v>7.43482065200806</v>
       </c>
       <c r="H472" t="n">
         <v>5500</v>
@@ -14289,7 +14289,7 @@
         <v>7.5</v>
       </c>
       <c r="G480" t="n">
-        <v>7.19498777389526</v>
+        <v>7.19498825073242</v>
       </c>
       <c r="H480" t="n">
         <v>1800</v>
@@ -14318,7 +14318,7 @@
         <v>7.34999990463257</v>
       </c>
       <c r="G481" t="n">
-        <v>7.05108785629272</v>
+        <v>7.05108833312988</v>
       </c>
       <c r="H481" t="n">
         <v>4200</v>
@@ -14347,7 +14347,7 @@
         <v>7.34999990463257</v>
       </c>
       <c r="G482" t="n">
-        <v>7.05108785629272</v>
+        <v>7.05108833312988</v>
       </c>
       <c r="H482" t="n">
         <v>7800</v>
@@ -14434,7 +14434,7 @@
         <v>7</v>
       </c>
       <c r="G485" t="n">
-        <v>6.71532201766968</v>
+        <v>6.71532249450684</v>
       </c>
       <c r="H485" t="n">
         <v>10100</v>
@@ -14724,7 +14724,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G495" t="n">
-        <v>6.04379034042358</v>
+        <v>6.04378986358643</v>
       </c>
       <c r="H495" t="n">
         <v>7900</v>
@@ -15014,7 +15014,7 @@
         <v>7</v>
       </c>
       <c r="G505" t="n">
-        <v>6.71532201766968</v>
+        <v>6.71532249450684</v>
       </c>
       <c r="H505" t="n">
         <v>13500</v>
@@ -15072,7 +15072,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G507" t="n">
-        <v>6.81125497817993</v>
+        <v>6.81125545501709</v>
       </c>
       <c r="H507" t="n">
         <v>3900</v>
@@ -15159,7 +15159,7 @@
         <v>7.75</v>
       </c>
       <c r="G510" t="n">
-        <v>7.43482112884521</v>
+        <v>7.43482065200806</v>
       </c>
       <c r="H510" t="n">
         <v>3700</v>
@@ -15681,7 +15681,7 @@
         <v>7.34999990463257</v>
       </c>
       <c r="G528" t="n">
-        <v>7.05108785629272</v>
+        <v>7.05108833312988</v>
       </c>
       <c r="H528" t="n">
         <v>4000</v>
@@ -15884,7 +15884,7 @@
         <v>7.5</v>
       </c>
       <c r="G535" t="n">
-        <v>7.19498777389526</v>
+        <v>7.19498825073242</v>
       </c>
       <c r="H535" t="n">
         <v>200</v>
@@ -16029,7 +16029,7 @@
         <v>7</v>
       </c>
       <c r="G540" t="n">
-        <v>6.71532201766968</v>
+        <v>6.71532249450684</v>
       </c>
       <c r="H540" t="n">
         <v>7000</v>
@@ -16203,7 +16203,7 @@
         <v>6.94999980926514</v>
       </c>
       <c r="G546" t="n">
-        <v>6.66735506057739</v>
+        <v>6.66735553741455</v>
       </c>
       <c r="H546" t="n">
         <v>2700</v>
@@ -16290,7 +16290,7 @@
         <v>7</v>
       </c>
       <c r="G549" t="n">
-        <v>6.71532201766968</v>
+        <v>6.71532249450684</v>
       </c>
       <c r="H549" t="n">
         <v>9500</v>
@@ -16319,7 +16319,7 @@
         <v>6.94999980926514</v>
       </c>
       <c r="G550" t="n">
-        <v>6.66735506057739</v>
+        <v>6.66735553741455</v>
       </c>
       <c r="H550" t="n">
         <v>16600</v>
@@ -16580,7 +16580,7 @@
         <v>7.75</v>
       </c>
       <c r="G559" t="n">
-        <v>7.43482112884521</v>
+        <v>7.43482065200806</v>
       </c>
       <c r="H559" t="n">
         <v>4000</v>
@@ -16725,7 +16725,7 @@
         <v>7.75</v>
       </c>
       <c r="G564" t="n">
-        <v>7.43482112884521</v>
+        <v>7.43482065200806</v>
       </c>
       <c r="H564" t="n">
         <v>700</v>
@@ -16841,7 +16841,7 @@
         <v>7.75</v>
       </c>
       <c r="G568" t="n">
-        <v>7.43482112884521</v>
+        <v>7.43482065200806</v>
       </c>
       <c r="H568" t="n">
         <v>6900</v>
@@ -17015,7 +17015,7 @@
         <v>8.14999961853027</v>
       </c>
       <c r="G574" t="n">
-        <v>7.81855344772339</v>
+        <v>7.81855297088623</v>
       </c>
       <c r="H574" t="n">
         <v>5200</v>
@@ -17160,7 +17160,7 @@
         <v>7.5</v>
       </c>
       <c r="G579" t="n">
-        <v>7.19498777389526</v>
+        <v>7.19498825073242</v>
       </c>
       <c r="H579" t="n">
         <v>3100</v>
@@ -17247,7 +17247,7 @@
         <v>8.25</v>
       </c>
       <c r="G582" t="n">
-        <v>7.91448736190796</v>
+        <v>7.91448640823364</v>
       </c>
       <c r="H582" t="n">
         <v>10200</v>
@@ -17276,7 +17276,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G583" t="n">
-        <v>7.86652040481567</v>
+        <v>7.86651945114136</v>
       </c>
       <c r="H583" t="n">
         <v>20900</v>
@@ -17334,7 +17334,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G585" t="n">
-        <v>7.86652040481567</v>
+        <v>7.86651945114136</v>
       </c>
       <c r="H585" t="n">
         <v>5700</v>
@@ -17363,7 +17363,7 @@
         <v>7.75</v>
       </c>
       <c r="G586" t="n">
-        <v>7.43482112884521</v>
+        <v>7.43482065200806</v>
       </c>
       <c r="H586" t="n">
         <v>8000</v>
@@ -17392,7 +17392,7 @@
         <v>7.75</v>
       </c>
       <c r="G587" t="n">
-        <v>7.43482112884521</v>
+        <v>7.43482065200806</v>
       </c>
       <c r="H587" t="n">
         <v>1500</v>
@@ -17421,7 +17421,7 @@
         <v>7.75</v>
       </c>
       <c r="G588" t="n">
-        <v>7.43482112884521</v>
+        <v>7.43482065200806</v>
       </c>
       <c r="H588" t="n">
         <v>100</v>
@@ -17479,7 +17479,7 @@
         <v>7.75</v>
       </c>
       <c r="G590" t="n">
-        <v>7.43482112884521</v>
+        <v>7.43482065200806</v>
       </c>
       <c r="H590" t="n">
         <v>2300</v>
@@ -17653,7 +17653,7 @@
         <v>6.94999980926514</v>
       </c>
       <c r="G596" t="n">
-        <v>6.66735506057739</v>
+        <v>6.66735553741455</v>
       </c>
       <c r="H596" t="n">
         <v>1100</v>
@@ -17682,7 +17682,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G597" t="n">
-        <v>6.90718841552734</v>
+        <v>6.90718793869019</v>
       </c>
       <c r="H597" t="n">
         <v>1200</v>
@@ -17711,7 +17711,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G598" t="n">
-        <v>6.90718841552734</v>
+        <v>6.90718793869019</v>
       </c>
       <c r="H598" t="n">
         <v>0</v>
@@ -17798,7 +17798,7 @@
         <v>7.34999990463257</v>
       </c>
       <c r="G601" t="n">
-        <v>7.05108785629272</v>
+        <v>7.05108833312988</v>
       </c>
       <c r="H601" t="n">
         <v>2100</v>
@@ -17827,7 +17827,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G602" t="n">
-        <v>6.90718841552734</v>
+        <v>6.90718793869019</v>
       </c>
       <c r="H602" t="n">
         <v>1600</v>
@@ -17885,7 +17885,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G604" t="n">
-        <v>6.81125497817993</v>
+        <v>6.81125545501709</v>
       </c>
       <c r="H604" t="n">
         <v>15300</v>
@@ -29027,6 +29027,35 @@
         <v>1600</v>
       </c>
       <c r="I988" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="989">
+      <c r="A989" t="s">
+        <v>9</v>
+      </c>
+      <c r="B989" s="1" t="n">
+        <v>46323.3333333333</v>
+      </c>
+      <c r="C989" t="n">
+        <v>10.6499996185303</v>
+      </c>
+      <c r="D989" t="n">
+        <v>10.9499998092651</v>
+      </c>
+      <c r="E989" t="n">
+        <v>10.6000003814697</v>
+      </c>
+      <c r="F989" t="n">
+        <v>10.75</v>
+      </c>
+      <c r="G989" t="n">
+        <v>10.75</v>
+      </c>
+      <c r="H989" t="n">
+        <v>2100</v>
+      </c>
+      <c r="I989" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/RDUE.MI.xlsx
+++ b/data/RDUE.MI.xlsx
@@ -572,7 +572,7 @@
         <v>12.0900001525879</v>
       </c>
       <c r="G7" t="n">
-        <v>11.3290958404541</v>
+        <v>11.3290967941284</v>
       </c>
       <c r="H7" t="n">
         <v>1000</v>
@@ -717,7 +717,7 @@
         <v>11.9899997711182</v>
       </c>
       <c r="G12" t="n">
-        <v>11.2353887557983</v>
+        <v>11.2353897094727</v>
       </c>
       <c r="H12" t="n">
         <v>500</v>
@@ -746,7 +746,7 @@
         <v>11.8800001144409</v>
       </c>
       <c r="G13" t="n">
-        <v>11.1323118209839</v>
+        <v>11.1323127746582</v>
       </c>
       <c r="H13" t="n">
         <v>5200</v>
@@ -804,7 +804,7 @@
         <v>11.6199998855591</v>
       </c>
       <c r="G15" t="n">
-        <v>10.8886747360229</v>
+        <v>10.8886756896973</v>
       </c>
       <c r="H15" t="n">
         <v>1900</v>
@@ -949,7 +949,7 @@
         <v>11.5900001525879</v>
       </c>
       <c r="G20" t="n">
-        <v>10.8605642318726</v>
+        <v>10.8605632781982</v>
       </c>
       <c r="H20" t="n">
         <v>800</v>
@@ -1007,7 +1007,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G22" t="n">
-        <v>10.682520866394</v>
+        <v>10.6825218200684</v>
       </c>
       <c r="H22" t="n">
         <v>600</v>
@@ -1152,7 +1152,7 @@
         <v>11.9840002059937</v>
       </c>
       <c r="G27" t="n">
-        <v>11.2297668457031</v>
+        <v>11.2297677993774</v>
       </c>
       <c r="H27" t="n">
         <v>14800</v>
@@ -1239,7 +1239,7 @@
         <v>11.8800001144409</v>
       </c>
       <c r="G30" t="n">
-        <v>11.1323118209839</v>
+        <v>11.1323127746582</v>
       </c>
       <c r="H30" t="n">
         <v>3900</v>
@@ -1268,7 +1268,7 @@
         <v>11.9799995422363</v>
       </c>
       <c r="G31" t="n">
-        <v>11.2260179519653</v>
+        <v>11.2260189056396</v>
       </c>
       <c r="H31" t="n">
         <v>200</v>
@@ -1471,7 +1471,7 @@
         <v>11.996000289917</v>
       </c>
       <c r="G38" t="n">
-        <v>11.2410116195679</v>
+        <v>11.2410125732422</v>
       </c>
       <c r="H38" t="n">
         <v>900</v>
@@ -1529,7 +1529,7 @@
         <v>11.9799995422363</v>
       </c>
       <c r="G40" t="n">
-        <v>11.2260179519653</v>
+        <v>11.2260189056396</v>
       </c>
       <c r="H40" t="n">
         <v>400</v>
@@ -1558,7 +1558,7 @@
         <v>11.9799995422363</v>
       </c>
       <c r="G41" t="n">
-        <v>11.2260179519653</v>
+        <v>11.2260189056396</v>
       </c>
       <c r="H41" t="n">
         <v>0</v>
@@ -1819,7 +1819,7 @@
         <v>11.5500001907349</v>
       </c>
       <c r="G50" t="n">
-        <v>10.8230810165405</v>
+        <v>10.8230819702148</v>
       </c>
       <c r="H50" t="n">
         <v>400</v>
@@ -1848,7 +1848,7 @@
         <v>11.5500001907349</v>
       </c>
       <c r="G51" t="n">
-        <v>10.8230810165405</v>
+        <v>10.8230819702148</v>
       </c>
       <c r="H51" t="n">
         <v>1700</v>
@@ -2196,7 +2196,7 @@
         <v>11.4499998092651</v>
       </c>
       <c r="G63" t="n">
-        <v>10.7293748855591</v>
+        <v>10.7293758392334</v>
       </c>
       <c r="H63" t="n">
         <v>2200</v>
@@ -2225,7 +2225,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G64" t="n">
-        <v>10.682520866394</v>
+        <v>10.6825218200684</v>
       </c>
       <c r="H64" t="n">
         <v>2900</v>
@@ -2254,7 +2254,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G65" t="n">
-        <v>10.682520866394</v>
+        <v>10.6825218200684</v>
       </c>
       <c r="H65" t="n">
         <v>500</v>
@@ -2283,7 +2283,7 @@
         <v>11.5500001907349</v>
       </c>
       <c r="G66" t="n">
-        <v>10.8230810165405</v>
+        <v>10.8230819702148</v>
       </c>
       <c r="H66" t="n">
         <v>4100</v>
@@ -2341,7 +2341,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G68" t="n">
-        <v>10.682520866394</v>
+        <v>10.6825218200684</v>
       </c>
       <c r="H68" t="n">
         <v>700</v>
@@ -2370,7 +2370,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G69" t="n">
-        <v>10.682520866394</v>
+        <v>10.6825218200684</v>
       </c>
       <c r="H69" t="n">
         <v>0</v>
@@ -2428,7 +2428,7 @@
         <v>11.5</v>
       </c>
       <c r="G71" t="n">
-        <v>10.7762269973755</v>
+        <v>10.7762279510498</v>
       </c>
       <c r="H71" t="n">
         <v>500</v>
@@ -2457,7 +2457,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G72" t="n">
-        <v>10.682520866394</v>
+        <v>10.6825218200684</v>
       </c>
       <c r="H72" t="n">
         <v>3100</v>
@@ -2660,7 +2660,7 @@
         <v>11.5</v>
       </c>
       <c r="G79" t="n">
-        <v>10.7762269973755</v>
+        <v>10.7762279510498</v>
       </c>
       <c r="H79" t="n">
         <v>2100</v>
@@ -2718,7 +2718,7 @@
         <v>11.5500001907349</v>
       </c>
       <c r="G81" t="n">
-        <v>10.8230810165405</v>
+        <v>10.8230819702148</v>
       </c>
       <c r="H81" t="n">
         <v>800</v>
@@ -2921,7 +2921,7 @@
         <v>10.25</v>
       </c>
       <c r="G88" t="n">
-        <v>9.60489940643311</v>
+        <v>9.60489845275879</v>
       </c>
       <c r="H88" t="n">
         <v>1800</v>
@@ -2979,7 +2979,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G90" t="n">
-        <v>9.55804634094238</v>
+        <v>9.55804538726807</v>
       </c>
       <c r="H90" t="n">
         <v>600</v>
@@ -3037,7 +3037,7 @@
         <v>9.92000007629395</v>
       </c>
       <c r="G92" t="n">
-        <v>9.29566860198975</v>
+        <v>9.29566764831543</v>
       </c>
       <c r="H92" t="n">
         <v>5200</v>
@@ -3095,7 +3095,7 @@
         <v>9.73999977111816</v>
       </c>
       <c r="G94" t="n">
-        <v>9.12699699401855</v>
+        <v>9.12699604034424</v>
       </c>
       <c r="H94" t="n">
         <v>2000</v>
@@ -3211,7 +3211,7 @@
         <v>9.53999996185303</v>
       </c>
       <c r="G98" t="n">
-        <v>8.93958473205566</v>
+        <v>8.93958377838135</v>
       </c>
       <c r="H98" t="n">
         <v>900</v>
@@ -3414,7 +3414,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G105" t="n">
-        <v>8.52727699279785</v>
+        <v>8.52727603912354</v>
       </c>
       <c r="H105" t="n">
         <v>1300</v>
@@ -3530,7 +3530,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G109" t="n">
-        <v>8.80839443206787</v>
+        <v>8.80839538574219</v>
       </c>
       <c r="H109" t="n">
         <v>300</v>
@@ -3559,7 +3559,7 @@
         <v>9.4399995803833</v>
       </c>
       <c r="G110" t="n">
-        <v>8.8458776473999</v>
+        <v>8.84587669372559</v>
       </c>
       <c r="H110" t="n">
         <v>200</v>
@@ -3675,7 +3675,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G114" t="n">
-        <v>9.55804634094238</v>
+        <v>9.55804538726807</v>
       </c>
       <c r="H114" t="n">
         <v>7600</v>
@@ -4110,7 +4110,7 @@
         <v>9.84000015258789</v>
       </c>
       <c r="G129" t="n">
-        <v>9.22070407867432</v>
+        <v>9.220703125</v>
       </c>
       <c r="H129" t="n">
         <v>200</v>
@@ -4139,7 +4139,7 @@
         <v>9.92000007629395</v>
       </c>
       <c r="G130" t="n">
-        <v>9.29566860198975</v>
+        <v>9.29566764831543</v>
       </c>
       <c r="H130" t="n">
         <v>200</v>
@@ -4168,7 +4168,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G131" t="n">
-        <v>9.65175342559814</v>
+        <v>9.65175247192383</v>
       </c>
       <c r="H131" t="n">
         <v>2700</v>
@@ -4197,7 +4197,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G132" t="n">
-        <v>9.65175342559814</v>
+        <v>9.65175247192383</v>
       </c>
       <c r="H132" t="n">
         <v>100</v>
@@ -4226,7 +4226,7 @@
         <v>9.97999954223633</v>
       </c>
       <c r="G133" t="n">
-        <v>9.35189151763916</v>
+        <v>9.35189056396484</v>
       </c>
       <c r="H133" t="n">
         <v>500</v>
@@ -4545,7 +4545,7 @@
         <v>9.47999954223633</v>
       </c>
       <c r="G144" t="n">
-        <v>8.88336086273193</v>
+        <v>8.88335990905762</v>
       </c>
       <c r="H144" t="n">
         <v>1800</v>
@@ -5125,7 +5125,7 @@
         <v>9.97999954223633</v>
       </c>
       <c r="G164" t="n">
-        <v>9.35189151763916</v>
+        <v>9.35189056396484</v>
       </c>
       <c r="H164" t="n">
         <v>400</v>
@@ -5328,7 +5328,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G171" t="n">
-        <v>8.80839443206787</v>
+        <v>8.80839538574219</v>
       </c>
       <c r="H171" t="n">
         <v>900</v>
@@ -5415,7 +5415,7 @@
         <v>9.27999973297119</v>
       </c>
       <c r="G174" t="n">
-        <v>8.69594764709473</v>
+        <v>8.69594669342041</v>
       </c>
       <c r="H174" t="n">
         <v>8500</v>
@@ -5473,7 +5473,7 @@
         <v>9.27999973297119</v>
       </c>
       <c r="G176" t="n">
-        <v>8.69594764709473</v>
+        <v>8.69594669342041</v>
       </c>
       <c r="H176" t="n">
         <v>1400</v>
@@ -5502,7 +5502,7 @@
         <v>9.27999973297119</v>
       </c>
       <c r="G177" t="n">
-        <v>8.69594764709473</v>
+        <v>8.69594669342041</v>
       </c>
       <c r="H177" t="n">
         <v>0</v>
@@ -5763,7 +5763,7 @@
         <v>9.84000015258789</v>
       </c>
       <c r="G186" t="n">
-        <v>9.22070407867432</v>
+        <v>9.220703125</v>
       </c>
       <c r="H186" t="n">
         <v>400</v>
@@ -5792,7 +5792,7 @@
         <v>9.97999954223633</v>
       </c>
       <c r="G187" t="n">
-        <v>9.35189151763916</v>
+        <v>9.35189056396484</v>
       </c>
       <c r="H187" t="n">
         <v>3900</v>
@@ -5821,7 +5821,7 @@
         <v>9.97999954223633</v>
       </c>
       <c r="G188" t="n">
-        <v>9.35189151763916</v>
+        <v>9.35189056396484</v>
       </c>
       <c r="H188" t="n">
         <v>300</v>
@@ -5995,7 +5995,7 @@
         <v>9.64000034332275</v>
       </c>
       <c r="G194" t="n">
-        <v>9.03329086303711</v>
+        <v>9.03328990936279</v>
       </c>
       <c r="H194" t="n">
         <v>100</v>
@@ -6024,7 +6024,7 @@
         <v>9.53999996185303</v>
       </c>
       <c r="G195" t="n">
-        <v>8.93958473205566</v>
+        <v>8.93958377838135</v>
       </c>
       <c r="H195" t="n">
         <v>600</v>
@@ -6053,7 +6053,7 @@
         <v>9.53999996185303</v>
       </c>
       <c r="G196" t="n">
-        <v>8.93958473205566</v>
+        <v>8.93958377838135</v>
       </c>
       <c r="H196" t="n">
         <v>0</v>
@@ -6082,7 +6082,7 @@
         <v>9.53999996185303</v>
       </c>
       <c r="G197" t="n">
-        <v>8.93958473205566</v>
+        <v>8.93958377838135</v>
       </c>
       <c r="H197" t="n">
         <v>0</v>
@@ -6169,7 +6169,7 @@
         <v>8.85999965667725</v>
       </c>
       <c r="G200" t="n">
-        <v>8.30238056182861</v>
+        <v>8.30238151550293</v>
       </c>
       <c r="H200" t="n">
         <v>12000</v>
@@ -6198,7 +6198,7 @@
         <v>9</v>
       </c>
       <c r="G201" t="n">
-        <v>8.43356990814209</v>
+        <v>8.43356895446777</v>
       </c>
       <c r="H201" t="n">
         <v>400</v>
@@ -6227,7 +6227,7 @@
         <v>9</v>
       </c>
       <c r="G202" t="n">
-        <v>8.43356990814209</v>
+        <v>8.43356895446777</v>
       </c>
       <c r="H202" t="n">
         <v>0</v>
@@ -6256,7 +6256,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G203" t="n">
-        <v>8.2461576461792</v>
+        <v>8.24615669250488</v>
       </c>
       <c r="H203" t="n">
         <v>2500</v>
@@ -6314,7 +6314,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G205" t="n">
-        <v>8.33986377716064</v>
+        <v>8.33986282348633</v>
       </c>
       <c r="H205" t="n">
         <v>100</v>
@@ -6343,7 +6343,7 @@
         <v>9</v>
       </c>
       <c r="G206" t="n">
-        <v>8.43356990814209</v>
+        <v>8.43356895446777</v>
       </c>
       <c r="H206" t="n">
         <v>2200</v>
@@ -6517,7 +6517,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G212" t="n">
-        <v>8.52727699279785</v>
+        <v>8.52727603912354</v>
       </c>
       <c r="H212" t="n">
         <v>1500</v>
@@ -6546,7 +6546,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G213" t="n">
-        <v>8.52727699279785</v>
+        <v>8.52727603912354</v>
       </c>
       <c r="H213" t="n">
         <v>0</v>
@@ -6575,7 +6575,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G214" t="n">
-        <v>8.52727699279785</v>
+        <v>8.52727603912354</v>
       </c>
       <c r="H214" t="n">
         <v>0</v>
@@ -6604,7 +6604,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G215" t="n">
-        <v>8.52727699279785</v>
+        <v>8.52727603912354</v>
       </c>
       <c r="H215" t="n">
         <v>0</v>
@@ -6633,7 +6633,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G216" t="n">
-        <v>8.52727699279785</v>
+        <v>8.52727603912354</v>
       </c>
       <c r="H216" t="n">
         <v>300</v>
@@ -6662,7 +6662,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G217" t="n">
-        <v>8.52727699279785</v>
+        <v>8.52727603912354</v>
       </c>
       <c r="H217" t="n">
         <v>0</v>
@@ -6691,7 +6691,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G218" t="n">
-        <v>8.52727699279785</v>
+        <v>8.52727603912354</v>
       </c>
       <c r="H218" t="n">
         <v>0</v>
@@ -6720,7 +6720,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G219" t="n">
-        <v>8.52727699279785</v>
+        <v>8.52727603912354</v>
       </c>
       <c r="H219" t="n">
         <v>0</v>
@@ -6749,7 +6749,7 @@
         <v>8.9399995803833</v>
       </c>
       <c r="G220" t="n">
-        <v>8.37734603881836</v>
+        <v>8.37734508514404</v>
       </c>
       <c r="H220" t="n">
         <v>200</v>
@@ -6778,7 +6778,7 @@
         <v>8.9399995803833</v>
       </c>
       <c r="G221" t="n">
-        <v>8.37734603881836</v>
+        <v>8.37734508514404</v>
       </c>
       <c r="H221" t="n">
         <v>0</v>
@@ -6807,7 +6807,7 @@
         <v>8.9399995803833</v>
       </c>
       <c r="G222" t="n">
-        <v>8.37734603881836</v>
+        <v>8.37734508514404</v>
       </c>
       <c r="H222" t="n">
         <v>0</v>
@@ -6836,7 +6836,7 @@
         <v>8.9399995803833</v>
       </c>
       <c r="G223" t="n">
-        <v>8.37734603881836</v>
+        <v>8.37734508514404</v>
       </c>
       <c r="H223" t="n">
         <v>0</v>
@@ -6865,7 +6865,7 @@
         <v>8.9399995803833</v>
       </c>
       <c r="G224" t="n">
-        <v>8.37734603881836</v>
+        <v>8.37734508514404</v>
       </c>
       <c r="H224" t="n">
         <v>0</v>
@@ -6894,7 +6894,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G225" t="n">
-        <v>8.52727699279785</v>
+        <v>8.52727603912354</v>
       </c>
       <c r="H225" t="n">
         <v>300</v>
@@ -6923,7 +6923,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G226" t="n">
-        <v>8.52727699279785</v>
+        <v>8.52727603912354</v>
       </c>
       <c r="H226" t="n">
         <v>0</v>
@@ -6952,7 +6952,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G227" t="n">
-        <v>8.52727699279785</v>
+        <v>8.52727603912354</v>
       </c>
       <c r="H227" t="n">
         <v>900</v>
@@ -6981,7 +6981,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G228" t="n">
-        <v>8.52727699279785</v>
+        <v>8.52727603912354</v>
       </c>
       <c r="H228" t="n">
         <v>0</v>
@@ -7010,7 +7010,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G229" t="n">
-        <v>8.52727699279785</v>
+        <v>8.52727603912354</v>
       </c>
       <c r="H229" t="n">
         <v>0</v>
@@ -7039,7 +7039,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G230" t="n">
-        <v>8.52727699279785</v>
+        <v>8.52727603912354</v>
       </c>
       <c r="H230" t="n">
         <v>0</v>
@@ -7068,7 +7068,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G231" t="n">
-        <v>8.52727699279785</v>
+        <v>8.52727603912354</v>
       </c>
       <c r="H231" t="n">
         <v>0</v>
@@ -7097,7 +7097,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G232" t="n">
-        <v>8.52727699279785</v>
+        <v>8.52727603912354</v>
       </c>
       <c r="H232" t="n">
         <v>0</v>
@@ -7126,7 +7126,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G233" t="n">
-        <v>8.52727699279785</v>
+        <v>8.52727603912354</v>
       </c>
       <c r="H233" t="n">
         <v>0</v>
@@ -7155,7 +7155,7 @@
         <v>8.9399995803833</v>
       </c>
       <c r="G234" t="n">
-        <v>8.37734603881836</v>
+        <v>8.37734508514404</v>
       </c>
       <c r="H234" t="n">
         <v>800</v>
@@ -7184,7 +7184,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G235" t="n">
-        <v>8.2461576461792</v>
+        <v>8.24615669250488</v>
       </c>
       <c r="H235" t="n">
         <v>1000</v>
@@ -7242,7 +7242,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G237" t="n">
-        <v>8.33986377716064</v>
+        <v>8.33986282348633</v>
       </c>
       <c r="H237" t="n">
         <v>9400</v>
@@ -7271,7 +7271,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G238" t="n">
-        <v>8.33986377716064</v>
+        <v>8.33986282348633</v>
       </c>
       <c r="H238" t="n">
         <v>300</v>
@@ -7300,7 +7300,7 @@
         <v>8.73999977111816</v>
       </c>
       <c r="G239" t="n">
-        <v>8.18993377685547</v>
+        <v>8.18993282318115</v>
       </c>
       <c r="H239" t="n">
         <v>500</v>
@@ -7358,7 +7358,7 @@
         <v>8.42000007629395</v>
       </c>
       <c r="G241" t="n">
-        <v>7.8900728225708</v>
+        <v>7.89007329940796</v>
       </c>
       <c r="H241" t="n">
         <v>1500</v>
@@ -7387,7 +7387,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G242" t="n">
-        <v>7.68391847610474</v>
+        <v>7.68391895294189</v>
       </c>
       <c r="H242" t="n">
         <v>10000</v>
@@ -7445,7 +7445,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G244" t="n">
-        <v>7.59021329879761</v>
+        <v>7.59021282196045</v>
       </c>
       <c r="H244" t="n">
         <v>300</v>
@@ -7822,7 +7822,7 @@
         <v>7.55999994277954</v>
       </c>
       <c r="G257" t="n">
-        <v>7.08419847488403</v>
+        <v>7.08419895172119</v>
       </c>
       <c r="H257" t="n">
         <v>6000</v>
@@ -7851,7 +7851,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G258" t="n">
-        <v>7.12168121337891</v>
+        <v>7.12168073654175</v>
       </c>
       <c r="H258" t="n">
         <v>4500</v>
@@ -7909,7 +7909,7 @@
         <v>7.67999982833862</v>
       </c>
       <c r="G260" t="n">
-        <v>7.19664621353149</v>
+        <v>7.19664573669434</v>
       </c>
       <c r="H260" t="n">
         <v>4200</v>
@@ -7996,7 +7996,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G263" t="n">
-        <v>7.40280055999756</v>
+        <v>7.4028000831604</v>
       </c>
       <c r="H263" t="n">
         <v>2900</v>
@@ -8373,7 +8373,7 @@
         <v>9.11999988555908</v>
       </c>
       <c r="G276" t="n">
-        <v>8.54601764678955</v>
+        <v>8.54601669311523</v>
       </c>
       <c r="H276" t="n">
         <v>1600</v>
@@ -8460,7 +8460,7 @@
         <v>9.11999988555908</v>
       </c>
       <c r="G279" t="n">
-        <v>8.54601764678955</v>
+        <v>8.54601669311523</v>
       </c>
       <c r="H279" t="n">
         <v>2000</v>
@@ -8489,7 +8489,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G280" t="n">
-        <v>8.52727699279785</v>
+        <v>8.52727603912354</v>
       </c>
       <c r="H280" t="n">
         <v>1100</v>
@@ -8576,7 +8576,7 @@
         <v>8.76000022888184</v>
       </c>
       <c r="G283" t="n">
-        <v>8.20867443084717</v>
+        <v>8.20867538452148</v>
       </c>
       <c r="H283" t="n">
         <v>2800</v>
@@ -8692,7 +8692,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G287" t="n">
-        <v>8.2461576461792</v>
+        <v>8.24615669250488</v>
       </c>
       <c r="H287" t="n">
         <v>200</v>
@@ -8750,7 +8750,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G289" t="n">
-        <v>8.52727699279785</v>
+        <v>8.52727603912354</v>
       </c>
       <c r="H289" t="n">
         <v>2100</v>
@@ -8808,7 +8808,7 @@
         <v>9.11999988555908</v>
       </c>
       <c r="G291" t="n">
-        <v>8.54601764678955</v>
+        <v>8.54601669311523</v>
       </c>
       <c r="H291" t="n">
         <v>3400</v>
@@ -8837,7 +8837,7 @@
         <v>9.11999988555908</v>
       </c>
       <c r="G292" t="n">
-        <v>8.54601764678955</v>
+        <v>8.54601669311523</v>
       </c>
       <c r="H292" t="n">
         <v>2100</v>
@@ -8895,7 +8895,7 @@
         <v>9</v>
       </c>
       <c r="G294" t="n">
-        <v>8.43356990814209</v>
+        <v>8.43356895446777</v>
       </c>
       <c r="H294" t="n">
         <v>1700</v>
@@ -9040,7 +9040,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G299" t="n">
-        <v>8.52727699279785</v>
+        <v>8.52727603912354</v>
       </c>
       <c r="H299" t="n">
         <v>700</v>
@@ -9069,7 +9069,7 @@
         <v>8.9399995803833</v>
       </c>
       <c r="G300" t="n">
-        <v>8.37734603881836</v>
+        <v>8.37734508514404</v>
       </c>
       <c r="H300" t="n">
         <v>300</v>
@@ -9098,7 +9098,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G301" t="n">
-        <v>8.52727699279785</v>
+        <v>8.52727603912354</v>
       </c>
       <c r="H301" t="n">
         <v>300</v>
@@ -9127,7 +9127,7 @@
         <v>9</v>
       </c>
       <c r="G302" t="n">
-        <v>8.43356990814209</v>
+        <v>8.43356895446777</v>
       </c>
       <c r="H302" t="n">
         <v>300</v>
@@ -9156,7 +9156,7 @@
         <v>9</v>
       </c>
       <c r="G303" t="n">
-        <v>8.43356990814209</v>
+        <v>8.43356895446777</v>
       </c>
       <c r="H303" t="n">
         <v>0</v>
@@ -9185,7 +9185,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G304" t="n">
-        <v>8.33986377716064</v>
+        <v>8.33986282348633</v>
       </c>
       <c r="H304" t="n">
         <v>300</v>
@@ -9214,7 +9214,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G305" t="n">
-        <v>8.2461576461792</v>
+        <v>8.24615669250488</v>
       </c>
       <c r="H305" t="n">
         <v>1700</v>
@@ -9243,7 +9243,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G306" t="n">
-        <v>8.2461576461792</v>
+        <v>8.24615669250488</v>
       </c>
       <c r="H306" t="n">
         <v>0</v>
@@ -9272,7 +9272,7 @@
         <v>8.64000034332275</v>
       </c>
       <c r="G307" t="n">
-        <v>8.09622764587402</v>
+        <v>8.09622669219971</v>
       </c>
       <c r="H307" t="n">
         <v>1600</v>
@@ -9359,7 +9359,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G310" t="n">
-        <v>8.2461576461792</v>
+        <v>8.24615669250488</v>
       </c>
       <c r="H310" t="n">
         <v>1000</v>
@@ -9388,7 +9388,7 @@
         <v>8.47999954223633</v>
       </c>
       <c r="G311" t="n">
-        <v>7.94629669189453</v>
+        <v>7.94629621505737</v>
       </c>
       <c r="H311" t="n">
         <v>4000</v>
@@ -9475,7 +9475,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G314" t="n">
-        <v>8.2461576461792</v>
+        <v>8.24615669250488</v>
       </c>
       <c r="H314" t="n">
         <v>1600</v>
@@ -9533,7 +9533,7 @@
         <v>8.47999954223633</v>
       </c>
       <c r="G316" t="n">
-        <v>7.94629669189453</v>
+        <v>7.94629621505737</v>
       </c>
       <c r="H316" t="n">
         <v>2000</v>
@@ -9591,7 +9591,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G318" t="n">
-        <v>8.2461576461792</v>
+        <v>8.24615669250488</v>
       </c>
       <c r="H318" t="n">
         <v>1600</v>
@@ -9620,7 +9620,7 @@
         <v>8.47999954223633</v>
       </c>
       <c r="G319" t="n">
-        <v>7.94629669189453</v>
+        <v>7.94629621505737</v>
       </c>
       <c r="H319" t="n">
         <v>1300</v>
@@ -9823,7 +9823,7 @@
         <v>8.31999969482422</v>
       </c>
       <c r="G326" t="n">
-        <v>7.79636716842651</v>
+        <v>7.79636669158936</v>
       </c>
       <c r="H326" t="n">
         <v>3800</v>
@@ -10084,7 +10084,7 @@
         <v>8.42000007629395</v>
       </c>
       <c r="G335" t="n">
-        <v>7.8900728225708</v>
+        <v>7.89007329940796</v>
       </c>
       <c r="H335" t="n">
         <v>4600</v>
@@ -10113,7 +10113,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G336" t="n">
-        <v>8.2461576461792</v>
+        <v>8.24615669250488</v>
       </c>
       <c r="H336" t="n">
         <v>7500</v>
@@ -10142,7 +10142,7 @@
         <v>9</v>
       </c>
       <c r="G337" t="n">
-        <v>8.43356990814209</v>
+        <v>8.43356895446777</v>
       </c>
       <c r="H337" t="n">
         <v>11600</v>
@@ -10171,7 +10171,7 @@
         <v>9</v>
       </c>
       <c r="G338" t="n">
-        <v>8.43356990814209</v>
+        <v>8.43356895446777</v>
       </c>
       <c r="H338" t="n">
         <v>3300</v>
@@ -10200,7 +10200,7 @@
         <v>9</v>
       </c>
       <c r="G339" t="n">
-        <v>8.43356990814209</v>
+        <v>8.43356895446777</v>
       </c>
       <c r="H339" t="n">
         <v>0</v>
@@ -10229,7 +10229,7 @@
         <v>9</v>
       </c>
       <c r="G340" t="n">
-        <v>8.43356990814209</v>
+        <v>8.43356895446777</v>
       </c>
       <c r="H340" t="n">
         <v>0</v>
@@ -10258,7 +10258,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G341" t="n">
-        <v>8.33986377716064</v>
+        <v>8.33986282348633</v>
       </c>
       <c r="H341" t="n">
         <v>3000</v>
@@ -10287,7 +10287,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G342" t="n">
-        <v>8.80839443206787</v>
+        <v>8.80839538574219</v>
       </c>
       <c r="H342" t="n">
         <v>10000</v>
@@ -29056,6 +29056,35 @@
         <v>2100</v>
       </c>
       <c r="I989" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="990">
+      <c r="A990" t="s">
+        <v>9</v>
+      </c>
+      <c r="B990" s="1" t="n">
+        <v>46324.3333333333</v>
+      </c>
+      <c r="C990" t="n">
+        <v>10.75</v>
+      </c>
+      <c r="D990" t="n">
+        <v>10.8000001907349</v>
+      </c>
+      <c r="E990" t="n">
+        <v>10.6000003814697</v>
+      </c>
+      <c r="F990" t="n">
+        <v>10.75</v>
+      </c>
+      <c r="G990" t="n">
+        <v>10.75</v>
+      </c>
+      <c r="H990" t="n">
+        <v>1300</v>
+      </c>
+      <c r="I990" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/RDUE.MI.xlsx
+++ b/data/RDUE.MI.xlsx
@@ -485,7 +485,7 @@
         <v>12.0600004196167</v>
       </c>
       <c r="G4" t="n">
-        <v>11.3009834289551</v>
+        <v>11.3009843826294</v>
       </c>
       <c r="H4" t="n">
         <v>2100</v>
@@ -514,7 +514,7 @@
         <v>12.1499996185303</v>
       </c>
       <c r="G5" t="n">
-        <v>11.3853197097778</v>
+        <v>11.3853187561035</v>
       </c>
       <c r="H5" t="n">
         <v>14000</v>
@@ -572,7 +572,7 @@
         <v>12.0900001525879</v>
       </c>
       <c r="G7" t="n">
-        <v>11.3290967941284</v>
+        <v>11.3290948867798</v>
       </c>
       <c r="H7" t="n">
         <v>1000</v>
@@ -688,7 +688,7 @@
         <v>11.9180002212524</v>
       </c>
       <c r="G11" t="n">
-        <v>11.1679210662842</v>
+        <v>11.1679201126099</v>
       </c>
       <c r="H11" t="n">
         <v>2300</v>
@@ -717,7 +717,7 @@
         <v>11.9899997711182</v>
       </c>
       <c r="G12" t="n">
-        <v>11.2353897094727</v>
+        <v>11.2353887557983</v>
       </c>
       <c r="H12" t="n">
         <v>500</v>
@@ -746,7 +746,7 @@
         <v>11.8800001144409</v>
       </c>
       <c r="G13" t="n">
-        <v>11.1323127746582</v>
+        <v>11.1323118209839</v>
       </c>
       <c r="H13" t="n">
         <v>5200</v>
@@ -804,7 +804,7 @@
         <v>11.6199998855591</v>
       </c>
       <c r="G15" t="n">
-        <v>10.8886756896973</v>
+        <v>10.8886747360229</v>
       </c>
       <c r="H15" t="n">
         <v>1900</v>
@@ -833,7 +833,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G16" t="n">
-        <v>11.0573472976685</v>
+        <v>11.0573463439941</v>
       </c>
       <c r="H16" t="n">
         <v>200</v>
@@ -862,7 +862,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G17" t="n">
-        <v>11.0573472976685</v>
+        <v>11.0573463439941</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
@@ -949,7 +949,7 @@
         <v>11.5900001525879</v>
       </c>
       <c r="G20" t="n">
-        <v>10.8605632781982</v>
+        <v>10.8605642318726</v>
       </c>
       <c r="H20" t="n">
         <v>800</v>
@@ -1007,7 +1007,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G22" t="n">
-        <v>10.6825218200684</v>
+        <v>10.682520866394</v>
       </c>
       <c r="H22" t="n">
         <v>600</v>
@@ -1094,7 +1094,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G25" t="n">
-        <v>10.5888156890869</v>
+        <v>10.5888147354126</v>
       </c>
       <c r="H25" t="n">
         <v>600</v>
@@ -1123,7 +1123,7 @@
         <v>11.25</v>
       </c>
       <c r="G26" t="n">
-        <v>10.5419626235962</v>
+        <v>10.5419616699219</v>
       </c>
       <c r="H26" t="n">
         <v>400</v>
@@ -1152,7 +1152,7 @@
         <v>11.9840002059937</v>
       </c>
       <c r="G27" t="n">
-        <v>11.2297677993774</v>
+        <v>11.2297668457031</v>
       </c>
       <c r="H27" t="n">
         <v>14800</v>
@@ -1181,7 +1181,7 @@
         <v>12.0100002288818</v>
       </c>
       <c r="G28" t="n">
-        <v>11.2541303634644</v>
+        <v>11.2541313171387</v>
       </c>
       <c r="H28" t="n">
         <v>5900</v>
@@ -1210,7 +1210,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G29" t="n">
-        <v>11.3384666442871</v>
+        <v>11.3384656906128</v>
       </c>
       <c r="H29" t="n">
         <v>12200</v>
@@ -1239,7 +1239,7 @@
         <v>11.8800001144409</v>
       </c>
       <c r="G30" t="n">
-        <v>11.1323127746582</v>
+        <v>11.1323118209839</v>
       </c>
       <c r="H30" t="n">
         <v>3900</v>
@@ -1268,7 +1268,7 @@
         <v>11.9799995422363</v>
       </c>
       <c r="G31" t="n">
-        <v>11.2260189056396</v>
+        <v>11.2260179519653</v>
       </c>
       <c r="H31" t="n">
         <v>200</v>
@@ -1384,7 +1384,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G35" t="n">
-        <v>11.0573472976685</v>
+        <v>11.0573463439941</v>
       </c>
       <c r="H35" t="n">
         <v>2200</v>
@@ -1413,7 +1413,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G36" t="n">
-        <v>11.0573472976685</v>
+        <v>11.0573463439941</v>
       </c>
       <c r="H36" t="n">
         <v>0</v>
@@ -1442,7 +1442,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G37" t="n">
-        <v>11.0573472976685</v>
+        <v>11.0573463439941</v>
       </c>
       <c r="H37" t="n">
         <v>3200</v>
@@ -1471,7 +1471,7 @@
         <v>11.996000289917</v>
       </c>
       <c r="G38" t="n">
-        <v>11.2410125732422</v>
+        <v>11.2410116195679</v>
       </c>
       <c r="H38" t="n">
         <v>900</v>
@@ -1529,7 +1529,7 @@
         <v>11.9799995422363</v>
       </c>
       <c r="G40" t="n">
-        <v>11.2260189056396</v>
+        <v>11.2260179519653</v>
       </c>
       <c r="H40" t="n">
         <v>400</v>
@@ -1558,7 +1558,7 @@
         <v>11.9799995422363</v>
       </c>
       <c r="G41" t="n">
-        <v>11.2260189056396</v>
+        <v>11.2260179519653</v>
       </c>
       <c r="H41" t="n">
         <v>0</v>
@@ -1616,7 +1616,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G43" t="n">
-        <v>11.0573472976685</v>
+        <v>11.0573463439941</v>
       </c>
       <c r="H43" t="n">
         <v>4800</v>
@@ -1761,7 +1761,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G48" t="n">
-        <v>11.0573472976685</v>
+        <v>11.0573463439941</v>
       </c>
       <c r="H48" t="n">
         <v>1200</v>
@@ -1819,7 +1819,7 @@
         <v>11.5500001907349</v>
       </c>
       <c r="G50" t="n">
-        <v>10.8230819702148</v>
+        <v>10.8230810165405</v>
       </c>
       <c r="H50" t="n">
         <v>400</v>
@@ -1848,7 +1848,7 @@
         <v>11.5500001907349</v>
       </c>
       <c r="G51" t="n">
-        <v>10.8230819702148</v>
+        <v>10.8230810165405</v>
       </c>
       <c r="H51" t="n">
         <v>1700</v>
@@ -1877,7 +1877,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G52" t="n">
-        <v>11.0573472976685</v>
+        <v>11.0573463439941</v>
       </c>
       <c r="H52" t="n">
         <v>100</v>
@@ -1935,7 +1935,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G54" t="n">
-        <v>11.0573472976685</v>
+        <v>11.0573463439941</v>
       </c>
       <c r="H54" t="n">
         <v>700</v>
@@ -1964,7 +1964,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G55" t="n">
-        <v>11.0573472976685</v>
+        <v>11.0573463439941</v>
       </c>
       <c r="H55" t="n">
         <v>100</v>
@@ -1993,7 +1993,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G56" t="n">
-        <v>11.0573472976685</v>
+        <v>11.0573463439941</v>
       </c>
       <c r="H56" t="n">
         <v>0</v>
@@ -2196,7 +2196,7 @@
         <v>11.4499998092651</v>
       </c>
       <c r="G63" t="n">
-        <v>10.7293758392334</v>
+        <v>10.7293748855591</v>
       </c>
       <c r="H63" t="n">
         <v>2200</v>
@@ -2225,7 +2225,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G64" t="n">
-        <v>10.6825218200684</v>
+        <v>10.682520866394</v>
       </c>
       <c r="H64" t="n">
         <v>2900</v>
@@ -2254,7 +2254,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G65" t="n">
-        <v>10.6825218200684</v>
+        <v>10.682520866394</v>
       </c>
       <c r="H65" t="n">
         <v>500</v>
@@ -2283,7 +2283,7 @@
         <v>11.5500001907349</v>
       </c>
       <c r="G66" t="n">
-        <v>10.8230819702148</v>
+        <v>10.8230810165405</v>
       </c>
       <c r="H66" t="n">
         <v>4100</v>
@@ -2341,7 +2341,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G68" t="n">
-        <v>10.6825218200684</v>
+        <v>10.682520866394</v>
       </c>
       <c r="H68" t="n">
         <v>700</v>
@@ -2370,7 +2370,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G69" t="n">
-        <v>10.6825218200684</v>
+        <v>10.682520866394</v>
       </c>
       <c r="H69" t="n">
         <v>0</v>
@@ -2428,7 +2428,7 @@
         <v>11.5</v>
       </c>
       <c r="G71" t="n">
-        <v>10.7762279510498</v>
+        <v>10.7762269973755</v>
       </c>
       <c r="H71" t="n">
         <v>500</v>
@@ -2457,7 +2457,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G72" t="n">
-        <v>10.6825218200684</v>
+        <v>10.682520866394</v>
       </c>
       <c r="H72" t="n">
         <v>3100</v>
@@ -2631,7 +2631,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G78" t="n">
-        <v>11.0573472976685</v>
+        <v>11.0573463439941</v>
       </c>
       <c r="H78" t="n">
         <v>2600</v>
@@ -2660,7 +2660,7 @@
         <v>11.5</v>
       </c>
       <c r="G79" t="n">
-        <v>10.7762279510498</v>
+        <v>10.7762269973755</v>
       </c>
       <c r="H79" t="n">
         <v>2100</v>
@@ -2718,7 +2718,7 @@
         <v>11.5500001907349</v>
       </c>
       <c r="G81" t="n">
-        <v>10.8230819702148</v>
+        <v>10.8230810165405</v>
       </c>
       <c r="H81" t="n">
         <v>800</v>
@@ -2747,7 +2747,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G82" t="n">
-        <v>9.74545764923096</v>
+        <v>9.74545860290527</v>
       </c>
       <c r="H82" t="n">
         <v>13600</v>
@@ -2921,7 +2921,7 @@
         <v>10.25</v>
       </c>
       <c r="G88" t="n">
-        <v>9.60489845275879</v>
+        <v>9.60489940643311</v>
       </c>
       <c r="H88" t="n">
         <v>1800</v>
@@ -2950,7 +2950,7 @@
         <v>10.5500001907349</v>
       </c>
       <c r="G89" t="n">
-        <v>9.88601779937744</v>
+        <v>9.88601875305176</v>
       </c>
       <c r="H89" t="n">
         <v>4400</v>
@@ -2979,7 +2979,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G90" t="n">
-        <v>9.55804538726807</v>
+        <v>9.55804634094238</v>
       </c>
       <c r="H90" t="n">
         <v>600</v>
@@ -3037,7 +3037,7 @@
         <v>9.92000007629395</v>
       </c>
       <c r="G92" t="n">
-        <v>9.29566764831543</v>
+        <v>9.29566860198975</v>
       </c>
       <c r="H92" t="n">
         <v>5200</v>
@@ -3095,7 +3095,7 @@
         <v>9.73999977111816</v>
       </c>
       <c r="G94" t="n">
-        <v>9.12699604034424</v>
+        <v>9.12699699401855</v>
       </c>
       <c r="H94" t="n">
         <v>2000</v>
@@ -3124,7 +3124,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G95" t="n">
-        <v>9.08951377868652</v>
+        <v>9.08951473236084</v>
       </c>
       <c r="H95" t="n">
         <v>800</v>
@@ -3153,7 +3153,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G96" t="n">
-        <v>9.08951377868652</v>
+        <v>9.08951473236084</v>
       </c>
       <c r="H96" t="n">
         <v>0</v>
@@ -3182,7 +3182,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G97" t="n">
-        <v>9.08951377868652</v>
+        <v>9.08951473236084</v>
       </c>
       <c r="H97" t="n">
         <v>0</v>
@@ -3385,7 +3385,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G104" t="n">
-        <v>8.6209831237793</v>
+        <v>8.62098217010498</v>
       </c>
       <c r="H104" t="n">
         <v>1400</v>
@@ -3414,7 +3414,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G105" t="n">
-        <v>8.52727603912354</v>
+        <v>8.52727699279785</v>
       </c>
       <c r="H105" t="n">
         <v>1300</v>
@@ -3443,7 +3443,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G106" t="n">
-        <v>8.6209831237793</v>
+        <v>8.62098217010498</v>
       </c>
       <c r="H106" t="n">
         <v>200</v>
@@ -3472,7 +3472,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G107" t="n">
-        <v>8.6209831237793</v>
+        <v>8.62098217010498</v>
       </c>
       <c r="H107" t="n">
         <v>0</v>
@@ -3559,7 +3559,7 @@
         <v>9.4399995803833</v>
       </c>
       <c r="G110" t="n">
-        <v>8.84587669372559</v>
+        <v>8.8458776473999</v>
       </c>
       <c r="H110" t="n">
         <v>200</v>
@@ -3588,7 +3588,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G111" t="n">
-        <v>9.08951377868652</v>
+        <v>9.08951473236084</v>
       </c>
       <c r="H111" t="n">
         <v>500</v>
@@ -3675,7 +3675,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G114" t="n">
-        <v>9.55804538726807</v>
+        <v>9.55804634094238</v>
       </c>
       <c r="H114" t="n">
         <v>7600</v>
@@ -3704,7 +3704,7 @@
         <v>10</v>
       </c>
       <c r="G115" t="n">
-        <v>9.37063312530518</v>
+        <v>9.37063407897949</v>
       </c>
       <c r="H115" t="n">
         <v>200</v>
@@ -3733,7 +3733,7 @@
         <v>10.5500001907349</v>
       </c>
       <c r="G116" t="n">
-        <v>9.88601779937744</v>
+        <v>9.88601875305176</v>
       </c>
       <c r="H116" t="n">
         <v>2700</v>
@@ -3762,7 +3762,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G117" t="n">
-        <v>9.74545764923096</v>
+        <v>9.74545860290527</v>
       </c>
       <c r="H117" t="n">
         <v>300</v>
@@ -3791,7 +3791,7 @@
         <v>10.5500001907349</v>
       </c>
       <c r="G118" t="n">
-        <v>9.88601779937744</v>
+        <v>9.88601875305176</v>
       </c>
       <c r="H118" t="n">
         <v>100</v>
@@ -3820,7 +3820,7 @@
         <v>10.5</v>
       </c>
       <c r="G119" t="n">
-        <v>9.83916473388672</v>
+        <v>9.83916568756104</v>
       </c>
       <c r="H119" t="n">
         <v>800</v>
@@ -3994,7 +3994,7 @@
         <v>9.57999992370605</v>
       </c>
       <c r="G125" t="n">
-        <v>8.97706604003906</v>
+        <v>8.97706699371338</v>
       </c>
       <c r="H125" t="n">
         <v>1400</v>
@@ -4081,7 +4081,7 @@
         <v>9.88000011444092</v>
       </c>
       <c r="G128" t="n">
-        <v>9.25818538665771</v>
+        <v>9.25818634033203</v>
       </c>
       <c r="H128" t="n">
         <v>2400</v>
@@ -4139,7 +4139,7 @@
         <v>9.92000007629395</v>
       </c>
       <c r="G130" t="n">
-        <v>9.29566764831543</v>
+        <v>9.29566860198975</v>
       </c>
       <c r="H130" t="n">
         <v>200</v>
@@ -4168,7 +4168,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G131" t="n">
-        <v>9.65175247192383</v>
+        <v>9.65175342559814</v>
       </c>
       <c r="H131" t="n">
         <v>2700</v>
@@ -4197,7 +4197,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G132" t="n">
-        <v>9.65175247192383</v>
+        <v>9.65175342559814</v>
       </c>
       <c r="H132" t="n">
         <v>100</v>
@@ -4226,7 +4226,7 @@
         <v>9.97999954223633</v>
       </c>
       <c r="G133" t="n">
-        <v>9.35189056396484</v>
+        <v>9.35189247131348</v>
       </c>
       <c r="H133" t="n">
         <v>500</v>
@@ -4313,7 +4313,7 @@
         <v>10.5</v>
       </c>
       <c r="G136" t="n">
-        <v>9.83916473388672</v>
+        <v>9.83916568756104</v>
       </c>
       <c r="H136" t="n">
         <v>700</v>
@@ -4342,7 +4342,7 @@
         <v>10.5500001907349</v>
       </c>
       <c r="G137" t="n">
-        <v>9.88601779937744</v>
+        <v>9.88601875305176</v>
       </c>
       <c r="H137" t="n">
         <v>1000</v>
@@ -4371,7 +4371,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G138" t="n">
-        <v>10.0265779495239</v>
+        <v>10.0265769958496</v>
       </c>
       <c r="H138" t="n">
         <v>500</v>
@@ -4400,7 +4400,7 @@
         <v>10.5</v>
       </c>
       <c r="G139" t="n">
-        <v>9.83916473388672</v>
+        <v>9.83916568756104</v>
       </c>
       <c r="H139" t="n">
         <v>300</v>
@@ -4429,7 +4429,7 @@
         <v>10.5</v>
       </c>
       <c r="G140" t="n">
-        <v>9.83916473388672</v>
+        <v>9.83916568756104</v>
       </c>
       <c r="H140" t="n">
         <v>100</v>
@@ -4458,7 +4458,7 @@
         <v>10.5</v>
       </c>
       <c r="G141" t="n">
-        <v>9.83916473388672</v>
+        <v>9.83916568756104</v>
       </c>
       <c r="H141" t="n">
         <v>0</v>
@@ -4487,7 +4487,7 @@
         <v>10</v>
       </c>
       <c r="G142" t="n">
-        <v>9.37063312530518</v>
+        <v>9.37063407897949</v>
       </c>
       <c r="H142" t="n">
         <v>7600</v>
@@ -4574,7 +4574,7 @@
         <v>9.5600004196167</v>
       </c>
       <c r="G145" t="n">
-        <v>8.95832633972168</v>
+        <v>8.95832538604736</v>
       </c>
       <c r="H145" t="n">
         <v>1400</v>
@@ -4748,7 +4748,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G151" t="n">
-        <v>9.08951377868652</v>
+        <v>9.08951473236084</v>
       </c>
       <c r="H151" t="n">
         <v>500</v>
@@ -4777,7 +4777,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G152" t="n">
-        <v>9.08951377868652</v>
+        <v>9.08951473236084</v>
       </c>
       <c r="H152" t="n">
         <v>0</v>
@@ -4806,7 +4806,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G153" t="n">
-        <v>9.08951377868652</v>
+        <v>9.08951473236084</v>
       </c>
       <c r="H153" t="n">
         <v>0</v>
@@ -4864,7 +4864,7 @@
         <v>10</v>
       </c>
       <c r="G155" t="n">
-        <v>9.37063312530518</v>
+        <v>9.37063407897949</v>
       </c>
       <c r="H155" t="n">
         <v>100</v>
@@ -4893,7 +4893,7 @@
         <v>10</v>
       </c>
       <c r="G156" t="n">
-        <v>9.37063312530518</v>
+        <v>9.37063407897949</v>
       </c>
       <c r="H156" t="n">
         <v>0</v>
@@ -4922,7 +4922,7 @@
         <v>10</v>
       </c>
       <c r="G157" t="n">
-        <v>9.37063312530518</v>
+        <v>9.37063407897949</v>
       </c>
       <c r="H157" t="n">
         <v>0</v>
@@ -4951,7 +4951,7 @@
         <v>10</v>
       </c>
       <c r="G158" t="n">
-        <v>9.37063312530518</v>
+        <v>9.37063407897949</v>
       </c>
       <c r="H158" t="n">
         <v>0</v>
@@ -4980,7 +4980,7 @@
         <v>10</v>
       </c>
       <c r="G159" t="n">
-        <v>9.37063312530518</v>
+        <v>9.37063407897949</v>
       </c>
       <c r="H159" t="n">
         <v>0</v>
@@ -5009,7 +5009,7 @@
         <v>10</v>
       </c>
       <c r="G160" t="n">
-        <v>9.37063312530518</v>
+        <v>9.37063407897949</v>
       </c>
       <c r="H160" t="n">
         <v>0</v>
@@ -5038,7 +5038,7 @@
         <v>10</v>
       </c>
       <c r="G161" t="n">
-        <v>9.37063312530518</v>
+        <v>9.37063407897949</v>
       </c>
       <c r="H161" t="n">
         <v>0</v>
@@ -5067,7 +5067,7 @@
         <v>10</v>
       </c>
       <c r="G162" t="n">
-        <v>9.37063312530518</v>
+        <v>9.37063407897949</v>
       </c>
       <c r="H162" t="n">
         <v>100</v>
@@ -5125,7 +5125,7 @@
         <v>9.97999954223633</v>
       </c>
       <c r="G164" t="n">
-        <v>9.35189056396484</v>
+        <v>9.35189247131348</v>
       </c>
       <c r="H164" t="n">
         <v>400</v>
@@ -5212,7 +5212,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G167" t="n">
-        <v>9.08951377868652</v>
+        <v>9.08951473236084</v>
       </c>
       <c r="H167" t="n">
         <v>1600</v>
@@ -5241,7 +5241,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G168" t="n">
-        <v>9.08951377868652</v>
+        <v>9.08951473236084</v>
       </c>
       <c r="H168" t="n">
         <v>5000</v>
@@ -5270,7 +5270,7 @@
         <v>9.15999984741211</v>
       </c>
       <c r="G169" t="n">
-        <v>8.58349990844727</v>
+        <v>8.58350086212158</v>
       </c>
       <c r="H169" t="n">
         <v>16200</v>
@@ -5357,7 +5357,7 @@
         <v>9.5600004196167</v>
       </c>
       <c r="G172" t="n">
-        <v>8.95832633972168</v>
+        <v>8.95832538604736</v>
       </c>
       <c r="H172" t="n">
         <v>200</v>
@@ -5415,7 +5415,7 @@
         <v>9.27999973297119</v>
       </c>
       <c r="G174" t="n">
-        <v>8.69594669342041</v>
+        <v>8.69594764709473</v>
       </c>
       <c r="H174" t="n">
         <v>8500</v>
@@ -5444,7 +5444,7 @@
         <v>9.42000007629395</v>
       </c>
       <c r="G175" t="n">
-        <v>8.82713603973389</v>
+        <v>8.8271369934082</v>
       </c>
       <c r="H175" t="n">
         <v>800</v>
@@ -5473,7 +5473,7 @@
         <v>9.27999973297119</v>
       </c>
       <c r="G176" t="n">
-        <v>8.69594669342041</v>
+        <v>8.69594764709473</v>
       </c>
       <c r="H176" t="n">
         <v>1400</v>
@@ -5502,7 +5502,7 @@
         <v>9.27999973297119</v>
       </c>
       <c r="G177" t="n">
-        <v>8.69594669342041</v>
+        <v>8.69594764709473</v>
       </c>
       <c r="H177" t="n">
         <v>0</v>
@@ -5676,7 +5676,7 @@
         <v>9.42000007629395</v>
       </c>
       <c r="G183" t="n">
-        <v>8.82713603973389</v>
+        <v>8.8271369934082</v>
       </c>
       <c r="H183" t="n">
         <v>300</v>
@@ -5705,7 +5705,7 @@
         <v>9.42000007629395</v>
       </c>
       <c r="G184" t="n">
-        <v>8.82713603973389</v>
+        <v>8.8271369934082</v>
       </c>
       <c r="H184" t="n">
         <v>0</v>
@@ -5792,7 +5792,7 @@
         <v>9.97999954223633</v>
       </c>
       <c r="G187" t="n">
-        <v>9.35189056396484</v>
+        <v>9.35189247131348</v>
       </c>
       <c r="H187" t="n">
         <v>3900</v>
@@ -5821,7 +5821,7 @@
         <v>9.97999954223633</v>
       </c>
       <c r="G188" t="n">
-        <v>9.35189056396484</v>
+        <v>9.35189247131348</v>
       </c>
       <c r="H188" t="n">
         <v>300</v>
@@ -5995,7 +5995,7 @@
         <v>9.64000034332275</v>
       </c>
       <c r="G194" t="n">
-        <v>9.03328990936279</v>
+        <v>9.03329086303711</v>
       </c>
       <c r="H194" t="n">
         <v>100</v>
@@ -6198,7 +6198,7 @@
         <v>9</v>
       </c>
       <c r="G201" t="n">
-        <v>8.43356895446777</v>
+        <v>8.43356990814209</v>
       </c>
       <c r="H201" t="n">
         <v>400</v>
@@ -6227,7 +6227,7 @@
         <v>9</v>
       </c>
       <c r="G202" t="n">
-        <v>8.43356895446777</v>
+        <v>8.43356990814209</v>
       </c>
       <c r="H202" t="n">
         <v>0</v>
@@ -6256,7 +6256,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G203" t="n">
-        <v>8.24615669250488</v>
+        <v>8.2461576461792</v>
       </c>
       <c r="H203" t="n">
         <v>2500</v>
@@ -6285,7 +6285,7 @@
         <v>9.0600004196167</v>
       </c>
       <c r="G204" t="n">
-        <v>8.48979377746582</v>
+        <v>8.48979473114014</v>
       </c>
       <c r="H204" t="n">
         <v>2200</v>
@@ -6343,7 +6343,7 @@
         <v>9</v>
       </c>
       <c r="G206" t="n">
-        <v>8.43356895446777</v>
+        <v>8.43356990814209</v>
       </c>
       <c r="H206" t="n">
         <v>2200</v>
@@ -6459,7 +6459,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G210" t="n">
-        <v>8.6209831237793</v>
+        <v>8.62098217010498</v>
       </c>
       <c r="H210" t="n">
         <v>100</v>
@@ -6488,7 +6488,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G211" t="n">
-        <v>8.6209831237793</v>
+        <v>8.62098217010498</v>
       </c>
       <c r="H211" t="n">
         <v>400</v>
@@ -6517,7 +6517,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G212" t="n">
-        <v>8.52727603912354</v>
+        <v>8.52727699279785</v>
       </c>
       <c r="H212" t="n">
         <v>1500</v>
@@ -6546,7 +6546,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G213" t="n">
-        <v>8.52727603912354</v>
+        <v>8.52727699279785</v>
       </c>
       <c r="H213" t="n">
         <v>0</v>
@@ -6575,7 +6575,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G214" t="n">
-        <v>8.52727603912354</v>
+        <v>8.52727699279785</v>
       </c>
       <c r="H214" t="n">
         <v>0</v>
@@ -6604,7 +6604,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G215" t="n">
-        <v>8.52727603912354</v>
+        <v>8.52727699279785</v>
       </c>
       <c r="H215" t="n">
         <v>0</v>
@@ -6633,7 +6633,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G216" t="n">
-        <v>8.52727603912354</v>
+        <v>8.52727699279785</v>
       </c>
       <c r="H216" t="n">
         <v>300</v>
@@ -6662,7 +6662,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G217" t="n">
-        <v>8.52727603912354</v>
+        <v>8.52727699279785</v>
       </c>
       <c r="H217" t="n">
         <v>0</v>
@@ -6691,7 +6691,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G218" t="n">
-        <v>8.52727603912354</v>
+        <v>8.52727699279785</v>
       </c>
       <c r="H218" t="n">
         <v>0</v>
@@ -6720,7 +6720,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G219" t="n">
-        <v>8.52727603912354</v>
+        <v>8.52727699279785</v>
       </c>
       <c r="H219" t="n">
         <v>0</v>
@@ -6894,7 +6894,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G225" t="n">
-        <v>8.52727603912354</v>
+        <v>8.52727699279785</v>
       </c>
       <c r="H225" t="n">
         <v>300</v>
@@ -6923,7 +6923,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G226" t="n">
-        <v>8.52727603912354</v>
+        <v>8.52727699279785</v>
       </c>
       <c r="H226" t="n">
         <v>0</v>
@@ -6952,7 +6952,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G227" t="n">
-        <v>8.52727603912354</v>
+        <v>8.52727699279785</v>
       </c>
       <c r="H227" t="n">
         <v>900</v>
@@ -6981,7 +6981,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G228" t="n">
-        <v>8.52727603912354</v>
+        <v>8.52727699279785</v>
       </c>
       <c r="H228" t="n">
         <v>0</v>
@@ -7010,7 +7010,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G229" t="n">
-        <v>8.52727603912354</v>
+        <v>8.52727699279785</v>
       </c>
       <c r="H229" t="n">
         <v>0</v>
@@ -7039,7 +7039,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G230" t="n">
-        <v>8.52727603912354</v>
+        <v>8.52727699279785</v>
       </c>
       <c r="H230" t="n">
         <v>0</v>
@@ -7068,7 +7068,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G231" t="n">
-        <v>8.52727603912354</v>
+        <v>8.52727699279785</v>
       </c>
       <c r="H231" t="n">
         <v>0</v>
@@ -7097,7 +7097,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G232" t="n">
-        <v>8.52727603912354</v>
+        <v>8.52727699279785</v>
       </c>
       <c r="H232" t="n">
         <v>0</v>
@@ -7126,7 +7126,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G233" t="n">
-        <v>8.52727603912354</v>
+        <v>8.52727699279785</v>
       </c>
       <c r="H233" t="n">
         <v>0</v>
@@ -7184,7 +7184,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G235" t="n">
-        <v>8.24615669250488</v>
+        <v>8.2461576461792</v>
       </c>
       <c r="H235" t="n">
         <v>1000</v>
@@ -7300,7 +7300,7 @@
         <v>8.73999977111816</v>
       </c>
       <c r="G239" t="n">
-        <v>8.18993282318115</v>
+        <v>8.18993377685547</v>
       </c>
       <c r="H239" t="n">
         <v>500</v>
@@ -7358,7 +7358,7 @@
         <v>8.42000007629395</v>
       </c>
       <c r="G241" t="n">
-        <v>7.89007329940796</v>
+        <v>7.8900728225708</v>
       </c>
       <c r="H241" t="n">
         <v>1500</v>
@@ -7387,7 +7387,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G242" t="n">
-        <v>7.68391895294189</v>
+        <v>7.68391942977905</v>
       </c>
       <c r="H242" t="n">
         <v>10000</v>
@@ -7445,7 +7445,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G244" t="n">
-        <v>7.59021282196045</v>
+        <v>7.59021329879761</v>
       </c>
       <c r="H244" t="n">
         <v>300</v>
@@ -7474,7 +7474,7 @@
         <v>8.0600004196167</v>
       </c>
       <c r="G245" t="n">
-        <v>7.55273056030273</v>
+        <v>7.55273103713989</v>
       </c>
       <c r="H245" t="n">
         <v>500</v>
@@ -7503,7 +7503,7 @@
         <v>8.0600004196167</v>
       </c>
       <c r="G246" t="n">
-        <v>7.55273056030273</v>
+        <v>7.55273103713989</v>
       </c>
       <c r="H246" t="n">
         <v>2400</v>
@@ -7532,7 +7532,7 @@
         <v>8.0600004196167</v>
       </c>
       <c r="G247" t="n">
-        <v>7.55273056030273</v>
+        <v>7.55273103713989</v>
       </c>
       <c r="H247" t="n">
         <v>300</v>
@@ -7561,7 +7561,7 @@
         <v>8.0600004196167</v>
       </c>
       <c r="G248" t="n">
-        <v>7.55273056030273</v>
+        <v>7.55273103713989</v>
       </c>
       <c r="H248" t="n">
         <v>0</v>
@@ -7648,7 +7648,7 @@
         <v>8.23999977111816</v>
       </c>
       <c r="G251" t="n">
-        <v>7.72140121459961</v>
+        <v>7.72140169143677</v>
       </c>
       <c r="H251" t="n">
         <v>100</v>
@@ -7677,7 +7677,7 @@
         <v>8.26000022888184</v>
       </c>
       <c r="G252" t="n">
-        <v>7.74014282226562</v>
+        <v>7.74014377593994</v>
       </c>
       <c r="H252" t="n">
         <v>300</v>
@@ -7822,7 +7822,7 @@
         <v>7.55999994277954</v>
       </c>
       <c r="G257" t="n">
-        <v>7.08419895172119</v>
+        <v>7.08419847488403</v>
       </c>
       <c r="H257" t="n">
         <v>6000</v>
@@ -7851,7 +7851,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G258" t="n">
-        <v>7.12168073654175</v>
+        <v>7.12168121337891</v>
       </c>
       <c r="H258" t="n">
         <v>4500</v>
@@ -7909,7 +7909,7 @@
         <v>7.67999982833862</v>
       </c>
       <c r="G260" t="n">
-        <v>7.19664573669434</v>
+        <v>7.19664621353149</v>
       </c>
       <c r="H260" t="n">
         <v>4200</v>
@@ -7938,7 +7938,7 @@
         <v>7.84000015258789</v>
       </c>
       <c r="G261" t="n">
-        <v>7.34657621383667</v>
+        <v>7.34657669067383</v>
       </c>
       <c r="H261" t="n">
         <v>2200</v>
@@ -7996,7 +7996,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G263" t="n">
-        <v>7.4028000831604</v>
+        <v>7.40280055999756</v>
       </c>
       <c r="H263" t="n">
         <v>2900</v>
@@ -8054,7 +8054,7 @@
         <v>7.48000001907349</v>
       </c>
       <c r="G265" t="n">
-        <v>7.00923347473145</v>
+        <v>7.0092339515686</v>
       </c>
       <c r="H265" t="n">
         <v>10400</v>
@@ -8141,7 +8141,7 @@
         <v>7.48000001907349</v>
       </c>
       <c r="G268" t="n">
-        <v>7.00923347473145</v>
+        <v>7.0092339515686</v>
       </c>
       <c r="H268" t="n">
         <v>4100</v>
@@ -8257,7 +8257,7 @@
         <v>8.53999996185303</v>
       </c>
       <c r="G272" t="n">
-        <v>8.00252056121826</v>
+        <v>8.00252151489258</v>
       </c>
       <c r="H272" t="n">
         <v>9400</v>
@@ -8373,7 +8373,7 @@
         <v>9.11999988555908</v>
       </c>
       <c r="G276" t="n">
-        <v>8.54601669311523</v>
+        <v>8.54601764678955</v>
       </c>
       <c r="H276" t="n">
         <v>1600</v>
@@ -8431,7 +8431,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G278" t="n">
-        <v>8.6209831237793</v>
+        <v>8.62098217010498</v>
       </c>
       <c r="H278" t="n">
         <v>300</v>
@@ -8460,7 +8460,7 @@
         <v>9.11999988555908</v>
       </c>
       <c r="G279" t="n">
-        <v>8.54601669311523</v>
+        <v>8.54601764678955</v>
       </c>
       <c r="H279" t="n">
         <v>2000</v>
@@ -8489,7 +8489,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G280" t="n">
-        <v>8.52727603912354</v>
+        <v>8.52727699279785</v>
       </c>
       <c r="H280" t="n">
         <v>1100</v>
@@ -8547,7 +8547,7 @@
         <v>8.92000007629395</v>
       </c>
       <c r="G282" t="n">
-        <v>8.35860538482666</v>
+        <v>8.35860443115234</v>
       </c>
       <c r="H282" t="n">
         <v>200</v>
@@ -8692,7 +8692,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G287" t="n">
-        <v>8.24615669250488</v>
+        <v>8.2461576461792</v>
       </c>
       <c r="H287" t="n">
         <v>200</v>
@@ -8750,7 +8750,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G289" t="n">
-        <v>8.52727603912354</v>
+        <v>8.52727699279785</v>
       </c>
       <c r="H289" t="n">
         <v>2100</v>
@@ -8808,7 +8808,7 @@
         <v>9.11999988555908</v>
       </c>
       <c r="G291" t="n">
-        <v>8.54601669311523</v>
+        <v>8.54601764678955</v>
       </c>
       <c r="H291" t="n">
         <v>3400</v>
@@ -8837,7 +8837,7 @@
         <v>9.11999988555908</v>
       </c>
       <c r="G292" t="n">
-        <v>8.54601669311523</v>
+        <v>8.54601764678955</v>
       </c>
       <c r="H292" t="n">
         <v>2100</v>
@@ -8895,7 +8895,7 @@
         <v>9</v>
       </c>
       <c r="G294" t="n">
-        <v>8.43356895446777</v>
+        <v>8.43356990814209</v>
       </c>
       <c r="H294" t="n">
         <v>1700</v>
@@ -8953,7 +8953,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G296" t="n">
-        <v>8.6209831237793</v>
+        <v>8.62098217010498</v>
       </c>
       <c r="H296" t="n">
         <v>1000</v>
@@ -9040,7 +9040,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G299" t="n">
-        <v>8.52727603912354</v>
+        <v>8.52727699279785</v>
       </c>
       <c r="H299" t="n">
         <v>700</v>
@@ -9098,7 +9098,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G301" t="n">
-        <v>8.52727603912354</v>
+        <v>8.52727699279785</v>
       </c>
       <c r="H301" t="n">
         <v>300</v>
@@ -9127,7 +9127,7 @@
         <v>9</v>
       </c>
       <c r="G302" t="n">
-        <v>8.43356895446777</v>
+        <v>8.43356990814209</v>
       </c>
       <c r="H302" t="n">
         <v>300</v>
@@ -9156,7 +9156,7 @@
         <v>9</v>
       </c>
       <c r="G303" t="n">
-        <v>8.43356895446777</v>
+        <v>8.43356990814209</v>
       </c>
       <c r="H303" t="n">
         <v>0</v>
@@ -9214,7 +9214,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G305" t="n">
-        <v>8.24615669250488</v>
+        <v>8.2461576461792</v>
       </c>
       <c r="H305" t="n">
         <v>1700</v>
@@ -9243,7 +9243,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G306" t="n">
-        <v>8.24615669250488</v>
+        <v>8.2461576461792</v>
       </c>
       <c r="H306" t="n">
         <v>0</v>
@@ -9272,7 +9272,7 @@
         <v>8.64000034332275</v>
       </c>
       <c r="G307" t="n">
-        <v>8.09622669219971</v>
+        <v>8.09622764587402</v>
       </c>
       <c r="H307" t="n">
         <v>1600</v>
@@ -9330,7 +9330,7 @@
         <v>8.53999996185303</v>
       </c>
       <c r="G309" t="n">
-        <v>8.00252056121826</v>
+        <v>8.00252151489258</v>
       </c>
       <c r="H309" t="n">
         <v>2500</v>
@@ -9359,7 +9359,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G310" t="n">
-        <v>8.24615669250488</v>
+        <v>8.2461576461792</v>
       </c>
       <c r="H310" t="n">
         <v>1000</v>
@@ -9388,7 +9388,7 @@
         <v>8.47999954223633</v>
       </c>
       <c r="G311" t="n">
-        <v>7.94629621505737</v>
+        <v>7.94629669189453</v>
       </c>
       <c r="H311" t="n">
         <v>4000</v>
@@ -9446,7 +9446,7 @@
         <v>8.61999988555908</v>
       </c>
       <c r="G313" t="n">
-        <v>8.07748603820801</v>
+        <v>8.07748508453369</v>
       </c>
       <c r="H313" t="n">
         <v>5400</v>
@@ -9475,7 +9475,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G314" t="n">
-        <v>8.24615669250488</v>
+        <v>8.2461576461792</v>
       </c>
       <c r="H314" t="n">
         <v>1600</v>
@@ -9533,7 +9533,7 @@
         <v>8.47999954223633</v>
       </c>
       <c r="G316" t="n">
-        <v>7.94629621505737</v>
+        <v>7.94629669189453</v>
       </c>
       <c r="H316" t="n">
         <v>2000</v>
@@ -9591,7 +9591,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G318" t="n">
-        <v>8.24615669250488</v>
+        <v>8.2461576461792</v>
       </c>
       <c r="H318" t="n">
         <v>1600</v>
@@ -9620,7 +9620,7 @@
         <v>8.47999954223633</v>
       </c>
       <c r="G319" t="n">
-        <v>7.94629621505737</v>
+        <v>7.94629669189453</v>
       </c>
       <c r="H319" t="n">
         <v>1300</v>
@@ -9823,7 +9823,7 @@
         <v>8.31999969482422</v>
       </c>
       <c r="G326" t="n">
-        <v>7.79636669158936</v>
+        <v>7.7963662147522</v>
       </c>
       <c r="H326" t="n">
         <v>3800</v>
@@ -10084,7 +10084,7 @@
         <v>8.42000007629395</v>
       </c>
       <c r="G335" t="n">
-        <v>7.89007329940796</v>
+        <v>7.8900728225708</v>
       </c>
       <c r="H335" t="n">
         <v>4600</v>
@@ -10113,7 +10113,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G336" t="n">
-        <v>8.24615669250488</v>
+        <v>8.2461576461792</v>
       </c>
       <c r="H336" t="n">
         <v>7500</v>
@@ -10142,7 +10142,7 @@
         <v>9</v>
       </c>
       <c r="G337" t="n">
-        <v>8.43356895446777</v>
+        <v>8.43356990814209</v>
       </c>
       <c r="H337" t="n">
         <v>11600</v>
@@ -10171,7 +10171,7 @@
         <v>9</v>
       </c>
       <c r="G338" t="n">
-        <v>8.43356895446777</v>
+        <v>8.43356990814209</v>
       </c>
       <c r="H338" t="n">
         <v>3300</v>
@@ -10200,7 +10200,7 @@
         <v>9</v>
       </c>
       <c r="G339" t="n">
-        <v>8.43356895446777</v>
+        <v>8.43356990814209</v>
       </c>
       <c r="H339" t="n">
         <v>0</v>
@@ -10229,7 +10229,7 @@
         <v>9</v>
       </c>
       <c r="G340" t="n">
-        <v>8.43356895446777</v>
+        <v>8.43356990814209</v>
       </c>
       <c r="H340" t="n">
         <v>0</v>
@@ -10316,7 +10316,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G343" t="n">
-        <v>9.08951377868652</v>
+        <v>9.08951473236084</v>
       </c>
       <c r="H343" t="n">
         <v>10200</v>
@@ -10374,7 +10374,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G345" t="n">
-        <v>9.08951377868652</v>
+        <v>9.08951473236084</v>
       </c>
       <c r="H345" t="n">
         <v>4500</v>
@@ -10548,7 +10548,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G351" t="n">
-        <v>9.08951377868652</v>
+        <v>9.08951473236084</v>
       </c>
       <c r="H351" t="n">
         <v>800</v>
@@ -10780,7 +10780,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G359" t="n">
-        <v>9.04265975952148</v>
+        <v>9.0426607131958</v>
       </c>
       <c r="H359" t="n">
         <v>4000</v>
@@ -10809,7 +10809,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G360" t="n">
-        <v>9.04265975952148</v>
+        <v>9.0426607131958</v>
       </c>
       <c r="H360" t="n">
         <v>0</v>
@@ -10896,7 +10896,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G363" t="n">
-        <v>9.04265975952148</v>
+        <v>9.0426607131958</v>
       </c>
       <c r="H363" t="n">
         <v>100</v>
@@ -10925,7 +10925,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G364" t="n">
-        <v>9.04265975952148</v>
+        <v>9.0426607131958</v>
       </c>
       <c r="H364" t="n">
         <v>0</v>
@@ -10954,7 +10954,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G365" t="n">
-        <v>9.04265975952148</v>
+        <v>9.0426607131958</v>
       </c>
       <c r="H365" t="n">
         <v>300</v>
@@ -11215,7 +11215,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G374" t="n">
-        <v>9.04265975952148</v>
+        <v>9.0426607131958</v>
       </c>
       <c r="H374" t="n">
         <v>100</v>
@@ -11244,7 +11244,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G375" t="n">
-        <v>9.30551719665527</v>
+        <v>9.30551815032959</v>
       </c>
       <c r="H375" t="n">
         <v>600</v>
@@ -11273,7 +11273,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G376" t="n">
-        <v>9.25755023956299</v>
+        <v>9.2575511932373</v>
       </c>
       <c r="H376" t="n">
         <v>2500</v>
@@ -11331,7 +11331,7 @@
         <v>10</v>
       </c>
       <c r="G378" t="n">
-        <v>9.59331703186035</v>
+        <v>9.59331798553467</v>
       </c>
       <c r="H378" t="n">
         <v>7200</v>
@@ -11708,7 +11708,7 @@
         <v>10</v>
       </c>
       <c r="G391" t="n">
-        <v>9.59331703186035</v>
+        <v>9.59331798553467</v>
       </c>
       <c r="H391" t="n">
         <v>300</v>
@@ -11853,7 +11853,7 @@
         <v>10</v>
       </c>
       <c r="G396" t="n">
-        <v>9.59331703186035</v>
+        <v>9.59331798553467</v>
       </c>
       <c r="H396" t="n">
         <v>500</v>
@@ -11882,7 +11882,7 @@
         <v>10</v>
       </c>
       <c r="G397" t="n">
-        <v>9.59331703186035</v>
+        <v>9.59331798553467</v>
       </c>
       <c r="H397" t="n">
         <v>0</v>
@@ -11940,7 +11940,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G399" t="n">
-        <v>9.30551719665527</v>
+        <v>9.30551815032959</v>
       </c>
       <c r="H399" t="n">
         <v>1600</v>
@@ -11998,7 +11998,7 @@
         <v>9.35000038146973</v>
       </c>
       <c r="G401" t="n">
-        <v>8.96975135803223</v>
+        <v>8.96975231170654</v>
       </c>
       <c r="H401" t="n">
         <v>5200</v>
@@ -12288,7 +12288,7 @@
         <v>10</v>
       </c>
       <c r="G411" t="n">
-        <v>9.59331703186035</v>
+        <v>9.59331798553467</v>
       </c>
       <c r="H411" t="n">
         <v>600</v>
@@ -12433,7 +12433,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G416" t="n">
-        <v>9.25755023956299</v>
+        <v>9.2575511932373</v>
       </c>
       <c r="H416" t="n">
         <v>700</v>
@@ -12462,7 +12462,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G417" t="n">
-        <v>9.25755023956299</v>
+        <v>9.2575511932373</v>
       </c>
       <c r="H417" t="n">
         <v>0</v>
@@ -12491,7 +12491,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G418" t="n">
-        <v>9.25755023956299</v>
+        <v>9.2575511932373</v>
       </c>
       <c r="H418" t="n">
         <v>0</v>
@@ -12520,7 +12520,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G419" t="n">
-        <v>9.30551719665527</v>
+        <v>9.30551815032959</v>
       </c>
       <c r="H419" t="n">
         <v>1700</v>
@@ -12578,7 +12578,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G421" t="n">
-        <v>9.0177173614502</v>
+        <v>9.01771831512451</v>
       </c>
       <c r="H421" t="n">
         <v>100</v>
@@ -12636,7 +12636,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G423" t="n">
-        <v>9.25755023956299</v>
+        <v>9.2575511932373</v>
       </c>
       <c r="H423" t="n">
         <v>1100</v>
@@ -12665,7 +12665,7 @@
         <v>9.35000038146973</v>
       </c>
       <c r="G424" t="n">
-        <v>8.96975135803223</v>
+        <v>8.96975231170654</v>
       </c>
       <c r="H424" t="n">
         <v>500</v>
@@ -12694,7 +12694,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G425" t="n">
-        <v>8.53805255889893</v>
+        <v>8.53805160522461</v>
       </c>
       <c r="H425" t="n">
         <v>1300</v>
@@ -12810,7 +12810,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G429" t="n">
-        <v>9.25755023956299</v>
+        <v>9.2575511932373</v>
       </c>
       <c r="H429" t="n">
         <v>700</v>
@@ -12839,7 +12839,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G430" t="n">
-        <v>9.25755023956299</v>
+        <v>9.2575511932373</v>
       </c>
       <c r="H430" t="n">
         <v>0</v>
@@ -12897,7 +12897,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G432" t="n">
-        <v>9.0177173614502</v>
+        <v>9.01771831512451</v>
       </c>
       <c r="H432" t="n">
         <v>100</v>
@@ -12926,7 +12926,7 @@
         <v>9.35000038146973</v>
       </c>
       <c r="G433" t="n">
-        <v>8.96975135803223</v>
+        <v>8.96975231170654</v>
       </c>
       <c r="H433" t="n">
         <v>1200</v>
@@ -12984,7 +12984,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G435" t="n">
-        <v>9.30551719665527</v>
+        <v>9.30551815032959</v>
       </c>
       <c r="H435" t="n">
         <v>200</v>
@@ -13013,7 +13013,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G436" t="n">
-        <v>9.25755023956299</v>
+        <v>9.2575511932373</v>
       </c>
       <c r="H436" t="n">
         <v>400</v>
@@ -13071,7 +13071,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G438" t="n">
-        <v>9.0177173614502</v>
+        <v>9.01771831512451</v>
       </c>
       <c r="H438" t="n">
         <v>600</v>
@@ -13100,7 +13100,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G439" t="n">
-        <v>9.30551719665527</v>
+        <v>9.30551815032959</v>
       </c>
       <c r="H439" t="n">
         <v>200</v>
@@ -13129,7 +13129,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G440" t="n">
-        <v>9.30551719665527</v>
+        <v>9.30551815032959</v>
       </c>
       <c r="H440" t="n">
         <v>500</v>
@@ -13158,7 +13158,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G441" t="n">
-        <v>9.30551719665527</v>
+        <v>9.30551815032959</v>
       </c>
       <c r="H441" t="n">
         <v>600</v>
@@ -13187,7 +13187,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G442" t="n">
-        <v>9.30551719665527</v>
+        <v>9.30551815032959</v>
       </c>
       <c r="H442" t="n">
         <v>800</v>
@@ -13274,7 +13274,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G445" t="n">
-        <v>9.0177173614502</v>
+        <v>9.01771831512451</v>
       </c>
       <c r="H445" t="n">
         <v>4900</v>
@@ -13303,7 +13303,7 @@
         <v>9.44999980926514</v>
       </c>
       <c r="G446" t="n">
-        <v>9.06568431854248</v>
+        <v>9.0656852722168</v>
       </c>
       <c r="H446" t="n">
         <v>4900</v>
@@ -13332,7 +13332,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G447" t="n">
-        <v>9.0177173614502</v>
+        <v>9.01771831512451</v>
       </c>
       <c r="H447" t="n">
         <v>2000</v>
@@ -13361,7 +13361,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G448" t="n">
-        <v>8.825852394104</v>
+        <v>8.82585144042969</v>
       </c>
       <c r="H448" t="n">
         <v>1200</v>
@@ -13535,7 +13535,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G454" t="n">
-        <v>8.825852394104</v>
+        <v>8.82585144042969</v>
       </c>
       <c r="H454" t="n">
         <v>100</v>
@@ -13564,7 +13564,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G455" t="n">
-        <v>8.825852394104</v>
+        <v>8.82585144042969</v>
       </c>
       <c r="H455" t="n">
         <v>0</v>
@@ -13593,7 +13593,7 @@
         <v>9.35000038146973</v>
       </c>
       <c r="G456" t="n">
-        <v>8.96975135803223</v>
+        <v>8.96975231170654</v>
       </c>
       <c r="H456" t="n">
         <v>9000</v>
@@ -13796,7 +13796,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G463" t="n">
-        <v>8.53805255889893</v>
+        <v>8.53805160522461</v>
       </c>
       <c r="H463" t="n">
         <v>800</v>
@@ -14057,7 +14057,7 @@
         <v>7.75</v>
       </c>
       <c r="G472" t="n">
-        <v>7.43482065200806</v>
+        <v>7.43482112884521</v>
       </c>
       <c r="H472" t="n">
         <v>5500</v>
@@ -14289,7 +14289,7 @@
         <v>7.5</v>
       </c>
       <c r="G480" t="n">
-        <v>7.19498825073242</v>
+        <v>7.19498777389526</v>
       </c>
       <c r="H480" t="n">
         <v>1800</v>
@@ -14318,7 +14318,7 @@
         <v>7.34999990463257</v>
       </c>
       <c r="G481" t="n">
-        <v>7.05108833312988</v>
+        <v>7.05108785629272</v>
       </c>
       <c r="H481" t="n">
         <v>4200</v>
@@ -14347,7 +14347,7 @@
         <v>7.34999990463257</v>
       </c>
       <c r="G482" t="n">
-        <v>7.05108833312988</v>
+        <v>7.05108785629272</v>
       </c>
       <c r="H482" t="n">
         <v>7800</v>
@@ -14434,7 +14434,7 @@
         <v>7</v>
       </c>
       <c r="G485" t="n">
-        <v>6.71532249450684</v>
+        <v>6.71532201766968</v>
       </c>
       <c r="H485" t="n">
         <v>10100</v>
@@ -14724,7 +14724,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G495" t="n">
-        <v>6.04378986358643</v>
+        <v>6.04379034042358</v>
       </c>
       <c r="H495" t="n">
         <v>7900</v>
@@ -15014,7 +15014,7 @@
         <v>7</v>
       </c>
       <c r="G505" t="n">
-        <v>6.71532249450684</v>
+        <v>6.71532201766968</v>
       </c>
       <c r="H505" t="n">
         <v>13500</v>
@@ -15072,7 +15072,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G507" t="n">
-        <v>6.81125545501709</v>
+        <v>6.81125497817993</v>
       </c>
       <c r="H507" t="n">
         <v>3900</v>
@@ -15159,7 +15159,7 @@
         <v>7.75</v>
       </c>
       <c r="G510" t="n">
-        <v>7.43482065200806</v>
+        <v>7.43482112884521</v>
       </c>
       <c r="H510" t="n">
         <v>3700</v>
@@ -15681,7 +15681,7 @@
         <v>7.34999990463257</v>
       </c>
       <c r="G528" t="n">
-        <v>7.05108833312988</v>
+        <v>7.05108785629272</v>
       </c>
       <c r="H528" t="n">
         <v>4000</v>
@@ -15884,7 +15884,7 @@
         <v>7.5</v>
       </c>
       <c r="G535" t="n">
-        <v>7.19498825073242</v>
+        <v>7.19498777389526</v>
       </c>
       <c r="H535" t="n">
         <v>200</v>
@@ -16029,7 +16029,7 @@
         <v>7</v>
       </c>
       <c r="G540" t="n">
-        <v>6.71532249450684</v>
+        <v>6.71532201766968</v>
       </c>
       <c r="H540" t="n">
         <v>7000</v>
@@ -16203,7 +16203,7 @@
         <v>6.94999980926514</v>
       </c>
       <c r="G546" t="n">
-        <v>6.66735553741455</v>
+        <v>6.66735506057739</v>
       </c>
       <c r="H546" t="n">
         <v>2700</v>
@@ -16290,7 +16290,7 @@
         <v>7</v>
       </c>
       <c r="G549" t="n">
-        <v>6.71532249450684</v>
+        <v>6.71532201766968</v>
       </c>
       <c r="H549" t="n">
         <v>9500</v>
@@ -16319,7 +16319,7 @@
         <v>6.94999980926514</v>
       </c>
       <c r="G550" t="n">
-        <v>6.66735553741455</v>
+        <v>6.66735506057739</v>
       </c>
       <c r="H550" t="n">
         <v>16600</v>
@@ -16580,7 +16580,7 @@
         <v>7.75</v>
       </c>
       <c r="G559" t="n">
-        <v>7.43482065200806</v>
+        <v>7.43482112884521</v>
       </c>
       <c r="H559" t="n">
         <v>4000</v>
@@ -16725,7 +16725,7 @@
         <v>7.75</v>
       </c>
       <c r="G564" t="n">
-        <v>7.43482065200806</v>
+        <v>7.43482112884521</v>
       </c>
       <c r="H564" t="n">
         <v>700</v>
@@ -16841,7 +16841,7 @@
         <v>7.75</v>
       </c>
       <c r="G568" t="n">
-        <v>7.43482065200806</v>
+        <v>7.43482112884521</v>
       </c>
       <c r="H568" t="n">
         <v>6900</v>
@@ -17015,7 +17015,7 @@
         <v>8.14999961853027</v>
       </c>
       <c r="G574" t="n">
-        <v>7.81855297088623</v>
+        <v>7.81855344772339</v>
       </c>
       <c r="H574" t="n">
         <v>5200</v>
@@ -17160,7 +17160,7 @@
         <v>7.5</v>
       </c>
       <c r="G579" t="n">
-        <v>7.19498825073242</v>
+        <v>7.19498777389526</v>
       </c>
       <c r="H579" t="n">
         <v>3100</v>
@@ -17247,7 +17247,7 @@
         <v>8.25</v>
       </c>
       <c r="G582" t="n">
-        <v>7.91448640823364</v>
+        <v>7.91448736190796</v>
       </c>
       <c r="H582" t="n">
         <v>10200</v>
@@ -17276,7 +17276,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G583" t="n">
-        <v>7.86651945114136</v>
+        <v>7.86652040481567</v>
       </c>
       <c r="H583" t="n">
         <v>20900</v>
@@ -17334,7 +17334,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G585" t="n">
-        <v>7.86651945114136</v>
+        <v>7.86652040481567</v>
       </c>
       <c r="H585" t="n">
         <v>5700</v>
@@ -17363,7 +17363,7 @@
         <v>7.75</v>
       </c>
       <c r="G586" t="n">
-        <v>7.43482065200806</v>
+        <v>7.43482112884521</v>
       </c>
       <c r="H586" t="n">
         <v>8000</v>
@@ -17392,7 +17392,7 @@
         <v>7.75</v>
       </c>
       <c r="G587" t="n">
-        <v>7.43482065200806</v>
+        <v>7.43482112884521</v>
       </c>
       <c r="H587" t="n">
         <v>1500</v>
@@ -17421,7 +17421,7 @@
         <v>7.75</v>
       </c>
       <c r="G588" t="n">
-        <v>7.43482065200806</v>
+        <v>7.43482112884521</v>
       </c>
       <c r="H588" t="n">
         <v>100</v>
@@ -17479,7 +17479,7 @@
         <v>7.75</v>
       </c>
       <c r="G590" t="n">
-        <v>7.43482065200806</v>
+        <v>7.43482112884521</v>
       </c>
       <c r="H590" t="n">
         <v>2300</v>
@@ -17653,7 +17653,7 @@
         <v>6.94999980926514</v>
       </c>
       <c r="G596" t="n">
-        <v>6.66735553741455</v>
+        <v>6.66735506057739</v>
       </c>
       <c r="H596" t="n">
         <v>1100</v>
@@ -17682,7 +17682,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G597" t="n">
-        <v>6.90718793869019</v>
+        <v>6.90718841552734</v>
       </c>
       <c r="H597" t="n">
         <v>1200</v>
@@ -17711,7 +17711,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G598" t="n">
-        <v>6.90718793869019</v>
+        <v>6.90718841552734</v>
       </c>
       <c r="H598" t="n">
         <v>0</v>
@@ -17798,7 +17798,7 @@
         <v>7.34999990463257</v>
       </c>
       <c r="G601" t="n">
-        <v>7.05108833312988</v>
+        <v>7.05108785629272</v>
       </c>
       <c r="H601" t="n">
         <v>2100</v>
@@ -17827,7 +17827,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G602" t="n">
-        <v>6.90718793869019</v>
+        <v>6.90718841552734</v>
       </c>
       <c r="H602" t="n">
         <v>1600</v>
@@ -17885,7 +17885,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G604" t="n">
-        <v>6.81125545501709</v>
+        <v>6.81125497817993</v>
       </c>
       <c r="H604" t="n">
         <v>15300</v>
@@ -29085,6 +29085,35 @@
         <v>1300</v>
       </c>
       <c r="I990" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="991">
+      <c r="A991" t="s">
+        <v>9</v>
+      </c>
+      <c r="B991" s="1" t="n">
+        <v>46325.3333333333</v>
+      </c>
+      <c r="C991" t="n">
+        <v>10.6499996185303</v>
+      </c>
+      <c r="D991" t="n">
+        <v>10.9499998092651</v>
+      </c>
+      <c r="E991" t="n">
+        <v>10.6000003814697</v>
+      </c>
+      <c r="F991" t="n">
+        <v>10.9499998092651</v>
+      </c>
+      <c r="G991" t="n">
+        <v>10.9499998092651</v>
+      </c>
+      <c r="H991" t="n">
+        <v>3100</v>
+      </c>
+      <c r="I991" t="s">
         <v>9</v>
       </c>
     </row>
